--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="192">
   <si>
     <t>ROOMS</t>
   </si>
@@ -603,438 +603,6 @@
   </si>
   <si>
     <t>OSTWAL SIDDHARTH</t>
-  </si>
-  <si>
-    <t>ROOM NO. 201</t>
-  </si>
-  <si>
-    <t>ADITYA MANOJ AGRAWAL</t>
-  </si>
-  <si>
-    <t>YOG AGRAWAL</t>
-  </si>
-  <si>
-    <t>PRERIT AGRAWAL</t>
-  </si>
-  <si>
-    <t>ROOM NO202</t>
-  </si>
-  <si>
-    <t>SLOK MANDLEWALA</t>
-  </si>
-  <si>
-    <t>BHAVESH BOTHARA</t>
-  </si>
-  <si>
-    <t>jainam gada</t>
-  </si>
-  <si>
-    <t>ROOM NO 203</t>
-  </si>
-  <si>
-    <t>TANISHQ SANDEEP JAIN</t>
-  </si>
-  <si>
-    <t>SIDDHANT KASLIWAL</t>
-  </si>
-  <si>
-    <t>SPARSH NISHANT JAIN</t>
-  </si>
-  <si>
-    <t>ATHARV RAJESH AGRWAL</t>
-  </si>
-  <si>
-    <t>ROOM NO204</t>
-  </si>
-  <si>
-    <t>VANSH THOLE</t>
-  </si>
-  <si>
-    <t>SMIT SINGHAVI</t>
-  </si>
-  <si>
-    <t>ADARSH HIRAN</t>
-  </si>
-  <si>
-    <t>aayush shital jain</t>
-  </si>
-  <si>
-    <t>ROOM NO205</t>
-  </si>
-  <si>
-    <t>laksh gogad</t>
-  </si>
-  <si>
-    <t>safal doshi</t>
-  </si>
-  <si>
-    <t>roshan  jain</t>
-  </si>
-  <si>
-    <t>DHAWAL KOTHARI</t>
-  </si>
-  <si>
-    <t>ROOM NO206</t>
-  </si>
-  <si>
-    <t>sidharth gandhi</t>
-  </si>
-  <si>
-    <t>pratham chordiya</t>
-  </si>
-  <si>
-    <t>harshit singhavi</t>
-  </si>
-  <si>
-    <t>rushab p singhavi</t>
-  </si>
-  <si>
-    <t>ROOM NO207</t>
-  </si>
-  <si>
-    <t>DHRUV N KATARIYA</t>
-  </si>
-  <si>
-    <t>daksh jain</t>
-  </si>
-  <si>
-    <t>rijul agrawal</t>
-  </si>
-  <si>
-    <t>shub agrawal</t>
-  </si>
-  <si>
-    <t>ROOM NO208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">harsh jain </t>
-  </si>
-  <si>
-    <t>TANMAY DAGADE</t>
-  </si>
-  <si>
-    <t>RONAK GANGWAL</t>
-  </si>
-  <si>
-    <t>MANAS AGRAWAL</t>
-  </si>
-  <si>
-    <t>ROOM NO209</t>
-  </si>
-  <si>
-    <t>PARSH JAIN</t>
-  </si>
-  <si>
-    <t>ANKIT JAIN</t>
-  </si>
-  <si>
-    <t>RUSHABH ATUL JAIN</t>
-  </si>
-  <si>
-    <t>YASH s JAIN</t>
-  </si>
-  <si>
-    <t>ROOM NO210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISHAN SANCHETI </t>
-  </si>
-  <si>
-    <t>DARSHIL HIRAN</t>
-  </si>
-  <si>
-    <t>MANTRAM SANCHETI</t>
-  </si>
-  <si>
-    <t>NAMAN BEDMUTHA</t>
-  </si>
-  <si>
-    <t>ROOM NO 301</t>
-  </si>
-  <si>
-    <t>NISHANT BHANDARI</t>
-  </si>
-  <si>
-    <t>RUSHABH GANDHI</t>
-  </si>
-  <si>
-    <t>VEER PAWAN JAIN</t>
-  </si>
-  <si>
-    <t>ROOM NO 302</t>
-  </si>
-  <si>
-    <t>VED JAIN</t>
-  </si>
-  <si>
-    <t>HARSHIT JAIN</t>
-  </si>
-  <si>
-    <t>KUSHAL LODHA</t>
-  </si>
-  <si>
-    <t>PUSHKAR SHAILESH CHHORIYA</t>
-  </si>
-  <si>
-    <t>ROOM NO 303</t>
-  </si>
-  <si>
-    <t>RITESH JAGATSHETTY</t>
-  </si>
-  <si>
-    <t>AAYUSH CHHORIYA</t>
-  </si>
-  <si>
-    <t>VISHWA SHRISHRIMAL</t>
-  </si>
-  <si>
-    <t>SAMYAK MUNOT</t>
-  </si>
-  <si>
-    <t>ROOM NO 304</t>
-  </si>
-  <si>
-    <t>KARAN JAIN</t>
-  </si>
-  <si>
-    <t>KUSHAL LALWANI</t>
-  </si>
-  <si>
-    <t>lucky bafna</t>
-  </si>
-  <si>
-    <t>SANKALP BURAD</t>
-  </si>
-  <si>
-    <t>ROOM NO 305</t>
-  </si>
-  <si>
-    <t>meet lodha</t>
-  </si>
-  <si>
-    <t>SARTHAK AGRAWAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMYAK MEHTA </t>
-  </si>
-  <si>
-    <t>PUSHPAK LODHA</t>
-  </si>
-  <si>
-    <t>ROOM NO 306</t>
-  </si>
-  <si>
-    <t>HARDIK PAWAN AGRAWAL</t>
-  </si>
-  <si>
-    <t>tanish chordiya</t>
-  </si>
-  <si>
-    <t>TANISH JAIN</t>
-  </si>
-  <si>
-    <t>LAKSH JAIN</t>
-  </si>
-  <si>
-    <t>ROOM NO 307</t>
-  </si>
-  <si>
-    <t>SUVRATH NAHAR</t>
-  </si>
-  <si>
-    <t>SAKSHAM DARDA</t>
-  </si>
-  <si>
-    <t>HARSH JAIN</t>
-  </si>
-  <si>
-    <t>NEW DIVYA</t>
-  </si>
-  <si>
-    <t>ROOM NO 308</t>
-  </si>
-  <si>
-    <t>sayyam lodha</t>
-  </si>
-  <si>
-    <t>yajat agrawal</t>
-  </si>
-  <si>
-    <t>SUJAL MUTHA</t>
-  </si>
-  <si>
-    <t>SAKSHAM SANCHETI</t>
-  </si>
-  <si>
-    <t>ROOM NO 309</t>
-  </si>
-  <si>
-    <t>DHWAJ JAIN</t>
-  </si>
-  <si>
-    <t>BHAVIK LALWANI</t>
-  </si>
-  <si>
-    <t>SAHIL CHHORIYA</t>
-  </si>
-  <si>
-    <t>ROOM NO 310</t>
-  </si>
-  <si>
-    <t>AGRAWAL NAMAN</t>
-  </si>
-  <si>
-    <t>DEEPAK GUPTA</t>
-  </si>
-  <si>
-    <t>BADER RAJAN</t>
-  </si>
-  <si>
-    <t>RAJVEER CHORDIYA</t>
-  </si>
-  <si>
-    <t>ROOM NO. 401</t>
-  </si>
-  <si>
-    <t>rushank v singhavi</t>
-  </si>
-  <si>
-    <t>AARYAN KOTHARI</t>
-  </si>
-  <si>
-    <t>sanket mutha</t>
-  </si>
-  <si>
-    <t>ROOM NO402</t>
-  </si>
-  <si>
-    <t>kalash p lodha</t>
-  </si>
-  <si>
-    <t>SHRAWAN PANDAY</t>
-  </si>
-  <si>
-    <t>PRATIK SANKLECHA</t>
-  </si>
-  <si>
-    <t>RUSHABH CHANDALIYA</t>
-  </si>
-  <si>
-    <t>ROOM NO 403</t>
-  </si>
-  <si>
-    <t>naman mahavir soni</t>
-  </si>
-  <si>
-    <t>DR. PRANIT LUNAWAT</t>
-  </si>
-  <si>
-    <t>SOHAM PANKAJ LODHA</t>
-  </si>
-  <si>
-    <t>ARHAM KEVAL LODHA</t>
-  </si>
-  <si>
-    <t>ROOM NO404</t>
-  </si>
-  <si>
-    <t>OM PARAS JAIN</t>
-  </si>
-  <si>
-    <t>YASH PANKAJ JAIN</t>
-  </si>
-  <si>
-    <t>SIDDHESH KOTHADIYA</t>
-  </si>
-  <si>
-    <t>ROOM NO405</t>
-  </si>
-  <si>
-    <t>bhagyesh burad</t>
-  </si>
-  <si>
-    <t>humesh r jain</t>
-  </si>
-  <si>
-    <t>piyush hemant darda</t>
-  </si>
-  <si>
-    <t>mohit harshad tathed</t>
-  </si>
-  <si>
-    <t>ROOM NO406</t>
-  </si>
-  <si>
-    <t>SHAURYA AGRAWAL</t>
-  </si>
-  <si>
-    <t>DHEERAJ LUNAWAT</t>
-  </si>
-  <si>
-    <t>ARYAN SANCHETI</t>
-  </si>
-  <si>
-    <t>ROOM NO407</t>
-  </si>
-  <si>
-    <t>GOGAD UTKARSH</t>
-  </si>
-  <si>
-    <t>yash sakhala</t>
-  </si>
-  <si>
-    <t>NITYAM SHAH</t>
-  </si>
-  <si>
-    <t>SIDDHARTH AGRAWAL</t>
-  </si>
-  <si>
-    <t>ROOM NO408</t>
-  </si>
-  <si>
-    <t>HARDIK UJJWAL JAIN</t>
-  </si>
-  <si>
-    <t>rishi zabak</t>
-  </si>
-  <si>
-    <t>parth agrawal</t>
-  </si>
-  <si>
-    <t>BHAVIK KHABIYA</t>
-  </si>
-  <si>
-    <t>ROOM NO409</t>
-  </si>
-  <si>
-    <t>vivek sandip gandhi</t>
-  </si>
-  <si>
-    <t>ADESH SANKLECHA</t>
-  </si>
-  <si>
-    <t>TEJAS  LALWANI</t>
-  </si>
-  <si>
-    <t>SMIT DANGI</t>
-  </si>
-  <si>
-    <t>ROOM NO410</t>
-  </si>
-  <si>
-    <t>BHAVI SURANA</t>
-  </si>
-  <si>
-    <t>HARSH ABBAD</t>
-  </si>
-  <si>
-    <t>SOHAM SURAN</t>
-  </si>
-  <si>
-    <t>MOKSH BURAD</t>
-  </si>
-  <si>
-    <t>namit bora</t>
   </si>
 </sst>
 </file>
@@ -1047,7 +615,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="46">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1222,13 +790,6 @@
       <color rgb="FFFF0000"/>
       <name val="Copperplate Gothic Bold"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1984,148 +1545,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="10" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="11" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="11" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="43" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="45" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2559,26 +2120,26 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -7944,1127 +7505,594 @@
       <c r="S203" s="35"/>
     </row>
     <row r="204" ht="16.35" spans="1:19">
-      <c r="D204" s="165" t="s">
-        <v>192</v>
-      </c>
-      <c r="E204" s="166">
-        <v>1</v>
-      </c>
-      <c r="F204" s="86" t="s">
-        <v>193</v>
-      </c>
+      <c r="D204" s="165"/>
+      <c r="E204" s="86"/>
     </row>
     <row r="205" spans="1:19">
-      <c r="D205" s="167"/>
-      <c r="E205" s="168">
-        <v>2</v>
-      </c>
-      <c r="F205" s="169" t="s">
-        <v>194</v>
-      </c>
+      <c r="D205" s="166"/>
+      <c r="E205" s="167"/>
     </row>
     <row r="206" spans="1:19">
-      <c r="D206" s="170"/>
-      <c r="E206" s="171">
-        <v>3</v>
-      </c>
-      <c r="F206" s="23" t="s">
-        <v>195</v>
-      </c>
+      <c r="D206" s="168"/>
+      <c r="E206" s="23"/>
     </row>
     <row r="207" spans="1:19">
-      <c r="D207" s="165" t="s">
-        <v>196</v>
-      </c>
-      <c r="E207" s="171">
-        <v>4</v>
-      </c>
-      <c r="F207" s="23" t="s">
-        <v>197</v>
-      </c>
+      <c r="D207" s="169"/>
+      <c r="E207" s="168"/>
+      <c r="F207" s="23"/>
     </row>
     <row r="208" spans="1:19">
-      <c r="D208" s="167"/>
-      <c r="E208" s="171">
-        <v>5</v>
-      </c>
-      <c r="F208" s="23" t="s">
-        <v>198</v>
-      </c>
+      <c r="D208" s="170"/>
+      <c r="E208" s="168"/>
+      <c r="F208" s="23"/>
     </row>
     <row r="209" spans="4:6">
-      <c r="D209" s="167"/>
-      <c r="E209" s="171">
-        <v>6</v>
-      </c>
-      <c r="F209" s="23" t="s">
-        <v>21</v>
-      </c>
+      <c r="D209" s="170"/>
+      <c r="E209" s="168"/>
+      <c r="F209" s="23"/>
     </row>
     <row r="210" spans="4:6">
-      <c r="D210" s="170"/>
-      <c r="E210" s="171">
-        <v>7</v>
-      </c>
-      <c r="F210" s="23" t="s">
-        <v>199</v>
-      </c>
+      <c r="D210" s="171"/>
+      <c r="E210" s="168"/>
+      <c r="F210" s="23"/>
     </row>
     <row r="211" spans="4:6">
-      <c r="D211" s="165" t="s">
-        <v>200</v>
-      </c>
-      <c r="E211" s="171">
-        <v>8</v>
-      </c>
-      <c r="F211" s="23" t="s">
-        <v>201</v>
-      </c>
+      <c r="D211" s="169"/>
+      <c r="E211" s="168"/>
+      <c r="F211" s="23"/>
     </row>
     <row r="212" spans="4:6">
-      <c r="D212" s="167"/>
-      <c r="E212" s="171">
-        <v>9</v>
-      </c>
-      <c r="F212" s="23" t="s">
-        <v>202</v>
-      </c>
+      <c r="D212" s="170"/>
+      <c r="E212" s="168"/>
+      <c r="F212" s="23"/>
     </row>
     <row r="213" spans="4:6">
-      <c r="D213" s="167"/>
-      <c r="E213" s="171">
-        <v>10</v>
-      </c>
-      <c r="F213" s="23" t="s">
-        <v>203</v>
-      </c>
+      <c r="D213" s="170"/>
+      <c r="E213" s="168"/>
+      <c r="F213" s="23"/>
     </row>
     <row r="214" spans="4:6">
-      <c r="D214" s="170"/>
-      <c r="E214" s="171">
-        <v>11</v>
-      </c>
-      <c r="F214" s="23" t="s">
-        <v>204</v>
-      </c>
+      <c r="D214" s="171"/>
+      <c r="E214" s="168"/>
+      <c r="F214" s="23"/>
     </row>
     <row r="215" spans="4:6">
-      <c r="D215" s="165" t="s">
-        <v>205</v>
-      </c>
-      <c r="E215" s="171">
-        <v>12</v>
-      </c>
-      <c r="F215" s="23" t="s">
-        <v>206</v>
-      </c>
+      <c r="D215" s="169"/>
+      <c r="E215" s="168"/>
+      <c r="F215" s="23"/>
     </row>
     <row r="216" spans="4:6">
-      <c r="D216" s="167"/>
-      <c r="E216" s="171">
-        <v>13</v>
-      </c>
-      <c r="F216" s="23" t="s">
-        <v>207</v>
-      </c>
+      <c r="D216" s="170"/>
+      <c r="E216" s="168"/>
+      <c r="F216" s="23"/>
     </row>
     <row r="217" spans="4:6">
-      <c r="D217" s="167"/>
-      <c r="E217" s="171">
-        <v>14</v>
-      </c>
-      <c r="F217" s="23" t="s">
-        <v>208</v>
-      </c>
+      <c r="D217" s="170"/>
+      <c r="E217" s="168"/>
+      <c r="F217" s="23"/>
     </row>
     <row r="218" spans="4:6">
-      <c r="D218" s="170"/>
-      <c r="E218" s="171">
-        <v>15</v>
-      </c>
-      <c r="F218" s="23" t="s">
-        <v>209</v>
-      </c>
+      <c r="D218" s="171"/>
+      <c r="E218" s="168"/>
+      <c r="F218" s="23"/>
     </row>
     <row r="219" spans="4:6">
-      <c r="D219" s="165" t="s">
-        <v>210</v>
-      </c>
-      <c r="E219" s="171">
-        <v>16</v>
-      </c>
-      <c r="F219" s="23" t="s">
-        <v>211</v>
-      </c>
+      <c r="D219" s="169"/>
+      <c r="E219" s="168"/>
+      <c r="F219" s="23"/>
     </row>
     <row r="220" spans="4:6">
-      <c r="D220" s="167"/>
-      <c r="E220" s="171">
-        <v>17</v>
-      </c>
-      <c r="F220" s="23" t="s">
-        <v>212</v>
-      </c>
+      <c r="D220" s="170"/>
+      <c r="E220" s="168"/>
+      <c r="F220" s="23"/>
     </row>
     <row r="221" spans="4:6">
-      <c r="D221" s="167"/>
-      <c r="E221" s="171">
-        <v>18</v>
-      </c>
-      <c r="F221" s="23" t="s">
-        <v>213</v>
-      </c>
+      <c r="D221" s="170"/>
+      <c r="E221" s="168"/>
+      <c r="F221" s="23"/>
     </row>
     <row r="222" spans="4:6">
-      <c r="D222" s="170"/>
-      <c r="E222" s="171">
-        <v>19</v>
-      </c>
-      <c r="F222" s="23" t="s">
-        <v>214</v>
-      </c>
+      <c r="D222" s="171"/>
+      <c r="E222" s="168"/>
+      <c r="F222" s="23"/>
     </row>
     <row r="223" spans="4:6">
-      <c r="D223" s="165" t="s">
-        <v>215</v>
-      </c>
-      <c r="E223" s="171">
-        <v>20</v>
-      </c>
-      <c r="F223" s="23" t="s">
-        <v>216</v>
-      </c>
+      <c r="D223" s="169"/>
+      <c r="E223" s="168"/>
+      <c r="F223" s="23"/>
     </row>
     <row r="224" spans="4:6">
-      <c r="D224" s="167"/>
-      <c r="E224" s="171">
-        <v>21</v>
-      </c>
-      <c r="F224" s="23" t="s">
-        <v>217</v>
-      </c>
+      <c r="D224" s="170"/>
+      <c r="E224" s="168"/>
+      <c r="F224" s="23"/>
     </row>
     <row r="225" spans="4:6">
-      <c r="D225" s="167"/>
-      <c r="E225" s="171">
-        <v>22</v>
-      </c>
-      <c r="F225" s="23" t="s">
-        <v>218</v>
-      </c>
+      <c r="D225" s="170"/>
+      <c r="E225" s="168"/>
+      <c r="F225" s="23"/>
     </row>
     <row r="226" spans="4:6">
-      <c r="D226" s="170"/>
-      <c r="E226" s="171">
-        <v>23</v>
-      </c>
-      <c r="F226" s="23" t="s">
-        <v>219</v>
-      </c>
+      <c r="D226" s="171"/>
+      <c r="E226" s="168"/>
+      <c r="F226" s="23"/>
     </row>
     <row r="227" ht="16.35" spans="4:6">
-      <c r="D227" s="165" t="s">
-        <v>220</v>
-      </c>
-      <c r="E227" s="171">
-        <v>24</v>
-      </c>
-      <c r="F227" s="37" t="s">
-        <v>221</v>
-      </c>
+      <c r="D227" s="169"/>
+      <c r="E227" s="168"/>
+      <c r="F227" s="37"/>
     </row>
     <row r="228" ht="16.35" spans="4:6">
-      <c r="D228" s="167"/>
-      <c r="E228" s="171">
-        <v>25</v>
-      </c>
-      <c r="F228" s="23" t="s">
-        <v>222</v>
-      </c>
+      <c r="D228" s="170"/>
+      <c r="E228" s="168"/>
+      <c r="F228" s="23"/>
     </row>
     <row r="229" spans="4:6">
-      <c r="D229" s="167"/>
-      <c r="E229" s="171">
-        <v>26</v>
-      </c>
-      <c r="F229" s="23" t="s">
-        <v>223</v>
-      </c>
+      <c r="D229" s="170"/>
+      <c r="E229" s="168"/>
+      <c r="F229" s="23"/>
     </row>
     <row r="230" spans="4:6">
-      <c r="D230" s="170"/>
-      <c r="E230" s="171">
-        <v>27</v>
-      </c>
-      <c r="F230" s="23" t="s">
-        <v>224</v>
-      </c>
+      <c r="D230" s="171"/>
+      <c r="E230" s="168"/>
+      <c r="F230" s="23"/>
     </row>
     <row r="231" spans="4:6">
-      <c r="D231" s="165" t="s">
-        <v>225</v>
-      </c>
-      <c r="E231" s="171">
-        <v>28</v>
-      </c>
-      <c r="F231" s="23" t="s">
-        <v>226</v>
-      </c>
+      <c r="D231" s="169"/>
+      <c r="E231" s="168"/>
+      <c r="F231" s="23"/>
     </row>
     <row r="232" spans="4:6">
-      <c r="D232" s="167"/>
-      <c r="E232" s="171">
-        <v>29</v>
-      </c>
-      <c r="F232" s="23" t="s">
-        <v>227</v>
-      </c>
+      <c r="D232" s="170"/>
+      <c r="E232" s="168"/>
+      <c r="F232" s="23"/>
     </row>
     <row r="233" spans="4:6">
-      <c r="D233" s="167"/>
-      <c r="E233" s="171">
-        <v>30</v>
-      </c>
-      <c r="F233" s="23" t="s">
-        <v>228</v>
-      </c>
+      <c r="D233" s="170"/>
+      <c r="E233" s="168"/>
+      <c r="F233" s="23"/>
     </row>
     <row r="234" spans="4:6">
-      <c r="D234" s="170"/>
-      <c r="E234" s="171">
-        <v>31</v>
-      </c>
-      <c r="F234" s="23" t="s">
-        <v>229</v>
-      </c>
+      <c r="D234" s="171"/>
+      <c r="E234" s="168"/>
+      <c r="F234" s="23"/>
     </row>
     <row r="235" spans="4:6">
-      <c r="D235" s="165" t="s">
-        <v>230</v>
-      </c>
-      <c r="E235" s="171">
-        <v>32</v>
-      </c>
-      <c r="F235" s="23" t="s">
-        <v>231</v>
-      </c>
+      <c r="D235" s="169"/>
+      <c r="E235" s="168"/>
+      <c r="F235" s="23"/>
     </row>
     <row r="236" spans="4:6">
-      <c r="D236" s="167"/>
-      <c r="E236" s="171">
-        <v>33</v>
-      </c>
-      <c r="F236" s="23" t="s">
-        <v>232</v>
-      </c>
+      <c r="D236" s="170"/>
+      <c r="E236" s="168"/>
+      <c r="F236" s="23"/>
     </row>
     <row r="237" spans="4:6">
-      <c r="D237" s="167"/>
-      <c r="E237" s="171">
-        <v>34</v>
-      </c>
-      <c r="F237" s="23" t="s">
-        <v>233</v>
-      </c>
+      <c r="D237" s="170"/>
+      <c r="E237" s="168"/>
+      <c r="F237" s="23"/>
     </row>
     <row r="238" spans="4:6">
-      <c r="D238" s="170"/>
-      <c r="E238" s="171">
-        <v>35</v>
-      </c>
-      <c r="F238" s="23" t="s">
-        <v>234</v>
-      </c>
+      <c r="D238" s="171"/>
+      <c r="E238" s="168"/>
+      <c r="F238" s="23"/>
     </row>
     <row r="239" spans="4:6">
-      <c r="D239" s="165" t="s">
-        <v>235</v>
-      </c>
-      <c r="E239" s="171">
-        <v>36</v>
-      </c>
-      <c r="F239" s="23" t="s">
-        <v>236</v>
-      </c>
+      <c r="D239" s="169"/>
+      <c r="E239" s="168"/>
+      <c r="F239" s="23"/>
     </row>
     <row r="240" spans="4:6">
-      <c r="D240" s="167"/>
-      <c r="E240" s="171">
-        <v>37</v>
-      </c>
-      <c r="F240" s="23" t="s">
-        <v>237</v>
-      </c>
+      <c r="D240" s="170"/>
+      <c r="E240" s="168"/>
+      <c r="F240" s="23"/>
     </row>
     <row r="241" spans="4:6">
-      <c r="D241" s="167"/>
-      <c r="E241" s="171">
-        <v>38</v>
-      </c>
-      <c r="F241" s="23" t="s">
-        <v>238</v>
-      </c>
+      <c r="D241" s="170"/>
+      <c r="E241" s="168"/>
+      <c r="F241" s="23"/>
     </row>
     <row r="242" spans="4:6">
-      <c r="D242" s="170"/>
-      <c r="E242" s="171">
-        <v>39</v>
-      </c>
-      <c r="F242" s="23" t="s">
-        <v>239</v>
-      </c>
+      <c r="D242" s="171"/>
+      <c r="E242" s="168"/>
+      <c r="F242" s="23"/>
     </row>
     <row r="243" spans="4:6">
-      <c r="D243" s="165" t="s">
-        <v>240</v>
-      </c>
-      <c r="E243" s="171">
-        <v>1</v>
-      </c>
-      <c r="F243" s="23" t="s">
-        <v>241</v>
-      </c>
+      <c r="D243" s="169"/>
+      <c r="E243" s="168"/>
+      <c r="F243" s="23"/>
     </row>
     <row r="244" spans="4:6">
-      <c r="D244" s="167"/>
-      <c r="E244" s="171">
-        <v>2</v>
-      </c>
-      <c r="F244" s="172" t="s">
-        <v>242</v>
-      </c>
+      <c r="D244" s="170"/>
+      <c r="E244" s="168"/>
+      <c r="F244" s="172"/>
     </row>
     <row r="245" spans="4:6">
-      <c r="D245" s="170"/>
-      <c r="E245" s="171">
-        <v>3</v>
-      </c>
-      <c r="F245" s="23" t="s">
-        <v>243</v>
-      </c>
+      <c r="D245" s="171"/>
+      <c r="E245" s="168"/>
+      <c r="F245" s="23"/>
     </row>
     <row r="246" spans="4:6">
-      <c r="D246" s="165" t="s">
-        <v>244</v>
-      </c>
-      <c r="E246" s="171">
-        <v>4</v>
-      </c>
-      <c r="F246" s="18" t="s">
-        <v>245</v>
-      </c>
+      <c r="D246" s="169"/>
+      <c r="E246" s="168"/>
+      <c r="F246" s="18"/>
     </row>
     <row r="247" spans="4:6">
-      <c r="D247" s="167"/>
-      <c r="E247" s="173">
-        <v>5</v>
-      </c>
-      <c r="F247" s="18" t="s">
-        <v>246</v>
-      </c>
+      <c r="D247" s="170"/>
+      <c r="E247" s="173"/>
+      <c r="F247" s="18"/>
     </row>
     <row r="248" spans="4:6">
-      <c r="D248" s="167"/>
-      <c r="E248" s="171">
-        <v>6</v>
-      </c>
-      <c r="F248" s="18" t="s">
-        <v>247</v>
-      </c>
+      <c r="D248" s="170"/>
+      <c r="E248" s="168"/>
+      <c r="F248" s="18"/>
     </row>
     <row r="249" spans="4:6">
-      <c r="D249" s="170"/>
-      <c r="E249" s="173">
-        <v>7</v>
-      </c>
-      <c r="F249" s="74" t="s">
-        <v>248</v>
-      </c>
+      <c r="D249" s="171"/>
+      <c r="E249" s="173"/>
+      <c r="F249" s="74"/>
     </row>
     <row r="250" spans="4:6">
-      <c r="D250" s="165" t="s">
-        <v>249</v>
-      </c>
-      <c r="E250" s="171">
-        <v>8</v>
-      </c>
-      <c r="F250" s="18" t="s">
-        <v>250</v>
-      </c>
+      <c r="D250" s="169"/>
+      <c r="E250" s="168"/>
+      <c r="F250" s="18"/>
     </row>
     <row r="251" spans="4:6">
-      <c r="D251" s="167"/>
-      <c r="E251" s="171">
-        <v>9</v>
-      </c>
-      <c r="F251" s="18" t="s">
-        <v>251</v>
-      </c>
+      <c r="D251" s="170"/>
+      <c r="E251" s="168"/>
+      <c r="F251" s="18"/>
     </row>
     <row r="252" spans="4:6">
-      <c r="D252" s="167"/>
-      <c r="E252" s="171">
-        <v>10</v>
-      </c>
-      <c r="F252" s="18" t="s">
-        <v>252</v>
-      </c>
+      <c r="D252" s="170"/>
+      <c r="E252" s="168"/>
+      <c r="F252" s="18"/>
     </row>
     <row r="253" spans="4:6">
-      <c r="D253" s="170"/>
-      <c r="E253" s="171">
-        <v>11</v>
-      </c>
-      <c r="F253" s="23" t="s">
-        <v>253</v>
-      </c>
+      <c r="D253" s="171"/>
+      <c r="E253" s="168"/>
+      <c r="F253" s="23"/>
     </row>
     <row r="254" spans="4:6">
-      <c r="D254" s="165" t="s">
-        <v>254</v>
-      </c>
-      <c r="E254" s="171">
-        <v>12</v>
-      </c>
-      <c r="F254" s="18" t="s">
-        <v>255</v>
-      </c>
+      <c r="D254" s="169"/>
+      <c r="E254" s="168"/>
+      <c r="F254" s="18"/>
     </row>
     <row r="255" spans="4:6">
-      <c r="D255" s="167"/>
-      <c r="E255" s="171">
-        <v>13</v>
-      </c>
-      <c r="F255" s="18" t="s">
-        <v>256</v>
-      </c>
+      <c r="D255" s="170"/>
+      <c r="E255" s="168"/>
+      <c r="F255" s="18"/>
     </row>
     <row r="256" spans="4:6">
-      <c r="D256" s="167"/>
-      <c r="E256" s="171">
-        <v>14</v>
-      </c>
-      <c r="F256" s="18" t="s">
-        <v>257</v>
-      </c>
+      <c r="D256" s="170"/>
+      <c r="E256" s="168"/>
+      <c r="F256" s="18"/>
     </row>
     <row r="257" spans="4:6">
-      <c r="D257" s="170"/>
-      <c r="E257" s="171">
-        <v>15</v>
-      </c>
-      <c r="F257" s="23" t="s">
-        <v>258</v>
-      </c>
+      <c r="D257" s="171"/>
+      <c r="E257" s="168"/>
+      <c r="F257" s="23"/>
     </row>
     <row r="258" spans="4:6">
-      <c r="D258" s="165" t="s">
-        <v>259</v>
-      </c>
-      <c r="E258" s="171">
-        <v>12</v>
-      </c>
-      <c r="F258" s="18" t="s">
-        <v>260</v>
-      </c>
+      <c r="D258" s="169"/>
+      <c r="E258" s="168"/>
+      <c r="F258" s="18"/>
     </row>
     <row r="259" spans="4:6">
-      <c r="D259" s="167"/>
-      <c r="E259" s="171">
-        <v>13</v>
-      </c>
-      <c r="F259" s="18" t="s">
-        <v>261</v>
-      </c>
+      <c r="D259" s="170"/>
+      <c r="E259" s="168"/>
+      <c r="F259" s="18"/>
     </row>
     <row r="260" spans="4:6">
-      <c r="D260" s="167"/>
-      <c r="E260" s="171">
-        <v>14</v>
-      </c>
-      <c r="F260" s="18" t="s">
-        <v>262</v>
-      </c>
+      <c r="D260" s="170"/>
+      <c r="E260" s="168"/>
+      <c r="F260" s="18"/>
     </row>
     <row r="261" spans="4:6">
-      <c r="D261" s="170"/>
-      <c r="E261" s="171">
-        <v>15</v>
-      </c>
-      <c r="F261" s="23" t="s">
-        <v>263</v>
-      </c>
+      <c r="D261" s="171"/>
+      <c r="E261" s="168"/>
+      <c r="F261" s="23"/>
     </row>
     <row r="262" spans="4:6">
-      <c r="D262" s="165" t="s">
-        <v>264</v>
-      </c>
-      <c r="E262" s="171">
-        <v>12</v>
-      </c>
-      <c r="F262" s="23" t="s">
-        <v>265</v>
-      </c>
+      <c r="D262" s="169"/>
+      <c r="E262" s="168"/>
+      <c r="F262" s="23"/>
     </row>
     <row r="263" spans="4:6">
-      <c r="D263" s="167"/>
-      <c r="E263" s="171">
-        <v>13</v>
-      </c>
-      <c r="F263" s="18" t="s">
-        <v>266</v>
-      </c>
+      <c r="D263" s="170"/>
+      <c r="E263" s="168"/>
+      <c r="F263" s="18"/>
     </row>
     <row r="264" spans="4:6">
-      <c r="D264" s="167"/>
-      <c r="E264" s="171">
-        <v>14</v>
-      </c>
-      <c r="F264" s="18" t="s">
-        <v>267</v>
-      </c>
+      <c r="D264" s="170"/>
+      <c r="E264" s="168"/>
+      <c r="F264" s="18"/>
     </row>
     <row r="265" spans="4:6">
-      <c r="D265" s="170"/>
-      <c r="E265" s="171">
-        <v>15</v>
-      </c>
-      <c r="F265" s="23" t="s">
-        <v>268</v>
-      </c>
+      <c r="D265" s="171"/>
+      <c r="E265" s="168"/>
+      <c r="F265" s="23"/>
     </row>
     <row r="266" spans="4:6">
-      <c r="D266" s="165" t="s">
-        <v>269</v>
-      </c>
-      <c r="E266" s="171">
-        <v>12</v>
-      </c>
-      <c r="F266" s="18" t="s">
-        <v>270</v>
-      </c>
+      <c r="D266" s="169"/>
+      <c r="E266" s="168"/>
+      <c r="F266" s="18"/>
     </row>
     <row r="267" spans="4:6">
-      <c r="D267" s="167"/>
-      <c r="E267" s="171">
-        <v>13</v>
-      </c>
-      <c r="F267" s="18" t="s">
-        <v>271</v>
-      </c>
+      <c r="D267" s="170"/>
+      <c r="E267" s="168"/>
+      <c r="F267" s="18"/>
     </row>
     <row r="268" spans="4:6">
-      <c r="D268" s="167"/>
-      <c r="E268" s="171">
-        <v>14</v>
-      </c>
-      <c r="F268" s="18" t="s">
-        <v>272</v>
-      </c>
+      <c r="D268" s="170"/>
+      <c r="E268" s="168"/>
+      <c r="F268" s="18"/>
     </row>
     <row r="269" spans="4:6">
-      <c r="D269" s="170"/>
-      <c r="E269" s="171">
-        <v>15</v>
-      </c>
-      <c r="F269" s="23" t="s">
-        <v>273</v>
-      </c>
+      <c r="D269" s="171"/>
+      <c r="E269" s="168"/>
+      <c r="F269" s="23"/>
     </row>
     <row r="270" spans="4:6">
-      <c r="D270" s="165" t="s">
-        <v>274</v>
-      </c>
-      <c r="E270" s="171">
-        <v>12</v>
-      </c>
-      <c r="F270" s="18" t="s">
-        <v>275</v>
-      </c>
+      <c r="D270" s="169"/>
+      <c r="E270" s="168"/>
+      <c r="F270" s="18"/>
     </row>
     <row r="271" spans="4:6">
-      <c r="D271" s="167"/>
-      <c r="E271" s="171">
-        <v>13</v>
-      </c>
-      <c r="F271" s="44" t="s">
-        <v>276</v>
-      </c>
+      <c r="D271" s="170"/>
+      <c r="E271" s="168"/>
+      <c r="F271" s="44"/>
     </row>
     <row r="272" spans="4:6">
-      <c r="D272" s="167"/>
-      <c r="E272" s="171">
-        <v>14</v>
-      </c>
-      <c r="F272" s="18" t="s">
-        <v>277</v>
-      </c>
+      <c r="D272" s="170"/>
+      <c r="E272" s="168"/>
+      <c r="F272" s="18"/>
     </row>
     <row r="273" spans="4:6">
-      <c r="D273" s="170"/>
-      <c r="E273" s="171">
-        <v>15</v>
-      </c>
-      <c r="F273" s="23" t="s">
-        <v>278</v>
-      </c>
+      <c r="D273" s="171"/>
+      <c r="E273" s="168"/>
+      <c r="F273" s="23"/>
     </row>
     <row r="274" ht="16.35" spans="4:6">
-      <c r="D274" s="165" t="s">
-        <v>279</v>
-      </c>
-      <c r="E274" s="171">
-        <v>12</v>
-      </c>
-      <c r="F274" s="72" t="s">
-        <v>33</v>
-      </c>
+      <c r="D274" s="169"/>
+      <c r="E274" s="168"/>
+      <c r="F274" s="72"/>
     </row>
     <row r="275" ht="16.35" spans="4:6">
-      <c r="D275" s="167"/>
-      <c r="E275" s="171">
-        <v>13</v>
-      </c>
-      <c r="F275" s="18" t="s">
-        <v>280</v>
-      </c>
+      <c r="D275" s="170"/>
+      <c r="E275" s="168"/>
+      <c r="F275" s="18"/>
     </row>
     <row r="276" spans="4:6">
-      <c r="D276" s="167"/>
-      <c r="E276" s="171">
-        <v>14</v>
-      </c>
-      <c r="F276" s="18" t="s">
-        <v>281</v>
-      </c>
+      <c r="D276" s="170"/>
+      <c r="E276" s="168"/>
+      <c r="F276" s="18"/>
     </row>
     <row r="277" spans="4:6">
-      <c r="D277" s="170"/>
-      <c r="E277" s="171">
-        <v>15</v>
-      </c>
-      <c r="F277" s="23" t="s">
-        <v>282</v>
-      </c>
+      <c r="D277" s="171"/>
+      <c r="E277" s="168"/>
+      <c r="F277" s="23"/>
     </row>
     <row r="278" spans="4:6">
-      <c r="D278" s="165" t="s">
-        <v>283</v>
-      </c>
-      <c r="E278" s="171">
-        <v>12</v>
-      </c>
-      <c r="F278" s="23" t="s">
-        <v>284</v>
-      </c>
+      <c r="D278" s="169"/>
+      <c r="E278" s="168"/>
+      <c r="F278" s="23"/>
     </row>
     <row r="279" spans="4:6">
-      <c r="D279" s="167"/>
-      <c r="E279" s="171">
-        <v>13</v>
-      </c>
-      <c r="F279" s="18" t="s">
-        <v>285</v>
-      </c>
+      <c r="D279" s="170"/>
+      <c r="E279" s="168"/>
+      <c r="F279" s="18"/>
     </row>
     <row r="280" spans="4:6">
-      <c r="D280" s="167"/>
-      <c r="E280" s="171">
-        <v>14</v>
-      </c>
-      <c r="F280" s="18" t="s">
-        <v>286</v>
-      </c>
+      <c r="D280" s="170"/>
+      <c r="E280" s="168"/>
+      <c r="F280" s="18"/>
     </row>
     <row r="281" spans="4:6">
-      <c r="D281" s="170"/>
-      <c r="E281" s="171">
-        <v>15</v>
-      </c>
-      <c r="F281" s="23" t="s">
-        <v>287</v>
-      </c>
+      <c r="D281" s="171"/>
+      <c r="E281" s="168"/>
+      <c r="F281" s="23"/>
     </row>
     <row r="282" ht="16.35" spans="4:6">
-      <c r="D282" s="165" t="s">
-        <v>288</v>
-      </c>
-      <c r="E282" s="171">
-        <v>1</v>
-      </c>
-      <c r="F282" s="37" t="s">
-        <v>289</v>
-      </c>
+      <c r="D282" s="169"/>
+      <c r="E282" s="168"/>
+      <c r="F282" s="37"/>
     </row>
     <row r="283" ht="17.1" spans="4:6">
-      <c r="D283" s="167"/>
-      <c r="E283" s="171">
-        <v>2</v>
-      </c>
-      <c r="F283" s="37" t="s">
-        <v>290</v>
-      </c>
+      <c r="D283" s="170"/>
+      <c r="E283" s="168"/>
+      <c r="F283" s="37"/>
     </row>
     <row r="284" ht="16.35" spans="4:6">
-      <c r="D284" s="170"/>
-      <c r="E284" s="171">
-        <v>3</v>
-      </c>
-      <c r="F284" s="48" t="s">
-        <v>291</v>
-      </c>
+      <c r="D284" s="171"/>
+      <c r="E284" s="168"/>
+      <c r="F284" s="48"/>
     </row>
     <row r="285" ht="16.35" spans="4:6">
-      <c r="D285" s="165" t="s">
-        <v>292</v>
-      </c>
-      <c r="E285" s="171">
-        <v>4</v>
-      </c>
-      <c r="F285" s="37" t="s">
-        <v>293</v>
-      </c>
+      <c r="D285" s="169"/>
+      <c r="E285" s="168"/>
+      <c r="F285" s="37"/>
     </row>
     <row r="286" ht="17.1" spans="4:6">
-      <c r="D286" s="167"/>
-      <c r="E286" s="171">
-        <v>5</v>
-      </c>
-      <c r="F286" s="37" t="s">
-        <v>294</v>
-      </c>
+      <c r="D286" s="170"/>
+      <c r="E286" s="168"/>
+      <c r="F286" s="37"/>
     </row>
     <row r="287" ht="16.35" spans="4:6">
-      <c r="D287" s="167"/>
-      <c r="E287" s="171">
-        <v>6</v>
-      </c>
-      <c r="F287" s="174" t="s">
-        <v>295</v>
-      </c>
+      <c r="D287" s="170"/>
+      <c r="E287" s="168"/>
+      <c r="F287" s="174"/>
     </row>
     <row r="288" spans="4:6">
-      <c r="D288" s="170"/>
-      <c r="E288" s="171">
-        <v>7</v>
-      </c>
-      <c r="F288" s="18" t="s">
-        <v>296</v>
-      </c>
+      <c r="D288" s="171"/>
+      <c r="E288" s="168"/>
+      <c r="F288" s="18"/>
     </row>
     <row r="289" ht="16.35" spans="4:6">
-      <c r="D289" s="165" t="s">
-        <v>297</v>
-      </c>
-      <c r="E289" s="171">
-        <v>8</v>
-      </c>
-      <c r="F289" s="37" t="s">
-        <v>298</v>
-      </c>
+      <c r="D289" s="169"/>
+      <c r="E289" s="168"/>
+      <c r="F289" s="37"/>
     </row>
     <row r="290" ht="16.35" spans="4:6">
-      <c r="D290" s="167"/>
-      <c r="E290" s="92">
-        <v>9</v>
-      </c>
-      <c r="F290" s="44" t="s">
-        <v>299</v>
-      </c>
+      <c r="D290" s="170"/>
+      <c r="E290" s="92"/>
+      <c r="F290" s="44"/>
     </row>
     <row r="291" spans="4:6">
-      <c r="D291" s="167"/>
-      <c r="E291" s="171">
-        <v>10</v>
-      </c>
-      <c r="F291" s="48" t="s">
-        <v>300</v>
-      </c>
+      <c r="D291" s="170"/>
+      <c r="E291" s="168"/>
+      <c r="F291" s="48"/>
     </row>
     <row r="292" spans="4:6">
-      <c r="D292" s="170"/>
-      <c r="E292" s="171">
-        <v>11</v>
-      </c>
-      <c r="F292" s="74" t="s">
-        <v>301</v>
-      </c>
+      <c r="D292" s="171"/>
+      <c r="E292" s="168"/>
+      <c r="F292" s="74"/>
     </row>
     <row r="293" ht="16.35" spans="4:6">
-      <c r="D293" s="165" t="s">
-        <v>302</v>
-      </c>
-      <c r="E293" s="171">
-        <v>12</v>
-      </c>
-      <c r="F293" s="72" t="s">
-        <v>33</v>
-      </c>
+      <c r="D293" s="169"/>
+      <c r="E293" s="168"/>
+      <c r="F293" s="72"/>
     </row>
     <row r="294" ht="16.35" spans="4:6">
-      <c r="D294" s="167"/>
-      <c r="E294" s="171">
-        <v>13</v>
-      </c>
-      <c r="F294" s="23" t="s">
-        <v>303</v>
-      </c>
+      <c r="D294" s="170"/>
+      <c r="E294" s="168"/>
+      <c r="F294" s="23"/>
     </row>
     <row r="295" spans="4:6">
-      <c r="D295" s="167"/>
-      <c r="E295" s="171">
-        <v>14</v>
-      </c>
-      <c r="F295" s="23" t="s">
-        <v>304</v>
-      </c>
+      <c r="D295" s="170"/>
+      <c r="E295" s="168"/>
+      <c r="F295" s="23"/>
     </row>
     <row r="296" spans="4:6">
-      <c r="D296" s="170"/>
-      <c r="E296" s="171">
-        <v>15</v>
-      </c>
-      <c r="F296" s="23" t="s">
-        <v>305</v>
-      </c>
+      <c r="D296" s="171"/>
+      <c r="E296" s="168"/>
+      <c r="F296" s="23"/>
     </row>
     <row r="297" spans="4:6">
-      <c r="D297" s="165" t="s">
-        <v>306</v>
-      </c>
-      <c r="E297" s="171">
-        <v>16</v>
-      </c>
-      <c r="F297" s="92" t="s">
-        <v>307</v>
-      </c>
+      <c r="D297" s="169"/>
+      <c r="E297" s="168"/>
+      <c r="F297" s="92"/>
     </row>
     <row r="298" spans="4:6">
-      <c r="D298" s="167"/>
-      <c r="E298" s="171">
-        <v>17</v>
-      </c>
-      <c r="F298" s="23" t="s">
-        <v>308</v>
-      </c>
+      <c r="D298" s="170"/>
+      <c r="E298" s="168"/>
+      <c r="F298" s="23"/>
     </row>
     <row r="299" ht="16.35" spans="4:6">
-      <c r="D299" s="167"/>
-      <c r="E299" s="171">
-        <v>18</v>
-      </c>
-      <c r="F299" s="37" t="s">
-        <v>309</v>
-      </c>
+      <c r="D299" s="170"/>
+      <c r="E299" s="168"/>
+      <c r="F299" s="37"/>
     </row>
     <row r="300" ht="17.1" spans="4:6">
-      <c r="D300" s="170"/>
-      <c r="E300" s="171">
-        <v>19</v>
-      </c>
-      <c r="F300" s="37" t="s">
-        <v>310</v>
-      </c>
+      <c r="D300" s="171"/>
+      <c r="E300" s="168"/>
+      <c r="F300" s="37"/>
     </row>
     <row r="301" ht="17.1" spans="4:6">
-      <c r="D301" s="165" t="s">
-        <v>311</v>
-      </c>
-      <c r="E301" s="171">
-        <v>20</v>
-      </c>
-      <c r="F301" s="72" t="s">
-        <v>33</v>
-      </c>
+      <c r="D301" s="169"/>
+      <c r="E301" s="168"/>
+      <c r="F301" s="72"/>
     </row>
     <row r="302" ht="16.35" spans="4:6">
-      <c r="D302" s="167"/>
-      <c r="E302" s="171">
-        <v>21</v>
-      </c>
-      <c r="F302" s="23" t="s">
-        <v>312</v>
-      </c>
+      <c r="D302" s="170"/>
+      <c r="E302" s="168"/>
+      <c r="F302" s="23"/>
     </row>
     <row r="303" spans="4:6">
-      <c r="D303" s="167"/>
-      <c r="E303" s="171">
-        <v>22</v>
-      </c>
-      <c r="F303" s="23" t="s">
-        <v>313</v>
-      </c>
+      <c r="D303" s="170"/>
+      <c r="E303" s="168"/>
+      <c r="F303" s="23"/>
     </row>
     <row r="304" spans="4:6">
-      <c r="D304" s="170"/>
-      <c r="E304" s="171">
-        <v>23</v>
-      </c>
-      <c r="F304" s="23" t="s">
-        <v>314</v>
-      </c>
+      <c r="D304" s="171"/>
+      <c r="E304" s="168"/>
+      <c r="F304" s="23"/>
     </row>
     <row r="305" spans="4:6">
-      <c r="D305" s="165" t="s">
-        <v>315</v>
-      </c>
-      <c r="E305" s="171">
-        <v>24</v>
-      </c>
-      <c r="F305" s="18" t="s">
-        <v>316</v>
-      </c>
+      <c r="D305" s="169"/>
+      <c r="E305" s="168"/>
+      <c r="F305" s="18"/>
     </row>
     <row r="306" ht="16.35" spans="4:6">
-      <c r="D306" s="167"/>
-      <c r="E306" s="171">
-        <v>25</v>
-      </c>
-      <c r="F306" s="37" t="s">
-        <v>317</v>
-      </c>
+      <c r="D306" s="170"/>
+      <c r="E306" s="168"/>
+      <c r="F306" s="37"/>
     </row>
     <row r="307" ht="16.35" spans="4:6">
-      <c r="D307" s="167"/>
-      <c r="E307" s="171">
-        <v>26</v>
-      </c>
-      <c r="F307" s="23" t="s">
-        <v>318</v>
-      </c>
+      <c r="D307" s="170"/>
+      <c r="E307" s="168"/>
+      <c r="F307" s="23"/>
     </row>
     <row r="308" spans="4:6">
-      <c r="D308" s="170"/>
-      <c r="E308" s="171">
-        <v>27</v>
-      </c>
-      <c r="F308" s="23" t="s">
-        <v>319</v>
-      </c>
+      <c r="D308" s="171"/>
+      <c r="E308" s="168"/>
+      <c r="F308" s="23"/>
     </row>
     <row r="309" spans="4:6">
-      <c r="D309" s="165" t="s">
-        <v>320</v>
-      </c>
-      <c r="E309" s="171">
-        <v>12</v>
-      </c>
-      <c r="F309" s="23" t="s">
-        <v>321</v>
-      </c>
+      <c r="D309" s="169"/>
+      <c r="E309" s="168"/>
+      <c r="F309" s="23"/>
     </row>
     <row r="310" spans="4:6">
-      <c r="D310" s="167"/>
-      <c r="E310" s="171">
-        <v>13</v>
-      </c>
-      <c r="F310" s="23" t="s">
-        <v>322</v>
-      </c>
+      <c r="D310" s="170"/>
+      <c r="E310" s="168"/>
+      <c r="F310" s="23"/>
     </row>
     <row r="311" spans="4:6">
-      <c r="D311" s="167"/>
-      <c r="E311" s="171">
-        <v>14</v>
-      </c>
-      <c r="F311" s="23" t="s">
-        <v>323</v>
-      </c>
+      <c r="D311" s="170"/>
+      <c r="E311" s="168"/>
+      <c r="F311" s="23"/>
     </row>
     <row r="312" spans="4:6">
-      <c r="D312" s="170"/>
-      <c r="E312" s="171">
-        <v>15</v>
-      </c>
-      <c r="F312" s="18" t="s">
-        <v>324</v>
-      </c>
+      <c r="D312" s="171"/>
+      <c r="E312" s="168"/>
+      <c r="F312" s="18"/>
     </row>
     <row r="313" spans="4:6">
-      <c r="D313" s="165" t="s">
-        <v>325</v>
-      </c>
-      <c r="E313" s="171">
-        <v>16</v>
-      </c>
-      <c r="F313" s="175" t="s">
-        <v>326</v>
-      </c>
+      <c r="D313" s="169"/>
+      <c r="E313" s="168"/>
+      <c r="F313" s="175"/>
     </row>
     <row r="314" spans="4:6">
-      <c r="D314" s="167"/>
-      <c r="E314" s="171">
-        <v>17</v>
-      </c>
-      <c r="F314" s="48" t="s">
-        <v>327</v>
-      </c>
+      <c r="D314" s="170"/>
+      <c r="E314" s="168"/>
+      <c r="F314" s="48"/>
     </row>
     <row r="315" spans="4:6">
-      <c r="D315" s="167"/>
-      <c r="E315" s="171">
-        <v>18</v>
-      </c>
-      <c r="F315" s="18" t="s">
-        <v>328</v>
-      </c>
+      <c r="D315" s="170"/>
+      <c r="E315" s="168"/>
+      <c r="F315" s="18"/>
     </row>
     <row r="316" spans="4:6">
-      <c r="D316" s="170"/>
-      <c r="E316" s="171">
-        <v>19</v>
-      </c>
-      <c r="F316" s="23" t="s">
-        <v>329</v>
-      </c>
+      <c r="D316" s="171"/>
+      <c r="E316" s="168"/>
+      <c r="F316" s="23"/>
     </row>
     <row r="317" spans="4:6">
-      <c r="D317" s="165" t="s">
-        <v>330</v>
-      </c>
-      <c r="E317" s="171">
-        <v>20</v>
-      </c>
-      <c r="F317" s="23" t="s">
-        <v>331</v>
-      </c>
+      <c r="D317" s="169"/>
+      <c r="E317" s="168"/>
+      <c r="F317" s="23"/>
     </row>
     <row r="318" spans="4:6">
-      <c r="D318" s="167"/>
-      <c r="E318" s="171">
-        <v>21</v>
-      </c>
-      <c r="F318" s="23" t="s">
-        <v>332</v>
-      </c>
+      <c r="D318" s="170"/>
+      <c r="E318" s="168"/>
+      <c r="F318" s="23"/>
     </row>
     <row r="319" spans="4:6">
-      <c r="D319" s="167"/>
-      <c r="E319" s="171">
-        <v>22</v>
-      </c>
-      <c r="F319" s="23" t="s">
-        <v>333</v>
-      </c>
+      <c r="D319" s="170"/>
+      <c r="E319" s="168"/>
+      <c r="F319" s="23"/>
     </row>
     <row r="320" spans="4:6">
-      <c r="D320" s="170"/>
-      <c r="E320" s="171">
-        <v>23</v>
-      </c>
-      <c r="F320" s="74" t="s">
-        <v>334</v>
-      </c>
+      <c r="D320" s="171"/>
+      <c r="E320" s="168"/>
+      <c r="F320" s="74"/>
     </row>
     <row r="321" spans="4:6">
       <c r="D321" s="176"/>
-      <c r="E321" s="171"/>
-      <c r="F321" s="23" t="s">
-        <v>335</v>
-      </c>
+      <c r="E321" s="168"/>
+      <c r="F321" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="67">
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="D7:D10"/>
     <mergeCell ref="D11:D14"/>
@@ -9103,7 +8131,6 @@
     <mergeCell ref="D186:D191"/>
     <mergeCell ref="D192:D197"/>
     <mergeCell ref="D198:D203"/>
-    <mergeCell ref="D204:D206"/>
     <mergeCell ref="D207:D210"/>
     <mergeCell ref="D211:D214"/>
     <mergeCell ref="D215:D218"/>

--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -27,12 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="193">
   <si>
     <t>ROOMS</t>
   </si>
   <si>
     <t xml:space="preserve">NAME OF THE STUDENTS </t>
+  </si>
+  <si>
+    <t>mobile number parentss</t>
   </si>
   <si>
     <t>NAKUL PARAKH</t>
@@ -615,7 +618,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="38">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -677,13 +680,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Copperplate Gothic Bold"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Copperplate Gothic Bold"/>
@@ -695,19 +691,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Copperplate Gothic Bold"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Copperplate Gothic Bold"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Copperplate Gothic Bold"/>
@@ -720,20 +703,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Copperplate Gothic Bold"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -751,21 +720,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Kokila"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Kokila"/>
@@ -782,13 +736,6 @@
       <sz val="12"/>
       <color rgb="FFFF0000"/>
       <name val="Copperplate Gothic Light"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Copperplate Gothic Bold"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1560,137 +1507,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="23" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="10" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="27" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="10" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1753,9 +1700,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1769,11 +1713,8 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1783,9 +1724,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1796,14 +1734,8 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1812,9 +1744,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1822,17 +1751,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1843,86 +1766,47 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1931,28 +1815,13 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1961,36 +1830,27 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1998,9 +1858,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2009,29 +1866,14 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2040,81 +1882,39 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2141,7 +1941,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2480,7 +2280,7 @@
     <col min="4" max="4" width="7" style="2" customWidth="1"/>
     <col min="5" max="5" width="5.88888888888889" style="2" customWidth="1"/>
     <col min="6" max="6" width="32.6666666666667" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.88888888888889" style="3" customWidth="1"/>
+    <col min="7" max="7" width="32.2962962962963" style="3" customWidth="1"/>
     <col min="8" max="8" width="7" style="2" customWidth="1"/>
     <col min="9" max="9" width="13.6666666666667" style="4" customWidth="1"/>
     <col min="10" max="10" width="11.3333333333333" style="4" customWidth="1"/>
@@ -2507,7 +2307,9 @@
       <c r="F2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="10"/>
+      <c r="G2" s="10" t="s">
+        <v>2</v>
+      </c>
       <c r="H2" s="9"/>
       <c r="I2" s="11"/>
       <c r="J2" s="10"/>
@@ -2532,9 +2334,11 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="19"/>
+        <v>3</v>
+      </c>
+      <c r="G3" s="19">
+        <v>1234567891</v>
+      </c>
       <c r="H3" s="18"/>
       <c r="I3" s="20"/>
       <c r="J3" s="21"/>
@@ -2557,9 +2361,11 @@
         <v>2</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="26"/>
+        <v>4</v>
+      </c>
+      <c r="G4" s="19">
+        <v>1234567892</v>
+      </c>
       <c r="H4" s="25"/>
       <c r="I4" s="20"/>
       <c r="J4" s="21"/>
@@ -2582,9 +2388,11 @@
         <v>3</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="26"/>
+        <v>5</v>
+      </c>
+      <c r="G5" s="19">
+        <v>1234567893</v>
+      </c>
       <c r="H5" s="18"/>
       <c r="I5" s="20"/>
       <c r="J5" s="21"/>
@@ -2602,14 +2410,16 @@
       <c r="A6" s="15"/>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="28">
+      <c r="D6" s="26"/>
+      <c r="E6" s="27">
         <v>4</v>
       </c>
-      <c r="F6" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="10"/>
+      <c r="F6" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1234567894</v>
+      </c>
       <c r="H6" s="25"/>
       <c r="I6" s="21"/>
       <c r="J6" s="21"/>
@@ -2627,27 +2437,29 @@
       <c r="A7" s="15"/>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="30">
+      <c r="D7" s="29">
         <v>102</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>1</v>
       </c>
-      <c r="F7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="33"/>
+      <c r="F7" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="19">
+        <v>1234567895</v>
+      </c>
       <c r="H7" s="18"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="35"/>
-      <c r="M7" s="35"/>
-      <c r="N7" s="35"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="21"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="36"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="34"/>
       <c r="S7" s="21"/>
     </row>
     <row r="8" spans="1:19">
@@ -2659,9 +2471,11 @@
         <v>2</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="26"/>
+        <v>8</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1234567896</v>
+      </c>
       <c r="H8" s="25"/>
       <c r="I8" s="20"/>
       <c r="J8" s="21"/>
@@ -2684,9 +2498,11 @@
         <v>3</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="26"/>
+        <v>9</v>
+      </c>
+      <c r="G9" s="19">
+        <v>1234567897</v>
+      </c>
       <c r="H9" s="18"/>
       <c r="I9" s="20"/>
       <c r="J9" s="21"/>
@@ -2704,21 +2520,23 @@
       <c r="A10" s="15"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="28">
+      <c r="D10" s="26"/>
+      <c r="E10" s="27">
         <v>4</v>
       </c>
-      <c r="F10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="38"/>
+      <c r="F10" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1234567898</v>
+      </c>
       <c r="H10" s="25"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
       <c r="O10" s="21"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
@@ -2732,20 +2550,22 @@
       <c r="D11" s="16">
         <v>103</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="38">
         <v>1</v>
       </c>
-      <c r="F11" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="43"/>
+      <c r="F11" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="19">
+        <v>1234567899</v>
+      </c>
       <c r="H11" s="18"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
       <c r="O11" s="21"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="21"/>
@@ -2761,9 +2581,11 @@
         <v>2</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="G12" s="19">
+        <v>1234567900</v>
+      </c>
       <c r="H12" s="25"/>
       <c r="I12" s="20"/>
       <c r="J12" s="21"/>
@@ -2782,13 +2604,15 @@
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="24"/>
-      <c r="E13" s="41">
+      <c r="E13" s="38">
         <v>3</v>
       </c>
-      <c r="F13" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="45"/>
+      <c r="F13" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="19">
+        <v>1234567901</v>
+      </c>
       <c r="H13" s="18"/>
       <c r="I13" s="20"/>
       <c r="J13" s="21"/>
@@ -2806,22 +2630,24 @@
       <c r="A14" s="15"/>
       <c r="B14" s="15"/>
       <c r="C14" s="15"/>
-      <c r="D14" s="27"/>
+      <c r="D14" s="26"/>
       <c r="E14" s="17">
         <v>4</v>
       </c>
-      <c r="F14" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="47"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
+      <c r="F14" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="19">
+        <v>1234567902</v>
+      </c>
+      <c r="H14" s="40"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
       <c r="R14" s="23"/>
@@ -2832,12 +2658,14 @@
       <c r="B15" s="15"/>
       <c r="C15" s="15"/>
       <c r="D15" s="24"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="19">
+        <v>1234567903</v>
+      </c>
+      <c r="H15" s="43"/>
       <c r="I15" s="20"/>
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
@@ -2854,24 +2682,26 @@
       <c r="A16" s="15"/>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>104</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>1</v>
       </c>
-      <c r="F16" s="50" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="33"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="52"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="35"/>
+      <c r="F16" s="44" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="19">
+        <v>1234567904</v>
+      </c>
+      <c r="H16" s="45"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
       <c r="R16" s="23"/>
@@ -2882,13 +2712,15 @@
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="24"/>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>2</v>
       </c>
-      <c r="F17" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17" s="45"/>
+      <c r="F17" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="19">
+        <v>1234567905</v>
+      </c>
       <c r="H17" s="25"/>
       <c r="I17" s="20"/>
       <c r="J17" s="21"/>
@@ -2907,13 +2739,15 @@
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="24"/>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <v>3</v>
       </c>
-      <c r="F18" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="45"/>
+      <c r="F18" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" s="19">
+        <v>1234567906</v>
+      </c>
       <c r="H18" s="18"/>
       <c r="I18" s="20"/>
       <c r="J18" s="21"/>
@@ -2931,21 +2765,23 @@
       <c r="A19" s="15"/>
       <c r="B19" s="15"/>
       <c r="C19" s="15"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="31">
+      <c r="D19" s="26"/>
+      <c r="E19" s="30">
         <v>4</v>
       </c>
-      <c r="F19" s="53" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="54"/>
+      <c r="F19" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="19">
+        <v>1234567907</v>
+      </c>
       <c r="H19" s="25"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="37"/>
+      <c r="M19" s="37"/>
+      <c r="N19" s="37"/>
       <c r="O19" s="21"/>
       <c r="P19" s="21"/>
       <c r="Q19" s="21"/>
@@ -2959,20 +2795,22 @@
       <c r="D20" s="16">
         <v>105</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="38">
         <v>1</v>
       </c>
-      <c r="F20" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="G20" s="56"/>
+      <c r="F20" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="19">
+        <v>1234567908</v>
+      </c>
       <c r="H20" s="18"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
-      <c r="M20" s="35"/>
-      <c r="N20" s="35"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
       <c r="O20" s="21"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
@@ -2984,13 +2822,15 @@
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="24"/>
-      <c r="E21" s="57">
+      <c r="E21" s="49">
         <v>2</v>
       </c>
-      <c r="F21" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="56"/>
+      <c r="F21" s="48" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="19">
+        <v>1234567909</v>
+      </c>
       <c r="H21" s="25"/>
       <c r="I21" s="20"/>
       <c r="J21" s="21"/>
@@ -3012,10 +2852,12 @@
       <c r="E22" s="17">
         <v>3</v>
       </c>
-      <c r="F22" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="43"/>
+      <c r="F22" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="19">
+        <v>1234567910</v>
+      </c>
       <c r="H22" s="18"/>
       <c r="I22" s="20"/>
       <c r="J22" s="21"/>
@@ -3033,22 +2875,24 @@
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28">
+      <c r="D23" s="26"/>
+      <c r="E23" s="27">
         <v>4</v>
       </c>
-      <c r="F23" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="G23" s="45"/>
+      <c r="F23" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="19">
+        <v>1234567911</v>
+      </c>
       <c r="H23" s="25"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
-      <c r="N23" s="47"/>
-      <c r="O23" s="47"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
       <c r="R23" s="23"/>
@@ -3059,11 +2903,13 @@
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="24"/>
-      <c r="E24" s="59"/>
-      <c r="F24" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="49"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="19">
+        <v>1234567912</v>
+      </c>
       <c r="H24" s="18"/>
       <c r="I24" s="20"/>
       <c r="J24" s="21"/>
@@ -3081,24 +2927,26 @@
       <c r="A25" s="15"/>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
-      <c r="D25" s="30">
+      <c r="D25" s="29">
         <v>106</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="38">
         <v>1</v>
       </c>
-      <c r="F25" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="61"/>
+      <c r="F25" s="52" t="s">
+        <v>25</v>
+      </c>
+      <c r="G25" s="19">
+        <v>1234567913</v>
+      </c>
       <c r="H25" s="25"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
       <c r="R25" s="23"/>
@@ -3112,10 +2960,12 @@
       <c r="E26" s="17">
         <v>2</v>
       </c>
-      <c r="F26" s="62" t="s">
-        <v>25</v>
-      </c>
-      <c r="G26" s="63"/>
+      <c r="F26" s="53" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="19">
+        <v>1234567914</v>
+      </c>
       <c r="H26" s="18"/>
       <c r="I26" s="20"/>
       <c r="J26" s="21"/>
@@ -3137,10 +2987,12 @@
       <c r="E27" s="17">
         <v>3</v>
       </c>
-      <c r="F27" s="64" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="65"/>
+      <c r="F27" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" s="19">
+        <v>1234567915</v>
+      </c>
       <c r="H27" s="25"/>
       <c r="I27" s="20"/>
       <c r="J27" s="21"/>
@@ -3158,21 +3010,23 @@
       <c r="A28" s="15"/>
       <c r="B28" s="15"/>
       <c r="C28" s="15"/>
-      <c r="D28" s="27"/>
+      <c r="D28" s="26"/>
       <c r="E28" s="17">
         <v>4</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G28" s="38"/>
+      <c r="F28" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="19">
+        <v>1234567916</v>
+      </c>
       <c r="H28" s="18"/>
-      <c r="I28" s="39"/>
-      <c r="J28" s="40"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="40"/>
-      <c r="N28" s="40"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
@@ -3183,23 +3037,25 @@
       <c r="A29" s="15"/>
       <c r="B29" s="15"/>
       <c r="C29" s="15"/>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>202</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="30">
         <v>1</v>
       </c>
-      <c r="F29" s="42" t="s">
-        <v>28</v>
-      </c>
-      <c r="G29" s="43"/>
+      <c r="F29" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="19">
+        <v>1234567917</v>
+      </c>
       <c r="H29" s="25"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
       <c r="O29" s="21"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="21"/>
@@ -3214,10 +3070,12 @@
       <c r="E30" s="17">
         <v>2</v>
       </c>
-      <c r="F30" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="G30" s="67"/>
+      <c r="F30" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="G30" s="19">
+        <v>1234567918</v>
+      </c>
       <c r="H30" s="18"/>
       <c r="I30" s="20"/>
       <c r="J30" s="21"/>
@@ -3239,10 +3097,12 @@
       <c r="E31" s="17">
         <v>3</v>
       </c>
-      <c r="F31" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="G31" s="45"/>
+      <c r="F31" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="19">
+        <v>1234567919</v>
+      </c>
       <c r="H31" s="25"/>
       <c r="I31" s="20"/>
       <c r="J31" s="21"/>
@@ -3264,10 +3124,12 @@
       <c r="E32" s="17">
         <v>4</v>
       </c>
-      <c r="F32" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="G32" s="69"/>
+      <c r="F32" s="56" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="19">
+        <v>1234567920</v>
+      </c>
       <c r="H32" s="18"/>
       <c r="I32" s="20"/>
       <c r="J32" s="21"/>
@@ -3286,20 +3148,22 @@
       <c r="B33" s="15"/>
       <c r="C33" s="15"/>
       <c r="D33" s="24"/>
-      <c r="E33" s="31">
+      <c r="E33" s="30">
         <v>5</v>
       </c>
-      <c r="F33" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="G33" s="71"/>
+      <c r="F33" s="57" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="19">
+        <v>1234567921</v>
+      </c>
       <c r="H33" s="25"/>
       <c r="I33" s="20"/>
-      <c r="J33" s="47"/>
+      <c r="J33" s="42"/>
       <c r="K33" s="21"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
-      <c r="N33" s="47"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
       <c r="O33" s="21"/>
       <c r="P33" s="21"/>
       <c r="Q33" s="21"/>
@@ -3311,48 +3175,56 @@
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
       <c r="D34" s="24"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="72" t="s">
-        <v>33</v>
+      <c r="E34" s="30"/>
+      <c r="F34" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="19">
+        <v>1234567922</v>
       </c>
     </row>
     <row r="35" ht="17.1" spans="1:21">
       <c r="A35" s="15"/>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="28">
+      <c r="D35" s="26"/>
+      <c r="E35" s="27">
         <v>6</v>
       </c>
-      <c r="F35" s="72" t="s">
-        <v>33</v>
+      <c r="F35" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="19">
+        <v>1234567923</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:21">
       <c r="A36" s="15"/>
       <c r="B36" s="15"/>
       <c r="C36" s="15"/>
-      <c r="D36" s="30">
+      <c r="D36" s="29">
         <v>203</v>
       </c>
       <c r="E36" s="17">
         <v>1</v>
       </c>
-      <c r="F36" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="G36" s="56"/>
+      <c r="F36" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="19">
+        <v>1234567924</v>
+      </c>
       <c r="H36" s="18"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="35"/>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
       <c r="P36" s="21"/>
       <c r="Q36" s="21"/>
-      <c r="R36" s="36"/>
+      <c r="R36" s="34"/>
       <c r="S36" s="21"/>
     </row>
     <row r="37" spans="1:21">
@@ -3363,10 +3235,12 @@
       <c r="E37" s="17">
         <v>2</v>
       </c>
-      <c r="F37" s="68" t="s">
-        <v>35</v>
-      </c>
-      <c r="G37" s="69"/>
+      <c r="F37" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="G37" s="19">
+        <v>1234567925</v>
+      </c>
       <c r="H37" s="25"/>
       <c r="I37" s="20"/>
       <c r="J37" s="21"/>
@@ -3389,9 +3263,11 @@
         <v>3</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="G38" s="26"/>
+        <v>37</v>
+      </c>
+      <c r="G38" s="19">
+        <v>1234567926</v>
+      </c>
       <c r="H38" s="18"/>
       <c r="I38" s="20"/>
       <c r="J38" s="21"/>
@@ -3404,8 +3280,8 @@
       <c r="Q38" s="21"/>
       <c r="R38" s="21"/>
       <c r="S38" s="21"/>
-      <c r="T38" s="73"/>
-      <c r="U38" s="74">
+      <c r="T38" s="59"/>
+      <c r="U38" s="60">
         <v>30000</v>
       </c>
     </row>
@@ -3418,9 +3294,11 @@
         <v>4</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="G39" s="75"/>
+        <v>38</v>
+      </c>
+      <c r="G39" s="19">
+        <v>1234567927</v>
+      </c>
       <c r="H39" s="25"/>
       <c r="I39" s="22"/>
       <c r="J39" s="22"/>
@@ -3442,10 +3320,12 @@
       <c r="E40" s="17">
         <v>5</v>
       </c>
-      <c r="F40" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="G40" s="45"/>
+      <c r="F40" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="G40" s="19">
+        <v>1234567928</v>
+      </c>
       <c r="H40" s="18"/>
       <c r="I40" s="20"/>
       <c r="J40" s="21"/>
@@ -3463,21 +3343,23 @@
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
-      <c r="D41" s="76"/>
-      <c r="E41" s="28">
+      <c r="D41" s="61"/>
+      <c r="E41" s="27">
         <v>6</v>
       </c>
-      <c r="F41" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="G41" s="38"/>
+      <c r="F41" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="G41" s="19">
+        <v>1234567929</v>
+      </c>
       <c r="H41" s="25"/>
-      <c r="I41" s="39"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
-      <c r="M41" s="40"/>
-      <c r="N41" s="40"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37"/>
+      <c r="M41" s="37"/>
+      <c r="N41" s="37"/>
       <c r="O41" s="21"/>
       <c r="P41" s="21"/>
       <c r="Q41" s="21"/>
@@ -3491,20 +3373,22 @@
       <c r="D42" s="16">
         <v>204</v>
       </c>
-      <c r="E42" s="57">
+      <c r="E42" s="49">
         <v>1</v>
       </c>
-      <c r="F42" s="55" t="s">
-        <v>40</v>
-      </c>
-      <c r="G42" s="56"/>
+      <c r="F42" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" s="19">
+        <v>1234567930</v>
+      </c>
       <c r="H42" s="18"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
-      <c r="L42" s="35"/>
-      <c r="M42" s="35"/>
-      <c r="N42" s="35"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
       <c r="O42" s="21"/>
       <c r="P42" s="21"/>
       <c r="Q42" s="21"/>
@@ -3519,10 +3403,12 @@
       <c r="E43" s="17">
         <v>2</v>
       </c>
-      <c r="F43" s="64" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43" s="65"/>
+      <c r="F43" s="54" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="19">
+        <v>1234567931</v>
+      </c>
       <c r="H43" s="25"/>
       <c r="I43" s="20"/>
       <c r="J43" s="21"/>
@@ -3540,21 +3426,23 @@
       <c r="A44" s="15"/>
       <c r="B44" s="15"/>
       <c r="C44" s="15"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="28">
+      <c r="D44" s="26"/>
+      <c r="E44" s="27">
         <v>3</v>
       </c>
-      <c r="F44" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="G44" s="78"/>
+      <c r="F44" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="19">
+        <v>1234567932</v>
+      </c>
       <c r="H44" s="18"/>
-      <c r="I44" s="39"/>
-      <c r="J44" s="40"/>
-      <c r="K44" s="40"/>
-      <c r="L44" s="40"/>
-      <c r="M44" s="40"/>
-      <c r="N44" s="40"/>
+      <c r="I44" s="36"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="37"/>
+      <c r="M44" s="37"/>
+      <c r="N44" s="37"/>
       <c r="O44" s="21"/>
       <c r="P44" s="21"/>
       <c r="Q44" s="21"/>
@@ -3565,23 +3453,25 @@
       <c r="A45" s="15"/>
       <c r="B45" s="15"/>
       <c r="C45" s="15"/>
-      <c r="D45" s="30">
+      <c r="D45" s="29">
         <v>205</v>
       </c>
-      <c r="E45" s="41">
+      <c r="E45" s="38">
         <v>1</v>
       </c>
-      <c r="F45" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="G45" s="43"/>
+      <c r="F45" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="G45" s="19">
+        <v>1234567933</v>
+      </c>
       <c r="H45" s="25"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
-      <c r="M45" s="35"/>
-      <c r="N45" s="35"/>
+      <c r="I45" s="32"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="33"/>
+      <c r="M45" s="33"/>
+      <c r="N45" s="33"/>
       <c r="O45" s="21"/>
       <c r="P45" s="21"/>
       <c r="Q45" s="21"/>
@@ -3593,13 +3483,15 @@
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="24"/>
-      <c r="E46" s="57">
+      <c r="E46" s="49">
         <v>2</v>
       </c>
-      <c r="F46" s="79" t="s">
-        <v>44</v>
-      </c>
-      <c r="G46" s="80"/>
+      <c r="F46" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="G46" s="19">
+        <v>1234567934</v>
+      </c>
       <c r="H46" s="18"/>
       <c r="I46" s="20"/>
       <c r="J46" s="21"/>
@@ -3618,22 +3510,24 @@
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
       <c r="D47" s="24"/>
-      <c r="E47" s="41">
+      <c r="E47" s="38">
         <v>3</v>
       </c>
-      <c r="F47" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="G47" s="56"/>
+      <c r="F47" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="G47" s="19">
+        <v>1234567935</v>
+      </c>
       <c r="H47" s="25"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="35"/>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="33"/>
+      <c r="M47" s="33"/>
+      <c r="N47" s="33"/>
       <c r="O47" s="21"/>
-      <c r="P47" s="35"/>
+      <c r="P47" s="33"/>
       <c r="Q47" s="21"/>
       <c r="R47" s="23"/>
       <c r="S47" s="21"/>
@@ -3643,13 +3537,15 @@
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
       <c r="D48" s="24"/>
-      <c r="E48" s="57">
+      <c r="E48" s="49">
         <v>4</v>
       </c>
-      <c r="F48" s="81" t="s">
-        <v>46</v>
-      </c>
-      <c r="G48" s="82"/>
+      <c r="F48" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="G48" s="19">
+        <v>1234567936</v>
+      </c>
       <c r="H48" s="18"/>
       <c r="I48" s="21"/>
       <c r="J48" s="21"/>
@@ -3668,13 +3564,15 @@
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
       <c r="D49" s="24"/>
-      <c r="E49" s="41">
+      <c r="E49" s="38">
         <v>5</v>
       </c>
-      <c r="F49" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="G49" s="45"/>
+      <c r="F49" s="40" t="s">
+        <v>48</v>
+      </c>
+      <c r="G49" s="19">
+        <v>1234567937</v>
+      </c>
       <c r="H49" s="25"/>
       <c r="I49" s="21"/>
       <c r="J49" s="21"/>
@@ -3692,14 +3590,16 @@
       <c r="A50" s="15"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
-      <c r="D50" s="76"/>
-      <c r="E50" s="57">
+      <c r="D50" s="61"/>
+      <c r="E50" s="49">
         <v>6</v>
       </c>
-      <c r="F50" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="G50" s="49"/>
+      <c r="F50" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="G50" s="19">
+        <v>1234567938</v>
+      </c>
       <c r="H50" s="18"/>
       <c r="I50" s="21"/>
       <c r="J50" s="21"/>
@@ -3723,10 +3623,12 @@
       <c r="E51" s="17">
         <v>1</v>
       </c>
-      <c r="F51" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="G51" s="45"/>
+      <c r="F51" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="G51" s="19">
+        <v>1234567939</v>
+      </c>
       <c r="H51" s="25"/>
       <c r="I51" s="21"/>
       <c r="J51" s="21"/>
@@ -3748,10 +3650,12 @@
       <c r="E52" s="17">
         <v>2</v>
       </c>
-      <c r="F52" s="83" t="s">
-        <v>50</v>
-      </c>
-      <c r="G52" s="84"/>
+      <c r="F52" s="65" t="s">
+        <v>51</v>
+      </c>
+      <c r="G52" s="19">
+        <v>1234567940</v>
+      </c>
       <c r="H52" s="18"/>
       <c r="I52" s="20"/>
       <c r="J52" s="21"/>
@@ -3774,9 +3678,11 @@
         <v>3</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G53" s="26"/>
+        <v>52</v>
+      </c>
+      <c r="G53" s="19">
+        <v>1234567941</v>
+      </c>
       <c r="H53" s="25"/>
       <c r="I53" s="20"/>
       <c r="J53" s="21"/>
@@ -3798,10 +3704,12 @@
       <c r="E54" s="17">
         <v>4</v>
       </c>
-      <c r="F54" s="79" t="s">
-        <v>52</v>
-      </c>
-      <c r="G54" s="80"/>
+      <c r="F54" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="19">
+        <v>1234567942</v>
+      </c>
       <c r="H54" s="18"/>
       <c r="I54" s="20"/>
       <c r="J54" s="21"/>
@@ -3823,10 +3731,12 @@
       <c r="E55" s="17">
         <v>5</v>
       </c>
-      <c r="F55" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55" s="49"/>
+      <c r="F55" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="G55" s="19">
+        <v>1234567943</v>
+      </c>
       <c r="H55" s="25"/>
       <c r="I55" s="21"/>
       <c r="J55" s="21"/>
@@ -3844,41 +3754,45 @@
       <c r="A56" s="15"/>
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
-      <c r="D56" s="27"/>
-      <c r="E56" s="74">
+      <c r="D56" s="26"/>
+      <c r="E56" s="60">
         <v>6</v>
       </c>
-      <c r="F56" s="44" t="s">
-        <v>54</v>
-      </c>
-      <c r="G56" s="45"/>
+      <c r="F56" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="G56" s="19">
+        <v>1234567944</v>
+      </c>
       <c r="H56" s="18"/>
-      <c r="I56" s="47"/>
-      <c r="J56" s="47"/>
-      <c r="K56" s="47"/>
-      <c r="L56" s="47"/>
-      <c r="M56" s="47"/>
-      <c r="N56" s="47"/>
-      <c r="O56" s="47"/>
+      <c r="I56" s="42"/>
+      <c r="J56" s="42"/>
+      <c r="K56" s="42"/>
+      <c r="L56" s="42"/>
+      <c r="M56" s="42"/>
+      <c r="N56" s="42"/>
+      <c r="O56" s="42"/>
       <c r="P56" s="21"/>
-      <c r="Q56" s="47"/>
-      <c r="R56" s="47"/>
-      <c r="S56" s="47"/>
+      <c r="Q56" s="42"/>
+      <c r="R56" s="42"/>
+      <c r="S56" s="42"/>
     </row>
     <row r="57" ht="16.35" spans="1:19">
       <c r="A57" s="15"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
-      <c r="D57" s="30">
+      <c r="D57" s="29">
         <v>207</v>
       </c>
-      <c r="E57" s="57">
+      <c r="E57" s="49">
         <v>1</v>
       </c>
-      <c r="F57" s="74" t="s">
-        <v>55</v>
-      </c>
-      <c r="G57" s="85"/>
+      <c r="F57" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="G57" s="19">
+        <v>1234567945</v>
+      </c>
       <c r="H57" s="25"/>
       <c r="I57" s="21"/>
       <c r="J57" s="21"/>
@@ -3900,10 +3814,12 @@
       <c r="E58" s="17">
         <v>2</v>
       </c>
-      <c r="F58" s="86" t="s">
-        <v>56</v>
-      </c>
-      <c r="G58" s="87"/>
+      <c r="F58" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="G58" s="19">
+        <v>1234567946</v>
+      </c>
       <c r="H58" s="18"/>
       <c r="I58" s="20"/>
       <c r="J58" s="21"/>
@@ -3921,21 +3837,23 @@
       <c r="A59" s="15"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
-      <c r="D59" s="76"/>
+      <c r="D59" s="61"/>
       <c r="E59" s="17">
         <v>3</v>
       </c>
-      <c r="F59" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="G59" s="38"/>
+      <c r="F59" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G59" s="19">
+        <v>1234567947</v>
+      </c>
       <c r="H59" s="25"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="40"/>
-      <c r="K59" s="40"/>
-      <c r="L59" s="40"/>
-      <c r="M59" s="40"/>
-      <c r="N59" s="40"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="37"/>
+      <c r="K59" s="37"/>
+      <c r="L59" s="37"/>
+      <c r="M59" s="37"/>
+      <c r="N59" s="37"/>
       <c r="O59" s="21"/>
       <c r="P59" s="21"/>
       <c r="Q59" s="21"/>
@@ -3952,20 +3870,22 @@
       <c r="E60" s="17">
         <v>1</v>
       </c>
-      <c r="F60" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="G60" s="33"/>
+      <c r="F60" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G60" s="19">
+        <v>1234567948</v>
+      </c>
       <c r="H60" s="18"/>
-      <c r="I60" s="88"/>
-      <c r="J60" s="52"/>
-      <c r="K60" s="52"/>
-      <c r="L60" s="52"/>
-      <c r="M60" s="52"/>
-      <c r="N60" s="52"/>
+      <c r="I60" s="67"/>
+      <c r="J60" s="46"/>
+      <c r="K60" s="46"/>
+      <c r="L60" s="46"/>
+      <c r="M60" s="46"/>
+      <c r="N60" s="46"/>
       <c r="O60" s="21"/>
-      <c r="P60" s="47"/>
-      <c r="Q60" s="47"/>
+      <c r="P60" s="42"/>
+      <c r="Q60" s="42"/>
       <c r="R60" s="23"/>
       <c r="S60" s="21"/>
     </row>
@@ -3974,13 +3894,15 @@
       <c r="B61" s="15"/>
       <c r="C61" s="15"/>
       <c r="D61" s="24"/>
-      <c r="E61" s="31">
+      <c r="E61" s="30">
         <v>2</v>
       </c>
-      <c r="F61" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="G61" s="45"/>
+      <c r="F61" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="G61" s="19">
+        <v>1234567949</v>
+      </c>
       <c r="H61" s="25"/>
       <c r="I61" s="20"/>
       <c r="J61" s="21"/>
@@ -3998,14 +3920,16 @@
       <c r="A62" s="15"/>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
-      <c r="D62" s="76"/>
-      <c r="E62" s="28">
+      <c r="D62" s="61"/>
+      <c r="E62" s="27">
         <v>3</v>
       </c>
-      <c r="F62" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G62" s="45"/>
+      <c r="F62" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="G62" s="19">
+        <v>1234567950</v>
+      </c>
       <c r="H62" s="18"/>
       <c r="I62" s="21"/>
       <c r="J62" s="21"/>
@@ -4026,38 +3950,42 @@
       <c r="D63" s="16">
         <v>209</v>
       </c>
-      <c r="E63" s="89">
+      <c r="E63" s="68">
         <v>1</v>
       </c>
-      <c r="F63" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="G63" s="43"/>
+      <c r="F63" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="G63" s="19">
+        <v>1234567951</v>
+      </c>
       <c r="H63" s="25"/>
-      <c r="I63" s="34"/>
-      <c r="J63" s="35"/>
-      <c r="K63" s="35"/>
-      <c r="L63" s="35"/>
-      <c r="M63" s="35"/>
-      <c r="N63" s="35"/>
-      <c r="O63" s="35"/>
-      <c r="P63" s="35"/>
-      <c r="Q63" s="35"/>
-      <c r="R63" s="36"/>
-      <c r="S63" s="35"/>
+      <c r="I63" s="32"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="34"/>
+      <c r="S63" s="33"/>
     </row>
     <row r="64" ht="16.35" spans="1:19">
       <c r="A64" s="15"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
       <c r="D64" s="24"/>
-      <c r="E64" s="41">
+      <c r="E64" s="38">
         <v>2</v>
       </c>
-      <c r="F64" s="68" t="s">
-        <v>62</v>
-      </c>
-      <c r="G64" s="69"/>
+      <c r="F64" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="G64" s="19">
+        <v>1234567952</v>
+      </c>
       <c r="H64" s="18"/>
       <c r="I64" s="20"/>
       <c r="J64" s="21"/>
@@ -4076,13 +4004,15 @@
       <c r="B65" s="15"/>
       <c r="C65" s="15"/>
       <c r="D65" s="24"/>
-      <c r="E65" s="28">
+      <c r="E65" s="27">
         <v>3</v>
       </c>
-      <c r="F65" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="G65" s="69"/>
+      <c r="F65" s="56" t="s">
+        <v>64</v>
+      </c>
+      <c r="G65" s="19">
+        <v>1234567953</v>
+      </c>
       <c r="H65" s="25"/>
       <c r="I65" s="20"/>
       <c r="J65" s="21"/>
@@ -4101,13 +4031,15 @@
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
       <c r="D66" s="24"/>
-      <c r="E66" s="41">
+      <c r="E66" s="38">
         <v>4</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="G66" s="26"/>
+        <v>65</v>
+      </c>
+      <c r="G66" s="19">
+        <v>1234567954</v>
+      </c>
       <c r="H66" s="18"/>
       <c r="I66" s="20"/>
       <c r="J66" s="21"/>
@@ -4126,14 +4058,16 @@
       <c r="B67" s="15"/>
       <c r="C67" s="15"/>
       <c r="D67" s="24"/>
-      <c r="E67" s="28">
+      <c r="E67" s="27">
         <v>5</v>
       </c>
-      <c r="F67" s="90" t="s">
-        <v>65</v>
-      </c>
-      <c r="G67" s="91"/>
-      <c r="H67" s="92"/>
+      <c r="F67" s="69" t="s">
+        <v>66</v>
+      </c>
+      <c r="G67" s="19">
+        <v>1234567955</v>
+      </c>
+      <c r="H67" s="70"/>
       <c r="I67" s="22"/>
       <c r="J67" s="22"/>
       <c r="K67" s="22"/>
@@ -4149,23 +4083,25 @@
       <c r="A68" s="15"/>
       <c r="B68" s="15"/>
       <c r="C68" s="15"/>
-      <c r="D68" s="27"/>
-      <c r="E68" s="28">
+      <c r="D68" s="26"/>
+      <c r="E68" s="27">
         <v>6</v>
       </c>
-      <c r="F68" s="93" t="s">
-        <v>66</v>
-      </c>
-      <c r="G68" s="94"/>
+      <c r="F68" s="71" t="s">
+        <v>67</v>
+      </c>
+      <c r="G68" s="19">
+        <v>1234567956</v>
+      </c>
       <c r="H68" s="18"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="40"/>
-      <c r="K68" s="40"/>
-      <c r="L68" s="40"/>
-      <c r="M68" s="40"/>
-      <c r="N68" s="40"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="37"/>
+      <c r="K68" s="37"/>
+      <c r="L68" s="37"/>
+      <c r="M68" s="37"/>
+      <c r="N68" s="37"/>
       <c r="O68" s="21"/>
-      <c r="P68" s="40"/>
+      <c r="P68" s="37"/>
       <c r="Q68" s="21"/>
       <c r="R68" s="23"/>
       <c r="S68" s="21"/>
@@ -4175,47 +4111,51 @@
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
       <c r="D69" s="24"/>
-      <c r="E69" s="59"/>
-      <c r="F69" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="G69" s="43"/>
+      <c r="E69" s="51"/>
+      <c r="F69" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="G69" s="19">
+        <v>1234567957</v>
+      </c>
       <c r="H69" s="25"/>
-      <c r="I69" s="34"/>
-      <c r="J69" s="35"/>
-      <c r="K69" s="35"/>
-      <c r="L69" s="35"/>
-      <c r="M69" s="35"/>
-      <c r="N69" s="35"/>
-      <c r="O69" s="35"/>
-      <c r="P69" s="35"/>
-      <c r="Q69" s="35"/>
-      <c r="R69" s="36"/>
-      <c r="S69" s="35"/>
+      <c r="I69" s="32"/>
+      <c r="J69" s="33"/>
+      <c r="K69" s="33"/>
+      <c r="L69" s="33"/>
+      <c r="M69" s="33"/>
+      <c r="N69" s="33"/>
+      <c r="O69" s="33"/>
+      <c r="P69" s="33"/>
+      <c r="Q69" s="33"/>
+      <c r="R69" s="34"/>
+      <c r="S69" s="33"/>
     </row>
     <row r="70" ht="16.35" spans="1:19">
       <c r="A70" s="15"/>
       <c r="B70" s="15"/>
       <c r="C70" s="15"/>
-      <c r="D70" s="30">
+      <c r="D70" s="29">
         <v>210</v>
       </c>
-      <c r="E70" s="57">
+      <c r="E70" s="49">
         <v>1</v>
       </c>
-      <c r="F70" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="G70" s="43"/>
+      <c r="F70" s="39" t="s">
+        <v>69</v>
+      </c>
+      <c r="G70" s="19">
+        <v>1234567958</v>
+      </c>
       <c r="H70" s="18"/>
-      <c r="I70" s="34"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="35"/>
-      <c r="L70" s="35"/>
-      <c r="M70" s="35"/>
-      <c r="N70" s="35"/>
+      <c r="I70" s="32"/>
+      <c r="J70" s="33"/>
+      <c r="K70" s="33"/>
+      <c r="L70" s="33"/>
+      <c r="M70" s="33"/>
+      <c r="N70" s="33"/>
       <c r="O70" s="21"/>
-      <c r="P70" s="35"/>
+      <c r="P70" s="33"/>
       <c r="Q70" s="21"/>
       <c r="R70" s="23"/>
       <c r="S70" s="21"/>
@@ -4225,13 +4165,15 @@
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
       <c r="D71" s="24"/>
-      <c r="E71" s="57">
+      <c r="E71" s="49">
         <v>2</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="G71" s="26"/>
+        <v>70</v>
+      </c>
+      <c r="G71" s="19">
+        <v>1234567959</v>
+      </c>
       <c r="H71" s="25"/>
       <c r="I71" s="20"/>
       <c r="J71" s="21"/>
@@ -4250,13 +4192,15 @@
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
       <c r="D72" s="24"/>
-      <c r="E72" s="41">
+      <c r="E72" s="38">
         <v>3</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="G72" s="26"/>
+        <v>71</v>
+      </c>
+      <c r="G72" s="19">
+        <v>1234567960</v>
+      </c>
       <c r="H72" s="18"/>
       <c r="I72" s="20"/>
       <c r="J72" s="21"/>
@@ -4275,13 +4219,15 @@
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
       <c r="D73" s="24"/>
-      <c r="E73" s="57">
+      <c r="E73" s="49">
         <v>4</v>
       </c>
-      <c r="F73" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="G73" s="43"/>
+      <c r="F73" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="G73" s="19">
+        <v>1234567961</v>
+      </c>
       <c r="H73" s="25"/>
       <c r="I73" s="20"/>
       <c r="J73" s="21"/>
@@ -4300,22 +4246,24 @@
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
       <c r="D74" s="24"/>
-      <c r="E74" s="41">
+      <c r="E74" s="38">
         <v>5</v>
       </c>
-      <c r="F74" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="G74" s="43"/>
+      <c r="F74" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G74" s="19">
+        <v>1234567962</v>
+      </c>
       <c r="H74" s="18"/>
-      <c r="I74" s="34"/>
-      <c r="J74" s="35"/>
-      <c r="K74" s="35"/>
-      <c r="L74" s="35"/>
-      <c r="M74" s="35"/>
-      <c r="N74" s="35"/>
+      <c r="I74" s="32"/>
+      <c r="J74" s="33"/>
+      <c r="K74" s="33"/>
+      <c r="L74" s="33"/>
+      <c r="M74" s="33"/>
+      <c r="N74" s="33"/>
       <c r="O74" s="21"/>
-      <c r="P74" s="35"/>
+      <c r="P74" s="33"/>
       <c r="Q74" s="21"/>
       <c r="R74" s="23"/>
       <c r="S74" s="21"/>
@@ -4324,12 +4272,15 @@
       <c r="A75" s="15"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
-      <c r="D75" s="76"/>
-      <c r="E75" s="28">
+      <c r="D75" s="61"/>
+      <c r="E75" s="27">
         <v>6</v>
       </c>
-      <c r="F75" s="72" t="s">
-        <v>33</v>
+      <c r="F75" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G75" s="19">
+        <v>1234567963</v>
       </c>
     </row>
     <row r="76" ht="16.35" spans="1:19">
@@ -4339,20 +4290,22 @@
       <c r="D76" s="16">
         <v>211</v>
       </c>
-      <c r="E76" s="57">
+      <c r="E76" s="49">
         <v>1</v>
       </c>
-      <c r="F76" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="G76" s="43"/>
+      <c r="F76" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="G76" s="19">
+        <v>1234567964</v>
+      </c>
       <c r="H76" s="18"/>
-      <c r="I76" s="34"/>
-      <c r="J76" s="35"/>
-      <c r="K76" s="35"/>
-      <c r="L76" s="35"/>
-      <c r="M76" s="35"/>
-      <c r="N76" s="35"/>
+      <c r="I76" s="32"/>
+      <c r="J76" s="33"/>
+      <c r="K76" s="33"/>
+      <c r="L76" s="33"/>
+      <c r="M76" s="33"/>
+      <c r="N76" s="33"/>
       <c r="O76" s="21"/>
       <c r="P76" s="21"/>
       <c r="Q76" s="21"/>
@@ -4364,13 +4317,15 @@
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
       <c r="D77" s="24"/>
-      <c r="E77" s="57">
+      <c r="E77" s="49">
         <v>2</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="G77" s="26"/>
+        <v>75</v>
+      </c>
+      <c r="G77" s="19">
+        <v>1234567965</v>
+      </c>
       <c r="H77" s="25"/>
       <c r="I77" s="20"/>
       <c r="J77" s="21"/>
@@ -4388,14 +4343,16 @@
       <c r="A78" s="15"/>
       <c r="B78" s="15"/>
       <c r="C78" s="15"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="28">
+      <c r="D78" s="26"/>
+      <c r="E78" s="27">
         <v>3</v>
       </c>
-      <c r="F78" s="48" t="s">
-        <v>75</v>
-      </c>
-      <c r="G78" s="95"/>
+      <c r="F78" s="43" t="s">
+        <v>76</v>
+      </c>
+      <c r="G78" s="19">
+        <v>1234567966</v>
+      </c>
       <c r="H78" s="18"/>
       <c r="I78" s="22"/>
       <c r="J78" s="21"/>
@@ -4413,66 +4370,72 @@
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
-      <c r="D79" s="30">
+      <c r="D79" s="29">
         <v>212</v>
       </c>
-      <c r="E79" s="57">
+      <c r="E79" s="49">
         <v>1</v>
       </c>
-      <c r="F79" s="96" t="s">
-        <v>76</v>
-      </c>
-      <c r="G79" s="97"/>
+      <c r="F79" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="G79" s="19">
+        <v>1234567967</v>
+      </c>
       <c r="H79" s="25"/>
-      <c r="I79" s="34"/>
-      <c r="J79" s="35"/>
-      <c r="K79" s="35"/>
-      <c r="L79" s="35"/>
-      <c r="M79" s="35"/>
-      <c r="N79" s="35"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="33"/>
+      <c r="K79" s="33"/>
+      <c r="L79" s="33"/>
+      <c r="M79" s="33"/>
+      <c r="N79" s="33"/>
       <c r="O79" s="21"/>
-      <c r="P79" s="35"/>
-      <c r="Q79" s="35"/>
-      <c r="R79" s="36"/>
-      <c r="S79" s="35"/>
+      <c r="P79" s="33"/>
+      <c r="Q79" s="33"/>
+      <c r="R79" s="34"/>
+      <c r="S79" s="33"/>
     </row>
     <row r="80" ht="16.35" spans="1:19">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
       <c r="D80" s="24"/>
-      <c r="E80" s="57">
+      <c r="E80" s="49">
         <v>2</v>
       </c>
-      <c r="F80" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G80" s="98"/>
-      <c r="H80" s="99"/>
-      <c r="O80" s="100"/>
-      <c r="P80" s="35"/>
+      <c r="F80" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G80" s="19">
+        <v>1234567968</v>
+      </c>
+      <c r="H80" s="73"/>
+      <c r="O80" s="74"/>
+      <c r="P80" s="33"/>
     </row>
     <row r="81" ht="17.1" spans="1:19">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
       <c r="D81" s="24"/>
-      <c r="E81" s="41">
+      <c r="E81" s="38">
         <v>3</v>
       </c>
-      <c r="F81" s="90" t="s">
-        <v>77</v>
-      </c>
-      <c r="G81" s="33"/>
-      <c r="H81" s="50"/>
-      <c r="I81" s="34"/>
+      <c r="F81" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="G81" s="19">
+        <v>1234567969</v>
+      </c>
+      <c r="H81" s="44"/>
+      <c r="I81" s="32"/>
       <c r="J81" s="21"/>
       <c r="K81" s="21"/>
       <c r="L81" s="21"/>
       <c r="M81" s="21"/>
       <c r="N81" s="21"/>
       <c r="O81" s="21"/>
-      <c r="P81" s="35"/>
+      <c r="P81" s="33"/>
       <c r="Q81" s="21"/>
       <c r="R81" s="21"/>
       <c r="S81" s="21"/>
@@ -4482,14 +4445,16 @@
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
       <c r="D82" s="24"/>
-      <c r="E82" s="57">
+      <c r="E82" s="49">
         <v>4</v>
       </c>
-      <c r="F82" s="48" t="s">
-        <v>78</v>
-      </c>
-      <c r="G82" s="49"/>
-      <c r="H82" s="48"/>
+      <c r="F82" s="43" t="s">
+        <v>79</v>
+      </c>
+      <c r="G82" s="19">
+        <v>1234567970</v>
+      </c>
+      <c r="H82" s="43"/>
       <c r="I82" s="20"/>
       <c r="J82" s="21"/>
       <c r="K82" s="21"/>
@@ -4507,15 +4472,17 @@
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
       <c r="D83" s="24"/>
-      <c r="E83" s="41">
+      <c r="E83" s="38">
         <v>5</v>
       </c>
-      <c r="F83" s="48" t="s">
-        <v>79</v>
-      </c>
-      <c r="G83" s="49"/>
-      <c r="H83" s="48"/>
-      <c r="I83" s="34"/>
+      <c r="F83" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="G83" s="19">
+        <v>1234567971</v>
+      </c>
+      <c r="H83" s="43"/>
+      <c r="I83" s="32"/>
       <c r="J83" s="21"/>
       <c r="K83" s="21"/>
       <c r="L83" s="21"/>
@@ -4531,41 +4498,45 @@
       <c r="A84" s="15"/>
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="101">
+      <c r="D84" s="26"/>
+      <c r="E84" s="75">
         <v>6</v>
       </c>
-      <c r="F84" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G84" s="102"/>
-      <c r="H84" s="72"/>
-      <c r="I84" s="103"/>
-      <c r="J84" s="104"/>
-      <c r="K84" s="104"/>
-      <c r="L84" s="104"/>
-      <c r="M84" s="104"/>
-      <c r="N84" s="104"/>
-      <c r="O84" s="100"/>
-      <c r="P84" s="100"/>
-      <c r="Q84" s="100"/>
-      <c r="R84" s="105"/>
-      <c r="S84" s="100"/>
+      <c r="F84" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G84" s="19">
+        <v>1234567972</v>
+      </c>
+      <c r="H84" s="58"/>
+      <c r="I84" s="76"/>
+      <c r="J84" s="77"/>
+      <c r="K84" s="77"/>
+      <c r="L84" s="77"/>
+      <c r="M84" s="77"/>
+      <c r="N84" s="77"/>
+      <c r="O84" s="74"/>
+      <c r="P84" s="74"/>
+      <c r="Q84" s="74"/>
+      <c r="R84" s="78"/>
+      <c r="S84" s="74"/>
     </row>
     <row r="85" ht="16.35" spans="1:19">
       <c r="A85" s="15"/>
       <c r="B85" s="15"/>
       <c r="C85" s="15"/>
-      <c r="D85" s="30">
+      <c r="D85" s="29">
         <v>213</v>
       </c>
-      <c r="E85" s="57">
+      <c r="E85" s="49">
         <v>1</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="G85" s="26"/>
+        <v>81</v>
+      </c>
+      <c r="G85" s="19">
+        <v>1234567973</v>
+      </c>
       <c r="H85" s="25"/>
       <c r="I85" s="20"/>
       <c r="J85" s="21"/>
@@ -4584,12 +4555,14 @@
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
       <c r="D86" s="24"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="48" t="s">
-        <v>81</v>
-      </c>
-      <c r="G86" s="49"/>
-      <c r="H86" s="48"/>
+      <c r="E86" s="49"/>
+      <c r="F86" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="G86" s="19">
+        <v>1234567974</v>
+      </c>
+      <c r="H86" s="43"/>
       <c r="I86" s="20"/>
       <c r="J86" s="21"/>
       <c r="K86" s="21"/>
@@ -4607,11 +4580,14 @@
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
       <c r="D87" s="24"/>
-      <c r="E87" s="57">
+      <c r="E87" s="49">
         <v>2</v>
       </c>
-      <c r="F87" s="72" t="s">
-        <v>33</v>
+      <c r="F87" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" s="19">
+        <v>1234567975</v>
       </c>
     </row>
     <row r="88" ht="17.1" spans="1:19">
@@ -4619,12 +4595,14 @@
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
       <c r="D88" s="24"/>
-      <c r="E88" s="57"/>
+      <c r="E88" s="49"/>
       <c r="F88" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="G88" s="26"/>
-      <c r="H88" s="48"/>
+        <v>83</v>
+      </c>
+      <c r="G88" s="19">
+        <v>1234567976</v>
+      </c>
+      <c r="H88" s="43"/>
       <c r="I88" s="20"/>
       <c r="J88" s="21"/>
       <c r="K88" s="21"/>
@@ -4642,11 +4620,14 @@
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
       <c r="D89" s="24"/>
-      <c r="E89" s="41">
+      <c r="E89" s="38">
         <v>3</v>
       </c>
-      <c r="F89" s="72" t="s">
-        <v>33</v>
+      <c r="F89" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G89" s="19">
+        <v>1234567977</v>
       </c>
     </row>
     <row r="90" ht="17.1" spans="1:19">
@@ -4654,14 +4635,16 @@
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
       <c r="D90" s="24"/>
-      <c r="E90" s="57">
+      <c r="E90" s="49">
         <v>4</v>
       </c>
-      <c r="F90" s="74" t="s">
-        <v>83</v>
-      </c>
-      <c r="G90" s="85"/>
-      <c r="H90" s="48"/>
+      <c r="F90" s="60" t="s">
+        <v>84</v>
+      </c>
+      <c r="G90" s="19">
+        <v>1234567978</v>
+      </c>
+      <c r="H90" s="43"/>
       <c r="I90" s="21"/>
       <c r="J90" s="21"/>
       <c r="K90" s="21"/>
@@ -4679,13 +4662,15 @@
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
       <c r="D91" s="24"/>
-      <c r="E91" s="41">
+      <c r="E91" s="38">
         <v>5</v>
       </c>
-      <c r="F91" s="79" t="s">
-        <v>84</v>
-      </c>
-      <c r="G91" s="80"/>
+      <c r="F91" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="G91" s="19">
+        <v>1234567979</v>
+      </c>
       <c r="H91" s="25"/>
       <c r="I91" s="20"/>
       <c r="J91" s="21"/>
@@ -4703,26 +4688,28 @@
       <c r="A92" s="15"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
-      <c r="D92" s="76"/>
-      <c r="E92" s="28">
+      <c r="D92" s="61"/>
+      <c r="E92" s="27">
         <v>6</v>
       </c>
-      <c r="F92" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="G92" s="106"/>
-      <c r="H92" s="48"/>
-      <c r="I92" s="107"/>
-      <c r="J92" s="108"/>
-      <c r="K92" s="108"/>
-      <c r="L92" s="108"/>
-      <c r="M92" s="108"/>
-      <c r="N92" s="108"/>
+      <c r="F92" s="47" t="s">
+        <v>86</v>
+      </c>
+      <c r="G92" s="19">
+        <v>1234567980</v>
+      </c>
+      <c r="H92" s="43"/>
+      <c r="I92" s="79"/>
+      <c r="J92" s="80"/>
+      <c r="K92" s="80"/>
+      <c r="L92" s="80"/>
+      <c r="M92" s="80"/>
+      <c r="N92" s="80"/>
       <c r="O92" s="21"/>
-      <c r="P92" s="108"/>
-      <c r="Q92" s="108"/>
-      <c r="R92" s="109"/>
-      <c r="S92" s="108"/>
+      <c r="P92" s="80"/>
+      <c r="Q92" s="80"/>
+      <c r="R92" s="81"/>
+      <c r="S92" s="80"/>
     </row>
     <row r="93" ht="16.35" spans="1:19">
       <c r="A93" s="15"/>
@@ -4731,25 +4718,27 @@
       <c r="D93" s="16">
         <v>214</v>
       </c>
-      <c r="E93" s="57">
+      <c r="E93" s="49">
         <v>1</v>
       </c>
-      <c r="F93" s="110" t="s">
-        <v>86</v>
-      </c>
-      <c r="G93" s="43"/>
+      <c r="F93" s="82" t="s">
+        <v>87</v>
+      </c>
+      <c r="G93" s="19">
+        <v>1234567981</v>
+      </c>
       <c r="H93" s="25"/>
-      <c r="I93" s="34"/>
-      <c r="J93" s="35"/>
-      <c r="K93" s="35"/>
-      <c r="L93" s="35"/>
-      <c r="M93" s="35"/>
-      <c r="N93" s="35"/>
-      <c r="O93" s="35"/>
-      <c r="P93" s="35"/>
-      <c r="Q93" s="35"/>
-      <c r="R93" s="36"/>
-      <c r="S93" s="35"/>
+      <c r="I93" s="32"/>
+      <c r="J93" s="33"/>
+      <c r="K93" s="33"/>
+      <c r="L93" s="33"/>
+      <c r="M93" s="33"/>
+      <c r="N93" s="33"/>
+      <c r="O93" s="33"/>
+      <c r="P93" s="33"/>
+      <c r="Q93" s="33"/>
+      <c r="R93" s="34"/>
+      <c r="S93" s="33"/>
     </row>
     <row r="94" spans="1:19">
       <c r="A94" s="15"/>
@@ -4760,10 +4749,12 @@
         <v>2</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="G94" s="26"/>
-      <c r="H94" s="48"/>
+        <v>88</v>
+      </c>
+      <c r="G94" s="19">
+        <v>1234567982</v>
+      </c>
+      <c r="H94" s="43"/>
       <c r="I94" s="20"/>
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
@@ -4780,21 +4771,23 @@
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
-      <c r="D95" s="76"/>
-      <c r="E95" s="28">
+      <c r="D95" s="61"/>
+      <c r="E95" s="27">
         <v>3</v>
       </c>
-      <c r="F95" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="G95" s="54"/>
+      <c r="F95" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="G95" s="19">
+        <v>1234567983</v>
+      </c>
       <c r="H95" s="25"/>
-      <c r="I95" s="39"/>
-      <c r="J95" s="40"/>
-      <c r="K95" s="40"/>
-      <c r="L95" s="40"/>
-      <c r="M95" s="40"/>
-      <c r="N95" s="40"/>
+      <c r="I95" s="36"/>
+      <c r="J95" s="37"/>
+      <c r="K95" s="37"/>
+      <c r="L95" s="37"/>
+      <c r="M95" s="37"/>
+      <c r="N95" s="37"/>
       <c r="O95" s="21"/>
       <c r="P95" s="21"/>
       <c r="Q95" s="21"/>
@@ -4808,20 +4801,22 @@
       <c r="D96" s="16">
         <v>215</v>
       </c>
-      <c r="E96" s="59">
+      <c r="E96" s="51">
         <v>1</v>
       </c>
-      <c r="F96" s="42" t="s">
-        <v>89</v>
-      </c>
-      <c r="G96" s="43"/>
-      <c r="H96" s="48"/>
-      <c r="I96" s="34"/>
-      <c r="J96" s="35"/>
-      <c r="K96" s="35"/>
-      <c r="L96" s="35"/>
-      <c r="M96" s="35"/>
-      <c r="N96" s="35"/>
+      <c r="F96" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="G96" s="19">
+        <v>1234567984</v>
+      </c>
+      <c r="H96" s="43"/>
+      <c r="I96" s="32"/>
+      <c r="J96" s="33"/>
+      <c r="K96" s="33"/>
+      <c r="L96" s="33"/>
+      <c r="M96" s="33"/>
+      <c r="N96" s="33"/>
       <c r="O96" s="21"/>
       <c r="P96" s="21"/>
       <c r="Q96" s="21"/>
@@ -4833,13 +4828,15 @@
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
       <c r="D97" s="24"/>
-      <c r="E97" s="41">
+      <c r="E97" s="38">
         <v>2</v>
       </c>
-      <c r="F97" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="G97" s="49"/>
+      <c r="F97" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G97" s="19">
+        <v>1234567985</v>
+      </c>
       <c r="H97" s="25"/>
       <c r="I97" s="20"/>
       <c r="J97" s="21"/>
@@ -4858,14 +4855,16 @@
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
       <c r="D98" s="24"/>
-      <c r="E98" s="59">
+      <c r="E98" s="51">
         <v>3</v>
       </c>
-      <c r="F98" s="48" t="s">
-        <v>91</v>
-      </c>
-      <c r="G98" s="49"/>
-      <c r="H98" s="48"/>
+      <c r="F98" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="G98" s="19">
+        <v>1234567986</v>
+      </c>
+      <c r="H98" s="43"/>
       <c r="I98" s="20"/>
       <c r="J98" s="21"/>
       <c r="K98" s="21"/>
@@ -4883,13 +4882,15 @@
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
       <c r="D99" s="24"/>
-      <c r="E99" s="41">
+      <c r="E99" s="38">
         <v>4</v>
       </c>
-      <c r="F99" s="48" t="s">
-        <v>92</v>
-      </c>
-      <c r="G99" s="49"/>
+      <c r="F99" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="G99" s="19">
+        <v>1234567987</v>
+      </c>
       <c r="H99" s="25"/>
       <c r="I99" s="21"/>
       <c r="J99" s="21"/>
@@ -4911,22 +4912,24 @@
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
       <c r="D100" s="24"/>
-      <c r="E100" s="111">
+      <c r="E100" s="83">
         <v>5</v>
       </c>
-      <c r="F100" s="112" t="s">
-        <v>93</v>
-      </c>
-      <c r="G100" s="97"/>
-      <c r="H100" s="48"/>
-      <c r="I100" s="34"/>
-      <c r="J100" s="35"/>
-      <c r="K100" s="35"/>
-      <c r="L100" s="35"/>
-      <c r="M100" s="35"/>
-      <c r="N100" s="35"/>
+      <c r="F100" s="84" t="s">
+        <v>94</v>
+      </c>
+      <c r="G100" s="19">
+        <v>1234567988</v>
+      </c>
+      <c r="H100" s="43"/>
+      <c r="I100" s="32"/>
+      <c r="J100" s="33"/>
+      <c r="K100" s="33"/>
+      <c r="L100" s="33"/>
+      <c r="M100" s="33"/>
+      <c r="N100" s="33"/>
       <c r="O100" s="21"/>
-      <c r="P100" s="35"/>
+      <c r="P100" s="33"/>
       <c r="Q100" s="21"/>
       <c r="R100" s="23"/>
       <c r="S100" s="21"/>
@@ -4935,26 +4938,28 @@
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
-      <c r="D101" s="76"/>
-      <c r="E101" s="113">
+      <c r="D101" s="61"/>
+      <c r="E101" s="85">
         <v>6</v>
       </c>
-      <c r="F101" s="90" t="s">
-        <v>94</v>
-      </c>
-      <c r="G101" s="114"/>
-      <c r="H101" s="90"/>
-      <c r="I101" s="115"/>
-      <c r="J101" s="116"/>
-      <c r="K101" s="116"/>
-      <c r="L101" s="116"/>
-      <c r="M101" s="116"/>
-      <c r="N101" s="116"/>
-      <c r="O101" s="100"/>
-      <c r="P101" s="117"/>
-      <c r="Q101" s="117"/>
-      <c r="R101" s="118"/>
-      <c r="S101" s="117"/>
+      <c r="F101" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="G101" s="19">
+        <v>1234567989</v>
+      </c>
+      <c r="H101" s="69"/>
+      <c r="I101" s="86"/>
+      <c r="J101" s="87"/>
+      <c r="K101" s="87"/>
+      <c r="L101" s="87"/>
+      <c r="M101" s="87"/>
+      <c r="N101" s="87"/>
+      <c r="O101" s="74"/>
+      <c r="P101" s="88"/>
+      <c r="Q101" s="88"/>
+      <c r="R101" s="89"/>
+      <c r="S101" s="88"/>
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:21">
       <c r="A102" s="15"/>
@@ -4963,20 +4968,22 @@
       <c r="D102" s="16">
         <v>216</v>
       </c>
-      <c r="E102" s="57">
+      <c r="E102" s="49">
         <v>1</v>
       </c>
-      <c r="F102" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="G102" s="43"/>
-      <c r="H102" s="42"/>
-      <c r="I102" s="34"/>
-      <c r="J102" s="35"/>
-      <c r="K102" s="35"/>
-      <c r="L102" s="35"/>
-      <c r="M102" s="35"/>
-      <c r="N102" s="35"/>
+      <c r="F102" s="39" t="s">
+        <v>96</v>
+      </c>
+      <c r="G102" s="19">
+        <v>1234567990</v>
+      </c>
+      <c r="H102" s="39"/>
+      <c r="I102" s="32"/>
+      <c r="J102" s="33"/>
+      <c r="K102" s="33"/>
+      <c r="L102" s="33"/>
+      <c r="M102" s="33"/>
+      <c r="N102" s="33"/>
       <c r="O102" s="21"/>
       <c r="P102" s="21"/>
       <c r="Q102" s="21"/>
@@ -4992,9 +4999,11 @@
         <v>2</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="G103" s="26"/>
+        <v>97</v>
+      </c>
+      <c r="G103" s="19">
+        <v>1234567991</v>
+      </c>
       <c r="H103" s="25"/>
       <c r="I103" s="20"/>
       <c r="J103" s="21"/>
@@ -5016,11 +5025,13 @@
       <c r="E104" s="17">
         <v>3</v>
       </c>
-      <c r="F104" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="G104" s="49"/>
-      <c r="H104" s="48"/>
+      <c r="F104" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="G104" s="19">
+        <v>1234567992</v>
+      </c>
+      <c r="H104" s="43"/>
       <c r="I104" s="20"/>
       <c r="J104" s="21"/>
       <c r="K104" s="21"/>
@@ -5041,36 +5052,40 @@
       <c r="E105" s="17">
         <v>4</v>
       </c>
-      <c r="F105" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G105" s="119"/>
-      <c r="H105" s="120"/>
-      <c r="I105" s="117"/>
-      <c r="J105" s="117"/>
-      <c r="K105" s="117"/>
-      <c r="L105" s="117"/>
-      <c r="M105" s="117"/>
-      <c r="N105" s="117"/>
-      <c r="O105" s="100"/>
-      <c r="P105" s="117"/>
-      <c r="Q105" s="117"/>
-      <c r="R105" s="117"/>
-      <c r="S105" s="117"/>
+      <c r="F105" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G105" s="19">
+        <v>1234567993</v>
+      </c>
+      <c r="H105" s="90"/>
+      <c r="I105" s="88"/>
+      <c r="J105" s="88"/>
+      <c r="K105" s="88"/>
+      <c r="L105" s="88"/>
+      <c r="M105" s="88"/>
+      <c r="N105" s="88"/>
+      <c r="O105" s="74"/>
+      <c r="P105" s="88"/>
+      <c r="Q105" s="88"/>
+      <c r="R105" s="88"/>
+      <c r="S105" s="88"/>
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:21">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
       <c r="D106" s="24"/>
-      <c r="E106" s="121">
+      <c r="E106" s="91">
         <v>5</v>
       </c>
-      <c r="F106" s="48" t="s">
-        <v>98</v>
-      </c>
-      <c r="G106" s="49"/>
-      <c r="H106" s="48"/>
+      <c r="F106" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G106" s="19">
+        <v>1234567994</v>
+      </c>
+      <c r="H106" s="43"/>
       <c r="I106" s="20"/>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
@@ -5087,25 +5102,27 @@
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
-      <c r="D107" s="76"/>
-      <c r="E107" s="101">
+      <c r="D107" s="61"/>
+      <c r="E107" s="75">
         <v>6</v>
       </c>
-      <c r="F107" s="90" t="s">
-        <v>99</v>
-      </c>
-      <c r="G107" s="33"/>
-      <c r="H107" s="50"/>
+      <c r="F107" s="69" t="s">
+        <v>100</v>
+      </c>
+      <c r="G107" s="19">
+        <v>1234567995</v>
+      </c>
+      <c r="H107" s="44"/>
       <c r="I107" s="20"/>
-      <c r="J107" s="40"/>
-      <c r="K107" s="40"/>
-      <c r="L107" s="40"/>
-      <c r="M107" s="40"/>
-      <c r="N107" s="40"/>
+      <c r="J107" s="37"/>
+      <c r="K107" s="37"/>
+      <c r="L107" s="37"/>
+      <c r="M107" s="37"/>
+      <c r="N107" s="37"/>
       <c r="O107" s="21"/>
-      <c r="P107" s="40"/>
-      <c r="Q107" s="40"/>
-      <c r="R107" s="122"/>
+      <c r="P107" s="37"/>
+      <c r="Q107" s="37"/>
+      <c r="R107" s="92"/>
       <c r="S107" s="21"/>
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:21">
@@ -5115,24 +5132,26 @@
       <c r="D108" s="16">
         <v>217</v>
       </c>
-      <c r="E108" s="57">
+      <c r="E108" s="49">
         <v>1</v>
       </c>
-      <c r="F108" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="G108" s="43"/>
-      <c r="H108" s="48"/>
-      <c r="I108" s="34"/>
-      <c r="J108" s="35"/>
-      <c r="K108" s="35"/>
-      <c r="L108" s="35"/>
-      <c r="M108" s="35"/>
-      <c r="N108" s="35"/>
+      <c r="F108" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="G108" s="19">
+        <v>1234567996</v>
+      </c>
+      <c r="H108" s="43"/>
+      <c r="I108" s="32"/>
+      <c r="J108" s="33"/>
+      <c r="K108" s="33"/>
+      <c r="L108" s="33"/>
+      <c r="M108" s="33"/>
+      <c r="N108" s="33"/>
       <c r="O108" s="21"/>
-      <c r="P108" s="35"/>
-      <c r="Q108" s="35"/>
-      <c r="R108" s="36"/>
+      <c r="P108" s="33"/>
+      <c r="Q108" s="33"/>
+      <c r="R108" s="34"/>
       <c r="S108" s="21"/>
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:21">
@@ -5143,11 +5162,13 @@
       <c r="E109" s="17">
         <v>2</v>
       </c>
-      <c r="F109" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="G109" s="45"/>
-      <c r="H109" s="50"/>
+      <c r="F109" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="G109" s="19">
+        <v>1234567997</v>
+      </c>
+      <c r="H109" s="44"/>
       <c r="I109" s="20"/>
       <c r="J109" s="21"/>
       <c r="K109" s="21"/>
@@ -5165,14 +5186,16 @@
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
       <c r="D110" s="24"/>
-      <c r="E110" s="41">
+      <c r="E110" s="38">
         <v>3</v>
       </c>
-      <c r="F110" s="86" t="s">
-        <v>102</v>
-      </c>
-      <c r="G110" s="87"/>
-      <c r="H110" s="48"/>
+      <c r="F110" s="66" t="s">
+        <v>103</v>
+      </c>
+      <c r="G110" s="19">
+        <v>1234567998</v>
+      </c>
+      <c r="H110" s="43"/>
       <c r="I110" s="20"/>
       <c r="J110" s="21"/>
       <c r="K110" s="21"/>
@@ -5193,12 +5216,14 @@
       <c r="E111" s="17">
         <v>4</v>
       </c>
-      <c r="F111" s="62" t="s">
-        <v>103</v>
-      </c>
-      <c r="G111" s="56"/>
-      <c r="H111" s="50"/>
-      <c r="I111" s="34"/>
+      <c r="F111" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="G111" s="19">
+        <v>1234567999</v>
+      </c>
+      <c r="H111" s="44"/>
+      <c r="I111" s="32"/>
       <c r="J111" s="21"/>
       <c r="K111" s="21"/>
       <c r="L111" s="21"/>
@@ -5215,14 +5240,16 @@
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
       <c r="D112" s="24"/>
-      <c r="E112" s="41">
+      <c r="E112" s="38">
         <v>5</v>
       </c>
-      <c r="F112" s="90" t="s">
-        <v>104</v>
-      </c>
-      <c r="G112" s="33"/>
-      <c r="H112" s="48"/>
+      <c r="F112" s="69" t="s">
+        <v>105</v>
+      </c>
+      <c r="G112" s="19">
+        <v>1234568000</v>
+      </c>
+      <c r="H112" s="43"/>
       <c r="I112" s="21"/>
       <c r="J112" s="21"/>
       <c r="K112" s="21"/>
@@ -5239,15 +5266,17 @@
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
-      <c r="D113" s="76"/>
-      <c r="E113" s="28">
+      <c r="D113" s="61"/>
+      <c r="E113" s="27">
         <v>6</v>
       </c>
-      <c r="F113" s="68" t="s">
-        <v>105</v>
-      </c>
-      <c r="G113" s="69"/>
-      <c r="H113" s="50"/>
+      <c r="F113" s="56" t="s">
+        <v>106</v>
+      </c>
+      <c r="G113" s="19">
+        <v>1234568001</v>
+      </c>
+      <c r="H113" s="44"/>
       <c r="I113" s="20"/>
       <c r="J113" s="21"/>
       <c r="K113" s="21"/>
@@ -5267,20 +5296,22 @@
       <c r="D114" s="16">
         <v>301</v>
       </c>
-      <c r="E114" s="57">
+      <c r="E114" s="49">
         <v>1</v>
       </c>
-      <c r="F114" s="60" t="s">
-        <v>106</v>
-      </c>
-      <c r="G114" s="61"/>
-      <c r="H114" s="48"/>
-      <c r="I114" s="34"/>
-      <c r="J114" s="35"/>
-      <c r="K114" s="35"/>
-      <c r="L114" s="35"/>
-      <c r="M114" s="35"/>
-      <c r="N114" s="35"/>
+      <c r="F114" s="52" t="s">
+        <v>107</v>
+      </c>
+      <c r="G114" s="19">
+        <v>1234568002</v>
+      </c>
+      <c r="H114" s="43"/>
+      <c r="I114" s="32"/>
+      <c r="J114" s="33"/>
+      <c r="K114" s="33"/>
+      <c r="L114" s="33"/>
+      <c r="M114" s="33"/>
+      <c r="N114" s="33"/>
       <c r="O114" s="21"/>
       <c r="P114" s="21"/>
       <c r="Q114" s="21"/>
@@ -5295,12 +5326,14 @@
       <c r="E115" s="17">
         <v>2</v>
       </c>
-      <c r="F115" s="123" t="s">
-        <v>107</v>
-      </c>
-      <c r="G115" s="124"/>
-      <c r="H115" s="50"/>
-      <c r="I115" s="34"/>
+      <c r="F115" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="G115" s="19">
+        <v>1234568003</v>
+      </c>
+      <c r="H115" s="44"/>
+      <c r="I115" s="32"/>
       <c r="J115" s="21"/>
       <c r="K115" s="21"/>
       <c r="L115" s="21"/>
@@ -5316,16 +5349,18 @@
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
-      <c r="D116" s="76"/>
-      <c r="E116" s="28">
+      <c r="D116" s="61"/>
+      <c r="E116" s="27">
         <v>3</v>
       </c>
-      <c r="F116" s="48" t="s">
-        <v>108</v>
-      </c>
-      <c r="G116" s="49"/>
-      <c r="H116" s="48"/>
-      <c r="I116" s="34"/>
+      <c r="F116" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="G116" s="19">
+        <v>1234568004</v>
+      </c>
+      <c r="H116" s="43"/>
+      <c r="I116" s="32"/>
       <c r="J116" s="21"/>
       <c r="K116" s="21"/>
       <c r="L116" s="21"/>
@@ -5344,23 +5379,25 @@
       <c r="D117" s="16">
         <v>302</v>
       </c>
-      <c r="E117" s="89">
+      <c r="E117" s="68">
         <v>1</v>
       </c>
-      <c r="F117" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="G117" s="43"/>
-      <c r="H117" s="50"/>
-      <c r="I117" s="34"/>
-      <c r="J117" s="35"/>
-      <c r="K117" s="35"/>
-      <c r="L117" s="35"/>
-      <c r="M117" s="35"/>
-      <c r="N117" s="35"/>
+      <c r="F117" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="G117" s="19">
+        <v>1234568005</v>
+      </c>
+      <c r="H117" s="44"/>
+      <c r="I117" s="32"/>
+      <c r="J117" s="33"/>
+      <c r="K117" s="33"/>
+      <c r="L117" s="33"/>
+      <c r="M117" s="33"/>
+      <c r="N117" s="33"/>
       <c r="O117" s="21"/>
-      <c r="P117" s="35"/>
-      <c r="Q117" s="35"/>
+      <c r="P117" s="33"/>
+      <c r="Q117" s="33"/>
       <c r="R117" s="23"/>
       <c r="S117" s="21"/>
     </row>
@@ -5369,14 +5406,16 @@
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
       <c r="D118" s="24"/>
-      <c r="E118" s="41">
+      <c r="E118" s="38">
         <v>2</v>
       </c>
-      <c r="F118" s="79" t="s">
-        <v>110</v>
-      </c>
-      <c r="G118" s="80"/>
-      <c r="H118" s="48"/>
+      <c r="F118" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="G118" s="19">
+        <v>1234568006</v>
+      </c>
+      <c r="H118" s="43"/>
       <c r="I118" s="20"/>
       <c r="J118" s="21"/>
       <c r="K118" s="21"/>
@@ -5394,14 +5433,16 @@
       <c r="B119" s="15"/>
       <c r="C119" s="15"/>
       <c r="D119" s="24"/>
-      <c r="E119" s="28">
+      <c r="E119" s="27">
         <v>3</v>
       </c>
-      <c r="F119" s="70" t="s">
-        <v>111</v>
-      </c>
-      <c r="G119" s="71"/>
-      <c r="H119" s="50"/>
+      <c r="F119" s="57" t="s">
+        <v>112</v>
+      </c>
+      <c r="G119" s="19">
+        <v>1234568007</v>
+      </c>
+      <c r="H119" s="44"/>
       <c r="I119" s="20"/>
       <c r="J119" s="21"/>
       <c r="K119" s="21"/>
@@ -5419,14 +5460,16 @@
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
       <c r="D120" s="24"/>
-      <c r="E120" s="41">
+      <c r="E120" s="38">
         <v>4</v>
       </c>
-      <c r="F120" s="125" t="s">
-        <v>112</v>
-      </c>
-      <c r="G120" s="126"/>
-      <c r="H120" s="48"/>
+      <c r="F120" s="94" t="s">
+        <v>113</v>
+      </c>
+      <c r="G120" s="19">
+        <v>1234568008</v>
+      </c>
+      <c r="H120" s="43"/>
       <c r="I120" s="20"/>
       <c r="J120" s="21"/>
       <c r="K120" s="21"/>
@@ -5444,22 +5487,24 @@
       <c r="B121" s="15"/>
       <c r="C121" s="15"/>
       <c r="D121" s="24"/>
-      <c r="E121" s="28">
+      <c r="E121" s="27">
         <v>5</v>
       </c>
-      <c r="F121" s="44" t="s">
-        <v>113</v>
-      </c>
-      <c r="G121" s="45"/>
-      <c r="H121" s="50"/>
-      <c r="I121" s="46"/>
-      <c r="J121" s="47"/>
-      <c r="K121" s="47"/>
-      <c r="L121" s="47"/>
-      <c r="M121" s="47"/>
-      <c r="N121" s="47"/>
+      <c r="F121" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="G121" s="19">
+        <v>1234568009</v>
+      </c>
+      <c r="H121" s="44"/>
+      <c r="I121" s="41"/>
+      <c r="J121" s="42"/>
+      <c r="K121" s="42"/>
+      <c r="L121" s="42"/>
+      <c r="M121" s="42"/>
+      <c r="N121" s="42"/>
       <c r="O121" s="21"/>
-      <c r="P121" s="47"/>
+      <c r="P121" s="42"/>
       <c r="Q121" s="21"/>
       <c r="R121" s="23"/>
       <c r="S121" s="21"/>
@@ -5468,26 +5513,28 @@
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
-      <c r="D122" s="76"/>
-      <c r="E122" s="127">
+      <c r="D122" s="61"/>
+      <c r="E122" s="95">
         <v>6</v>
       </c>
-      <c r="F122" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="G122" s="38"/>
-      <c r="H122" s="48"/>
-      <c r="I122" s="39"/>
-      <c r="J122" s="40"/>
-      <c r="K122" s="40"/>
-      <c r="L122" s="40"/>
-      <c r="M122" s="40"/>
-      <c r="N122" s="40"/>
-      <c r="O122" s="40"/>
-      <c r="P122" s="40"/>
-      <c r="Q122" s="40"/>
-      <c r="R122" s="122"/>
-      <c r="S122" s="40"/>
+      <c r="F122" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="G122" s="19">
+        <v>1234568010</v>
+      </c>
+      <c r="H122" s="43"/>
+      <c r="I122" s="36"/>
+      <c r="J122" s="37"/>
+      <c r="K122" s="37"/>
+      <c r="L122" s="37"/>
+      <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
+      <c r="O122" s="37"/>
+      <c r="P122" s="37"/>
+      <c r="Q122" s="37"/>
+      <c r="R122" s="92"/>
+      <c r="S122" s="37"/>
     </row>
     <row r="123" ht="16.35" spans="1:19">
       <c r="A123" s="15"/>
@@ -5496,25 +5543,27 @@
       <c r="D123" s="16">
         <v>303</v>
       </c>
-      <c r="E123" s="57">
+      <c r="E123" s="49">
         <v>1</v>
       </c>
-      <c r="F123" s="128" t="s">
-        <v>115</v>
-      </c>
-      <c r="G123" s="129"/>
-      <c r="H123" s="50"/>
-      <c r="I123" s="34"/>
-      <c r="J123" s="35"/>
-      <c r="K123" s="35"/>
-      <c r="L123" s="35"/>
-      <c r="M123" s="35"/>
-      <c r="N123" s="35"/>
-      <c r="O123" s="35"/>
-      <c r="P123" s="35"/>
-      <c r="Q123" s="35"/>
-      <c r="R123" s="36"/>
-      <c r="S123" s="35"/>
+      <c r="F123" s="96" t="s">
+        <v>116</v>
+      </c>
+      <c r="G123" s="19">
+        <v>1234568011</v>
+      </c>
+      <c r="H123" s="44"/>
+      <c r="I123" s="32"/>
+      <c r="J123" s="33"/>
+      <c r="K123" s="33"/>
+      <c r="L123" s="33"/>
+      <c r="M123" s="33"/>
+      <c r="N123" s="33"/>
+      <c r="O123" s="33"/>
+      <c r="P123" s="33"/>
+      <c r="Q123" s="33"/>
+      <c r="R123" s="34"/>
+      <c r="S123" s="33"/>
     </row>
     <row r="124" spans="1:19">
       <c r="A124" s="15"/>
@@ -5525,10 +5574,12 @@
         <v>2</v>
       </c>
       <c r="F124" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="G124" s="26"/>
-      <c r="H124" s="48"/>
+        <v>117</v>
+      </c>
+      <c r="G124" s="19">
+        <v>1234568012</v>
+      </c>
+      <c r="H124" s="43"/>
       <c r="I124" s="20"/>
       <c r="J124" s="21"/>
       <c r="K124" s="21"/>
@@ -5550,10 +5601,12 @@
         <v>3</v>
       </c>
       <c r="F125" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="G125" s="26"/>
-      <c r="H125" s="50"/>
+        <v>118</v>
+      </c>
+      <c r="G125" s="19">
+        <v>1234568013</v>
+      </c>
+      <c r="H125" s="44"/>
       <c r="I125" s="20"/>
       <c r="J125" s="21"/>
       <c r="K125" s="21"/>
@@ -5574,11 +5627,13 @@
       <c r="E126" s="17">
         <v>4</v>
       </c>
-      <c r="F126" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="G126" s="45"/>
-      <c r="H126" s="48"/>
+      <c r="F126" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="G126" s="19">
+        <v>1234568014</v>
+      </c>
+      <c r="H126" s="43"/>
       <c r="I126" s="20"/>
       <c r="J126" s="21"/>
       <c r="K126" s="21"/>
@@ -5599,11 +5654,13 @@
       <c r="E127" s="17">
         <v>5</v>
       </c>
-      <c r="F127" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="G127" s="69"/>
-      <c r="H127" s="50"/>
+      <c r="F127" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="G127" s="19">
+        <v>1234568015</v>
+      </c>
+      <c r="H127" s="44"/>
       <c r="I127" s="20"/>
       <c r="J127" s="21"/>
       <c r="K127" s="21"/>
@@ -5621,20 +5678,22 @@
       <c r="B128" s="15"/>
       <c r="C128" s="15"/>
       <c r="D128" s="24"/>
-      <c r="E128" s="28">
+      <c r="E128" s="27">
         <v>6</v>
       </c>
-      <c r="F128" s="93" t="s">
-        <v>120</v>
-      </c>
-      <c r="G128" s="94"/>
-      <c r="H128" s="48"/>
-      <c r="I128" s="39"/>
-      <c r="J128" s="40"/>
-      <c r="K128" s="40"/>
-      <c r="L128" s="40"/>
-      <c r="M128" s="40"/>
-      <c r="N128" s="40"/>
+      <c r="F128" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="G128" s="19">
+        <v>1234568016</v>
+      </c>
+      <c r="H128" s="43"/>
+      <c r="I128" s="36"/>
+      <c r="J128" s="37"/>
+      <c r="K128" s="37"/>
+      <c r="L128" s="37"/>
+      <c r="M128" s="37"/>
+      <c r="N128" s="37"/>
       <c r="O128" s="21"/>
       <c r="P128" s="21"/>
       <c r="Q128" s="21"/>
@@ -5648,22 +5707,24 @@
       <c r="D129" s="16">
         <v>304</v>
       </c>
-      <c r="E129" s="57">
+      <c r="E129" s="49">
         <v>1</v>
       </c>
-      <c r="F129" s="96" t="s">
-        <v>121</v>
-      </c>
-      <c r="G129" s="130"/>
-      <c r="H129" s="50"/>
-      <c r="I129" s="88"/>
-      <c r="J129" s="52"/>
+      <c r="F129" s="72" t="s">
+        <v>122</v>
+      </c>
+      <c r="G129" s="19">
+        <v>1234568017</v>
+      </c>
+      <c r="H129" s="44"/>
+      <c r="I129" s="67"/>
+      <c r="J129" s="46"/>
       <c r="K129" s="22"/>
-      <c r="L129" s="52"/>
+      <c r="L129" s="46"/>
       <c r="M129" s="22"/>
-      <c r="N129" s="52"/>
+      <c r="N129" s="46"/>
       <c r="O129" s="21"/>
-      <c r="P129" s="52"/>
+      <c r="P129" s="46"/>
       <c r="Q129" s="21"/>
       <c r="R129" s="23"/>
       <c r="S129" s="21"/>
@@ -5673,14 +5734,16 @@
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
       <c r="D130" s="24"/>
-      <c r="E130" s="57">
+      <c r="E130" s="49">
         <v>2</v>
       </c>
-      <c r="F130" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="G130" s="43"/>
-      <c r="H130" s="48"/>
+      <c r="F130" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="G130" s="19">
+        <v>1234568018</v>
+      </c>
+      <c r="H130" s="43"/>
       <c r="I130" s="20"/>
       <c r="J130" s="21"/>
       <c r="K130" s="21"/>
@@ -5698,24 +5761,26 @@
       <c r="B131" s="15"/>
       <c r="C131" s="15"/>
       <c r="D131" s="24"/>
-      <c r="E131" s="28">
+      <c r="E131" s="27">
         <v>3</v>
       </c>
-      <c r="F131" s="112" t="s">
-        <v>123</v>
-      </c>
-      <c r="G131" s="131"/>
-      <c r="H131" s="50"/>
-      <c r="I131" s="46"/>
-      <c r="J131" s="47"/>
-      <c r="K131" s="47"/>
-      <c r="L131" s="47"/>
-      <c r="M131" s="47"/>
-      <c r="N131" s="47"/>
-      <c r="O131" s="47"/>
-      <c r="P131" s="47"/>
-      <c r="Q131" s="47"/>
-      <c r="R131" s="132"/>
+      <c r="F131" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="G131" s="19">
+        <v>1234568019</v>
+      </c>
+      <c r="H131" s="44"/>
+      <c r="I131" s="41"/>
+      <c r="J131" s="42"/>
+      <c r="K131" s="42"/>
+      <c r="L131" s="42"/>
+      <c r="M131" s="42"/>
+      <c r="N131" s="42"/>
+      <c r="O131" s="42"/>
+      <c r="P131" s="42"/>
+      <c r="Q131" s="42"/>
+      <c r="R131" s="97"/>
       <c r="S131" s="21"/>
     </row>
     <row r="132" ht="17.1" spans="1:19">
@@ -5723,11 +5788,14 @@
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
       <c r="D132" s="24"/>
-      <c r="E132" s="41">
+      <c r="E132" s="38">
         <v>4</v>
       </c>
-      <c r="F132" s="72" t="s">
-        <v>33</v>
+      <c r="F132" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G132" s="19">
+        <v>1234568020</v>
       </c>
     </row>
     <row r="133" ht="17.1" spans="1:19">
@@ -5735,22 +5803,24 @@
       <c r="B133" s="15"/>
       <c r="C133" s="15"/>
       <c r="D133" s="24"/>
-      <c r="E133" s="28">
+      <c r="E133" s="27">
         <v>5</v>
       </c>
-      <c r="F133" s="50" t="s">
-        <v>124</v>
-      </c>
-      <c r="G133" s="33"/>
-      <c r="H133" s="50"/>
-      <c r="I133" s="46"/>
+      <c r="F133" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="G133" s="19">
+        <v>1234568021</v>
+      </c>
+      <c r="H133" s="44"/>
+      <c r="I133" s="41"/>
       <c r="J133" s="21"/>
       <c r="K133" s="21"/>
       <c r="L133" s="21"/>
       <c r="M133" s="21"/>
       <c r="N133" s="21"/>
       <c r="O133" s="21"/>
-      <c r="P133" s="47"/>
+      <c r="P133" s="42"/>
       <c r="Q133" s="21"/>
       <c r="R133" s="23"/>
       <c r="S133" s="21"/>
@@ -5759,26 +5829,28 @@
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
-      <c r="D134" s="76"/>
-      <c r="E134" s="133">
+      <c r="D134" s="61"/>
+      <c r="E134" s="98">
         <v>6</v>
       </c>
-      <c r="F134" s="134" t="s">
-        <v>125</v>
-      </c>
-      <c r="G134" s="135"/>
-      <c r="H134" s="48"/>
-      <c r="I134" s="46"/>
-      <c r="J134" s="47"/>
-      <c r="K134" s="47"/>
-      <c r="L134" s="47"/>
-      <c r="M134" s="47"/>
-      <c r="N134" s="47"/>
-      <c r="O134" s="47"/>
-      <c r="P134" s="47"/>
-      <c r="Q134" s="47"/>
-      <c r="R134" s="47"/>
-      <c r="S134" s="47"/>
+      <c r="F134" s="99" t="s">
+        <v>126</v>
+      </c>
+      <c r="G134" s="19">
+        <v>1234568022</v>
+      </c>
+      <c r="H134" s="43"/>
+      <c r="I134" s="41"/>
+      <c r="J134" s="42"/>
+      <c r="K134" s="42"/>
+      <c r="L134" s="42"/>
+      <c r="M134" s="42"/>
+      <c r="N134" s="42"/>
+      <c r="O134" s="42"/>
+      <c r="P134" s="42"/>
+      <c r="Q134" s="42"/>
+      <c r="R134" s="42"/>
+      <c r="S134" s="42"/>
     </row>
     <row r="135" spans="1:19">
       <c r="A135" s="15"/>
@@ -5790,11 +5862,13 @@
       <c r="E135" s="17">
         <v>1</v>
       </c>
-      <c r="F135" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="G135" s="49"/>
-      <c r="H135" s="50"/>
+      <c r="F135" s="43" t="s">
+        <v>127</v>
+      </c>
+      <c r="G135" s="19">
+        <v>1234568023</v>
+      </c>
+      <c r="H135" s="44"/>
       <c r="I135" s="20"/>
       <c r="J135" s="21"/>
       <c r="K135" s="21"/>
@@ -5807,30 +5881,32 @@
       <c r="R135" s="21"/>
       <c r="S135" s="21"/>
     </row>
-    <row r="136" ht="17.4" spans="1:19">
+    <row r="136" ht="16.8" spans="1:19">
       <c r="A136" s="15"/>
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
       <c r="D136" s="24"/>
-      <c r="E136" s="57">
+      <c r="E136" s="49">
         <v>2</v>
       </c>
-      <c r="F136" s="136" t="s">
-        <v>127</v>
-      </c>
-      <c r="G136" s="137"/>
-      <c r="H136" s="48"/>
-      <c r="I136" s="34"/>
-      <c r="J136" s="35"/>
-      <c r="K136" s="35"/>
-      <c r="L136" s="35"/>
-      <c r="M136" s="35"/>
-      <c r="N136" s="35"/>
-      <c r="O136" s="35"/>
-      <c r="P136" s="35"/>
-      <c r="Q136" s="35"/>
-      <c r="R136" s="36"/>
-      <c r="S136" s="35"/>
+      <c r="F136" s="100" t="s">
+        <v>128</v>
+      </c>
+      <c r="G136" s="19">
+        <v>1234568024</v>
+      </c>
+      <c r="H136" s="43"/>
+      <c r="I136" s="32"/>
+      <c r="J136" s="33"/>
+      <c r="K136" s="33"/>
+      <c r="L136" s="33"/>
+      <c r="M136" s="33"/>
+      <c r="N136" s="33"/>
+      <c r="O136" s="33"/>
+      <c r="P136" s="33"/>
+      <c r="Q136" s="33"/>
+      <c r="R136" s="34"/>
+      <c r="S136" s="33"/>
     </row>
     <row r="137" spans="1:19">
       <c r="A137" s="15"/>
@@ -5841,10 +5917,12 @@
         <v>3</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>128</v>
-      </c>
-      <c r="G137" s="26"/>
-      <c r="H137" s="50"/>
+        <v>129</v>
+      </c>
+      <c r="G137" s="19">
+        <v>1234568025</v>
+      </c>
+      <c r="H137" s="44"/>
       <c r="I137" s="20"/>
       <c r="J137" s="21"/>
       <c r="K137" s="21"/>
@@ -5865,11 +5943,13 @@
       <c r="E138" s="17">
         <v>4</v>
       </c>
-      <c r="F138" s="112" t="s">
-        <v>129</v>
-      </c>
-      <c r="G138" s="138"/>
-      <c r="H138" s="48"/>
+      <c r="F138" s="84" t="s">
+        <v>130</v>
+      </c>
+      <c r="G138" s="19">
+        <v>1234568026</v>
+      </c>
+      <c r="H138" s="43"/>
       <c r="I138" s="20"/>
       <c r="J138" s="21"/>
       <c r="K138" s="21"/>
@@ -5890,11 +5970,13 @@
       <c r="E139" s="17">
         <v>5</v>
       </c>
-      <c r="F139" s="48" t="s">
-        <v>130</v>
-      </c>
-      <c r="G139" s="49"/>
-      <c r="H139" s="50"/>
+      <c r="F139" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="G139" s="19">
+        <v>1234568027</v>
+      </c>
+      <c r="H139" s="44"/>
       <c r="I139" s="21"/>
       <c r="J139" s="21"/>
       <c r="K139" s="21"/>
@@ -5911,15 +5993,17 @@
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
-      <c r="D140" s="76"/>
-      <c r="E140" s="28">
+      <c r="D140" s="61"/>
+      <c r="E140" s="27">
         <v>6</v>
       </c>
-      <c r="F140" s="86" t="s">
-        <v>131</v>
-      </c>
-      <c r="G140" s="87"/>
-      <c r="H140" s="48"/>
+      <c r="F140" s="66" t="s">
+        <v>132</v>
+      </c>
+      <c r="G140" s="19">
+        <v>1234568028</v>
+      </c>
+      <c r="H140" s="43"/>
       <c r="I140" s="20"/>
       <c r="J140" s="21"/>
       <c r="K140" s="21"/>
@@ -5939,14 +6023,16 @@
       <c r="D141" s="16">
         <v>306</v>
       </c>
-      <c r="E141" s="57">
+      <c r="E141" s="49">
         <v>1</v>
       </c>
-      <c r="F141" s="139" t="s">
-        <v>132</v>
-      </c>
-      <c r="G141" s="140"/>
-      <c r="H141" s="50"/>
+      <c r="F141" s="101" t="s">
+        <v>133</v>
+      </c>
+      <c r="G141" s="19">
+        <v>1234568029</v>
+      </c>
+      <c r="H141" s="44"/>
       <c r="I141" s="20"/>
       <c r="J141" s="21"/>
       <c r="K141" s="21"/>
@@ -5967,11 +6053,13 @@
       <c r="E142" s="17">
         <v>2</v>
       </c>
-      <c r="F142" s="141" t="s">
-        <v>133</v>
-      </c>
-      <c r="G142" s="142"/>
-      <c r="H142" s="48"/>
+      <c r="F142" s="102" t="s">
+        <v>134</v>
+      </c>
+      <c r="G142" s="19">
+        <v>1234568030</v>
+      </c>
+      <c r="H142" s="43"/>
       <c r="I142" s="20"/>
       <c r="J142" s="21"/>
       <c r="K142" s="21"/>
@@ -5989,14 +6077,16 @@
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
       <c r="D143" s="24"/>
-      <c r="E143" s="41">
+      <c r="E143" s="38">
         <v>3</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>134</v>
-      </c>
-      <c r="G143" s="26"/>
-      <c r="H143" s="50"/>
+        <v>135</v>
+      </c>
+      <c r="G143" s="19">
+        <v>1234568031</v>
+      </c>
+      <c r="H143" s="44"/>
       <c r="I143" s="20"/>
       <c r="J143" s="21"/>
       <c r="K143" s="21"/>
@@ -6017,17 +6107,19 @@
       <c r="E144" s="17">
         <v>4</v>
       </c>
-      <c r="F144" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="G144" s="43"/>
-      <c r="H144" s="48"/>
-      <c r="I144" s="34"/>
-      <c r="J144" s="35"/>
-      <c r="K144" s="35"/>
-      <c r="L144" s="35"/>
-      <c r="M144" s="35"/>
-      <c r="N144" s="35"/>
+      <c r="F144" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="G144" s="19">
+        <v>1234568032</v>
+      </c>
+      <c r="H144" s="43"/>
+      <c r="I144" s="32"/>
+      <c r="J144" s="33"/>
+      <c r="K144" s="33"/>
+      <c r="L144" s="33"/>
+      <c r="M144" s="33"/>
+      <c r="N144" s="33"/>
       <c r="O144" s="21"/>
       <c r="P144" s="21"/>
       <c r="Q144" s="21"/>
@@ -6039,14 +6131,16 @@
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
       <c r="D145" s="24"/>
-      <c r="E145" s="41">
+      <c r="E145" s="38">
         <v>5</v>
       </c>
-      <c r="F145" s="68" t="s">
-        <v>136</v>
-      </c>
-      <c r="G145" s="69"/>
-      <c r="H145" s="50"/>
+      <c r="F145" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="G145" s="19">
+        <v>1234568033</v>
+      </c>
+      <c r="H145" s="44"/>
       <c r="I145" s="20"/>
       <c r="J145" s="21"/>
       <c r="K145" s="21"/>
@@ -6063,23 +6157,25 @@
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
-      <c r="D146" s="76"/>
-      <c r="E146" s="28">
+      <c r="D146" s="61"/>
+      <c r="E146" s="27">
         <v>6</v>
       </c>
-      <c r="F146" s="143" t="s">
-        <v>137</v>
-      </c>
-      <c r="G146" s="144"/>
-      <c r="H146" s="48"/>
-      <c r="I146" s="39"/>
-      <c r="J146" s="40"/>
-      <c r="K146" s="40"/>
-      <c r="L146" s="40"/>
-      <c r="M146" s="40"/>
-      <c r="N146" s="40"/>
+      <c r="F146" s="103" t="s">
+        <v>138</v>
+      </c>
+      <c r="G146" s="19">
+        <v>1234568034</v>
+      </c>
+      <c r="H146" s="43"/>
+      <c r="I146" s="36"/>
+      <c r="J146" s="37"/>
+      <c r="K146" s="37"/>
+      <c r="L146" s="37"/>
+      <c r="M146" s="37"/>
+      <c r="N146" s="37"/>
       <c r="O146" s="21"/>
-      <c r="P146" s="40"/>
+      <c r="P146" s="37"/>
       <c r="Q146" s="21"/>
       <c r="R146" s="23"/>
       <c r="S146" s="21"/>
@@ -6091,22 +6187,24 @@
       <c r="D147" s="16">
         <v>307</v>
       </c>
-      <c r="E147" s="57">
+      <c r="E147" s="49">
         <v>1</v>
       </c>
-      <c r="F147" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="G147" s="43"/>
-      <c r="H147" s="50"/>
-      <c r="I147" s="34"/>
-      <c r="J147" s="35"/>
-      <c r="K147" s="35"/>
-      <c r="L147" s="35"/>
-      <c r="M147" s="35"/>
-      <c r="N147" s="35"/>
+      <c r="F147" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="G147" s="19">
+        <v>1234568035</v>
+      </c>
+      <c r="H147" s="44"/>
+      <c r="I147" s="32"/>
+      <c r="J147" s="33"/>
+      <c r="K147" s="33"/>
+      <c r="L147" s="33"/>
+      <c r="M147" s="33"/>
+      <c r="N147" s="33"/>
       <c r="O147" s="21"/>
-      <c r="P147" s="35"/>
+      <c r="P147" s="33"/>
       <c r="Q147" s="21"/>
       <c r="R147" s="23"/>
       <c r="S147" s="21"/>
@@ -6119,11 +6217,13 @@
       <c r="E148" s="17">
         <v>2</v>
       </c>
-      <c r="F148" s="145" t="s">
-        <v>139</v>
-      </c>
-      <c r="G148" s="146"/>
-      <c r="H148" s="48"/>
+      <c r="F148" s="104" t="s">
+        <v>140</v>
+      </c>
+      <c r="G148" s="19">
+        <v>1234568036</v>
+      </c>
+      <c r="H148" s="43"/>
       <c r="I148" s="20"/>
       <c r="J148" s="21"/>
       <c r="K148" s="21"/>
@@ -6131,12 +6231,12 @@
       <c r="M148" s="21"/>
       <c r="N148" s="21"/>
       <c r="O148" s="21"/>
-      <c r="P148" s="139"/>
+      <c r="P148" s="101"/>
       <c r="Q148" s="21"/>
       <c r="R148" s="23"/>
       <c r="S148" s="21"/>
       <c r="U148" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="149" spans="1:21">
@@ -6147,11 +6247,13 @@
       <c r="E149" s="17">
         <v>3</v>
       </c>
-      <c r="F149" s="48" t="s">
-        <v>141</v>
-      </c>
-      <c r="G149" s="49"/>
-      <c r="H149" s="50"/>
+      <c r="F149" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="G149" s="19">
+        <v>1234568037</v>
+      </c>
+      <c r="H149" s="44"/>
       <c r="I149" s="20"/>
       <c r="J149" s="21"/>
       <c r="K149" s="21"/>
@@ -6172,17 +6274,19 @@
       <c r="E150" s="17">
         <v>4</v>
       </c>
-      <c r="F150" s="48" t="s">
-        <v>142</v>
-      </c>
-      <c r="G150" s="97"/>
-      <c r="H150" s="48"/>
-      <c r="I150" s="34"/>
-      <c r="J150" s="35"/>
-      <c r="K150" s="35"/>
-      <c r="L150" s="35"/>
-      <c r="M150" s="35"/>
-      <c r="N150" s="35"/>
+      <c r="F150" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="G150" s="19">
+        <v>1234568038</v>
+      </c>
+      <c r="H150" s="43"/>
+      <c r="I150" s="32"/>
+      <c r="J150" s="33"/>
+      <c r="K150" s="33"/>
+      <c r="L150" s="33"/>
+      <c r="M150" s="33"/>
+      <c r="N150" s="33"/>
       <c r="O150" s="21"/>
       <c r="P150" s="21"/>
       <c r="Q150" s="21"/>
@@ -6197,11 +6301,13 @@
       <c r="E151" s="17">
         <v>5</v>
       </c>
-      <c r="F151" s="143" t="s">
-        <v>143</v>
-      </c>
-      <c r="G151" s="147"/>
-      <c r="H151" s="50"/>
+      <c r="F151" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="G151" s="19">
+        <v>1234568039</v>
+      </c>
+      <c r="H151" s="44"/>
       <c r="I151" s="20"/>
       <c r="J151" s="21"/>
       <c r="K151" s="21"/>
@@ -6222,11 +6328,13 @@
       <c r="E152" s="17">
         <v>6</v>
       </c>
-      <c r="F152" s="148" t="s">
-        <v>144</v>
-      </c>
-      <c r="G152" s="149"/>
-      <c r="H152" s="48"/>
+      <c r="F152" s="105" t="s">
+        <v>145</v>
+      </c>
+      <c r="G152" s="19">
+        <v>1234568040</v>
+      </c>
+      <c r="H152" s="43"/>
       <c r="I152" s="20"/>
       <c r="J152" s="21"/>
       <c r="K152" s="21"/>
@@ -6246,25 +6354,27 @@
       <c r="D153" s="16">
         <v>308</v>
       </c>
-      <c r="E153" s="57">
+      <c r="E153" s="49">
         <v>1</v>
       </c>
-      <c r="F153" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="G153" s="43"/>
-      <c r="H153" s="50"/>
-      <c r="I153" s="34"/>
-      <c r="J153" s="35"/>
-      <c r="K153" s="35"/>
-      <c r="L153" s="35"/>
-      <c r="M153" s="35"/>
-      <c r="N153" s="35"/>
-      <c r="O153" s="35"/>
-      <c r="P153" s="35"/>
-      <c r="Q153" s="35"/>
-      <c r="R153" s="36"/>
-      <c r="S153" s="35"/>
+      <c r="F153" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="G153" s="19">
+        <v>1234568041</v>
+      </c>
+      <c r="H153" s="44"/>
+      <c r="I153" s="32"/>
+      <c r="J153" s="33"/>
+      <c r="K153" s="33"/>
+      <c r="L153" s="33"/>
+      <c r="M153" s="33"/>
+      <c r="N153" s="33"/>
+      <c r="O153" s="33"/>
+      <c r="P153" s="33"/>
+      <c r="Q153" s="33"/>
+      <c r="R153" s="34"/>
+      <c r="S153" s="33"/>
     </row>
     <row r="154" ht="16.35" spans="1:21">
       <c r="A154" s="15"/>
@@ -6274,11 +6384,13 @@
       <c r="E154" s="17">
         <v>2</v>
       </c>
-      <c r="F154" s="37" t="s">
-        <v>146</v>
-      </c>
-      <c r="G154" s="45"/>
-      <c r="H154" s="48"/>
+      <c r="F154" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="G154" s="19">
+        <v>1234568042</v>
+      </c>
+      <c r="H154" s="43"/>
       <c r="I154" s="20"/>
       <c r="J154" s="21"/>
       <c r="K154" s="21"/>
@@ -6299,11 +6411,13 @@
       <c r="E155" s="17">
         <v>3</v>
       </c>
-      <c r="F155" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="G155" s="65"/>
-      <c r="H155" s="50"/>
+      <c r="F155" s="54" t="s">
+        <v>148</v>
+      </c>
+      <c r="G155" s="19">
+        <v>1234568043</v>
+      </c>
+      <c r="H155" s="44"/>
       <c r="I155" s="20"/>
       <c r="J155" s="21"/>
       <c r="K155" s="21"/>
@@ -6325,10 +6439,12 @@
         <v>4</v>
       </c>
       <c r="F156" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="G156" s="26"/>
-      <c r="H156" s="48"/>
+        <v>149</v>
+      </c>
+      <c r="G156" s="19">
+        <v>1234568044</v>
+      </c>
+      <c r="H156" s="43"/>
       <c r="I156" s="20"/>
       <c r="J156" s="21"/>
       <c r="K156" s="21"/>
@@ -6346,14 +6462,16 @@
       <c r="B157" s="15"/>
       <c r="C157" s="15"/>
       <c r="D157" s="24"/>
-      <c r="E157" s="31">
+      <c r="E157" s="30">
         <v>5</v>
       </c>
-      <c r="F157" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="G157" s="45"/>
-      <c r="H157" s="50"/>
+      <c r="F157" s="35" t="s">
+        <v>150</v>
+      </c>
+      <c r="G157" s="19">
+        <v>1234568045</v>
+      </c>
+      <c r="H157" s="44"/>
       <c r="I157" s="20"/>
       <c r="J157" s="21"/>
       <c r="K157" s="21"/>
@@ -6370,26 +6488,28 @@
       <c r="A158" s="15"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
-      <c r="D158" s="76"/>
-      <c r="E158" s="28">
+      <c r="D158" s="61"/>
+      <c r="E158" s="27">
         <v>6</v>
       </c>
-      <c r="F158" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="G158" s="45"/>
-      <c r="H158" s="48"/>
-      <c r="I158" s="46"/>
-      <c r="J158" s="47"/>
-      <c r="K158" s="47"/>
-      <c r="L158" s="47"/>
-      <c r="M158" s="47"/>
-      <c r="N158" s="47"/>
-      <c r="O158" s="47"/>
-      <c r="P158" s="47"/>
-      <c r="Q158" s="47"/>
-      <c r="R158" s="132"/>
-      <c r="S158" s="47"/>
+      <c r="F158" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="G158" s="19">
+        <v>1234568046</v>
+      </c>
+      <c r="H158" s="43"/>
+      <c r="I158" s="41"/>
+      <c r="J158" s="42"/>
+      <c r="K158" s="42"/>
+      <c r="L158" s="42"/>
+      <c r="M158" s="42"/>
+      <c r="N158" s="42"/>
+      <c r="O158" s="42"/>
+      <c r="P158" s="42"/>
+      <c r="Q158" s="42"/>
+      <c r="R158" s="97"/>
+      <c r="S158" s="42"/>
     </row>
     <row r="159" ht="17.1" spans="1:21">
       <c r="A159" s="15"/>
@@ -6398,14 +6518,16 @@
       <c r="D159" s="16">
         <v>309</v>
       </c>
-      <c r="E159" s="57">
+      <c r="E159" s="49">
         <v>1</v>
       </c>
-      <c r="F159" s="90" t="s">
-        <v>151</v>
-      </c>
-      <c r="G159" s="33"/>
-      <c r="H159" s="50"/>
+      <c r="F159" s="69" t="s">
+        <v>152</v>
+      </c>
+      <c r="G159" s="19">
+        <v>1234568047</v>
+      </c>
+      <c r="H159" s="44"/>
       <c r="I159" s="21"/>
       <c r="J159" s="21"/>
       <c r="K159" s="21"/>
@@ -6426,11 +6548,13 @@
       <c r="E160" s="17">
         <v>2</v>
       </c>
-      <c r="F160" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="G160" s="45"/>
-      <c r="H160" s="44"/>
+      <c r="F160" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="G160" s="19">
+        <v>1234568048</v>
+      </c>
+      <c r="H160" s="40"/>
       <c r="I160" s="20"/>
       <c r="J160" s="21"/>
       <c r="K160" s="21"/>
@@ -6451,11 +6575,13 @@
       <c r="E161" s="17">
         <v>3</v>
       </c>
-      <c r="F161" s="68" t="s">
-        <v>153</v>
-      </c>
-      <c r="G161" s="69"/>
-      <c r="H161" s="68"/>
+      <c r="F161" s="56" t="s">
+        <v>154</v>
+      </c>
+      <c r="G161" s="19">
+        <v>1234568049</v>
+      </c>
+      <c r="H161" s="56"/>
       <c r="I161" s="20"/>
       <c r="J161" s="21"/>
       <c r="K161" s="21"/>
@@ -6476,11 +6602,13 @@
       <c r="E162" s="17">
         <v>4</v>
       </c>
-      <c r="F162" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="G162" s="69"/>
-      <c r="H162" s="44"/>
+      <c r="F162" s="56" t="s">
+        <v>155</v>
+      </c>
+      <c r="G162" s="19">
+        <v>1234568050</v>
+      </c>
+      <c r="H162" s="40"/>
       <c r="I162" s="20"/>
       <c r="J162" s="21"/>
       <c r="K162" s="21"/>
@@ -6498,14 +6626,16 @@
       <c r="B163" s="15"/>
       <c r="C163" s="15"/>
       <c r="D163" s="24"/>
-      <c r="E163" s="31">
+      <c r="E163" s="30">
         <v>5</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="G163" s="75"/>
-      <c r="H163" s="68"/>
+        <v>156</v>
+      </c>
+      <c r="G163" s="19">
+        <v>1234568051</v>
+      </c>
+      <c r="H163" s="56"/>
       <c r="I163" s="22"/>
       <c r="J163" s="22"/>
       <c r="K163" s="22"/>
@@ -6522,15 +6652,17 @@
       <c r="A164" s="15"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
-      <c r="D164" s="76"/>
-      <c r="E164" s="127">
+      <c r="D164" s="61"/>
+      <c r="E164" s="95">
         <v>6</v>
       </c>
-      <c r="F164" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="G164" s="45"/>
-      <c r="H164" s="44"/>
+      <c r="F164" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="G164" s="19">
+        <v>1234568052</v>
+      </c>
+      <c r="H164" s="40"/>
       <c r="I164" s="20"/>
       <c r="J164" s="21"/>
       <c r="K164" s="21"/>
@@ -6550,14 +6682,16 @@
       <c r="D165" s="16">
         <v>310</v>
       </c>
-      <c r="E165" s="89">
+      <c r="E165" s="68">
         <v>1</v>
       </c>
-      <c r="F165" s="48" t="s">
-        <v>157</v>
-      </c>
-      <c r="G165" s="49"/>
-      <c r="H165" s="68"/>
+      <c r="F165" s="43" t="s">
+        <v>158</v>
+      </c>
+      <c r="G165" s="19">
+        <v>1234568053</v>
+      </c>
+      <c r="H165" s="56"/>
       <c r="I165" s="21"/>
       <c r="J165" s="21"/>
       <c r="K165" s="21"/>
@@ -6575,14 +6709,16 @@
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
       <c r="D166" s="24"/>
-      <c r="E166" s="41">
+      <c r="E166" s="38">
         <v>2</v>
       </c>
-      <c r="F166" s="48" t="s">
-        <v>158</v>
-      </c>
-      <c r="G166" s="49"/>
-      <c r="H166" s="44"/>
+      <c r="F166" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="G166" s="19">
+        <v>1234568054</v>
+      </c>
+      <c r="H166" s="40"/>
       <c r="I166" s="21"/>
       <c r="J166" s="21"/>
       <c r="K166" s="21"/>
@@ -6600,14 +6736,16 @@
       <c r="B167" s="15"/>
       <c r="C167" s="15"/>
       <c r="D167" s="24"/>
-      <c r="E167" s="28">
+      <c r="E167" s="27">
         <v>3</v>
       </c>
       <c r="F167" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="G167" s="26"/>
-      <c r="H167" s="68"/>
+        <v>160</v>
+      </c>
+      <c r="G167" s="19">
+        <v>1234568055</v>
+      </c>
+      <c r="H167" s="56"/>
       <c r="I167" s="20"/>
       <c r="J167" s="21"/>
       <c r="K167" s="21"/>
@@ -6625,14 +6763,16 @@
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
       <c r="D168" s="24"/>
-      <c r="E168" s="41">
+      <c r="E168" s="38">
         <v>4</v>
       </c>
-      <c r="F168" s="83" t="s">
-        <v>160</v>
-      </c>
-      <c r="G168" s="84"/>
-      <c r="H168" s="44"/>
+      <c r="F168" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="G168" s="19">
+        <v>1234568056</v>
+      </c>
+      <c r="H168" s="40"/>
       <c r="I168" s="20"/>
       <c r="J168" s="21"/>
       <c r="K168" s="21"/>
@@ -6650,14 +6790,16 @@
       <c r="B169" s="15"/>
       <c r="C169" s="15"/>
       <c r="D169" s="24"/>
-      <c r="E169" s="28">
+      <c r="E169" s="27">
         <v>5</v>
       </c>
-      <c r="F169" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="G169" s="69"/>
-      <c r="H169" s="68"/>
+      <c r="F169" s="56" t="s">
+        <v>162</v>
+      </c>
+      <c r="G169" s="19">
+        <v>1234568057</v>
+      </c>
+      <c r="H169" s="56"/>
       <c r="I169" s="20"/>
       <c r="J169" s="21"/>
       <c r="K169" s="21"/>
@@ -6674,21 +6816,23 @@
       <c r="A170" s="15"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
-      <c r="D170" s="76"/>
-      <c r="E170" s="127">
+      <c r="D170" s="61"/>
+      <c r="E170" s="95">
         <v>6</v>
       </c>
-      <c r="F170" s="37" t="s">
-        <v>162</v>
-      </c>
-      <c r="G170" s="38"/>
-      <c r="H170" s="44"/>
-      <c r="I170" s="39"/>
-      <c r="J170" s="40"/>
-      <c r="K170" s="40"/>
-      <c r="L170" s="40"/>
-      <c r="M170" s="40"/>
-      <c r="N170" s="40"/>
+      <c r="F170" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="G170" s="19">
+        <v>1234568058</v>
+      </c>
+      <c r="H170" s="40"/>
+      <c r="I170" s="36"/>
+      <c r="J170" s="37"/>
+      <c r="K170" s="37"/>
+      <c r="L170" s="37"/>
+      <c r="M170" s="37"/>
+      <c r="N170" s="37"/>
       <c r="O170" s="21"/>
       <c r="P170" s="21"/>
       <c r="Q170" s="21"/>
@@ -6702,20 +6846,22 @@
       <c r="D171" s="16">
         <v>311</v>
       </c>
-      <c r="E171" s="89">
+      <c r="E171" s="68">
         <v>1</v>
       </c>
-      <c r="F171" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="G171" s="43"/>
-      <c r="H171" s="68"/>
-      <c r="I171" s="34"/>
-      <c r="J171" s="35"/>
-      <c r="K171" s="35"/>
-      <c r="L171" s="35"/>
-      <c r="M171" s="35"/>
-      <c r="N171" s="35"/>
+      <c r="F171" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="G171" s="19">
+        <v>1234568059</v>
+      </c>
+      <c r="H171" s="56"/>
+      <c r="I171" s="32"/>
+      <c r="J171" s="33"/>
+      <c r="K171" s="33"/>
+      <c r="L171" s="33"/>
+      <c r="M171" s="33"/>
+      <c r="N171" s="33"/>
       <c r="O171" s="21"/>
       <c r="P171" s="21"/>
       <c r="Q171" s="21"/>
@@ -6727,15 +6873,17 @@
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
       <c r="D172" s="24"/>
-      <c r="E172" s="57">
+      <c r="E172" s="49">
         <v>2</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="G172" s="43"/>
-      <c r="H172" s="44"/>
-      <c r="I172" s="34"/>
+        <v>123</v>
+      </c>
+      <c r="G172" s="19">
+        <v>1234568060</v>
+      </c>
+      <c r="H172" s="40"/>
+      <c r="I172" s="32"/>
       <c r="J172" s="21"/>
       <c r="K172" s="21"/>
       <c r="L172" s="21"/>
@@ -6752,15 +6900,17 @@
       <c r="B173" s="15"/>
       <c r="C173" s="15"/>
       <c r="D173" s="24"/>
-      <c r="E173" s="28">
+      <c r="E173" s="27">
         <v>3</v>
       </c>
-      <c r="F173" s="150" t="s">
-        <v>164</v>
-      </c>
-      <c r="G173" s="91"/>
-      <c r="H173" s="68"/>
-      <c r="I173" s="34"/>
+      <c r="F173" s="106" t="s">
+        <v>165</v>
+      </c>
+      <c r="G173" s="19">
+        <v>1234568061</v>
+      </c>
+      <c r="H173" s="56"/>
+      <c r="I173" s="32"/>
       <c r="J173" s="21"/>
       <c r="K173" s="21"/>
       <c r="L173" s="21"/>
@@ -6777,14 +6927,16 @@
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
       <c r="D174" s="24"/>
-      <c r="E174" s="57">
+      <c r="E174" s="49">
         <v>4</v>
       </c>
-      <c r="F174" s="93" t="s">
-        <v>165</v>
-      </c>
-      <c r="G174" s="135"/>
-      <c r="H174" s="44"/>
+      <c r="F174" s="71" t="s">
+        <v>166</v>
+      </c>
+      <c r="G174" s="19">
+        <v>1234568062</v>
+      </c>
+      <c r="H174" s="40"/>
       <c r="I174" s="21"/>
       <c r="J174" s="21"/>
       <c r="K174" s="21"/>
@@ -6802,14 +6954,16 @@
       <c r="B175" s="15"/>
       <c r="C175" s="15"/>
       <c r="D175" s="24"/>
-      <c r="E175" s="28">
+      <c r="E175" s="27">
         <v>5</v>
       </c>
-      <c r="F175" s="48" t="s">
-        <v>166</v>
-      </c>
-      <c r="G175" s="49"/>
-      <c r="H175" s="68"/>
+      <c r="F175" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="G175" s="19">
+        <v>1234568063</v>
+      </c>
+      <c r="H175" s="56"/>
       <c r="I175" s="21"/>
       <c r="J175" s="21"/>
       <c r="K175" s="21"/>
@@ -6826,23 +6980,25 @@
       <c r="A176" s="15"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
-      <c r="D176" s="76"/>
-      <c r="E176" s="89">
+      <c r="D176" s="61"/>
+      <c r="E176" s="68">
         <v>6</v>
       </c>
-      <c r="F176" s="151" t="s">
-        <v>167</v>
-      </c>
-      <c r="G176" s="152"/>
-      <c r="H176" s="44"/>
+      <c r="F176" s="107" t="s">
+        <v>168</v>
+      </c>
+      <c r="G176" s="19">
+        <v>1234568064</v>
+      </c>
+      <c r="H176" s="40"/>
       <c r="I176" s="21"/>
-      <c r="J176" s="40"/>
-      <c r="K176" s="40"/>
-      <c r="L176" s="40"/>
-      <c r="M176" s="40"/>
-      <c r="N176" s="40"/>
+      <c r="J176" s="37"/>
+      <c r="K176" s="37"/>
+      <c r="L176" s="37"/>
+      <c r="M176" s="37"/>
+      <c r="N176" s="37"/>
       <c r="O176" s="21"/>
-      <c r="P176" s="40"/>
+      <c r="P176" s="37"/>
       <c r="Q176" s="21"/>
       <c r="R176" s="23"/>
       <c r="S176" s="21"/>
@@ -6854,17 +7010,19 @@
       <c r="D177" s="16">
         <v>312</v>
       </c>
-      <c r="E177" s="57">
+      <c r="E177" s="49">
         <v>1</v>
       </c>
-      <c r="F177" s="128" t="s">
-        <v>168</v>
-      </c>
-      <c r="G177" s="129"/>
-      <c r="H177" s="68"/>
-      <c r="I177" s="34"/>
-      <c r="J177" s="35"/>
-      <c r="K177" s="35"/>
+      <c r="F177" s="96" t="s">
+        <v>169</v>
+      </c>
+      <c r="G177" s="19">
+        <v>1234568065</v>
+      </c>
+      <c r="H177" s="56"/>
+      <c r="I177" s="32"/>
+      <c r="J177" s="33"/>
+      <c r="K177" s="33"/>
       <c r="L177" s="21"/>
       <c r="M177" s="21"/>
       <c r="N177" s="21"/>
@@ -6882,36 +7040,40 @@
       <c r="E178" s="17">
         <v>2</v>
       </c>
-      <c r="F178" s="86" t="s">
-        <v>169</v>
-      </c>
-      <c r="G178" s="153"/>
-      <c r="H178" s="44"/>
-      <c r="I178" s="46"/>
-      <c r="J178" s="47"/>
-      <c r="K178" s="47"/>
-      <c r="L178" s="47"/>
-      <c r="M178" s="47"/>
-      <c r="N178" s="47"/>
+      <c r="F178" s="66" t="s">
+        <v>170</v>
+      </c>
+      <c r="G178" s="19">
+        <v>1234568066</v>
+      </c>
+      <c r="H178" s="40"/>
+      <c r="I178" s="41"/>
+      <c r="J178" s="42"/>
+      <c r="K178" s="42"/>
+      <c r="L178" s="42"/>
+      <c r="M178" s="42"/>
+      <c r="N178" s="42"/>
       <c r="O178" s="21"/>
-      <c r="P178" s="47"/>
-      <c r="Q178" s="47"/>
+      <c r="P178" s="42"/>
+      <c r="Q178" s="42"/>
       <c r="R178" s="23"/>
       <c r="S178" s="21"/>
     </row>
     <row r="179" s="1" customFormat="1" ht="16.35" spans="1:20">
       <c r="A179" s="15"/>
       <c r="B179" s="15"/>
-      <c r="C179" s="154"/>
-      <c r="D179" s="27"/>
-      <c r="E179" s="28">
+      <c r="C179" s="108"/>
+      <c r="D179" s="26"/>
+      <c r="E179" s="27">
         <v>3</v>
       </c>
-      <c r="F179" s="42" t="s">
-        <v>170</v>
-      </c>
-      <c r="G179" s="43"/>
-      <c r="H179" s="68"/>
+      <c r="F179" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="G179" s="19">
+        <v>1234568067</v>
+      </c>
+      <c r="H179" s="56"/>
       <c r="I179" s="20"/>
       <c r="J179" s="21"/>
       <c r="K179" s="21"/>
@@ -6928,26 +7090,28 @@
       <c r="A180" s="15"/>
       <c r="B180" s="15"/>
       <c r="C180" s="15"/>
-      <c r="D180" s="30">
+      <c r="D180" s="29">
         <v>313</v>
       </c>
-      <c r="E180" s="57">
+      <c r="E180" s="49">
         <v>1</v>
       </c>
-      <c r="F180" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="G180" s="43"/>
-      <c r="H180" s="44"/>
-      <c r="I180" s="34"/>
-      <c r="J180" s="35"/>
-      <c r="K180" s="35"/>
-      <c r="L180" s="35"/>
-      <c r="M180" s="35"/>
-      <c r="N180" s="35"/>
+      <c r="F180" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="G180" s="19">
+        <v>1234568068</v>
+      </c>
+      <c r="H180" s="40"/>
+      <c r="I180" s="32"/>
+      <c r="J180" s="33"/>
+      <c r="K180" s="33"/>
+      <c r="L180" s="33"/>
+      <c r="M180" s="33"/>
+      <c r="N180" s="33"/>
       <c r="O180" s="21"/>
-      <c r="P180" s="35"/>
-      <c r="Q180" s="35"/>
+      <c r="P180" s="33"/>
+      <c r="Q180" s="33"/>
       <c r="R180" s="23"/>
       <c r="S180" s="21"/>
     </row>
@@ -6959,13 +7123,15 @@
       <c r="E181" s="17">
         <v>2</v>
       </c>
-      <c r="F181" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G181" s="98"/>
-      <c r="H181" s="99"/>
-      <c r="O181" s="100"/>
-      <c r="P181" s="35"/>
+      <c r="F181" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G181" s="19">
+        <v>1234568069</v>
+      </c>
+      <c r="H181" s="73"/>
+      <c r="O181" s="74"/>
+      <c r="P181" s="33"/>
     </row>
     <row r="182" ht="17.1" spans="1:20">
       <c r="A182" s="15"/>
@@ -6975,13 +7141,15 @@
       <c r="E182" s="17">
         <v>3</v>
       </c>
-      <c r="F182" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G182" s="98"/>
-      <c r="H182" s="99"/>
-      <c r="O182" s="100"/>
-      <c r="P182" s="35"/>
+      <c r="F182" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G182" s="19">
+        <v>1234568070</v>
+      </c>
+      <c r="H182" s="73"/>
+      <c r="O182" s="74"/>
+      <c r="P182" s="33"/>
     </row>
     <row r="183" ht="16.35" spans="1:20">
       <c r="A183" s="15"/>
@@ -6991,11 +7159,13 @@
       <c r="E183" s="17">
         <v>4</v>
       </c>
-      <c r="F183" s="155" t="s">
-        <v>172</v>
-      </c>
-      <c r="G183" s="156"/>
-      <c r="H183" s="155"/>
+      <c r="F183" s="109" t="s">
+        <v>173</v>
+      </c>
+      <c r="G183" s="19">
+        <v>1234568071</v>
+      </c>
+      <c r="H183" s="109"/>
       <c r="I183" s="21"/>
       <c r="J183" s="21"/>
       <c r="K183" s="21"/>
@@ -7003,7 +7173,7 @@
       <c r="M183" s="21"/>
       <c r="N183" s="21"/>
       <c r="O183" s="21"/>
-      <c r="P183" s="35"/>
+      <c r="P183" s="33"/>
       <c r="Q183" s="21"/>
       <c r="R183" s="21"/>
       <c r="S183" s="21"/>
@@ -7016,11 +7186,13 @@
       <c r="E184" s="17">
         <v>5</v>
       </c>
-      <c r="F184" s="155" t="s">
-        <v>173</v>
-      </c>
-      <c r="G184" s="156"/>
-      <c r="H184" s="155"/>
+      <c r="F184" s="109" t="s">
+        <v>174</v>
+      </c>
+      <c r="G184" s="19">
+        <v>1234568072</v>
+      </c>
+      <c r="H184" s="109"/>
       <c r="I184" s="20"/>
       <c r="J184" s="21"/>
       <c r="K184" s="21"/>
@@ -7037,15 +7209,17 @@
       <c r="A185" s="15"/>
       <c r="B185" s="15"/>
       <c r="C185" s="15"/>
-      <c r="D185" s="27"/>
-      <c r="E185" s="28">
+      <c r="D185" s="26"/>
+      <c r="E185" s="27">
         <v>6</v>
       </c>
-      <c r="F185" s="157" t="s">
-        <v>174</v>
-      </c>
-      <c r="G185" s="158"/>
-      <c r="H185" s="155"/>
+      <c r="F185" s="110" t="s">
+        <v>175</v>
+      </c>
+      <c r="G185" s="19">
+        <v>1234568073</v>
+      </c>
+      <c r="H185" s="109"/>
       <c r="I185" s="20"/>
       <c r="J185" s="21"/>
       <c r="K185" s="21"/>
@@ -7062,23 +7236,25 @@
       <c r="A186" s="15"/>
       <c r="B186" s="15"/>
       <c r="C186" s="15"/>
-      <c r="D186" s="30">
+      <c r="D186" s="29">
         <v>314</v>
       </c>
-      <c r="E186" s="57">
+      <c r="E186" s="49">
         <v>1</v>
       </c>
-      <c r="F186" s="128" t="s">
-        <v>175</v>
-      </c>
-      <c r="G186" s="129"/>
-      <c r="H186" s="155"/>
-      <c r="I186" s="34"/>
-      <c r="J186" s="35"/>
-      <c r="K186" s="35"/>
-      <c r="L186" s="35"/>
-      <c r="M186" s="35"/>
-      <c r="N186" s="35"/>
+      <c r="F186" s="96" t="s">
+        <v>176</v>
+      </c>
+      <c r="G186" s="19">
+        <v>1234568074</v>
+      </c>
+      <c r="H186" s="109"/>
+      <c r="I186" s="32"/>
+      <c r="J186" s="33"/>
+      <c r="K186" s="33"/>
+      <c r="L186" s="33"/>
+      <c r="M186" s="33"/>
+      <c r="N186" s="33"/>
       <c r="O186" s="21"/>
       <c r="P186" s="21"/>
       <c r="Q186" s="21"/>
@@ -7094,10 +7270,12 @@
         <v>2</v>
       </c>
       <c r="F187" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="G187" s="26"/>
-      <c r="H187" s="155"/>
+        <v>177</v>
+      </c>
+      <c r="G187" s="19">
+        <v>1234568075</v>
+      </c>
+      <c r="H187" s="109"/>
       <c r="I187" s="20"/>
       <c r="J187" s="21"/>
       <c r="K187" s="21"/>
@@ -7118,11 +7296,13 @@
       <c r="E188" s="17">
         <v>3</v>
       </c>
-      <c r="F188" s="48" t="s">
-        <v>177</v>
-      </c>
-      <c r="G188" s="49"/>
-      <c r="H188" s="155"/>
+      <c r="F188" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="G188" s="19">
+        <v>1234568076</v>
+      </c>
+      <c r="H188" s="109"/>
       <c r="I188" s="20"/>
       <c r="J188" s="21"/>
       <c r="K188" s="21"/>
@@ -7143,11 +7323,13 @@
       <c r="E189" s="17">
         <v>4</v>
       </c>
-      <c r="F189" s="72" t="s">
-        <v>33</v>
-      </c>
-      <c r="G189" s="98"/>
-      <c r="H189" s="99"/>
+      <c r="F189" s="58" t="s">
+        <v>34</v>
+      </c>
+      <c r="G189" s="19">
+        <v>1234568077</v>
+      </c>
+      <c r="H189" s="73"/>
     </row>
     <row r="190" ht="16.35" spans="1:20">
       <c r="A190" s="15"/>
@@ -7157,17 +7339,19 @@
       <c r="E190" s="17">
         <v>5</v>
       </c>
-      <c r="F190" s="48" t="s">
-        <v>178</v>
-      </c>
-      <c r="G190" s="97"/>
-      <c r="H190" s="96"/>
-      <c r="I190" s="34"/>
-      <c r="J190" s="35"/>
-      <c r="K190" s="35"/>
-      <c r="L190" s="35"/>
-      <c r="M190" s="35"/>
-      <c r="N190" s="35"/>
+      <c r="F190" s="43" t="s">
+        <v>179</v>
+      </c>
+      <c r="G190" s="19">
+        <v>1234568078</v>
+      </c>
+      <c r="H190" s="72"/>
+      <c r="I190" s="32"/>
+      <c r="J190" s="33"/>
+      <c r="K190" s="33"/>
+      <c r="L190" s="33"/>
+      <c r="M190" s="33"/>
+      <c r="N190" s="33"/>
       <c r="O190" s="21"/>
       <c r="P190" s="21"/>
       <c r="Q190" s="21"/>
@@ -7178,15 +7362,17 @@
       <c r="A191" s="15"/>
       <c r="B191" s="15"/>
       <c r="C191" s="15"/>
-      <c r="D191" s="27"/>
-      <c r="E191" s="28">
+      <c r="D191" s="26"/>
+      <c r="E191" s="27">
         <v>6</v>
       </c>
-      <c r="F191" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="G191" s="85"/>
-      <c r="H191" s="159"/>
+      <c r="F191" s="60" t="s">
+        <v>180</v>
+      </c>
+      <c r="G191" s="19">
+        <v>1234568079</v>
+      </c>
+      <c r="H191" s="111"/>
       <c r="I191" s="21"/>
       <c r="J191" s="21"/>
       <c r="K191" s="21"/>
@@ -7198,23 +7384,25 @@
       <c r="Q191" s="21"/>
       <c r="R191" s="21"/>
       <c r="S191" s="21"/>
-      <c r="T191" s="160"/>
+      <c r="T191" s="112"/>
     </row>
     <row r="192" ht="16.35" spans="1:20">
       <c r="A192" s="15"/>
       <c r="B192" s="15"/>
       <c r="C192" s="15"/>
-      <c r="D192" s="30">
+      <c r="D192" s="29">
         <v>315</v>
       </c>
-      <c r="E192" s="57">
+      <c r="E192" s="49">
         <v>1</v>
       </c>
-      <c r="F192" s="48" t="s">
-        <v>180</v>
-      </c>
-      <c r="G192" s="49"/>
-      <c r="H192" s="96"/>
+      <c r="F192" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="G192" s="19">
+        <v>1234568080</v>
+      </c>
+      <c r="H192" s="72"/>
       <c r="I192" s="20"/>
       <c r="J192" s="21"/>
       <c r="K192" s="21"/>
@@ -7235,11 +7423,13 @@
       <c r="E193" s="17">
         <v>2</v>
       </c>
-      <c r="F193" s="161" t="s">
-        <v>181</v>
-      </c>
-      <c r="G193" s="162"/>
-      <c r="H193" s="159"/>
+      <c r="F193" s="113" t="s">
+        <v>182</v>
+      </c>
+      <c r="G193" s="19">
+        <v>1234568081</v>
+      </c>
+      <c r="H193" s="111"/>
       <c r="I193" s="20"/>
       <c r="J193" s="21"/>
       <c r="K193" s="21"/>
@@ -7260,11 +7450,13 @@
       <c r="E194" s="17">
         <v>3</v>
       </c>
-      <c r="F194" s="161" t="s">
-        <v>182</v>
-      </c>
-      <c r="G194" s="162"/>
-      <c r="H194" s="96"/>
+      <c r="F194" s="113" t="s">
+        <v>183</v>
+      </c>
+      <c r="G194" s="19">
+        <v>1234568082</v>
+      </c>
+      <c r="H194" s="72"/>
       <c r="I194" s="20"/>
       <c r="J194" s="21"/>
       <c r="K194" s="21"/>
@@ -7285,11 +7477,13 @@
       <c r="E195" s="17">
         <v>4</v>
       </c>
-      <c r="F195" s="161" t="s">
-        <v>183</v>
-      </c>
-      <c r="G195" s="162"/>
-      <c r="H195" s="159"/>
+      <c r="F195" s="113" t="s">
+        <v>184</v>
+      </c>
+      <c r="G195" s="19">
+        <v>1234568083</v>
+      </c>
+      <c r="H195" s="111"/>
       <c r="I195" s="20"/>
       <c r="J195" s="21"/>
       <c r="K195" s="21"/>
@@ -7310,11 +7504,13 @@
       <c r="E196" s="17">
         <v>5</v>
       </c>
-      <c r="F196" s="161" t="s">
-        <v>184</v>
-      </c>
-      <c r="G196" s="162"/>
-      <c r="H196" s="96"/>
+      <c r="F196" s="113" t="s">
+        <v>185</v>
+      </c>
+      <c r="G196" s="19">
+        <v>1234568084</v>
+      </c>
+      <c r="H196" s="72"/>
       <c r="I196" s="20"/>
       <c r="J196" s="21"/>
       <c r="K196" s="21"/>
@@ -7331,23 +7527,25 @@
       <c r="A197" s="15"/>
       <c r="B197" s="15"/>
       <c r="C197" s="15"/>
-      <c r="D197" s="27"/>
-      <c r="E197" s="28">
+      <c r="D197" s="26"/>
+      <c r="E197" s="27">
         <v>6</v>
       </c>
-      <c r="F197" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="G197" s="45"/>
-      <c r="H197" s="159"/>
-      <c r="I197" s="39"/>
-      <c r="J197" s="40"/>
-      <c r="K197" s="40"/>
-      <c r="L197" s="40"/>
-      <c r="M197" s="40"/>
-      <c r="N197" s="40"/>
+      <c r="F197" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="G197" s="19">
+        <v>1234568085</v>
+      </c>
+      <c r="H197" s="111"/>
+      <c r="I197" s="36"/>
+      <c r="J197" s="37"/>
+      <c r="K197" s="37"/>
+      <c r="L197" s="37"/>
+      <c r="M197" s="37"/>
+      <c r="N197" s="37"/>
       <c r="O197" s="21"/>
-      <c r="P197" s="40"/>
+      <c r="P197" s="37"/>
       <c r="Q197" s="21"/>
       <c r="R197" s="23"/>
       <c r="S197" s="21"/>
@@ -7356,25 +7554,27 @@
       <c r="A198" s="15"/>
       <c r="B198" s="15"/>
       <c r="C198" s="15"/>
-      <c r="D198" s="30">
+      <c r="D198" s="29">
         <v>316</v>
       </c>
-      <c r="E198" s="57">
+      <c r="E198" s="49">
         <v>1</v>
       </c>
-      <c r="F198" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="G198" s="97"/>
-      <c r="H198" s="96"/>
-      <c r="I198" s="34"/>
-      <c r="J198" s="35"/>
-      <c r="K198" s="35"/>
-      <c r="L198" s="52"/>
-      <c r="M198" s="35"/>
-      <c r="N198" s="35"/>
+      <c r="F198" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="G198" s="19">
+        <v>1234568086</v>
+      </c>
+      <c r="H198" s="72"/>
+      <c r="I198" s="32"/>
+      <c r="J198" s="33"/>
+      <c r="K198" s="33"/>
+      <c r="L198" s="46"/>
+      <c r="M198" s="33"/>
+      <c r="N198" s="33"/>
       <c r="O198" s="21"/>
-      <c r="P198" s="40"/>
+      <c r="P198" s="37"/>
       <c r="Q198" s="21"/>
       <c r="R198" s="23"/>
       <c r="S198" s="21"/>
@@ -7387,11 +7587,13 @@
       <c r="E199" s="17">
         <v>2</v>
       </c>
-      <c r="F199" s="48" t="s">
-        <v>187</v>
-      </c>
-      <c r="G199" s="49"/>
-      <c r="H199" s="159"/>
+      <c r="F199" s="43" t="s">
+        <v>188</v>
+      </c>
+      <c r="G199" s="19">
+        <v>1234568087</v>
+      </c>
+      <c r="H199" s="111"/>
       <c r="I199" s="20"/>
       <c r="J199" s="21"/>
       <c r="K199" s="21"/>
@@ -7412,11 +7614,13 @@
       <c r="E200" s="17">
         <v>3</v>
       </c>
-      <c r="F200" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="G200" s="43"/>
-      <c r="H200" s="96"/>
+      <c r="F200" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="G200" s="19">
+        <v>1234568088</v>
+      </c>
+      <c r="H200" s="72"/>
       <c r="I200" s="20"/>
       <c r="J200" s="21"/>
       <c r="K200" s="21"/>
@@ -7438,10 +7642,12 @@
         <v>4</v>
       </c>
       <c r="F201" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="G201" s="26"/>
-      <c r="H201" s="159"/>
+        <v>190</v>
+      </c>
+      <c r="G201" s="19">
+        <v>1234568089</v>
+      </c>
+      <c r="H201" s="111"/>
       <c r="I201" s="20"/>
       <c r="J201" s="21"/>
       <c r="K201" s="21"/>
@@ -7462,11 +7668,13 @@
       <c r="E202" s="17">
         <v>5</v>
       </c>
-      <c r="F202" s="48" t="s">
-        <v>190</v>
-      </c>
-      <c r="G202" s="49"/>
-      <c r="H202" s="96"/>
+      <c r="F202" s="43" t="s">
+        <v>191</v>
+      </c>
+      <c r="G202" s="19">
+        <v>1234568090</v>
+      </c>
+      <c r="H202" s="72"/>
       <c r="I202" s="21"/>
       <c r="J202" s="21"/>
       <c r="K202" s="21"/>
@@ -7483,612 +7691,614 @@
       <c r="A203" s="15"/>
       <c r="B203" s="15"/>
       <c r="C203" s="15"/>
-      <c r="D203" s="27"/>
-      <c r="E203" s="28">
+      <c r="D203" s="26"/>
+      <c r="E203" s="27">
         <v>6</v>
       </c>
-      <c r="F203" s="90" t="s">
-        <v>191</v>
-      </c>
-      <c r="G203" s="114"/>
-      <c r="H203" s="159"/>
-      <c r="I203" s="163"/>
-      <c r="J203" s="164"/>
-      <c r="K203" s="164"/>
-      <c r="L203" s="164"/>
-      <c r="M203" s="164"/>
-      <c r="N203" s="164"/>
-      <c r="O203" s="35"/>
-      <c r="P203" s="35"/>
-      <c r="Q203" s="35"/>
-      <c r="R203" s="36"/>
-      <c r="S203" s="35"/>
+      <c r="F203" s="69" t="s">
+        <v>192</v>
+      </c>
+      <c r="G203" s="19">
+        <v>1234568091</v>
+      </c>
+      <c r="H203" s="111"/>
+      <c r="I203" s="114"/>
+      <c r="J203" s="115"/>
+      <c r="K203" s="115"/>
+      <c r="L203" s="115"/>
+      <c r="M203" s="115"/>
+      <c r="N203" s="115"/>
+      <c r="O203" s="33"/>
+      <c r="P203" s="33"/>
+      <c r="Q203" s="33"/>
+      <c r="R203" s="34"/>
+      <c r="S203" s="33"/>
     </row>
     <row r="204" ht="16.35" spans="1:19">
-      <c r="D204" s="165"/>
-      <c r="E204" s="86"/>
+      <c r="D204" s="116"/>
+      <c r="E204" s="66"/>
     </row>
     <row r="205" spans="1:19">
-      <c r="D205" s="166"/>
-      <c r="E205" s="167"/>
+      <c r="D205" s="117"/>
+      <c r="E205" s="118"/>
     </row>
     <row r="206" spans="1:19">
-      <c r="D206" s="168"/>
+      <c r="D206" s="119"/>
       <c r="E206" s="23"/>
     </row>
     <row r="207" spans="1:19">
-      <c r="D207" s="169"/>
-      <c r="E207" s="168"/>
+      <c r="D207" s="120"/>
+      <c r="E207" s="119"/>
       <c r="F207" s="23"/>
     </row>
     <row r="208" spans="1:19">
-      <c r="D208" s="170"/>
-      <c r="E208" s="168"/>
+      <c r="D208" s="121"/>
+      <c r="E208" s="119"/>
       <c r="F208" s="23"/>
     </row>
     <row r="209" spans="4:6">
-      <c r="D209" s="170"/>
-      <c r="E209" s="168"/>
+      <c r="D209" s="121"/>
+      <c r="E209" s="119"/>
       <c r="F209" s="23"/>
     </row>
     <row r="210" spans="4:6">
-      <c r="D210" s="171"/>
-      <c r="E210" s="168"/>
+      <c r="D210" s="122"/>
+      <c r="E210" s="119"/>
       <c r="F210" s="23"/>
     </row>
     <row r="211" spans="4:6">
-      <c r="D211" s="169"/>
-      <c r="E211" s="168"/>
+      <c r="D211" s="120"/>
+      <c r="E211" s="119"/>
       <c r="F211" s="23"/>
     </row>
     <row r="212" spans="4:6">
-      <c r="D212" s="170"/>
-      <c r="E212" s="168"/>
+      <c r="D212" s="121"/>
+      <c r="E212" s="119"/>
       <c r="F212" s="23"/>
     </row>
     <row r="213" spans="4:6">
-      <c r="D213" s="170"/>
-      <c r="E213" s="168"/>
+      <c r="D213" s="121"/>
+      <c r="E213" s="119"/>
       <c r="F213" s="23"/>
     </row>
     <row r="214" spans="4:6">
-      <c r="D214" s="171"/>
-      <c r="E214" s="168"/>
+      <c r="D214" s="122"/>
+      <c r="E214" s="119"/>
       <c r="F214" s="23"/>
     </row>
     <row r="215" spans="4:6">
-      <c r="D215" s="169"/>
-      <c r="E215" s="168"/>
+      <c r="D215" s="120"/>
+      <c r="E215" s="119"/>
       <c r="F215" s="23"/>
     </row>
     <row r="216" spans="4:6">
-      <c r="D216" s="170"/>
-      <c r="E216" s="168"/>
+      <c r="D216" s="121"/>
+      <c r="E216" s="119"/>
       <c r="F216" s="23"/>
     </row>
     <row r="217" spans="4:6">
-      <c r="D217" s="170"/>
-      <c r="E217" s="168"/>
+      <c r="D217" s="121"/>
+      <c r="E217" s="119"/>
       <c r="F217" s="23"/>
     </row>
     <row r="218" spans="4:6">
-      <c r="D218" s="171"/>
-      <c r="E218" s="168"/>
+      <c r="D218" s="122"/>
+      <c r="E218" s="119"/>
       <c r="F218" s="23"/>
     </row>
     <row r="219" spans="4:6">
-      <c r="D219" s="169"/>
-      <c r="E219" s="168"/>
+      <c r="D219" s="120"/>
+      <c r="E219" s="119"/>
       <c r="F219" s="23"/>
     </row>
     <row r="220" spans="4:6">
-      <c r="D220" s="170"/>
-      <c r="E220" s="168"/>
+      <c r="D220" s="121"/>
+      <c r="E220" s="119"/>
       <c r="F220" s="23"/>
     </row>
     <row r="221" spans="4:6">
-      <c r="D221" s="170"/>
-      <c r="E221" s="168"/>
+      <c r="D221" s="121"/>
+      <c r="E221" s="119"/>
       <c r="F221" s="23"/>
     </row>
     <row r="222" spans="4:6">
-      <c r="D222" s="171"/>
-      <c r="E222" s="168"/>
+      <c r="D222" s="122"/>
+      <c r="E222" s="119"/>
       <c r="F222" s="23"/>
     </row>
     <row r="223" spans="4:6">
-      <c r="D223" s="169"/>
-      <c r="E223" s="168"/>
+      <c r="D223" s="120"/>
+      <c r="E223" s="119"/>
       <c r="F223" s="23"/>
     </row>
     <row r="224" spans="4:6">
-      <c r="D224" s="170"/>
-      <c r="E224" s="168"/>
+      <c r="D224" s="121"/>
+      <c r="E224" s="119"/>
       <c r="F224" s="23"/>
     </row>
     <row r="225" spans="4:6">
-      <c r="D225" s="170"/>
-      <c r="E225" s="168"/>
+      <c r="D225" s="121"/>
+      <c r="E225" s="119"/>
       <c r="F225" s="23"/>
     </row>
     <row r="226" spans="4:6">
-      <c r="D226" s="171"/>
-      <c r="E226" s="168"/>
+      <c r="D226" s="122"/>
+      <c r="E226" s="119"/>
       <c r="F226" s="23"/>
     </row>
     <row r="227" ht="16.35" spans="4:6">
-      <c r="D227" s="169"/>
-      <c r="E227" s="168"/>
-      <c r="F227" s="37"/>
+      <c r="D227" s="120"/>
+      <c r="E227" s="119"/>
+      <c r="F227" s="35"/>
     </row>
     <row r="228" ht="16.35" spans="4:6">
-      <c r="D228" s="170"/>
-      <c r="E228" s="168"/>
+      <c r="D228" s="121"/>
+      <c r="E228" s="119"/>
       <c r="F228" s="23"/>
     </row>
     <row r="229" spans="4:6">
-      <c r="D229" s="170"/>
-      <c r="E229" s="168"/>
+      <c r="D229" s="121"/>
+      <c r="E229" s="119"/>
       <c r="F229" s="23"/>
     </row>
     <row r="230" spans="4:6">
-      <c r="D230" s="171"/>
-      <c r="E230" s="168"/>
+      <c r="D230" s="122"/>
+      <c r="E230" s="119"/>
       <c r="F230" s="23"/>
     </row>
     <row r="231" spans="4:6">
-      <c r="D231" s="169"/>
-      <c r="E231" s="168"/>
+      <c r="D231" s="120"/>
+      <c r="E231" s="119"/>
       <c r="F231" s="23"/>
     </row>
     <row r="232" spans="4:6">
-      <c r="D232" s="170"/>
-      <c r="E232" s="168"/>
+      <c r="D232" s="121"/>
+      <c r="E232" s="119"/>
       <c r="F232" s="23"/>
     </row>
     <row r="233" spans="4:6">
-      <c r="D233" s="170"/>
-      <c r="E233" s="168"/>
+      <c r="D233" s="121"/>
+      <c r="E233" s="119"/>
       <c r="F233" s="23"/>
     </row>
     <row r="234" spans="4:6">
-      <c r="D234" s="171"/>
-      <c r="E234" s="168"/>
+      <c r="D234" s="122"/>
+      <c r="E234" s="119"/>
       <c r="F234" s="23"/>
     </row>
     <row r="235" spans="4:6">
-      <c r="D235" s="169"/>
-      <c r="E235" s="168"/>
+      <c r="D235" s="120"/>
+      <c r="E235" s="119"/>
       <c r="F235" s="23"/>
     </row>
     <row r="236" spans="4:6">
-      <c r="D236" s="170"/>
-      <c r="E236" s="168"/>
+      <c r="D236" s="121"/>
+      <c r="E236" s="119"/>
       <c r="F236" s="23"/>
     </row>
     <row r="237" spans="4:6">
-      <c r="D237" s="170"/>
-      <c r="E237" s="168"/>
+      <c r="D237" s="121"/>
+      <c r="E237" s="119"/>
       <c r="F237" s="23"/>
     </row>
     <row r="238" spans="4:6">
-      <c r="D238" s="171"/>
-      <c r="E238" s="168"/>
+      <c r="D238" s="122"/>
+      <c r="E238" s="119"/>
       <c r="F238" s="23"/>
     </row>
     <row r="239" spans="4:6">
-      <c r="D239" s="169"/>
-      <c r="E239" s="168"/>
+      <c r="D239" s="120"/>
+      <c r="E239" s="119"/>
       <c r="F239" s="23"/>
     </row>
     <row r="240" spans="4:6">
-      <c r="D240" s="170"/>
-      <c r="E240" s="168"/>
+      <c r="D240" s="121"/>
+      <c r="E240" s="119"/>
       <c r="F240" s="23"/>
     </row>
     <row r="241" spans="4:6">
-      <c r="D241" s="170"/>
-      <c r="E241" s="168"/>
+      <c r="D241" s="121"/>
+      <c r="E241" s="119"/>
       <c r="F241" s="23"/>
     </row>
     <row r="242" spans="4:6">
-      <c r="D242" s="171"/>
-      <c r="E242" s="168"/>
+      <c r="D242" s="122"/>
+      <c r="E242" s="119"/>
       <c r="F242" s="23"/>
     </row>
     <row r="243" spans="4:6">
-      <c r="D243" s="169"/>
-      <c r="E243" s="168"/>
+      <c r="D243" s="120"/>
+      <c r="E243" s="119"/>
       <c r="F243" s="23"/>
     </row>
     <row r="244" spans="4:6">
-      <c r="D244" s="170"/>
-      <c r="E244" s="168"/>
-      <c r="F244" s="172"/>
+      <c r="D244" s="121"/>
+      <c r="E244" s="119"/>
+      <c r="F244" s="123"/>
     </row>
     <row r="245" spans="4:6">
-      <c r="D245" s="171"/>
-      <c r="E245" s="168"/>
+      <c r="D245" s="122"/>
+      <c r="E245" s="119"/>
       <c r="F245" s="23"/>
     </row>
     <row r="246" spans="4:6">
-      <c r="D246" s="169"/>
-      <c r="E246" s="168"/>
+      <c r="D246" s="120"/>
+      <c r="E246" s="119"/>
       <c r="F246" s="18"/>
     </row>
     <row r="247" spans="4:6">
-      <c r="D247" s="170"/>
-      <c r="E247" s="173"/>
+      <c r="D247" s="121"/>
+      <c r="E247" s="124"/>
       <c r="F247" s="18"/>
     </row>
     <row r="248" spans="4:6">
-      <c r="D248" s="170"/>
-      <c r="E248" s="168"/>
+      <c r="D248" s="121"/>
+      <c r="E248" s="119"/>
       <c r="F248" s="18"/>
     </row>
     <row r="249" spans="4:6">
-      <c r="D249" s="171"/>
-      <c r="E249" s="173"/>
-      <c r="F249" s="74"/>
+      <c r="D249" s="122"/>
+      <c r="E249" s="124"/>
+      <c r="F249" s="60"/>
     </row>
     <row r="250" spans="4:6">
-      <c r="D250" s="169"/>
-      <c r="E250" s="168"/>
+      <c r="D250" s="120"/>
+      <c r="E250" s="119"/>
       <c r="F250" s="18"/>
     </row>
     <row r="251" spans="4:6">
-      <c r="D251" s="170"/>
-      <c r="E251" s="168"/>
+      <c r="D251" s="121"/>
+      <c r="E251" s="119"/>
       <c r="F251" s="18"/>
     </row>
     <row r="252" spans="4:6">
-      <c r="D252" s="170"/>
-      <c r="E252" s="168"/>
+      <c r="D252" s="121"/>
+      <c r="E252" s="119"/>
       <c r="F252" s="18"/>
     </row>
     <row r="253" spans="4:6">
-      <c r="D253" s="171"/>
-      <c r="E253" s="168"/>
+      <c r="D253" s="122"/>
+      <c r="E253" s="119"/>
       <c r="F253" s="23"/>
     </row>
     <row r="254" spans="4:6">
-      <c r="D254" s="169"/>
-      <c r="E254" s="168"/>
+      <c r="D254" s="120"/>
+      <c r="E254" s="119"/>
       <c r="F254" s="18"/>
     </row>
     <row r="255" spans="4:6">
-      <c r="D255" s="170"/>
-      <c r="E255" s="168"/>
+      <c r="D255" s="121"/>
+      <c r="E255" s="119"/>
       <c r="F255" s="18"/>
     </row>
     <row r="256" spans="4:6">
-      <c r="D256" s="170"/>
-      <c r="E256" s="168"/>
+      <c r="D256" s="121"/>
+      <c r="E256" s="119"/>
       <c r="F256" s="18"/>
     </row>
     <row r="257" spans="4:6">
-      <c r="D257" s="171"/>
-      <c r="E257" s="168"/>
+      <c r="D257" s="122"/>
+      <c r="E257" s="119"/>
       <c r="F257" s="23"/>
     </row>
     <row r="258" spans="4:6">
-      <c r="D258" s="169"/>
-      <c r="E258" s="168"/>
+      <c r="D258" s="120"/>
+      <c r="E258" s="119"/>
       <c r="F258" s="18"/>
     </row>
     <row r="259" spans="4:6">
-      <c r="D259" s="170"/>
-      <c r="E259" s="168"/>
+      <c r="D259" s="121"/>
+      <c r="E259" s="119"/>
       <c r="F259" s="18"/>
     </row>
     <row r="260" spans="4:6">
-      <c r="D260" s="170"/>
-      <c r="E260" s="168"/>
+      <c r="D260" s="121"/>
+      <c r="E260" s="119"/>
       <c r="F260" s="18"/>
     </row>
     <row r="261" spans="4:6">
-      <c r="D261" s="171"/>
-      <c r="E261" s="168"/>
+      <c r="D261" s="122"/>
+      <c r="E261" s="119"/>
       <c r="F261" s="23"/>
     </row>
     <row r="262" spans="4:6">
-      <c r="D262" s="169"/>
-      <c r="E262" s="168"/>
+      <c r="D262" s="120"/>
+      <c r="E262" s="119"/>
       <c r="F262" s="23"/>
     </row>
     <row r="263" spans="4:6">
-      <c r="D263" s="170"/>
-      <c r="E263" s="168"/>
+      <c r="D263" s="121"/>
+      <c r="E263" s="119"/>
       <c r="F263" s="18"/>
     </row>
     <row r="264" spans="4:6">
-      <c r="D264" s="170"/>
-      <c r="E264" s="168"/>
+      <c r="D264" s="121"/>
+      <c r="E264" s="119"/>
       <c r="F264" s="18"/>
     </row>
     <row r="265" spans="4:6">
-      <c r="D265" s="171"/>
-      <c r="E265" s="168"/>
+      <c r="D265" s="122"/>
+      <c r="E265" s="119"/>
       <c r="F265" s="23"/>
     </row>
     <row r="266" spans="4:6">
-      <c r="D266" s="169"/>
-      <c r="E266" s="168"/>
+      <c r="D266" s="120"/>
+      <c r="E266" s="119"/>
       <c r="F266" s="18"/>
     </row>
     <row r="267" spans="4:6">
-      <c r="D267" s="170"/>
-      <c r="E267" s="168"/>
+      <c r="D267" s="121"/>
+      <c r="E267" s="119"/>
       <c r="F267" s="18"/>
     </row>
     <row r="268" spans="4:6">
-      <c r="D268" s="170"/>
-      <c r="E268" s="168"/>
+      <c r="D268" s="121"/>
+      <c r="E268" s="119"/>
       <c r="F268" s="18"/>
     </row>
     <row r="269" spans="4:6">
-      <c r="D269" s="171"/>
-      <c r="E269" s="168"/>
+      <c r="D269" s="122"/>
+      <c r="E269" s="119"/>
       <c r="F269" s="23"/>
     </row>
     <row r="270" spans="4:6">
-      <c r="D270" s="169"/>
-      <c r="E270" s="168"/>
+      <c r="D270" s="120"/>
+      <c r="E270" s="119"/>
       <c r="F270" s="18"/>
     </row>
     <row r="271" spans="4:6">
-      <c r="D271" s="170"/>
-      <c r="E271" s="168"/>
-      <c r="F271" s="44"/>
+      <c r="D271" s="121"/>
+      <c r="E271" s="119"/>
+      <c r="F271" s="40"/>
     </row>
     <row r="272" spans="4:6">
-      <c r="D272" s="170"/>
-      <c r="E272" s="168"/>
+      <c r="D272" s="121"/>
+      <c r="E272" s="119"/>
       <c r="F272" s="18"/>
     </row>
     <row r="273" spans="4:6">
-      <c r="D273" s="171"/>
-      <c r="E273" s="168"/>
+      <c r="D273" s="122"/>
+      <c r="E273" s="119"/>
       <c r="F273" s="23"/>
     </row>
     <row r="274" ht="16.35" spans="4:6">
-      <c r="D274" s="169"/>
-      <c r="E274" s="168"/>
-      <c r="F274" s="72"/>
+      <c r="D274" s="120"/>
+      <c r="E274" s="119"/>
+      <c r="F274" s="58"/>
     </row>
     <row r="275" ht="16.35" spans="4:6">
-      <c r="D275" s="170"/>
-      <c r="E275" s="168"/>
+      <c r="D275" s="121"/>
+      <c r="E275" s="119"/>
       <c r="F275" s="18"/>
     </row>
     <row r="276" spans="4:6">
-      <c r="D276" s="170"/>
-      <c r="E276" s="168"/>
+      <c r="D276" s="121"/>
+      <c r="E276" s="119"/>
       <c r="F276" s="18"/>
     </row>
     <row r="277" spans="4:6">
-      <c r="D277" s="171"/>
-      <c r="E277" s="168"/>
+      <c r="D277" s="122"/>
+      <c r="E277" s="119"/>
       <c r="F277" s="23"/>
     </row>
     <row r="278" spans="4:6">
-      <c r="D278" s="169"/>
-      <c r="E278" s="168"/>
+      <c r="D278" s="120"/>
+      <c r="E278" s="119"/>
       <c r="F278" s="23"/>
     </row>
     <row r="279" spans="4:6">
-      <c r="D279" s="170"/>
-      <c r="E279" s="168"/>
+      <c r="D279" s="121"/>
+      <c r="E279" s="119"/>
       <c r="F279" s="18"/>
     </row>
     <row r="280" spans="4:6">
-      <c r="D280" s="170"/>
-      <c r="E280" s="168"/>
+      <c r="D280" s="121"/>
+      <c r="E280" s="119"/>
       <c r="F280" s="18"/>
     </row>
     <row r="281" spans="4:6">
-      <c r="D281" s="171"/>
-      <c r="E281" s="168"/>
+      <c r="D281" s="122"/>
+      <c r="E281" s="119"/>
       <c r="F281" s="23"/>
     </row>
     <row r="282" ht="16.35" spans="4:6">
-      <c r="D282" s="169"/>
-      <c r="E282" s="168"/>
-      <c r="F282" s="37"/>
+      <c r="D282" s="120"/>
+      <c r="E282" s="119"/>
+      <c r="F282" s="35"/>
     </row>
     <row r="283" ht="17.1" spans="4:6">
-      <c r="D283" s="170"/>
-      <c r="E283" s="168"/>
-      <c r="F283" s="37"/>
+      <c r="D283" s="121"/>
+      <c r="E283" s="119"/>
+      <c r="F283" s="35"/>
     </row>
     <row r="284" ht="16.35" spans="4:6">
-      <c r="D284" s="171"/>
-      <c r="E284" s="168"/>
-      <c r="F284" s="48"/>
+      <c r="D284" s="122"/>
+      <c r="E284" s="119"/>
+      <c r="F284" s="43"/>
     </row>
     <row r="285" ht="16.35" spans="4:6">
-      <c r="D285" s="169"/>
-      <c r="E285" s="168"/>
-      <c r="F285" s="37"/>
+      <c r="D285" s="120"/>
+      <c r="E285" s="119"/>
+      <c r="F285" s="35"/>
     </row>
     <row r="286" ht="17.1" spans="4:6">
-      <c r="D286" s="170"/>
-      <c r="E286" s="168"/>
-      <c r="F286" s="37"/>
+      <c r="D286" s="121"/>
+      <c r="E286" s="119"/>
+      <c r="F286" s="35"/>
     </row>
     <row r="287" ht="16.35" spans="4:6">
-      <c r="D287" s="170"/>
-      <c r="E287" s="168"/>
-      <c r="F287" s="174"/>
+      <c r="D287" s="121"/>
+      <c r="E287" s="119"/>
+      <c r="F287" s="125"/>
     </row>
     <row r="288" spans="4:6">
-      <c r="D288" s="171"/>
-      <c r="E288" s="168"/>
+      <c r="D288" s="122"/>
+      <c r="E288" s="119"/>
       <c r="F288" s="18"/>
     </row>
     <row r="289" ht="16.35" spans="4:6">
-      <c r="D289" s="169"/>
-      <c r="E289" s="168"/>
-      <c r="F289" s="37"/>
+      <c r="D289" s="120"/>
+      <c r="E289" s="119"/>
+      <c r="F289" s="35"/>
     </row>
     <row r="290" ht="16.35" spans="4:6">
-      <c r="D290" s="170"/>
-      <c r="E290" s="92"/>
-      <c r="F290" s="44"/>
+      <c r="D290" s="121"/>
+      <c r="E290" s="70"/>
+      <c r="F290" s="40"/>
     </row>
     <row r="291" spans="4:6">
-      <c r="D291" s="170"/>
-      <c r="E291" s="168"/>
-      <c r="F291" s="48"/>
+      <c r="D291" s="121"/>
+      <c r="E291" s="119"/>
+      <c r="F291" s="43"/>
     </row>
     <row r="292" spans="4:6">
-      <c r="D292" s="171"/>
-      <c r="E292" s="168"/>
-      <c r="F292" s="74"/>
+      <c r="D292" s="122"/>
+      <c r="E292" s="119"/>
+      <c r="F292" s="60"/>
     </row>
     <row r="293" ht="16.35" spans="4:6">
-      <c r="D293" s="169"/>
-      <c r="E293" s="168"/>
-      <c r="F293" s="72"/>
+      <c r="D293" s="120"/>
+      <c r="E293" s="119"/>
+      <c r="F293" s="58"/>
     </row>
     <row r="294" ht="16.35" spans="4:6">
-      <c r="D294" s="170"/>
-      <c r="E294" s="168"/>
+      <c r="D294" s="121"/>
+      <c r="E294" s="119"/>
       <c r="F294" s="23"/>
     </row>
     <row r="295" spans="4:6">
-      <c r="D295" s="170"/>
-      <c r="E295" s="168"/>
+      <c r="D295" s="121"/>
+      <c r="E295" s="119"/>
       <c r="F295" s="23"/>
     </row>
     <row r="296" spans="4:6">
-      <c r="D296" s="171"/>
-      <c r="E296" s="168"/>
+      <c r="D296" s="122"/>
+      <c r="E296" s="119"/>
       <c r="F296" s="23"/>
     </row>
     <row r="297" spans="4:6">
-      <c r="D297" s="169"/>
-      <c r="E297" s="168"/>
-      <c r="F297" s="92"/>
+      <c r="D297" s="120"/>
+      <c r="E297" s="119"/>
+      <c r="F297" s="70"/>
     </row>
     <row r="298" spans="4:6">
-      <c r="D298" s="170"/>
-      <c r="E298" s="168"/>
+      <c r="D298" s="121"/>
+      <c r="E298" s="119"/>
       <c r="F298" s="23"/>
     </row>
     <row r="299" ht="16.35" spans="4:6">
-      <c r="D299" s="170"/>
-      <c r="E299" s="168"/>
-      <c r="F299" s="37"/>
+      <c r="D299" s="121"/>
+      <c r="E299" s="119"/>
+      <c r="F299" s="35"/>
     </row>
     <row r="300" ht="17.1" spans="4:6">
-      <c r="D300" s="171"/>
-      <c r="E300" s="168"/>
-      <c r="F300" s="37"/>
+      <c r="D300" s="122"/>
+      <c r="E300" s="119"/>
+      <c r="F300" s="35"/>
     </row>
     <row r="301" ht="17.1" spans="4:6">
-      <c r="D301" s="169"/>
-      <c r="E301" s="168"/>
-      <c r="F301" s="72"/>
+      <c r="D301" s="120"/>
+      <c r="E301" s="119"/>
+      <c r="F301" s="58"/>
     </row>
     <row r="302" ht="16.35" spans="4:6">
-      <c r="D302" s="170"/>
-      <c r="E302" s="168"/>
+      <c r="D302" s="121"/>
+      <c r="E302" s="119"/>
       <c r="F302" s="23"/>
     </row>
     <row r="303" spans="4:6">
-      <c r="D303" s="170"/>
-      <c r="E303" s="168"/>
+      <c r="D303" s="121"/>
+      <c r="E303" s="119"/>
       <c r="F303" s="23"/>
     </row>
     <row r="304" spans="4:6">
-      <c r="D304" s="171"/>
-      <c r="E304" s="168"/>
+      <c r="D304" s="122"/>
+      <c r="E304" s="119"/>
       <c r="F304" s="23"/>
     </row>
     <row r="305" spans="4:6">
-      <c r="D305" s="169"/>
-      <c r="E305" s="168"/>
+      <c r="D305" s="120"/>
+      <c r="E305" s="119"/>
       <c r="F305" s="18"/>
     </row>
     <row r="306" ht="16.35" spans="4:6">
-      <c r="D306" s="170"/>
-      <c r="E306" s="168"/>
-      <c r="F306" s="37"/>
+      <c r="D306" s="121"/>
+      <c r="E306" s="119"/>
+      <c r="F306" s="35"/>
     </row>
     <row r="307" ht="16.35" spans="4:6">
-      <c r="D307" s="170"/>
-      <c r="E307" s="168"/>
+      <c r="D307" s="121"/>
+      <c r="E307" s="119"/>
       <c r="F307" s="23"/>
     </row>
     <row r="308" spans="4:6">
-      <c r="D308" s="171"/>
-      <c r="E308" s="168"/>
+      <c r="D308" s="122"/>
+      <c r="E308" s="119"/>
       <c r="F308" s="23"/>
     </row>
     <row r="309" spans="4:6">
-      <c r="D309" s="169"/>
-      <c r="E309" s="168"/>
+      <c r="D309" s="120"/>
+      <c r="E309" s="119"/>
       <c r="F309" s="23"/>
     </row>
     <row r="310" spans="4:6">
-      <c r="D310" s="170"/>
-      <c r="E310" s="168"/>
+      <c r="D310" s="121"/>
+      <c r="E310" s="119"/>
       <c r="F310" s="23"/>
     </row>
     <row r="311" spans="4:6">
-      <c r="D311" s="170"/>
-      <c r="E311" s="168"/>
+      <c r="D311" s="121"/>
+      <c r="E311" s="119"/>
       <c r="F311" s="23"/>
     </row>
     <row r="312" spans="4:6">
-      <c r="D312" s="171"/>
-      <c r="E312" s="168"/>
+      <c r="D312" s="122"/>
+      <c r="E312" s="119"/>
       <c r="F312" s="18"/>
     </row>
     <row r="313" spans="4:6">
-      <c r="D313" s="169"/>
-      <c r="E313" s="168"/>
-      <c r="F313" s="175"/>
+      <c r="D313" s="120"/>
+      <c r="E313" s="119"/>
+      <c r="F313" s="126"/>
     </row>
     <row r="314" spans="4:6">
-      <c r="D314" s="170"/>
-      <c r="E314" s="168"/>
-      <c r="F314" s="48"/>
+      <c r="D314" s="121"/>
+      <c r="E314" s="119"/>
+      <c r="F314" s="43"/>
     </row>
     <row r="315" spans="4:6">
-      <c r="D315" s="170"/>
-      <c r="E315" s="168"/>
+      <c r="D315" s="121"/>
+      <c r="E315" s="119"/>
       <c r="F315" s="18"/>
     </row>
     <row r="316" spans="4:6">
-      <c r="D316" s="171"/>
-      <c r="E316" s="168"/>
+      <c r="D316" s="122"/>
+      <c r="E316" s="119"/>
       <c r="F316" s="23"/>
     </row>
     <row r="317" spans="4:6">
-      <c r="D317" s="169"/>
-      <c r="E317" s="168"/>
+      <c r="D317" s="120"/>
+      <c r="E317" s="119"/>
       <c r="F317" s="23"/>
     </row>
     <row r="318" spans="4:6">
-      <c r="D318" s="170"/>
-      <c r="E318" s="168"/>
+      <c r="D318" s="121"/>
+      <c r="E318" s="119"/>
       <c r="F318" s="23"/>
     </row>
     <row r="319" spans="4:6">
-      <c r="D319" s="170"/>
-      <c r="E319" s="168"/>
+      <c r="D319" s="121"/>
+      <c r="E319" s="119"/>
       <c r="F319" s="23"/>
     </row>
     <row r="320" spans="4:6">
-      <c r="D320" s="171"/>
-      <c r="E320" s="168"/>
-      <c r="F320" s="74"/>
+      <c r="D320" s="122"/>
+      <c r="E320" s="119"/>
+      <c r="F320" s="60"/>
     </row>
     <row r="321" spans="4:6">
-      <c r="D321" s="176"/>
-      <c r="E321" s="168"/>
+      <c r="D321" s="127"/>
+      <c r="E321" s="119"/>
       <c r="F321" s="23"/>
     </row>
   </sheetData>

--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="196">
   <si>
     <t>ROOMS</t>
   </si>
@@ -38,7 +38,16 @@
     <t>mobile number parentss</t>
   </si>
   <si>
+    <t xml:space="preserve">city </t>
+  </si>
+  <si>
+    <t>outstanding fees</t>
+  </si>
+  <si>
     <t>NAKUL PARAKH</t>
+  </si>
+  <si>
+    <t>dhule</t>
   </si>
   <si>
     <t>BHAVISHYA JAIN</t>
@@ -1637,7 +1646,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1688,7 +1697,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1716,17 +1725,11 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1737,18 +1740,12 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1807,37 +1804,24 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1852,15 +1836,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1909,16 +1887,10 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1946,6 +1918,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2281,8 +2254,8 @@
     <col min="5" max="5" width="5.88888888888889" style="2" customWidth="1"/>
     <col min="6" max="6" width="32.6666666666667" style="2" customWidth="1"/>
     <col min="7" max="7" width="32.2962962962963" style="3" customWidth="1"/>
-    <col min="8" max="8" width="7" style="2" customWidth="1"/>
-    <col min="9" max="9" width="13.6666666666667" style="4" customWidth="1"/>
+    <col min="8" max="8" width="9.68518518518519" style="2" customWidth="1"/>
+    <col min="9" max="9" width="22.0833333333333" style="4" customWidth="1"/>
     <col min="10" max="10" width="11.3333333333333" style="4" customWidth="1"/>
     <col min="11" max="11" width="12.3333333333333" style="4" customWidth="1"/>
     <col min="12" max="12" width="16.3333333333333" style="4" customWidth="1"/>
@@ -2310,8 +2283,12 @@
       <c r="G2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="9"/>
-      <c r="I2" s="11"/>
+      <c r="H2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>4</v>
+      </c>
       <c r="J2" s="10"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
@@ -2334,13 +2311,17 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G3" s="19">
         <v>1234567891</v>
       </c>
-      <c r="H3" s="18"/>
-      <c r="I3" s="20"/>
+      <c r="H3" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="20">
+        <v>10000</v>
+      </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
@@ -2361,13 +2342,17 @@
         <v>2</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G4" s="19">
         <v>1234567892</v>
       </c>
-      <c r="H4" s="25"/>
-      <c r="I4" s="20"/>
+      <c r="H4" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="20">
+        <v>10001</v>
+      </c>
       <c r="J4" s="21"/>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
@@ -2388,13 +2373,17 @@
         <v>3</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G5" s="19">
         <v>1234567893</v>
       </c>
-      <c r="H5" s="18"/>
-      <c r="I5" s="20"/>
+      <c r="H5" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="20">
+        <v>10002</v>
+      </c>
       <c r="J5" s="21"/>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
@@ -2415,13 +2404,17 @@
         <v>4</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G6" s="19">
         <v>1234567894</v>
       </c>
-      <c r="H6" s="25"/>
-      <c r="I6" s="21"/>
+      <c r="H6" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="20">
+        <v>10003</v>
+      </c>
       <c r="J6" s="21"/>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
@@ -2444,22 +2437,26 @@
         <v>1</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7" s="19">
         <v>1234567895</v>
       </c>
-      <c r="H7" s="18"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="33"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="33"/>
+      <c r="H7" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="20">
+        <v>10004</v>
+      </c>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
       <c r="O7" s="21"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="34"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="33"/>
       <c r="S7" s="21"/>
     </row>
     <row r="8" spans="1:19">
@@ -2471,13 +2468,17 @@
         <v>2</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G8" s="19">
         <v>1234567896</v>
       </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="20"/>
+      <c r="H8" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="20">
+        <v>10005</v>
+      </c>
       <c r="J8" s="21"/>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
@@ -2498,13 +2499,17 @@
         <v>3</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G9" s="19">
         <v>1234567897</v>
       </c>
-      <c r="H9" s="18"/>
-      <c r="I9" s="20"/>
+      <c r="H9" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="20">
+        <v>10006</v>
+      </c>
       <c r="J9" s="21"/>
       <c r="K9" s="21"/>
       <c r="L9" s="21"/>
@@ -2524,19 +2529,23 @@
       <c r="E10" s="27">
         <v>4</v>
       </c>
-      <c r="F10" s="35" t="s">
-        <v>10</v>
+      <c r="F10" s="34" t="s">
+        <v>13</v>
       </c>
       <c r="G10" s="19">
         <v>1234567898</v>
       </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37"/>
+      <c r="H10" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="20">
+        <v>10007</v>
+      </c>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
       <c r="O10" s="21"/>
       <c r="P10" s="21"/>
       <c r="Q10" s="21"/>
@@ -2550,22 +2559,26 @@
       <c r="D11" s="16">
         <v>103</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="36">
         <v>1</v>
       </c>
-      <c r="F11" s="39" t="s">
-        <v>11</v>
+      <c r="F11" s="37" t="s">
+        <v>14</v>
       </c>
       <c r="G11" s="19">
         <v>1234567899</v>
       </c>
-      <c r="H11" s="18"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="33"/>
-      <c r="M11" s="33"/>
-      <c r="N11" s="33"/>
+      <c r="H11" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="20">
+        <v>10008</v>
+      </c>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
       <c r="O11" s="21"/>
       <c r="P11" s="21"/>
       <c r="Q11" s="21"/>
@@ -2581,13 +2594,17 @@
         <v>2</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G12" s="19">
         <v>1234567900</v>
       </c>
-      <c r="H12" s="25"/>
-      <c r="I12" s="20"/>
+      <c r="H12" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="20">
+        <v>10009</v>
+      </c>
       <c r="J12" s="21"/>
       <c r="K12" s="21"/>
       <c r="L12" s="21"/>
@@ -2604,17 +2621,21 @@
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
       <c r="D13" s="24"/>
-      <c r="E13" s="38">
+      <c r="E13" s="36">
         <v>3</v>
       </c>
-      <c r="F13" s="40" t="s">
-        <v>13</v>
+      <c r="F13" s="38" t="s">
+        <v>16</v>
       </c>
       <c r="G13" s="19">
         <v>1234567901</v>
       </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="20"/>
+      <c r="H13" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="20">
+        <v>10010</v>
+      </c>
       <c r="J13" s="21"/>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
@@ -2634,20 +2655,24 @@
       <c r="E14" s="17">
         <v>4</v>
       </c>
-      <c r="F14" s="40" t="s">
-        <v>14</v>
+      <c r="F14" s="38" t="s">
+        <v>17</v>
       </c>
       <c r="G14" s="19">
         <v>1234567902</v>
       </c>
-      <c r="H14" s="40"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
+      <c r="H14" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="20">
+        <v>10011</v>
+      </c>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="39"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="21"/>
       <c r="R14" s="23"/>
@@ -2659,14 +2684,18 @@
       <c r="C15" s="15"/>
       <c r="D15" s="24"/>
       <c r="E15" s="30"/>
-      <c r="F15" s="43" t="s">
-        <v>15</v>
+      <c r="F15" s="40" t="s">
+        <v>18</v>
       </c>
       <c r="G15" s="19">
         <v>1234567903</v>
       </c>
-      <c r="H15" s="43"/>
-      <c r="I15" s="20"/>
+      <c r="H15" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="20">
+        <v>10012</v>
+      </c>
       <c r="J15" s="21"/>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
@@ -2688,20 +2717,24 @@
       <c r="E16" s="30">
         <v>1</v>
       </c>
-      <c r="F16" s="44" t="s">
-        <v>16</v>
+      <c r="F16" s="41" t="s">
+        <v>19</v>
       </c>
       <c r="G16" s="19">
         <v>1234567904</v>
       </c>
-      <c r="H16" s="45"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
+      <c r="H16" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="20">
+        <v>10013</v>
+      </c>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
       <c r="P16" s="21"/>
       <c r="Q16" s="21"/>
       <c r="R16" s="23"/>
@@ -2715,14 +2748,18 @@
       <c r="E17" s="30">
         <v>2</v>
       </c>
-      <c r="F17" s="40" t="s">
-        <v>17</v>
+      <c r="F17" s="38" t="s">
+        <v>20</v>
       </c>
       <c r="G17" s="19">
         <v>1234567905</v>
       </c>
-      <c r="H17" s="25"/>
-      <c r="I17" s="20"/>
+      <c r="H17" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="20">
+        <v>10014</v>
+      </c>
       <c r="J17" s="21"/>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
@@ -2742,14 +2779,18 @@
       <c r="E18" s="30">
         <v>3</v>
       </c>
-      <c r="F18" s="40" t="s">
-        <v>18</v>
+      <c r="F18" s="38" t="s">
+        <v>21</v>
       </c>
       <c r="G18" s="19">
         <v>1234567906</v>
       </c>
-      <c r="H18" s="18"/>
-      <c r="I18" s="20"/>
+      <c r="H18" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="20">
+        <v>10015</v>
+      </c>
       <c r="J18" s="21"/>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
@@ -2769,19 +2810,23 @@
       <c r="E19" s="30">
         <v>4</v>
       </c>
-      <c r="F19" s="47" t="s">
-        <v>19</v>
+      <c r="F19" s="43" t="s">
+        <v>22</v>
       </c>
       <c r="G19" s="19">
         <v>1234567907</v>
       </c>
-      <c r="H19" s="25"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
+      <c r="H19" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="20">
+        <v>10016</v>
+      </c>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
       <c r="O19" s="21"/>
       <c r="P19" s="21"/>
       <c r="Q19" s="21"/>
@@ -2795,22 +2840,26 @@
       <c r="D20" s="16">
         <v>105</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="36">
         <v>1</v>
       </c>
-      <c r="F20" s="48" t="s">
-        <v>20</v>
+      <c r="F20" s="44" t="s">
+        <v>23</v>
       </c>
       <c r="G20" s="19">
         <v>1234567908</v>
       </c>
-      <c r="H20" s="18"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
+      <c r="H20" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="20">
+        <v>10017</v>
+      </c>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
       <c r="O20" s="21"/>
       <c r="P20" s="21"/>
       <c r="Q20" s="21"/>
@@ -2822,17 +2871,21 @@
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="24"/>
-      <c r="E21" s="49">
+      <c r="E21" s="45">
         <v>2</v>
       </c>
-      <c r="F21" s="48" t="s">
-        <v>21</v>
+      <c r="F21" s="44" t="s">
+        <v>24</v>
       </c>
       <c r="G21" s="19">
         <v>1234567909</v>
       </c>
-      <c r="H21" s="25"/>
-      <c r="I21" s="20"/>
+      <c r="H21" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="20">
+        <v>10018</v>
+      </c>
       <c r="J21" s="21"/>
       <c r="K21" s="21"/>
       <c r="L21" s="21"/>
@@ -2852,14 +2905,18 @@
       <c r="E22" s="17">
         <v>3</v>
       </c>
-      <c r="F22" s="50" t="s">
-        <v>22</v>
+      <c r="F22" s="46" t="s">
+        <v>25</v>
       </c>
       <c r="G22" s="19">
         <v>1234567910</v>
       </c>
-      <c r="H22" s="18"/>
-      <c r="I22" s="20"/>
+      <c r="H22" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="20">
+        <v>10019</v>
+      </c>
       <c r="J22" s="21"/>
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
@@ -2879,20 +2936,24 @@
       <c r="E23" s="27">
         <v>4</v>
       </c>
-      <c r="F23" s="40" t="s">
-        <v>23</v>
+      <c r="F23" s="38" t="s">
+        <v>26</v>
       </c>
       <c r="G23" s="19">
         <v>1234567911</v>
       </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="41"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42"/>
+      <c r="H23" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="20">
+        <v>10020</v>
+      </c>
+      <c r="J23" s="39"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="39"/>
       <c r="P23" s="21"/>
       <c r="Q23" s="21"/>
       <c r="R23" s="23"/>
@@ -2903,15 +2964,19 @@
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="24"/>
-      <c r="E24" s="51"/>
-      <c r="F24" s="43" t="s">
-        <v>24</v>
+      <c r="E24" s="47"/>
+      <c r="F24" s="40" t="s">
+        <v>27</v>
       </c>
       <c r="G24" s="19">
         <v>1234567912</v>
       </c>
-      <c r="H24" s="18"/>
-      <c r="I24" s="20"/>
+      <c r="H24" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" s="20">
+        <v>10021</v>
+      </c>
       <c r="J24" s="21"/>
       <c r="K24" s="21"/>
       <c r="L24" s="21"/>
@@ -2930,23 +2995,27 @@
       <c r="D25" s="29">
         <v>106</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="36">
         <v>1</v>
       </c>
-      <c r="F25" s="52" t="s">
-        <v>25</v>
+      <c r="F25" s="48" t="s">
+        <v>28</v>
       </c>
       <c r="G25" s="19">
         <v>1234567913</v>
       </c>
-      <c r="H25" s="25"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="33"/>
+      <c r="H25" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I25" s="20">
+        <v>10022</v>
+      </c>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
+      <c r="O25" s="32"/>
       <c r="P25" s="21"/>
       <c r="Q25" s="21"/>
       <c r="R25" s="23"/>
@@ -2960,14 +3029,18 @@
       <c r="E26" s="17">
         <v>2</v>
       </c>
-      <c r="F26" s="53" t="s">
-        <v>26</v>
+      <c r="F26" s="49" t="s">
+        <v>29</v>
       </c>
       <c r="G26" s="19">
         <v>1234567914</v>
       </c>
-      <c r="H26" s="18"/>
-      <c r="I26" s="20"/>
+      <c r="H26" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="20">
+        <v>10023</v>
+      </c>
       <c r="J26" s="21"/>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
@@ -2987,14 +3060,18 @@
       <c r="E27" s="17">
         <v>3</v>
       </c>
-      <c r="F27" s="54" t="s">
-        <v>27</v>
+      <c r="F27" s="50" t="s">
+        <v>30</v>
       </c>
       <c r="G27" s="19">
         <v>1234567915</v>
       </c>
-      <c r="H27" s="25"/>
-      <c r="I27" s="20"/>
+      <c r="H27" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I27" s="20">
+        <v>10024</v>
+      </c>
       <c r="J27" s="21"/>
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
@@ -3014,19 +3091,23 @@
       <c r="E28" s="17">
         <v>4</v>
       </c>
-      <c r="F28" s="35" t="s">
-        <v>28</v>
+      <c r="F28" s="34" t="s">
+        <v>31</v>
       </c>
       <c r="G28" s="19">
         <v>1234567916</v>
       </c>
-      <c r="H28" s="18"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="37"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="37"/>
-      <c r="M28" s="37"/>
-      <c r="N28" s="37"/>
+      <c r="H28" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I28" s="20">
+        <v>10025</v>
+      </c>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
       <c r="O28" s="21"/>
       <c r="P28" s="21"/>
       <c r="Q28" s="21"/>
@@ -3043,19 +3124,23 @@
       <c r="E29" s="30">
         <v>1</v>
       </c>
-      <c r="F29" s="39" t="s">
-        <v>29</v>
+      <c r="F29" s="37" t="s">
+        <v>32</v>
       </c>
       <c r="G29" s="19">
         <v>1234567917</v>
       </c>
-      <c r="H29" s="25"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="33"/>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
+      <c r="H29" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I29" s="20">
+        <v>10026</v>
+      </c>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
       <c r="O29" s="21"/>
       <c r="P29" s="21"/>
       <c r="Q29" s="21"/>
@@ -3070,14 +3155,18 @@
       <c r="E30" s="17">
         <v>2</v>
       </c>
-      <c r="F30" s="55" t="s">
-        <v>30</v>
+      <c r="F30" s="51" t="s">
+        <v>33</v>
       </c>
       <c r="G30" s="19">
         <v>1234567918</v>
       </c>
-      <c r="H30" s="18"/>
-      <c r="I30" s="20"/>
+      <c r="H30" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I30" s="20">
+        <v>10027</v>
+      </c>
       <c r="J30" s="21"/>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
@@ -3097,14 +3186,18 @@
       <c r="E31" s="17">
         <v>3</v>
       </c>
-      <c r="F31" s="40" t="s">
-        <v>31</v>
+      <c r="F31" s="38" t="s">
+        <v>34</v>
       </c>
       <c r="G31" s="19">
         <v>1234567919</v>
       </c>
-      <c r="H31" s="25"/>
-      <c r="I31" s="20"/>
+      <c r="H31" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="20">
+        <v>10028</v>
+      </c>
       <c r="J31" s="21"/>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
@@ -3124,14 +3217,18 @@
       <c r="E32" s="17">
         <v>4</v>
       </c>
-      <c r="F32" s="56" t="s">
-        <v>32</v>
+      <c r="F32" s="52" t="s">
+        <v>35</v>
       </c>
       <c r="G32" s="19">
         <v>1234567920</v>
       </c>
-      <c r="H32" s="18"/>
-      <c r="I32" s="20"/>
+      <c r="H32" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I32" s="20">
+        <v>10029</v>
+      </c>
       <c r="J32" s="21"/>
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
@@ -3151,19 +3248,23 @@
       <c r="E33" s="30">
         <v>5</v>
       </c>
-      <c r="F33" s="57" t="s">
-        <v>33</v>
+      <c r="F33" s="53" t="s">
+        <v>36</v>
       </c>
       <c r="G33" s="19">
         <v>1234567921</v>
       </c>
-      <c r="H33" s="25"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="42"/>
+      <c r="H33" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I33" s="20">
+        <v>10030</v>
+      </c>
+      <c r="J33" s="39"/>
       <c r="K33" s="21"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
+      <c r="L33" s="39"/>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
       <c r="O33" s="21"/>
       <c r="P33" s="21"/>
       <c r="Q33" s="21"/>
@@ -3176,11 +3277,17 @@
       <c r="C34" s="15"/>
       <c r="D34" s="24"/>
       <c r="E34" s="30"/>
-      <c r="F34" s="58" t="s">
-        <v>34</v>
+      <c r="F34" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G34" s="19">
         <v>1234567922</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I34" s="20">
+        <v>10031</v>
       </c>
     </row>
     <row r="35" ht="17.1" spans="1:21">
@@ -3191,11 +3298,17 @@
       <c r="E35" s="27">
         <v>6</v>
       </c>
-      <c r="F35" s="58" t="s">
-        <v>34</v>
+      <c r="F35" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G35" s="19">
         <v>1234567923</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I35" s="20">
+        <v>10032</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:21">
@@ -3208,23 +3321,27 @@
       <c r="E36" s="17">
         <v>1</v>
       </c>
-      <c r="F36" s="48" t="s">
-        <v>35</v>
+      <c r="F36" s="44" t="s">
+        <v>38</v>
       </c>
       <c r="G36" s="19">
         <v>1234567924</v>
       </c>
-      <c r="H36" s="18"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="33"/>
-      <c r="M36" s="33"/>
-      <c r="N36" s="33"/>
-      <c r="O36" s="33"/>
+      <c r="H36" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I36" s="20">
+        <v>10033</v>
+      </c>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="32"/>
       <c r="P36" s="21"/>
       <c r="Q36" s="21"/>
-      <c r="R36" s="34"/>
+      <c r="R36" s="33"/>
       <c r="S36" s="21"/>
     </row>
     <row r="37" spans="1:21">
@@ -3235,14 +3352,18 @@
       <c r="E37" s="17">
         <v>2</v>
       </c>
-      <c r="F37" s="56" t="s">
-        <v>36</v>
+      <c r="F37" s="52" t="s">
+        <v>39</v>
       </c>
       <c r="G37" s="19">
         <v>1234567925</v>
       </c>
-      <c r="H37" s="25"/>
-      <c r="I37" s="20"/>
+      <c r="H37" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I37" s="20">
+        <v>10034</v>
+      </c>
       <c r="J37" s="21"/>
       <c r="K37" s="21"/>
       <c r="L37" s="21"/>
@@ -3263,13 +3384,17 @@
         <v>3</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G38" s="19">
         <v>1234567926</v>
       </c>
-      <c r="H38" s="18"/>
-      <c r="I38" s="20"/>
+      <c r="H38" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I38" s="20">
+        <v>10035</v>
+      </c>
       <c r="J38" s="21"/>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
@@ -3280,8 +3405,8 @@
       <c r="Q38" s="21"/>
       <c r="R38" s="21"/>
       <c r="S38" s="21"/>
-      <c r="T38" s="59"/>
-      <c r="U38" s="60">
+      <c r="T38" s="55"/>
+      <c r="U38" s="56">
         <v>30000</v>
       </c>
     </row>
@@ -3294,13 +3419,17 @@
         <v>4</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G39" s="19">
         <v>1234567927</v>
       </c>
-      <c r="H39" s="25"/>
-      <c r="I39" s="22"/>
+      <c r="H39" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I39" s="20">
+        <v>10036</v>
+      </c>
       <c r="J39" s="22"/>
       <c r="K39" s="21"/>
       <c r="L39" s="21"/>
@@ -3320,14 +3449,18 @@
       <c r="E40" s="17">
         <v>5</v>
       </c>
-      <c r="F40" s="35" t="s">
-        <v>39</v>
+      <c r="F40" s="34" t="s">
+        <v>42</v>
       </c>
       <c r="G40" s="19">
         <v>1234567928</v>
       </c>
-      <c r="H40" s="18"/>
-      <c r="I40" s="20"/>
+      <c r="H40" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I40" s="20">
+        <v>10037</v>
+      </c>
       <c r="J40" s="21"/>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
@@ -3343,23 +3476,27 @@
       <c r="A41" s="15"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
-      <c r="D41" s="61"/>
+      <c r="D41" s="57"/>
       <c r="E41" s="27">
         <v>6</v>
       </c>
-      <c r="F41" s="35" t="s">
-        <v>40</v>
+      <c r="F41" s="34" t="s">
+        <v>43</v>
       </c>
       <c r="G41" s="19">
         <v>1234567929</v>
       </c>
-      <c r="H41" s="25"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
+      <c r="H41" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I41" s="20">
+        <v>10038</v>
+      </c>
+      <c r="J41" s="35"/>
+      <c r="K41" s="35"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="35"/>
+      <c r="N41" s="35"/>
       <c r="O41" s="21"/>
       <c r="P41" s="21"/>
       <c r="Q41" s="21"/>
@@ -3373,22 +3510,26 @@
       <c r="D42" s="16">
         <v>204</v>
       </c>
-      <c r="E42" s="49">
+      <c r="E42" s="45">
         <v>1</v>
       </c>
-      <c r="F42" s="48" t="s">
-        <v>41</v>
+      <c r="F42" s="44" t="s">
+        <v>44</v>
       </c>
       <c r="G42" s="19">
         <v>1234567930</v>
       </c>
-      <c r="H42" s="18"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
+      <c r="H42" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I42" s="20">
+        <v>10039</v>
+      </c>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
       <c r="O42" s="21"/>
       <c r="P42" s="21"/>
       <c r="Q42" s="21"/>
@@ -3403,14 +3544,18 @@
       <c r="E43" s="17">
         <v>2</v>
       </c>
-      <c r="F43" s="54" t="s">
-        <v>42</v>
+      <c r="F43" s="50" t="s">
+        <v>45</v>
       </c>
       <c r="G43" s="19">
         <v>1234567931</v>
       </c>
-      <c r="H43" s="25"/>
-      <c r="I43" s="20"/>
+      <c r="H43" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I43" s="20">
+        <v>10040</v>
+      </c>
       <c r="J43" s="21"/>
       <c r="K43" s="21"/>
       <c r="L43" s="21"/>
@@ -3430,19 +3575,23 @@
       <c r="E44" s="27">
         <v>3</v>
       </c>
-      <c r="F44" s="62" t="s">
-        <v>43</v>
+      <c r="F44" s="58" t="s">
+        <v>46</v>
       </c>
       <c r="G44" s="19">
         <v>1234567932</v>
       </c>
-      <c r="H44" s="18"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="37"/>
-      <c r="K44" s="37"/>
-      <c r="L44" s="37"/>
-      <c r="M44" s="37"/>
-      <c r="N44" s="37"/>
+      <c r="H44" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I44" s="20">
+        <v>10041</v>
+      </c>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
       <c r="O44" s="21"/>
       <c r="P44" s="21"/>
       <c r="Q44" s="21"/>
@@ -3456,22 +3605,26 @@
       <c r="D45" s="29">
         <v>205</v>
       </c>
-      <c r="E45" s="38">
+      <c r="E45" s="36">
         <v>1</v>
       </c>
-      <c r="F45" s="39" t="s">
-        <v>44</v>
+      <c r="F45" s="37" t="s">
+        <v>47</v>
       </c>
       <c r="G45" s="19">
         <v>1234567933</v>
       </c>
-      <c r="H45" s="25"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="33"/>
-      <c r="M45" s="33"/>
-      <c r="N45" s="33"/>
+      <c r="H45" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I45" s="20">
+        <v>10042</v>
+      </c>
+      <c r="J45" s="32"/>
+      <c r="K45" s="32"/>
+      <c r="L45" s="32"/>
+      <c r="M45" s="32"/>
+      <c r="N45" s="32"/>
       <c r="O45" s="21"/>
       <c r="P45" s="21"/>
       <c r="Q45" s="21"/>
@@ -3483,17 +3636,21 @@
       <c r="B46" s="15"/>
       <c r="C46" s="15"/>
       <c r="D46" s="24"/>
-      <c r="E46" s="49">
+      <c r="E46" s="45">
         <v>2</v>
       </c>
-      <c r="F46" s="63" t="s">
-        <v>45</v>
+      <c r="F46" s="59" t="s">
+        <v>48</v>
       </c>
       <c r="G46" s="19">
         <v>1234567934</v>
       </c>
-      <c r="H46" s="18"/>
-      <c r="I46" s="20"/>
+      <c r="H46" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I46" s="20">
+        <v>10043</v>
+      </c>
       <c r="J46" s="21"/>
       <c r="K46" s="21"/>
       <c r="L46" s="21"/>
@@ -3510,24 +3667,28 @@
       <c r="B47" s="15"/>
       <c r="C47" s="15"/>
       <c r="D47" s="24"/>
-      <c r="E47" s="38">
+      <c r="E47" s="36">
         <v>3</v>
       </c>
-      <c r="F47" s="48" t="s">
-        <v>46</v>
+      <c r="F47" s="44" t="s">
+        <v>49</v>
       </c>
       <c r="G47" s="19">
         <v>1234567935</v>
       </c>
-      <c r="H47" s="25"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33"/>
+      <c r="H47" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I47" s="20">
+        <v>10044</v>
+      </c>
+      <c r="J47" s="32"/>
+      <c r="K47" s="32"/>
+      <c r="L47" s="32"/>
+      <c r="M47" s="32"/>
+      <c r="N47" s="32"/>
       <c r="O47" s="21"/>
-      <c r="P47" s="33"/>
+      <c r="P47" s="32"/>
       <c r="Q47" s="21"/>
       <c r="R47" s="23"/>
       <c r="S47" s="21"/>
@@ -3537,17 +3698,21 @@
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
       <c r="D48" s="24"/>
-      <c r="E48" s="49">
+      <c r="E48" s="45">
         <v>4</v>
       </c>
-      <c r="F48" s="64" t="s">
-        <v>47</v>
+      <c r="F48" s="60" t="s">
+        <v>50</v>
       </c>
       <c r="G48" s="19">
         <v>1234567936</v>
       </c>
-      <c r="H48" s="18"/>
-      <c r="I48" s="21"/>
+      <c r="H48" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I48" s="20">
+        <v>10045</v>
+      </c>
       <c r="J48" s="21"/>
       <c r="K48" s="21"/>
       <c r="L48" s="21"/>
@@ -3564,17 +3729,21 @@
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>
       <c r="D49" s="24"/>
-      <c r="E49" s="38">
+      <c r="E49" s="36">
         <v>5</v>
       </c>
-      <c r="F49" s="40" t="s">
-        <v>48</v>
+      <c r="F49" s="38" t="s">
+        <v>51</v>
       </c>
       <c r="G49" s="19">
         <v>1234567937</v>
       </c>
-      <c r="H49" s="25"/>
-      <c r="I49" s="21"/>
+      <c r="H49" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I49" s="20">
+        <v>10046</v>
+      </c>
       <c r="J49" s="21"/>
       <c r="K49" s="21"/>
       <c r="L49" s="21"/>
@@ -3590,18 +3759,22 @@
       <c r="A50" s="15"/>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="49">
-        <v>6</v>
-      </c>
-      <c r="F50" s="43" t="s">
-        <v>49</v>
+      <c r="D50" s="57"/>
+      <c r="E50" s="45">
+        <v>6</v>
+      </c>
+      <c r="F50" s="40" t="s">
+        <v>52</v>
       </c>
       <c r="G50" s="19">
         <v>1234567938</v>
       </c>
-      <c r="H50" s="18"/>
-      <c r="I50" s="21"/>
+      <c r="H50" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I50" s="20">
+        <v>10047</v>
+      </c>
       <c r="J50" s="21"/>
       <c r="K50" s="21"/>
       <c r="L50" s="21"/>
@@ -3623,14 +3796,18 @@
       <c r="E51" s="17">
         <v>1</v>
       </c>
-      <c r="F51" s="35" t="s">
-        <v>50</v>
+      <c r="F51" s="34" t="s">
+        <v>53</v>
       </c>
       <c r="G51" s="19">
         <v>1234567939</v>
       </c>
-      <c r="H51" s="25"/>
-      <c r="I51" s="21"/>
+      <c r="H51" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I51" s="20">
+        <v>10048</v>
+      </c>
       <c r="J51" s="21"/>
       <c r="K51" s="21"/>
       <c r="L51" s="21"/>
@@ -3650,14 +3827,18 @@
       <c r="E52" s="17">
         <v>2</v>
       </c>
-      <c r="F52" s="65" t="s">
-        <v>51</v>
+      <c r="F52" s="61" t="s">
+        <v>54</v>
       </c>
       <c r="G52" s="19">
         <v>1234567940</v>
       </c>
-      <c r="H52" s="18"/>
-      <c r="I52" s="20"/>
+      <c r="H52" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I52" s="20">
+        <v>10049</v>
+      </c>
       <c r="J52" s="21"/>
       <c r="K52" s="21"/>
       <c r="L52" s="21"/>
@@ -3678,13 +3859,17 @@
         <v>3</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G53" s="19">
         <v>1234567941</v>
       </c>
-      <c r="H53" s="25"/>
-      <c r="I53" s="20"/>
+      <c r="H53" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I53" s="20">
+        <v>10050</v>
+      </c>
       <c r="J53" s="21"/>
       <c r="K53" s="21"/>
       <c r="L53" s="21"/>
@@ -3704,14 +3889,18 @@
       <c r="E54" s="17">
         <v>4</v>
       </c>
-      <c r="F54" s="63" t="s">
-        <v>53</v>
+      <c r="F54" s="59" t="s">
+        <v>56</v>
       </c>
       <c r="G54" s="19">
         <v>1234567942</v>
       </c>
-      <c r="H54" s="18"/>
-      <c r="I54" s="20"/>
+      <c r="H54" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I54" s="20">
+        <v>10051</v>
+      </c>
       <c r="J54" s="21"/>
       <c r="K54" s="21"/>
       <c r="L54" s="21"/>
@@ -3731,14 +3920,18 @@
       <c r="E55" s="17">
         <v>5</v>
       </c>
-      <c r="F55" s="43" t="s">
-        <v>54</v>
+      <c r="F55" s="40" t="s">
+        <v>57</v>
       </c>
       <c r="G55" s="19">
         <v>1234567943</v>
       </c>
-      <c r="H55" s="25"/>
-      <c r="I55" s="21"/>
+      <c r="H55" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I55" s="20">
+        <v>10052</v>
+      </c>
       <c r="J55" s="21"/>
       <c r="K55" s="21"/>
       <c r="L55" s="21"/>
@@ -3755,27 +3948,31 @@
       <c r="B56" s="15"/>
       <c r="C56" s="15"/>
       <c r="D56" s="26"/>
-      <c r="E56" s="60">
-        <v>6</v>
-      </c>
-      <c r="F56" s="40" t="s">
-        <v>55</v>
+      <c r="E56" s="56">
+        <v>6</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>58</v>
       </c>
       <c r="G56" s="19">
         <v>1234567944</v>
       </c>
-      <c r="H56" s="18"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="42"/>
-      <c r="N56" s="42"/>
-      <c r="O56" s="42"/>
+      <c r="H56" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I56" s="20">
+        <v>10053</v>
+      </c>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
+      <c r="L56" s="39"/>
+      <c r="M56" s="39"/>
+      <c r="N56" s="39"/>
+      <c r="O56" s="39"/>
       <c r="P56" s="21"/>
-      <c r="Q56" s="42"/>
-      <c r="R56" s="42"/>
-      <c r="S56" s="42"/>
+      <c r="Q56" s="39"/>
+      <c r="R56" s="39"/>
+      <c r="S56" s="39"/>
     </row>
     <row r="57" ht="16.35" spans="1:19">
       <c r="A57" s="15"/>
@@ -3784,17 +3981,21 @@
       <c r="D57" s="29">
         <v>207</v>
       </c>
-      <c r="E57" s="49">
+      <c r="E57" s="45">
         <v>1</v>
       </c>
-      <c r="F57" s="60" t="s">
-        <v>56</v>
+      <c r="F57" s="56" t="s">
+        <v>59</v>
       </c>
       <c r="G57" s="19">
         <v>1234567945</v>
       </c>
-      <c r="H57" s="25"/>
-      <c r="I57" s="21"/>
+      <c r="H57" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I57" s="20">
+        <v>10054</v>
+      </c>
       <c r="J57" s="21"/>
       <c r="K57" s="21"/>
       <c r="L57" s="21"/>
@@ -3814,14 +4015,18 @@
       <c r="E58" s="17">
         <v>2</v>
       </c>
-      <c r="F58" s="66" t="s">
-        <v>57</v>
+      <c r="F58" s="62" t="s">
+        <v>60</v>
       </c>
       <c r="G58" s="19">
         <v>1234567946</v>
       </c>
-      <c r="H58" s="18"/>
-      <c r="I58" s="20"/>
+      <c r="H58" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I58" s="20">
+        <v>10055</v>
+      </c>
       <c r="J58" s="21"/>
       <c r="K58" s="21"/>
       <c r="L58" s="21"/>
@@ -3837,23 +4042,27 @@
       <c r="A59" s="15"/>
       <c r="B59" s="15"/>
       <c r="C59" s="15"/>
-      <c r="D59" s="61"/>
+      <c r="D59" s="57"/>
       <c r="E59" s="17">
         <v>3</v>
       </c>
-      <c r="F59" s="35" t="s">
-        <v>58</v>
+      <c r="F59" s="34" t="s">
+        <v>61</v>
       </c>
       <c r="G59" s="19">
         <v>1234567947</v>
       </c>
-      <c r="H59" s="25"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="37"/>
-      <c r="K59" s="37"/>
-      <c r="L59" s="37"/>
-      <c r="M59" s="37"/>
-      <c r="N59" s="37"/>
+      <c r="H59" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I59" s="20">
+        <v>10056</v>
+      </c>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
       <c r="O59" s="21"/>
       <c r="P59" s="21"/>
       <c r="Q59" s="21"/>
@@ -3870,22 +4079,26 @@
       <c r="E60" s="17">
         <v>1</v>
       </c>
-      <c r="F60" s="44" t="s">
-        <v>59</v>
+      <c r="F60" s="41" t="s">
+        <v>62</v>
       </c>
       <c r="G60" s="19">
         <v>1234567948</v>
       </c>
-      <c r="H60" s="18"/>
-      <c r="I60" s="67"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-      <c r="M60" s="46"/>
-      <c r="N60" s="46"/>
+      <c r="H60" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I60" s="20">
+        <v>10057</v>
+      </c>
+      <c r="J60" s="42"/>
+      <c r="K60" s="42"/>
+      <c r="L60" s="42"/>
+      <c r="M60" s="42"/>
+      <c r="N60" s="42"/>
       <c r="O60" s="21"/>
-      <c r="P60" s="42"/>
-      <c r="Q60" s="42"/>
+      <c r="P60" s="39"/>
+      <c r="Q60" s="39"/>
       <c r="R60" s="23"/>
       <c r="S60" s="21"/>
     </row>
@@ -3897,14 +4110,18 @@
       <c r="E61" s="30">
         <v>2</v>
       </c>
-      <c r="F61" s="35" t="s">
-        <v>60</v>
+      <c r="F61" s="34" t="s">
+        <v>63</v>
       </c>
       <c r="G61" s="19">
         <v>1234567949</v>
       </c>
-      <c r="H61" s="25"/>
-      <c r="I61" s="20"/>
+      <c r="H61" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="20">
+        <v>10058</v>
+      </c>
       <c r="J61" s="21"/>
       <c r="K61" s="21"/>
       <c r="L61" s="21"/>
@@ -3920,18 +4137,22 @@
       <c r="A62" s="15"/>
       <c r="B62" s="15"/>
       <c r="C62" s="15"/>
-      <c r="D62" s="61"/>
+      <c r="D62" s="57"/>
       <c r="E62" s="27">
         <v>3</v>
       </c>
-      <c r="F62" s="35" t="s">
-        <v>61</v>
+      <c r="F62" s="34" t="s">
+        <v>64</v>
       </c>
       <c r="G62" s="19">
         <v>1234567950</v>
       </c>
-      <c r="H62" s="18"/>
-      <c r="I62" s="21"/>
+      <c r="H62" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I62" s="20">
+        <v>10059</v>
+      </c>
       <c r="J62" s="21"/>
       <c r="K62" s="21"/>
       <c r="L62" s="21"/>
@@ -3950,44 +4171,52 @@
       <c r="D63" s="16">
         <v>209</v>
       </c>
-      <c r="E63" s="68">
+      <c r="E63" s="63">
         <v>1</v>
       </c>
-      <c r="F63" s="39" t="s">
-        <v>62</v>
+      <c r="F63" s="37" t="s">
+        <v>65</v>
       </c>
       <c r="G63" s="19">
         <v>1234567951</v>
       </c>
-      <c r="H63" s="25"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33"/>
-      <c r="N63" s="33"/>
-      <c r="O63" s="33"/>
-      <c r="P63" s="33"/>
-      <c r="Q63" s="33"/>
-      <c r="R63" s="34"/>
-      <c r="S63" s="33"/>
+      <c r="H63" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I63" s="20">
+        <v>10060</v>
+      </c>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="32"/>
+      <c r="M63" s="32"/>
+      <c r="N63" s="32"/>
+      <c r="O63" s="32"/>
+      <c r="P63" s="32"/>
+      <c r="Q63" s="32"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="32"/>
     </row>
     <row r="64" ht="16.35" spans="1:19">
       <c r="A64" s="15"/>
       <c r="B64" s="15"/>
       <c r="C64" s="15"/>
       <c r="D64" s="24"/>
-      <c r="E64" s="38">
+      <c r="E64" s="36">
         <v>2</v>
       </c>
-      <c r="F64" s="56" t="s">
-        <v>63</v>
+      <c r="F64" s="52" t="s">
+        <v>66</v>
       </c>
       <c r="G64" s="19">
         <v>1234567952</v>
       </c>
-      <c r="H64" s="18"/>
-      <c r="I64" s="20"/>
+      <c r="H64" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I64" s="20">
+        <v>10061</v>
+      </c>
       <c r="J64" s="21"/>
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
@@ -4007,14 +4236,18 @@
       <c r="E65" s="27">
         <v>3</v>
       </c>
-      <c r="F65" s="56" t="s">
-        <v>64</v>
+      <c r="F65" s="52" t="s">
+        <v>67</v>
       </c>
       <c r="G65" s="19">
         <v>1234567953</v>
       </c>
-      <c r="H65" s="25"/>
-      <c r="I65" s="20"/>
+      <c r="H65" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="20">
+        <v>10062</v>
+      </c>
       <c r="J65" s="21"/>
       <c r="K65" s="21"/>
       <c r="L65" s="21"/>
@@ -4031,17 +4264,21 @@
       <c r="B66" s="15"/>
       <c r="C66" s="15"/>
       <c r="D66" s="24"/>
-      <c r="E66" s="38">
+      <c r="E66" s="36">
         <v>4</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G66" s="19">
         <v>1234567954</v>
       </c>
-      <c r="H66" s="18"/>
-      <c r="I66" s="20"/>
+      <c r="H66" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I66" s="20">
+        <v>10063</v>
+      </c>
       <c r="J66" s="21"/>
       <c r="K66" s="21"/>
       <c r="L66" s="21"/>
@@ -4061,14 +4298,18 @@
       <c r="E67" s="27">
         <v>5</v>
       </c>
-      <c r="F67" s="69" t="s">
-        <v>66</v>
+      <c r="F67" s="64" t="s">
+        <v>69</v>
       </c>
       <c r="G67" s="19">
         <v>1234567955</v>
       </c>
-      <c r="H67" s="70"/>
-      <c r="I67" s="22"/>
+      <c r="H67" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I67" s="20">
+        <v>10064</v>
+      </c>
       <c r="J67" s="22"/>
       <c r="K67" s="22"/>
       <c r="L67" s="22"/>
@@ -4087,21 +4328,25 @@
       <c r="E68" s="27">
         <v>6</v>
       </c>
-      <c r="F68" s="71" t="s">
-        <v>67</v>
+      <c r="F68" s="65" t="s">
+        <v>70</v>
       </c>
       <c r="G68" s="19">
         <v>1234567956</v>
       </c>
-      <c r="H68" s="18"/>
-      <c r="I68" s="36"/>
-      <c r="J68" s="37"/>
-      <c r="K68" s="37"/>
-      <c r="L68" s="37"/>
-      <c r="M68" s="37"/>
-      <c r="N68" s="37"/>
+      <c r="H68" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I68" s="20">
+        <v>10065</v>
+      </c>
+      <c r="J68" s="35"/>
+      <c r="K68" s="35"/>
+      <c r="L68" s="35"/>
+      <c r="M68" s="35"/>
+      <c r="N68" s="35"/>
       <c r="O68" s="21"/>
-      <c r="P68" s="37"/>
+      <c r="P68" s="35"/>
       <c r="Q68" s="21"/>
       <c r="R68" s="23"/>
       <c r="S68" s="21"/>
@@ -4111,25 +4356,29 @@
       <c r="B69" s="15"/>
       <c r="C69" s="15"/>
       <c r="D69" s="24"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="39" t="s">
-        <v>68</v>
+      <c r="E69" s="47"/>
+      <c r="F69" s="37" t="s">
+        <v>71</v>
       </c>
       <c r="G69" s="19">
         <v>1234567957</v>
       </c>
-      <c r="H69" s="25"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="33"/>
-      <c r="K69" s="33"/>
-      <c r="L69" s="33"/>
-      <c r="M69" s="33"/>
-      <c r="N69" s="33"/>
-      <c r="O69" s="33"/>
-      <c r="P69" s="33"/>
-      <c r="Q69" s="33"/>
-      <c r="R69" s="34"/>
-      <c r="S69" s="33"/>
+      <c r="H69" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I69" s="20">
+        <v>10066</v>
+      </c>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="32"/>
+      <c r="M69" s="32"/>
+      <c r="N69" s="32"/>
+      <c r="O69" s="32"/>
+      <c r="P69" s="32"/>
+      <c r="Q69" s="32"/>
+      <c r="R69" s="33"/>
+      <c r="S69" s="32"/>
     </row>
     <row r="70" ht="16.35" spans="1:19">
       <c r="A70" s="15"/>
@@ -4138,24 +4387,28 @@
       <c r="D70" s="29">
         <v>210</v>
       </c>
-      <c r="E70" s="49">
+      <c r="E70" s="45">
         <v>1</v>
       </c>
-      <c r="F70" s="39" t="s">
-        <v>69</v>
+      <c r="F70" s="37" t="s">
+        <v>72</v>
       </c>
       <c r="G70" s="19">
         <v>1234567958</v>
       </c>
-      <c r="H70" s="18"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="33"/>
-      <c r="K70" s="33"/>
-      <c r="L70" s="33"/>
-      <c r="M70" s="33"/>
-      <c r="N70" s="33"/>
+      <c r="H70" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I70" s="20">
+        <v>10067</v>
+      </c>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="32"/>
+      <c r="M70" s="32"/>
+      <c r="N70" s="32"/>
       <c r="O70" s="21"/>
-      <c r="P70" s="33"/>
+      <c r="P70" s="32"/>
       <c r="Q70" s="21"/>
       <c r="R70" s="23"/>
       <c r="S70" s="21"/>
@@ -4165,17 +4418,21 @@
       <c r="B71" s="15"/>
       <c r="C71" s="15"/>
       <c r="D71" s="24"/>
-      <c r="E71" s="49">
+      <c r="E71" s="45">
         <v>2</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G71" s="19">
         <v>1234567959</v>
       </c>
-      <c r="H71" s="25"/>
-      <c r="I71" s="20"/>
+      <c r="H71" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I71" s="20">
+        <v>10068</v>
+      </c>
       <c r="J71" s="21"/>
       <c r="K71" s="21"/>
       <c r="L71" s="21"/>
@@ -4192,17 +4449,21 @@
       <c r="B72" s="15"/>
       <c r="C72" s="15"/>
       <c r="D72" s="24"/>
-      <c r="E72" s="38">
+      <c r="E72" s="36">
         <v>3</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G72" s="19">
         <v>1234567960</v>
       </c>
-      <c r="H72" s="18"/>
-      <c r="I72" s="20"/>
+      <c r="H72" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I72" s="20">
+        <v>10069</v>
+      </c>
       <c r="J72" s="21"/>
       <c r="K72" s="21"/>
       <c r="L72" s="21"/>
@@ -4219,17 +4480,21 @@
       <c r="B73" s="15"/>
       <c r="C73" s="15"/>
       <c r="D73" s="24"/>
-      <c r="E73" s="49">
+      <c r="E73" s="45">
         <v>4</v>
       </c>
-      <c r="F73" s="39" t="s">
-        <v>72</v>
+      <c r="F73" s="37" t="s">
+        <v>75</v>
       </c>
       <c r="G73" s="19">
         <v>1234567961</v>
       </c>
-      <c r="H73" s="25"/>
-      <c r="I73" s="20"/>
+      <c r="H73" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I73" s="20">
+        <v>10070</v>
+      </c>
       <c r="J73" s="21"/>
       <c r="K73" s="21"/>
       <c r="L73" s="21"/>
@@ -4246,24 +4511,28 @@
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
       <c r="D74" s="24"/>
-      <c r="E74" s="38">
+      <c r="E74" s="36">
         <v>5</v>
       </c>
-      <c r="F74" s="39" t="s">
-        <v>73</v>
+      <c r="F74" s="37" t="s">
+        <v>76</v>
       </c>
       <c r="G74" s="19">
         <v>1234567962</v>
       </c>
-      <c r="H74" s="18"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="33"/>
-      <c r="K74" s="33"/>
-      <c r="L74" s="33"/>
-      <c r="M74" s="33"/>
-      <c r="N74" s="33"/>
+      <c r="H74" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="20">
+        <v>10071</v>
+      </c>
+      <c r="J74" s="32"/>
+      <c r="K74" s="32"/>
+      <c r="L74" s="32"/>
+      <c r="M74" s="32"/>
+      <c r="N74" s="32"/>
       <c r="O74" s="21"/>
-      <c r="P74" s="33"/>
+      <c r="P74" s="32"/>
       <c r="Q74" s="21"/>
       <c r="R74" s="23"/>
       <c r="S74" s="21"/>
@@ -4272,15 +4541,21 @@
       <c r="A75" s="15"/>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
-      <c r="D75" s="61"/>
+      <c r="D75" s="57"/>
       <c r="E75" s="27">
         <v>6</v>
       </c>
-      <c r="F75" s="58" t="s">
-        <v>34</v>
+      <c r="F75" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G75" s="19">
         <v>1234567963</v>
+      </c>
+      <c r="H75" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I75" s="20">
+        <v>10072</v>
       </c>
     </row>
     <row r="76" ht="16.35" spans="1:19">
@@ -4290,22 +4565,26 @@
       <c r="D76" s="16">
         <v>211</v>
       </c>
-      <c r="E76" s="49">
+      <c r="E76" s="45">
         <v>1</v>
       </c>
-      <c r="F76" s="39" t="s">
-        <v>74</v>
+      <c r="F76" s="37" t="s">
+        <v>77</v>
       </c>
       <c r="G76" s="19">
         <v>1234567964</v>
       </c>
-      <c r="H76" s="18"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="33"/>
-      <c r="K76" s="33"/>
-      <c r="L76" s="33"/>
-      <c r="M76" s="33"/>
-      <c r="N76" s="33"/>
+      <c r="H76" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I76" s="20">
+        <v>10073</v>
+      </c>
+      <c r="J76" s="32"/>
+      <c r="K76" s="32"/>
+      <c r="L76" s="32"/>
+      <c r="M76" s="32"/>
+      <c r="N76" s="32"/>
       <c r="O76" s="21"/>
       <c r="P76" s="21"/>
       <c r="Q76" s="21"/>
@@ -4317,17 +4596,21 @@
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
       <c r="D77" s="24"/>
-      <c r="E77" s="49">
+      <c r="E77" s="45">
         <v>2</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G77" s="19">
         <v>1234567965</v>
       </c>
-      <c r="H77" s="25"/>
-      <c r="I77" s="20"/>
+      <c r="H77" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I77" s="20">
+        <v>10074</v>
+      </c>
       <c r="J77" s="21"/>
       <c r="K77" s="21"/>
       <c r="L77" s="21"/>
@@ -4347,14 +4630,18 @@
       <c r="E78" s="27">
         <v>3</v>
       </c>
-      <c r="F78" s="43" t="s">
-        <v>76</v>
+      <c r="F78" s="40" t="s">
+        <v>79</v>
       </c>
       <c r="G78" s="19">
         <v>1234567966</v>
       </c>
-      <c r="H78" s="18"/>
-      <c r="I78" s="22"/>
+      <c r="H78" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I78" s="20">
+        <v>10075</v>
+      </c>
       <c r="J78" s="21"/>
       <c r="K78" s="21"/>
       <c r="L78" s="21"/>
@@ -4373,69 +4660,82 @@
       <c r="D79" s="29">
         <v>212</v>
       </c>
-      <c r="E79" s="49">
+      <c r="E79" s="45">
         <v>1</v>
       </c>
-      <c r="F79" s="72" t="s">
-        <v>77</v>
+      <c r="F79" s="66" t="s">
+        <v>80</v>
       </c>
       <c r="G79" s="19">
         <v>1234567967</v>
       </c>
-      <c r="H79" s="25"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="33"/>
-      <c r="K79" s="33"/>
-      <c r="L79" s="33"/>
-      <c r="M79" s="33"/>
-      <c r="N79" s="33"/>
+      <c r="H79" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I79" s="20">
+        <v>10076</v>
+      </c>
+      <c r="J79" s="32"/>
+      <c r="K79" s="32"/>
+      <c r="L79" s="32"/>
+      <c r="M79" s="32"/>
+      <c r="N79" s="32"/>
       <c r="O79" s="21"/>
-      <c r="P79" s="33"/>
-      <c r="Q79" s="33"/>
-      <c r="R79" s="34"/>
-      <c r="S79" s="33"/>
+      <c r="P79" s="32"/>
+      <c r="Q79" s="32"/>
+      <c r="R79" s="33"/>
+      <c r="S79" s="32"/>
     </row>
     <row r="80" ht="16.35" spans="1:19">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="15"/>
       <c r="D80" s="24"/>
-      <c r="E80" s="49">
+      <c r="E80" s="45">
         <v>2</v>
       </c>
-      <c r="F80" s="58" t="s">
-        <v>34</v>
+      <c r="F80" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G80" s="19">
         <v>1234567968</v>
       </c>
-      <c r="H80" s="73"/>
-      <c r="O80" s="74"/>
-      <c r="P80" s="33"/>
+      <c r="H80" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I80" s="20">
+        <v>10077</v>
+      </c>
+      <c r="O80" s="67"/>
+      <c r="P80" s="32"/>
     </row>
     <row r="81" ht="17.1" spans="1:19">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
       <c r="D81" s="24"/>
-      <c r="E81" s="38">
+      <c r="E81" s="36">
         <v>3</v>
       </c>
-      <c r="F81" s="69" t="s">
-        <v>78</v>
+      <c r="F81" s="64" t="s">
+        <v>81</v>
       </c>
       <c r="G81" s="19">
         <v>1234567969</v>
       </c>
-      <c r="H81" s="44"/>
-      <c r="I81" s="32"/>
+      <c r="H81" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I81" s="20">
+        <v>10078</v>
+      </c>
       <c r="J81" s="21"/>
       <c r="K81" s="21"/>
       <c r="L81" s="21"/>
       <c r="M81" s="21"/>
       <c r="N81" s="21"/>
       <c r="O81" s="21"/>
-      <c r="P81" s="33"/>
+      <c r="P81" s="32"/>
       <c r="Q81" s="21"/>
       <c r="R81" s="21"/>
       <c r="S81" s="21"/>
@@ -4445,17 +4745,21 @@
       <c r="B82" s="15"/>
       <c r="C82" s="15"/>
       <c r="D82" s="24"/>
-      <c r="E82" s="49">
+      <c r="E82" s="45">
         <v>4</v>
       </c>
-      <c r="F82" s="43" t="s">
-        <v>79</v>
+      <c r="F82" s="40" t="s">
+        <v>82</v>
       </c>
       <c r="G82" s="19">
         <v>1234567970</v>
       </c>
-      <c r="H82" s="43"/>
-      <c r="I82" s="20"/>
+      <c r="H82" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I82" s="20">
+        <v>10079</v>
+      </c>
       <c r="J82" s="21"/>
       <c r="K82" s="21"/>
       <c r="L82" s="21"/>
@@ -4472,17 +4776,21 @@
       <c r="B83" s="15"/>
       <c r="C83" s="15"/>
       <c r="D83" s="24"/>
-      <c r="E83" s="38">
+      <c r="E83" s="36">
         <v>5</v>
       </c>
-      <c r="F83" s="43" t="s">
-        <v>80</v>
+      <c r="F83" s="40" t="s">
+        <v>83</v>
       </c>
       <c r="G83" s="19">
         <v>1234567971</v>
       </c>
-      <c r="H83" s="43"/>
-      <c r="I83" s="32"/>
+      <c r="H83" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I83" s="20">
+        <v>10080</v>
+      </c>
       <c r="J83" s="21"/>
       <c r="K83" s="21"/>
       <c r="L83" s="21"/>
@@ -4499,27 +4807,31 @@
       <c r="B84" s="15"/>
       <c r="C84" s="15"/>
       <c r="D84" s="26"/>
-      <c r="E84" s="75">
-        <v>6</v>
-      </c>
-      <c r="F84" s="58" t="s">
-        <v>34</v>
+      <c r="E84" s="68">
+        <v>6</v>
+      </c>
+      <c r="F84" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G84" s="19">
         <v>1234567972</v>
       </c>
-      <c r="H84" s="58"/>
-      <c r="I84" s="76"/>
-      <c r="J84" s="77"/>
-      <c r="K84" s="77"/>
-      <c r="L84" s="77"/>
-      <c r="M84" s="77"/>
-      <c r="N84" s="77"/>
-      <c r="O84" s="74"/>
-      <c r="P84" s="74"/>
-      <c r="Q84" s="74"/>
-      <c r="R84" s="78"/>
-      <c r="S84" s="74"/>
+      <c r="H84" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I84" s="20">
+        <v>10081</v>
+      </c>
+      <c r="J84" s="69"/>
+      <c r="K84" s="69"/>
+      <c r="L84" s="69"/>
+      <c r="M84" s="69"/>
+      <c r="N84" s="69"/>
+      <c r="O84" s="67"/>
+      <c r="P84" s="67"/>
+      <c r="Q84" s="67"/>
+      <c r="R84" s="70"/>
+      <c r="S84" s="67"/>
     </row>
     <row r="85" ht="16.35" spans="1:19">
       <c r="A85" s="15"/>
@@ -4528,17 +4840,21 @@
       <c r="D85" s="29">
         <v>213</v>
       </c>
-      <c r="E85" s="49">
+      <c r="E85" s="45">
         <v>1</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G85" s="19">
         <v>1234567973</v>
       </c>
-      <c r="H85" s="25"/>
-      <c r="I85" s="20"/>
+      <c r="H85" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I85" s="20">
+        <v>10082</v>
+      </c>
       <c r="J85" s="21"/>
       <c r="K85" s="21"/>
       <c r="L85" s="21"/>
@@ -4555,15 +4871,19 @@
       <c r="B86" s="15"/>
       <c r="C86" s="15"/>
       <c r="D86" s="24"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="43" t="s">
-        <v>82</v>
+      <c r="E86" s="45"/>
+      <c r="F86" s="40" t="s">
+        <v>85</v>
       </c>
       <c r="G86" s="19">
         <v>1234567974</v>
       </c>
-      <c r="H86" s="43"/>
-      <c r="I86" s="20"/>
+      <c r="H86" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I86" s="20">
+        <v>10083</v>
+      </c>
       <c r="J86" s="21"/>
       <c r="K86" s="21"/>
       <c r="L86" s="21"/>
@@ -4580,14 +4900,20 @@
       <c r="B87" s="15"/>
       <c r="C87" s="15"/>
       <c r="D87" s="24"/>
-      <c r="E87" s="49">
+      <c r="E87" s="45">
         <v>2</v>
       </c>
-      <c r="F87" s="58" t="s">
-        <v>34</v>
+      <c r="F87" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G87" s="19">
         <v>1234567975</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I87" s="20">
+        <v>10084</v>
       </c>
     </row>
     <row r="88" ht="17.1" spans="1:19">
@@ -4595,15 +4921,19 @@
       <c r="B88" s="15"/>
       <c r="C88" s="15"/>
       <c r="D88" s="24"/>
-      <c r="E88" s="49"/>
+      <c r="E88" s="45"/>
       <c r="F88" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G88" s="19">
         <v>1234567976</v>
       </c>
-      <c r="H88" s="43"/>
-      <c r="I88" s="20"/>
+      <c r="H88" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I88" s="20">
+        <v>10085</v>
+      </c>
       <c r="J88" s="21"/>
       <c r="K88" s="21"/>
       <c r="L88" s="21"/>
@@ -4620,14 +4950,20 @@
       <c r="B89" s="15"/>
       <c r="C89" s="15"/>
       <c r="D89" s="24"/>
-      <c r="E89" s="38">
+      <c r="E89" s="36">
         <v>3</v>
       </c>
-      <c r="F89" s="58" t="s">
-        <v>34</v>
+      <c r="F89" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G89" s="19">
         <v>1234567977</v>
+      </c>
+      <c r="H89" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I89" s="20">
+        <v>10086</v>
       </c>
     </row>
     <row r="90" ht="17.1" spans="1:19">
@@ -4635,17 +4971,21 @@
       <c r="B90" s="15"/>
       <c r="C90" s="15"/>
       <c r="D90" s="24"/>
-      <c r="E90" s="49">
+      <c r="E90" s="45">
         <v>4</v>
       </c>
-      <c r="F90" s="60" t="s">
-        <v>84</v>
+      <c r="F90" s="56" t="s">
+        <v>87</v>
       </c>
       <c r="G90" s="19">
         <v>1234567978</v>
       </c>
-      <c r="H90" s="43"/>
-      <c r="I90" s="21"/>
+      <c r="H90" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I90" s="20">
+        <v>10087</v>
+      </c>
       <c r="J90" s="21"/>
       <c r="K90" s="21"/>
       <c r="L90" s="21"/>
@@ -4662,17 +5002,21 @@
       <c r="B91" s="15"/>
       <c r="C91" s="15"/>
       <c r="D91" s="24"/>
-      <c r="E91" s="38">
+      <c r="E91" s="36">
         <v>5</v>
       </c>
-      <c r="F91" s="63" t="s">
-        <v>85</v>
+      <c r="F91" s="59" t="s">
+        <v>88</v>
       </c>
       <c r="G91" s="19">
         <v>1234567979</v>
       </c>
-      <c r="H91" s="25"/>
-      <c r="I91" s="20"/>
+      <c r="H91" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I91" s="20">
+        <v>10088</v>
+      </c>
       <c r="J91" s="21"/>
       <c r="K91" s="21"/>
       <c r="L91" s="21"/>
@@ -4688,28 +5032,32 @@
       <c r="A92" s="15"/>
       <c r="B92" s="15"/>
       <c r="C92" s="15"/>
-      <c r="D92" s="61"/>
+      <c r="D92" s="57"/>
       <c r="E92" s="27">
         <v>6</v>
       </c>
-      <c r="F92" s="47" t="s">
-        <v>86</v>
+      <c r="F92" s="43" t="s">
+        <v>89</v>
       </c>
       <c r="G92" s="19">
         <v>1234567980</v>
       </c>
-      <c r="H92" s="43"/>
-      <c r="I92" s="79"/>
-      <c r="J92" s="80"/>
-      <c r="K92" s="80"/>
-      <c r="L92" s="80"/>
-      <c r="M92" s="80"/>
-      <c r="N92" s="80"/>
+      <c r="H92" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I92" s="20">
+        <v>10089</v>
+      </c>
+      <c r="J92" s="71"/>
+      <c r="K92" s="71"/>
+      <c r="L92" s="71"/>
+      <c r="M92" s="71"/>
+      <c r="N92" s="71"/>
       <c r="O92" s="21"/>
-      <c r="P92" s="80"/>
-      <c r="Q92" s="80"/>
-      <c r="R92" s="81"/>
-      <c r="S92" s="80"/>
+      <c r="P92" s="71"/>
+      <c r="Q92" s="71"/>
+      <c r="R92" s="72"/>
+      <c r="S92" s="71"/>
     </row>
     <row r="93" ht="16.35" spans="1:19">
       <c r="A93" s="15"/>
@@ -4718,27 +5066,31 @@
       <c r="D93" s="16">
         <v>214</v>
       </c>
-      <c r="E93" s="49">
+      <c r="E93" s="45">
         <v>1</v>
       </c>
-      <c r="F93" s="82" t="s">
-        <v>87</v>
+      <c r="F93" s="73" t="s">
+        <v>90</v>
       </c>
       <c r="G93" s="19">
         <v>1234567981</v>
       </c>
-      <c r="H93" s="25"/>
-      <c r="I93" s="32"/>
-      <c r="J93" s="33"/>
-      <c r="K93" s="33"/>
-      <c r="L93" s="33"/>
-      <c r="M93" s="33"/>
-      <c r="N93" s="33"/>
-      <c r="O93" s="33"/>
-      <c r="P93" s="33"/>
-      <c r="Q93" s="33"/>
-      <c r="R93" s="34"/>
-      <c r="S93" s="33"/>
+      <c r="H93" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I93" s="20">
+        <v>10090</v>
+      </c>
+      <c r="J93" s="32"/>
+      <c r="K93" s="32"/>
+      <c r="L93" s="32"/>
+      <c r="M93" s="32"/>
+      <c r="N93" s="32"/>
+      <c r="O93" s="32"/>
+      <c r="P93" s="32"/>
+      <c r="Q93" s="32"/>
+      <c r="R93" s="33"/>
+      <c r="S93" s="32"/>
     </row>
     <row r="94" spans="1:19">
       <c r="A94" s="15"/>
@@ -4749,13 +5101,17 @@
         <v>2</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G94" s="19">
         <v>1234567982</v>
       </c>
-      <c r="H94" s="43"/>
-      <c r="I94" s="20"/>
+      <c r="H94" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I94" s="20">
+        <v>10091</v>
+      </c>
       <c r="J94" s="21"/>
       <c r="K94" s="21"/>
       <c r="L94" s="21"/>
@@ -4771,23 +5127,27 @@
       <c r="A95" s="15"/>
       <c r="B95" s="15"/>
       <c r="C95" s="15"/>
-      <c r="D95" s="61"/>
+      <c r="D95" s="57"/>
       <c r="E95" s="27">
         <v>3</v>
       </c>
-      <c r="F95" s="47" t="s">
-        <v>89</v>
+      <c r="F95" s="43" t="s">
+        <v>92</v>
       </c>
       <c r="G95" s="19">
         <v>1234567983</v>
       </c>
-      <c r="H95" s="25"/>
-      <c r="I95" s="36"/>
-      <c r="J95" s="37"/>
-      <c r="K95" s="37"/>
-      <c r="L95" s="37"/>
-      <c r="M95" s="37"/>
-      <c r="N95" s="37"/>
+      <c r="H95" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I95" s="20">
+        <v>10092</v>
+      </c>
+      <c r="J95" s="35"/>
+      <c r="K95" s="35"/>
+      <c r="L95" s="35"/>
+      <c r="M95" s="35"/>
+      <c r="N95" s="35"/>
       <c r="O95" s="21"/>
       <c r="P95" s="21"/>
       <c r="Q95" s="21"/>
@@ -4801,22 +5161,26 @@
       <c r="D96" s="16">
         <v>215</v>
       </c>
-      <c r="E96" s="51">
+      <c r="E96" s="47">
         <v>1</v>
       </c>
-      <c r="F96" s="39" t="s">
-        <v>90</v>
+      <c r="F96" s="37" t="s">
+        <v>93</v>
       </c>
       <c r="G96" s="19">
         <v>1234567984</v>
       </c>
-      <c r="H96" s="43"/>
-      <c r="I96" s="32"/>
-      <c r="J96" s="33"/>
-      <c r="K96" s="33"/>
-      <c r="L96" s="33"/>
-      <c r="M96" s="33"/>
-      <c r="N96" s="33"/>
+      <c r="H96" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I96" s="20">
+        <v>10093</v>
+      </c>
+      <c r="J96" s="32"/>
+      <c r="K96" s="32"/>
+      <c r="L96" s="32"/>
+      <c r="M96" s="32"/>
+      <c r="N96" s="32"/>
       <c r="O96" s="21"/>
       <c r="P96" s="21"/>
       <c r="Q96" s="21"/>
@@ -4828,17 +5192,21 @@
       <c r="B97" s="15"/>
       <c r="C97" s="15"/>
       <c r="D97" s="24"/>
-      <c r="E97" s="38">
+      <c r="E97" s="36">
         <v>2</v>
       </c>
-      <c r="F97" s="43" t="s">
-        <v>91</v>
+      <c r="F97" s="40" t="s">
+        <v>94</v>
       </c>
       <c r="G97" s="19">
         <v>1234567985</v>
       </c>
-      <c r="H97" s="25"/>
-      <c r="I97" s="20"/>
+      <c r="H97" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I97" s="20">
+        <v>10094</v>
+      </c>
       <c r="J97" s="21"/>
       <c r="K97" s="21"/>
       <c r="L97" s="21"/>
@@ -4855,17 +5223,21 @@
       <c r="B98" s="15"/>
       <c r="C98" s="15"/>
       <c r="D98" s="24"/>
-      <c r="E98" s="51">
+      <c r="E98" s="47">
         <v>3</v>
       </c>
-      <c r="F98" s="43" t="s">
-        <v>92</v>
+      <c r="F98" s="40" t="s">
+        <v>95</v>
       </c>
       <c r="G98" s="19">
         <v>1234567986</v>
       </c>
-      <c r="H98" s="43"/>
-      <c r="I98" s="20"/>
+      <c r="H98" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I98" s="20">
+        <v>10095</v>
+      </c>
       <c r="J98" s="21"/>
       <c r="K98" s="21"/>
       <c r="L98" s="21"/>
@@ -4882,17 +5254,21 @@
       <c r="B99" s="15"/>
       <c r="C99" s="15"/>
       <c r="D99" s="24"/>
-      <c r="E99" s="38">
+      <c r="E99" s="36">
         <v>4</v>
       </c>
-      <c r="F99" s="43" t="s">
-        <v>93</v>
+      <c r="F99" s="40" t="s">
+        <v>96</v>
       </c>
       <c r="G99" s="19">
         <v>1234567987</v>
       </c>
-      <c r="H99" s="25"/>
-      <c r="I99" s="21"/>
+      <c r="H99" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I99" s="20">
+        <v>10096</v>
+      </c>
       <c r="J99" s="21"/>
       <c r="K99" s="21"/>
       <c r="L99" s="21"/>
@@ -4912,24 +5288,28 @@
       <c r="B100" s="15"/>
       <c r="C100" s="15"/>
       <c r="D100" s="24"/>
-      <c r="E100" s="83">
+      <c r="E100" s="74">
         <v>5</v>
       </c>
-      <c r="F100" s="84" t="s">
-        <v>94</v>
+      <c r="F100" s="75" t="s">
+        <v>97</v>
       </c>
       <c r="G100" s="19">
         <v>1234567988</v>
       </c>
-      <c r="H100" s="43"/>
-      <c r="I100" s="32"/>
-      <c r="J100" s="33"/>
-      <c r="K100" s="33"/>
-      <c r="L100" s="33"/>
-      <c r="M100" s="33"/>
-      <c r="N100" s="33"/>
+      <c r="H100" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I100" s="20">
+        <v>10097</v>
+      </c>
+      <c r="J100" s="32"/>
+      <c r="K100" s="32"/>
+      <c r="L100" s="32"/>
+      <c r="M100" s="32"/>
+      <c r="N100" s="32"/>
       <c r="O100" s="21"/>
-      <c r="P100" s="33"/>
+      <c r="P100" s="32"/>
       <c r="Q100" s="21"/>
       <c r="R100" s="23"/>
       <c r="S100" s="21"/>
@@ -4938,28 +5318,32 @@
       <c r="A101" s="15"/>
       <c r="B101" s="15"/>
       <c r="C101" s="15"/>
-      <c r="D101" s="61"/>
-      <c r="E101" s="85">
-        <v>6</v>
-      </c>
-      <c r="F101" s="69" t="s">
-        <v>95</v>
+      <c r="D101" s="57"/>
+      <c r="E101" s="76">
+        <v>6</v>
+      </c>
+      <c r="F101" s="64" t="s">
+        <v>98</v>
       </c>
       <c r="G101" s="19">
         <v>1234567989</v>
       </c>
-      <c r="H101" s="69"/>
-      <c r="I101" s="86"/>
-      <c r="J101" s="87"/>
-      <c r="K101" s="87"/>
-      <c r="L101" s="87"/>
-      <c r="M101" s="87"/>
-      <c r="N101" s="87"/>
-      <c r="O101" s="74"/>
-      <c r="P101" s="88"/>
-      <c r="Q101" s="88"/>
-      <c r="R101" s="89"/>
-      <c r="S101" s="88"/>
+      <c r="H101" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I101" s="20">
+        <v>10098</v>
+      </c>
+      <c r="J101" s="77"/>
+      <c r="K101" s="77"/>
+      <c r="L101" s="77"/>
+      <c r="M101" s="77"/>
+      <c r="N101" s="77"/>
+      <c r="O101" s="67"/>
+      <c r="P101" s="78"/>
+      <c r="Q101" s="78"/>
+      <c r="R101" s="79"/>
+      <c r="S101" s="78"/>
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="1:21">
       <c r="A102" s="15"/>
@@ -4968,22 +5352,26 @@
       <c r="D102" s="16">
         <v>216</v>
       </c>
-      <c r="E102" s="49">
+      <c r="E102" s="45">
         <v>1</v>
       </c>
-      <c r="F102" s="39" t="s">
-        <v>96</v>
+      <c r="F102" s="37" t="s">
+        <v>99</v>
       </c>
       <c r="G102" s="19">
         <v>1234567990</v>
       </c>
-      <c r="H102" s="39"/>
-      <c r="I102" s="32"/>
-      <c r="J102" s="33"/>
-      <c r="K102" s="33"/>
-      <c r="L102" s="33"/>
-      <c r="M102" s="33"/>
-      <c r="N102" s="33"/>
+      <c r="H102" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I102" s="20">
+        <v>10099</v>
+      </c>
+      <c r="J102" s="32"/>
+      <c r="K102" s="32"/>
+      <c r="L102" s="32"/>
+      <c r="M102" s="32"/>
+      <c r="N102" s="32"/>
       <c r="O102" s="21"/>
       <c r="P102" s="21"/>
       <c r="Q102" s="21"/>
@@ -4999,13 +5387,17 @@
         <v>2</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="G103" s="19">
         <v>1234567991</v>
       </c>
-      <c r="H103" s="25"/>
-      <c r="I103" s="20"/>
+      <c r="H103" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I103" s="20">
+        <v>10100</v>
+      </c>
       <c r="J103" s="21"/>
       <c r="K103" s="21"/>
       <c r="L103" s="21"/>
@@ -5025,14 +5417,18 @@
       <c r="E104" s="17">
         <v>3</v>
       </c>
-      <c r="F104" s="43" t="s">
-        <v>98</v>
+      <c r="F104" s="40" t="s">
+        <v>101</v>
       </c>
       <c r="G104" s="19">
         <v>1234567992</v>
       </c>
-      <c r="H104" s="43"/>
-      <c r="I104" s="20"/>
+      <c r="H104" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I104" s="20">
+        <v>10101</v>
+      </c>
       <c r="J104" s="21"/>
       <c r="K104" s="21"/>
       <c r="L104" s="21"/>
@@ -5052,41 +5448,49 @@
       <c r="E105" s="17">
         <v>4</v>
       </c>
-      <c r="F105" s="58" t="s">
-        <v>34</v>
+      <c r="F105" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G105" s="19">
         <v>1234567993</v>
       </c>
-      <c r="H105" s="90"/>
-      <c r="I105" s="88"/>
-      <c r="J105" s="88"/>
-      <c r="K105" s="88"/>
-      <c r="L105" s="88"/>
-      <c r="M105" s="88"/>
-      <c r="N105" s="88"/>
-      <c r="O105" s="74"/>
-      <c r="P105" s="88"/>
-      <c r="Q105" s="88"/>
-      <c r="R105" s="88"/>
-      <c r="S105" s="88"/>
+      <c r="H105" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I105" s="20">
+        <v>10102</v>
+      </c>
+      <c r="J105" s="78"/>
+      <c r="K105" s="78"/>
+      <c r="L105" s="78"/>
+      <c r="M105" s="78"/>
+      <c r="N105" s="78"/>
+      <c r="O105" s="67"/>
+      <c r="P105" s="78"/>
+      <c r="Q105" s="78"/>
+      <c r="R105" s="78"/>
+      <c r="S105" s="78"/>
     </row>
     <row r="106" ht="18.75" customHeight="1" spans="1:21">
       <c r="A106" s="15"/>
       <c r="B106" s="15"/>
       <c r="C106" s="15"/>
       <c r="D106" s="24"/>
-      <c r="E106" s="91">
+      <c r="E106" s="80">
         <v>5</v>
       </c>
-      <c r="F106" s="43" t="s">
-        <v>99</v>
+      <c r="F106" s="40" t="s">
+        <v>102</v>
       </c>
       <c r="G106" s="19">
         <v>1234567994</v>
       </c>
-      <c r="H106" s="43"/>
-      <c r="I106" s="20"/>
+      <c r="H106" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I106" s="20">
+        <v>10103</v>
+      </c>
       <c r="J106" s="21"/>
       <c r="K106" s="21"/>
       <c r="L106" s="21"/>
@@ -5102,27 +5506,31 @@
       <c r="A107" s="15"/>
       <c r="B107" s="15"/>
       <c r="C107" s="15"/>
-      <c r="D107" s="61"/>
-      <c r="E107" s="75">
-        <v>6</v>
-      </c>
-      <c r="F107" s="69" t="s">
-        <v>100</v>
+      <c r="D107" s="57"/>
+      <c r="E107" s="68">
+        <v>6</v>
+      </c>
+      <c r="F107" s="64" t="s">
+        <v>103</v>
       </c>
       <c r="G107" s="19">
         <v>1234567995</v>
       </c>
-      <c r="H107" s="44"/>
-      <c r="I107" s="20"/>
-      <c r="J107" s="37"/>
-      <c r="K107" s="37"/>
-      <c r="L107" s="37"/>
-      <c r="M107" s="37"/>
-      <c r="N107" s="37"/>
+      <c r="H107" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I107" s="20">
+        <v>10104</v>
+      </c>
+      <c r="J107" s="35"/>
+      <c r="K107" s="35"/>
+      <c r="L107" s="35"/>
+      <c r="M107" s="35"/>
+      <c r="N107" s="35"/>
       <c r="O107" s="21"/>
-      <c r="P107" s="37"/>
-      <c r="Q107" s="37"/>
-      <c r="R107" s="92"/>
+      <c r="P107" s="35"/>
+      <c r="Q107" s="35"/>
+      <c r="R107" s="81"/>
       <c r="S107" s="21"/>
     </row>
     <row r="108" ht="18.75" customHeight="1" spans="1:21">
@@ -5132,26 +5540,30 @@
       <c r="D108" s="16">
         <v>217</v>
       </c>
-      <c r="E108" s="49">
+      <c r="E108" s="45">
         <v>1</v>
       </c>
-      <c r="F108" s="39" t="s">
-        <v>101</v>
+      <c r="F108" s="37" t="s">
+        <v>104</v>
       </c>
       <c r="G108" s="19">
         <v>1234567996</v>
       </c>
-      <c r="H108" s="43"/>
-      <c r="I108" s="32"/>
-      <c r="J108" s="33"/>
-      <c r="K108" s="33"/>
-      <c r="L108" s="33"/>
-      <c r="M108" s="33"/>
-      <c r="N108" s="33"/>
+      <c r="H108" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I108" s="20">
+        <v>10105</v>
+      </c>
+      <c r="J108" s="32"/>
+      <c r="K108" s="32"/>
+      <c r="L108" s="32"/>
+      <c r="M108" s="32"/>
+      <c r="N108" s="32"/>
       <c r="O108" s="21"/>
-      <c r="P108" s="33"/>
-      <c r="Q108" s="33"/>
-      <c r="R108" s="34"/>
+      <c r="P108" s="32"/>
+      <c r="Q108" s="32"/>
+      <c r="R108" s="33"/>
       <c r="S108" s="21"/>
     </row>
     <row r="109" ht="18.75" customHeight="1" spans="1:21">
@@ -5162,14 +5574,18 @@
       <c r="E109" s="17">
         <v>2</v>
       </c>
-      <c r="F109" s="40" t="s">
-        <v>102</v>
+      <c r="F109" s="38" t="s">
+        <v>105</v>
       </c>
       <c r="G109" s="19">
         <v>1234567997</v>
       </c>
-      <c r="H109" s="44"/>
-      <c r="I109" s="20"/>
+      <c r="H109" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I109" s="20">
+        <v>10106</v>
+      </c>
       <c r="J109" s="21"/>
       <c r="K109" s="21"/>
       <c r="L109" s="21"/>
@@ -5186,17 +5602,21 @@
       <c r="B110" s="15"/>
       <c r="C110" s="15"/>
       <c r="D110" s="24"/>
-      <c r="E110" s="38">
+      <c r="E110" s="36">
         <v>3</v>
       </c>
-      <c r="F110" s="66" t="s">
-        <v>103</v>
+      <c r="F110" s="62" t="s">
+        <v>106</v>
       </c>
       <c r="G110" s="19">
         <v>1234567998</v>
       </c>
-      <c r="H110" s="43"/>
-      <c r="I110" s="20"/>
+      <c r="H110" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I110" s="20">
+        <v>10107</v>
+      </c>
       <c r="J110" s="21"/>
       <c r="K110" s="21"/>
       <c r="L110" s="21"/>
@@ -5216,14 +5636,18 @@
       <c r="E111" s="17">
         <v>4</v>
       </c>
-      <c r="F111" s="53" t="s">
-        <v>104</v>
+      <c r="F111" s="49" t="s">
+        <v>107</v>
       </c>
       <c r="G111" s="19">
         <v>1234567999</v>
       </c>
-      <c r="H111" s="44"/>
-      <c r="I111" s="32"/>
+      <c r="H111" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I111" s="20">
+        <v>10108</v>
+      </c>
       <c r="J111" s="21"/>
       <c r="K111" s="21"/>
       <c r="L111" s="21"/>
@@ -5240,17 +5664,21 @@
       <c r="B112" s="15"/>
       <c r="C112" s="15"/>
       <c r="D112" s="24"/>
-      <c r="E112" s="38">
+      <c r="E112" s="36">
         <v>5</v>
       </c>
-      <c r="F112" s="69" t="s">
-        <v>105</v>
+      <c r="F112" s="64" t="s">
+        <v>108</v>
       </c>
       <c r="G112" s="19">
         <v>1234568000</v>
       </c>
-      <c r="H112" s="43"/>
-      <c r="I112" s="21"/>
+      <c r="H112" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I112" s="20">
+        <v>10109</v>
+      </c>
       <c r="J112" s="21"/>
       <c r="K112" s="21"/>
       <c r="L112" s="21"/>
@@ -5266,18 +5694,22 @@
       <c r="A113" s="15"/>
       <c r="B113" s="15"/>
       <c r="C113" s="15"/>
-      <c r="D113" s="61"/>
+      <c r="D113" s="57"/>
       <c r="E113" s="27">
         <v>6</v>
       </c>
-      <c r="F113" s="56" t="s">
-        <v>106</v>
+      <c r="F113" s="52" t="s">
+        <v>109</v>
       </c>
       <c r="G113" s="19">
         <v>1234568001</v>
       </c>
-      <c r="H113" s="44"/>
-      <c r="I113" s="20"/>
+      <c r="H113" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I113" s="20">
+        <v>10110</v>
+      </c>
       <c r="J113" s="21"/>
       <c r="K113" s="21"/>
       <c r="L113" s="21"/>
@@ -5296,22 +5728,26 @@
       <c r="D114" s="16">
         <v>301</v>
       </c>
-      <c r="E114" s="49">
+      <c r="E114" s="45">
         <v>1</v>
       </c>
-      <c r="F114" s="52" t="s">
-        <v>107</v>
+      <c r="F114" s="48" t="s">
+        <v>110</v>
       </c>
       <c r="G114" s="19">
         <v>1234568002</v>
       </c>
-      <c r="H114" s="43"/>
-      <c r="I114" s="32"/>
-      <c r="J114" s="33"/>
-      <c r="K114" s="33"/>
-      <c r="L114" s="33"/>
-      <c r="M114" s="33"/>
-      <c r="N114" s="33"/>
+      <c r="H114" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I114" s="20">
+        <v>10111</v>
+      </c>
+      <c r="J114" s="32"/>
+      <c r="K114" s="32"/>
+      <c r="L114" s="32"/>
+      <c r="M114" s="32"/>
+      <c r="N114" s="32"/>
       <c r="O114" s="21"/>
       <c r="P114" s="21"/>
       <c r="Q114" s="21"/>
@@ -5326,14 +5762,18 @@
       <c r="E115" s="17">
         <v>2</v>
       </c>
-      <c r="F115" s="93" t="s">
-        <v>108</v>
+      <c r="F115" s="82" t="s">
+        <v>111</v>
       </c>
       <c r="G115" s="19">
         <v>1234568003</v>
       </c>
-      <c r="H115" s="44"/>
-      <c r="I115" s="32"/>
+      <c r="H115" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I115" s="20">
+        <v>10112</v>
+      </c>
       <c r="J115" s="21"/>
       <c r="K115" s="21"/>
       <c r="L115" s="21"/>
@@ -5349,18 +5789,22 @@
       <c r="A116" s="15"/>
       <c r="B116" s="15"/>
       <c r="C116" s="15"/>
-      <c r="D116" s="61"/>
+      <c r="D116" s="57"/>
       <c r="E116" s="27">
         <v>3</v>
       </c>
-      <c r="F116" s="43" t="s">
-        <v>109</v>
+      <c r="F116" s="40" t="s">
+        <v>112</v>
       </c>
       <c r="G116" s="19">
         <v>1234568004</v>
       </c>
-      <c r="H116" s="43"/>
-      <c r="I116" s="32"/>
+      <c r="H116" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I116" s="20">
+        <v>10113</v>
+      </c>
       <c r="J116" s="21"/>
       <c r="K116" s="21"/>
       <c r="L116" s="21"/>
@@ -5379,25 +5823,29 @@
       <c r="D117" s="16">
         <v>302</v>
       </c>
-      <c r="E117" s="68">
+      <c r="E117" s="63">
         <v>1</v>
       </c>
-      <c r="F117" s="39" t="s">
-        <v>110</v>
+      <c r="F117" s="37" t="s">
+        <v>113</v>
       </c>
       <c r="G117" s="19">
         <v>1234568005</v>
       </c>
-      <c r="H117" s="44"/>
-      <c r="I117" s="32"/>
-      <c r="J117" s="33"/>
-      <c r="K117" s="33"/>
-      <c r="L117" s="33"/>
-      <c r="M117" s="33"/>
-      <c r="N117" s="33"/>
+      <c r="H117" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I117" s="20">
+        <v>10114</v>
+      </c>
+      <c r="J117" s="32"/>
+      <c r="K117" s="32"/>
+      <c r="L117" s="32"/>
+      <c r="M117" s="32"/>
+      <c r="N117" s="32"/>
       <c r="O117" s="21"/>
-      <c r="P117" s="33"/>
-      <c r="Q117" s="33"/>
+      <c r="P117" s="32"/>
+      <c r="Q117" s="32"/>
       <c r="R117" s="23"/>
       <c r="S117" s="21"/>
     </row>
@@ -5406,17 +5854,21 @@
       <c r="B118" s="15"/>
       <c r="C118" s="15"/>
       <c r="D118" s="24"/>
-      <c r="E118" s="38">
+      <c r="E118" s="36">
         <v>2</v>
       </c>
-      <c r="F118" s="63" t="s">
-        <v>111</v>
+      <c r="F118" s="59" t="s">
+        <v>114</v>
       </c>
       <c r="G118" s="19">
         <v>1234568006</v>
       </c>
-      <c r="H118" s="43"/>
-      <c r="I118" s="20"/>
+      <c r="H118" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I118" s="20">
+        <v>10115</v>
+      </c>
       <c r="J118" s="21"/>
       <c r="K118" s="21"/>
       <c r="L118" s="21"/>
@@ -5436,14 +5888,18 @@
       <c r="E119" s="27">
         <v>3</v>
       </c>
-      <c r="F119" s="57" t="s">
-        <v>112</v>
+      <c r="F119" s="53" t="s">
+        <v>115</v>
       </c>
       <c r="G119" s="19">
         <v>1234568007</v>
       </c>
-      <c r="H119" s="44"/>
-      <c r="I119" s="20"/>
+      <c r="H119" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I119" s="20">
+        <v>10116</v>
+      </c>
       <c r="J119" s="21"/>
       <c r="K119" s="21"/>
       <c r="L119" s="21"/>
@@ -5460,17 +5916,21 @@
       <c r="B120" s="15"/>
       <c r="C120" s="15"/>
       <c r="D120" s="24"/>
-      <c r="E120" s="38">
+      <c r="E120" s="36">
         <v>4</v>
       </c>
-      <c r="F120" s="94" t="s">
-        <v>113</v>
+      <c r="F120" s="83" t="s">
+        <v>116</v>
       </c>
       <c r="G120" s="19">
         <v>1234568008</v>
       </c>
-      <c r="H120" s="43"/>
-      <c r="I120" s="20"/>
+      <c r="H120" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I120" s="20">
+        <v>10117</v>
+      </c>
       <c r="J120" s="21"/>
       <c r="K120" s="21"/>
       <c r="L120" s="21"/>
@@ -5490,21 +5950,25 @@
       <c r="E121" s="27">
         <v>5</v>
       </c>
-      <c r="F121" s="40" t="s">
-        <v>114</v>
+      <c r="F121" s="38" t="s">
+        <v>117</v>
       </c>
       <c r="G121" s="19">
         <v>1234568009</v>
       </c>
-      <c r="H121" s="44"/>
-      <c r="I121" s="41"/>
-      <c r="J121" s="42"/>
-      <c r="K121" s="42"/>
-      <c r="L121" s="42"/>
-      <c r="M121" s="42"/>
-      <c r="N121" s="42"/>
+      <c r="H121" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I121" s="20">
+        <v>10118</v>
+      </c>
+      <c r="J121" s="39"/>
+      <c r="K121" s="39"/>
+      <c r="L121" s="39"/>
+      <c r="M121" s="39"/>
+      <c r="N121" s="39"/>
       <c r="O121" s="21"/>
-      <c r="P121" s="42"/>
+      <c r="P121" s="39"/>
       <c r="Q121" s="21"/>
       <c r="R121" s="23"/>
       <c r="S121" s="21"/>
@@ -5513,28 +5977,32 @@
       <c r="A122" s="15"/>
       <c r="B122" s="15"/>
       <c r="C122" s="15"/>
-      <c r="D122" s="61"/>
-      <c r="E122" s="95">
-        <v>6</v>
-      </c>
-      <c r="F122" s="35" t="s">
-        <v>115</v>
+      <c r="D122" s="57"/>
+      <c r="E122" s="84">
+        <v>6</v>
+      </c>
+      <c r="F122" s="34" t="s">
+        <v>118</v>
       </c>
       <c r="G122" s="19">
         <v>1234568010</v>
       </c>
-      <c r="H122" s="43"/>
-      <c r="I122" s="36"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
-      <c r="R122" s="92"/>
-      <c r="S122" s="37"/>
+      <c r="H122" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I122" s="20">
+        <v>10119</v>
+      </c>
+      <c r="J122" s="35"/>
+      <c r="K122" s="35"/>
+      <c r="L122" s="35"/>
+      <c r="M122" s="35"/>
+      <c r="N122" s="35"/>
+      <c r="O122" s="35"/>
+      <c r="P122" s="35"/>
+      <c r="Q122" s="35"/>
+      <c r="R122" s="81"/>
+      <c r="S122" s="35"/>
     </row>
     <row r="123" ht="16.35" spans="1:19">
       <c r="A123" s="15"/>
@@ -5543,27 +6011,31 @@
       <c r="D123" s="16">
         <v>303</v>
       </c>
-      <c r="E123" s="49">
+      <c r="E123" s="45">
         <v>1</v>
       </c>
-      <c r="F123" s="96" t="s">
-        <v>116</v>
+      <c r="F123" s="85" t="s">
+        <v>119</v>
       </c>
       <c r="G123" s="19">
         <v>1234568011</v>
       </c>
-      <c r="H123" s="44"/>
-      <c r="I123" s="32"/>
-      <c r="J123" s="33"/>
-      <c r="K123" s="33"/>
-      <c r="L123" s="33"/>
-      <c r="M123" s="33"/>
-      <c r="N123" s="33"/>
-      <c r="O123" s="33"/>
-      <c r="P123" s="33"/>
-      <c r="Q123" s="33"/>
-      <c r="R123" s="34"/>
-      <c r="S123" s="33"/>
+      <c r="H123" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I123" s="20">
+        <v>10120</v>
+      </c>
+      <c r="J123" s="32"/>
+      <c r="K123" s="32"/>
+      <c r="L123" s="32"/>
+      <c r="M123" s="32"/>
+      <c r="N123" s="32"/>
+      <c r="O123" s="32"/>
+      <c r="P123" s="32"/>
+      <c r="Q123" s="32"/>
+      <c r="R123" s="33"/>
+      <c r="S123" s="32"/>
     </row>
     <row r="124" spans="1:19">
       <c r="A124" s="15"/>
@@ -5574,13 +6046,17 @@
         <v>2</v>
       </c>
       <c r="F124" s="25" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G124" s="19">
         <v>1234568012</v>
       </c>
-      <c r="H124" s="43"/>
-      <c r="I124" s="20"/>
+      <c r="H124" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I124" s="20">
+        <v>10121</v>
+      </c>
       <c r="J124" s="21"/>
       <c r="K124" s="21"/>
       <c r="L124" s="21"/>
@@ -5601,13 +6077,17 @@
         <v>3</v>
       </c>
       <c r="F125" s="25" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G125" s="19">
         <v>1234568013</v>
       </c>
-      <c r="H125" s="44"/>
-      <c r="I125" s="20"/>
+      <c r="H125" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I125" s="20">
+        <v>10122</v>
+      </c>
       <c r="J125" s="21"/>
       <c r="K125" s="21"/>
       <c r="L125" s="21"/>
@@ -5627,14 +6107,18 @@
       <c r="E126" s="17">
         <v>4</v>
       </c>
-      <c r="F126" s="40" t="s">
-        <v>119</v>
+      <c r="F126" s="38" t="s">
+        <v>122</v>
       </c>
       <c r="G126" s="19">
         <v>1234568014</v>
       </c>
-      <c r="H126" s="43"/>
-      <c r="I126" s="20"/>
+      <c r="H126" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I126" s="20">
+        <v>10123</v>
+      </c>
       <c r="J126" s="21"/>
       <c r="K126" s="21"/>
       <c r="L126" s="21"/>
@@ -5654,14 +6138,18 @@
       <c r="E127" s="17">
         <v>5</v>
       </c>
-      <c r="F127" s="56" t="s">
-        <v>120</v>
+      <c r="F127" s="52" t="s">
+        <v>123</v>
       </c>
       <c r="G127" s="19">
         <v>1234568015</v>
       </c>
-      <c r="H127" s="44"/>
-      <c r="I127" s="20"/>
+      <c r="H127" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I127" s="20">
+        <v>10124</v>
+      </c>
       <c r="J127" s="21"/>
       <c r="K127" s="21"/>
       <c r="L127" s="21"/>
@@ -5681,19 +6169,23 @@
       <c r="E128" s="27">
         <v>6</v>
       </c>
-      <c r="F128" s="71" t="s">
-        <v>121</v>
+      <c r="F128" s="65" t="s">
+        <v>124</v>
       </c>
       <c r="G128" s="19">
         <v>1234568016</v>
       </c>
-      <c r="H128" s="43"/>
-      <c r="I128" s="36"/>
-      <c r="J128" s="37"/>
-      <c r="K128" s="37"/>
-      <c r="L128" s="37"/>
-      <c r="M128" s="37"/>
-      <c r="N128" s="37"/>
+      <c r="H128" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I128" s="20">
+        <v>10125</v>
+      </c>
+      <c r="J128" s="35"/>
+      <c r="K128" s="35"/>
+      <c r="L128" s="35"/>
+      <c r="M128" s="35"/>
+      <c r="N128" s="35"/>
       <c r="O128" s="21"/>
       <c r="P128" s="21"/>
       <c r="Q128" s="21"/>
@@ -5707,24 +6199,28 @@
       <c r="D129" s="16">
         <v>304</v>
       </c>
-      <c r="E129" s="49">
+      <c r="E129" s="45">
         <v>1</v>
       </c>
-      <c r="F129" s="72" t="s">
-        <v>122</v>
+      <c r="F129" s="66" t="s">
+        <v>125</v>
       </c>
       <c r="G129" s="19">
         <v>1234568017</v>
       </c>
-      <c r="H129" s="44"/>
-      <c r="I129" s="67"/>
-      <c r="J129" s="46"/>
+      <c r="H129" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I129" s="20">
+        <v>10126</v>
+      </c>
+      <c r="J129" s="42"/>
       <c r="K129" s="22"/>
-      <c r="L129" s="46"/>
+      <c r="L129" s="42"/>
       <c r="M129" s="22"/>
-      <c r="N129" s="46"/>
+      <c r="N129" s="42"/>
       <c r="O129" s="21"/>
-      <c r="P129" s="46"/>
+      <c r="P129" s="42"/>
       <c r="Q129" s="21"/>
       <c r="R129" s="23"/>
       <c r="S129" s="21"/>
@@ -5734,17 +6230,21 @@
       <c r="B130" s="15"/>
       <c r="C130" s="15"/>
       <c r="D130" s="24"/>
-      <c r="E130" s="49">
+      <c r="E130" s="45">
         <v>2</v>
       </c>
-      <c r="F130" s="39" t="s">
-        <v>123</v>
+      <c r="F130" s="37" t="s">
+        <v>126</v>
       </c>
       <c r="G130" s="19">
         <v>1234568018</v>
       </c>
-      <c r="H130" s="43"/>
-      <c r="I130" s="20"/>
+      <c r="H130" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I130" s="20">
+        <v>10127</v>
+      </c>
       <c r="J130" s="21"/>
       <c r="K130" s="21"/>
       <c r="L130" s="21"/>
@@ -5764,23 +6264,27 @@
       <c r="E131" s="27">
         <v>3</v>
       </c>
-      <c r="F131" s="84" t="s">
-        <v>124</v>
+      <c r="F131" s="75" t="s">
+        <v>127</v>
       </c>
       <c r="G131" s="19">
         <v>1234568019</v>
       </c>
-      <c r="H131" s="44"/>
-      <c r="I131" s="41"/>
-      <c r="J131" s="42"/>
-      <c r="K131" s="42"/>
-      <c r="L131" s="42"/>
-      <c r="M131" s="42"/>
-      <c r="N131" s="42"/>
-      <c r="O131" s="42"/>
-      <c r="P131" s="42"/>
-      <c r="Q131" s="42"/>
-      <c r="R131" s="97"/>
+      <c r="H131" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I131" s="20">
+        <v>10128</v>
+      </c>
+      <c r="J131" s="39"/>
+      <c r="K131" s="39"/>
+      <c r="L131" s="39"/>
+      <c r="M131" s="39"/>
+      <c r="N131" s="39"/>
+      <c r="O131" s="39"/>
+      <c r="P131" s="39"/>
+      <c r="Q131" s="39"/>
+      <c r="R131" s="86"/>
       <c r="S131" s="21"/>
     </row>
     <row r="132" ht="17.1" spans="1:19">
@@ -5788,14 +6292,20 @@
       <c r="B132" s="15"/>
       <c r="C132" s="15"/>
       <c r="D132" s="24"/>
-      <c r="E132" s="38">
+      <c r="E132" s="36">
         <v>4</v>
       </c>
-      <c r="F132" s="58" t="s">
-        <v>34</v>
+      <c r="F132" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G132" s="19">
         <v>1234568020</v>
+      </c>
+      <c r="H132" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I132" s="20">
+        <v>10129</v>
       </c>
     </row>
     <row r="133" ht="17.1" spans="1:19">
@@ -5806,21 +6316,25 @@
       <c r="E133" s="27">
         <v>5</v>
       </c>
-      <c r="F133" s="44" t="s">
-        <v>125</v>
+      <c r="F133" s="41" t="s">
+        <v>128</v>
       </c>
       <c r="G133" s="19">
         <v>1234568021</v>
       </c>
-      <c r="H133" s="44"/>
-      <c r="I133" s="41"/>
+      <c r="H133" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I133" s="20">
+        <v>10130</v>
+      </c>
       <c r="J133" s="21"/>
       <c r="K133" s="21"/>
       <c r="L133" s="21"/>
       <c r="M133" s="21"/>
       <c r="N133" s="21"/>
       <c r="O133" s="21"/>
-      <c r="P133" s="42"/>
+      <c r="P133" s="39"/>
       <c r="Q133" s="21"/>
       <c r="R133" s="23"/>
       <c r="S133" s="21"/>
@@ -5829,28 +6343,32 @@
       <c r="A134" s="15"/>
       <c r="B134" s="15"/>
       <c r="C134" s="15"/>
-      <c r="D134" s="61"/>
-      <c r="E134" s="98">
-        <v>6</v>
-      </c>
-      <c r="F134" s="99" t="s">
-        <v>126</v>
+      <c r="D134" s="57"/>
+      <c r="E134" s="87">
+        <v>6</v>
+      </c>
+      <c r="F134" s="88" t="s">
+        <v>129</v>
       </c>
       <c r="G134" s="19">
         <v>1234568022</v>
       </c>
-      <c r="H134" s="43"/>
-      <c r="I134" s="41"/>
-      <c r="J134" s="42"/>
-      <c r="K134" s="42"/>
-      <c r="L134" s="42"/>
-      <c r="M134" s="42"/>
-      <c r="N134" s="42"/>
-      <c r="O134" s="42"/>
-      <c r="P134" s="42"/>
-      <c r="Q134" s="42"/>
-      <c r="R134" s="42"/>
-      <c r="S134" s="42"/>
+      <c r="H134" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I134" s="20">
+        <v>10131</v>
+      </c>
+      <c r="J134" s="39"/>
+      <c r="K134" s="39"/>
+      <c r="L134" s="39"/>
+      <c r="M134" s="39"/>
+      <c r="N134" s="39"/>
+      <c r="O134" s="39"/>
+      <c r="P134" s="39"/>
+      <c r="Q134" s="39"/>
+      <c r="R134" s="39"/>
+      <c r="S134" s="39"/>
     </row>
     <row r="135" spans="1:19">
       <c r="A135" s="15"/>
@@ -5862,14 +6380,18 @@
       <c r="E135" s="17">
         <v>1</v>
       </c>
-      <c r="F135" s="43" t="s">
-        <v>127</v>
+      <c r="F135" s="40" t="s">
+        <v>130</v>
       </c>
       <c r="G135" s="19">
         <v>1234568023</v>
       </c>
-      <c r="H135" s="44"/>
-      <c r="I135" s="20"/>
+      <c r="H135" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I135" s="20">
+        <v>10132</v>
+      </c>
       <c r="J135" s="21"/>
       <c r="K135" s="21"/>
       <c r="L135" s="21"/>
@@ -5886,27 +6408,31 @@
       <c r="B136" s="15"/>
       <c r="C136" s="15"/>
       <c r="D136" s="24"/>
-      <c r="E136" s="49">
+      <c r="E136" s="45">
         <v>2</v>
       </c>
-      <c r="F136" s="100" t="s">
-        <v>128</v>
+      <c r="F136" s="89" t="s">
+        <v>131</v>
       </c>
       <c r="G136" s="19">
         <v>1234568024</v>
       </c>
-      <c r="H136" s="43"/>
-      <c r="I136" s="32"/>
-      <c r="J136" s="33"/>
-      <c r="K136" s="33"/>
-      <c r="L136" s="33"/>
-      <c r="M136" s="33"/>
-      <c r="N136" s="33"/>
-      <c r="O136" s="33"/>
-      <c r="P136" s="33"/>
-      <c r="Q136" s="33"/>
-      <c r="R136" s="34"/>
-      <c r="S136" s="33"/>
+      <c r="H136" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I136" s="20">
+        <v>10133</v>
+      </c>
+      <c r="J136" s="32"/>
+      <c r="K136" s="32"/>
+      <c r="L136" s="32"/>
+      <c r="M136" s="32"/>
+      <c r="N136" s="32"/>
+      <c r="O136" s="32"/>
+      <c r="P136" s="32"/>
+      <c r="Q136" s="32"/>
+      <c r="R136" s="33"/>
+      <c r="S136" s="32"/>
     </row>
     <row r="137" spans="1:19">
       <c r="A137" s="15"/>
@@ -5917,13 +6443,17 @@
         <v>3</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="G137" s="19">
         <v>1234568025</v>
       </c>
-      <c r="H137" s="44"/>
-      <c r="I137" s="20"/>
+      <c r="H137" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I137" s="20">
+        <v>10134</v>
+      </c>
       <c r="J137" s="21"/>
       <c r="K137" s="21"/>
       <c r="L137" s="21"/>
@@ -5943,14 +6473,18 @@
       <c r="E138" s="17">
         <v>4</v>
       </c>
-      <c r="F138" s="84" t="s">
-        <v>130</v>
+      <c r="F138" s="75" t="s">
+        <v>133</v>
       </c>
       <c r="G138" s="19">
         <v>1234568026</v>
       </c>
-      <c r="H138" s="43"/>
-      <c r="I138" s="20"/>
+      <c r="H138" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I138" s="20">
+        <v>10135</v>
+      </c>
       <c r="J138" s="21"/>
       <c r="K138" s="21"/>
       <c r="L138" s="21"/>
@@ -5970,14 +6504,18 @@
       <c r="E139" s="17">
         <v>5</v>
       </c>
-      <c r="F139" s="43" t="s">
-        <v>131</v>
+      <c r="F139" s="40" t="s">
+        <v>134</v>
       </c>
       <c r="G139" s="19">
         <v>1234568027</v>
       </c>
-      <c r="H139" s="44"/>
-      <c r="I139" s="21"/>
+      <c r="H139" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I139" s="20">
+        <v>10136</v>
+      </c>
       <c r="J139" s="21"/>
       <c r="K139" s="21"/>
       <c r="L139" s="21"/>
@@ -5993,18 +6531,22 @@
       <c r="A140" s="15"/>
       <c r="B140" s="15"/>
       <c r="C140" s="15"/>
-      <c r="D140" s="61"/>
+      <c r="D140" s="57"/>
       <c r="E140" s="27">
         <v>6</v>
       </c>
-      <c r="F140" s="66" t="s">
-        <v>132</v>
+      <c r="F140" s="62" t="s">
+        <v>135</v>
       </c>
       <c r="G140" s="19">
         <v>1234568028</v>
       </c>
-      <c r="H140" s="43"/>
-      <c r="I140" s="20"/>
+      <c r="H140" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I140" s="20">
+        <v>10137</v>
+      </c>
       <c r="J140" s="21"/>
       <c r="K140" s="21"/>
       <c r="L140" s="21"/>
@@ -6023,17 +6565,21 @@
       <c r="D141" s="16">
         <v>306</v>
       </c>
-      <c r="E141" s="49">
+      <c r="E141" s="45">
         <v>1</v>
       </c>
-      <c r="F141" s="101" t="s">
-        <v>133</v>
+      <c r="F141" s="90" t="s">
+        <v>136</v>
       </c>
       <c r="G141" s="19">
         <v>1234568029</v>
       </c>
-      <c r="H141" s="44"/>
-      <c r="I141" s="20"/>
+      <c r="H141" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I141" s="20">
+        <v>10138</v>
+      </c>
       <c r="J141" s="21"/>
       <c r="K141" s="21"/>
       <c r="L141" s="21"/>
@@ -6053,14 +6599,18 @@
       <c r="E142" s="17">
         <v>2</v>
       </c>
-      <c r="F142" s="102" t="s">
-        <v>134</v>
+      <c r="F142" s="91" t="s">
+        <v>137</v>
       </c>
       <c r="G142" s="19">
         <v>1234568030</v>
       </c>
-      <c r="H142" s="43"/>
-      <c r="I142" s="20"/>
+      <c r="H142" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I142" s="20">
+        <v>10139</v>
+      </c>
       <c r="J142" s="21"/>
       <c r="K142" s="21"/>
       <c r="L142" s="21"/>
@@ -6077,17 +6627,21 @@
       <c r="B143" s="15"/>
       <c r="C143" s="15"/>
       <c r="D143" s="24"/>
-      <c r="E143" s="38">
+      <c r="E143" s="36">
         <v>3</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G143" s="19">
         <v>1234568031</v>
       </c>
-      <c r="H143" s="44"/>
-      <c r="I143" s="20"/>
+      <c r="H143" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I143" s="20">
+        <v>10140</v>
+      </c>
       <c r="J143" s="21"/>
       <c r="K143" s="21"/>
       <c r="L143" s="21"/>
@@ -6107,19 +6661,23 @@
       <c r="E144" s="17">
         <v>4</v>
       </c>
-      <c r="F144" s="39" t="s">
-        <v>136</v>
+      <c r="F144" s="37" t="s">
+        <v>139</v>
       </c>
       <c r="G144" s="19">
         <v>1234568032</v>
       </c>
-      <c r="H144" s="43"/>
-      <c r="I144" s="32"/>
-      <c r="J144" s="33"/>
-      <c r="K144" s="33"/>
-      <c r="L144" s="33"/>
-      <c r="M144" s="33"/>
-      <c r="N144" s="33"/>
+      <c r="H144" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I144" s="20">
+        <v>10141</v>
+      </c>
+      <c r="J144" s="32"/>
+      <c r="K144" s="32"/>
+      <c r="L144" s="32"/>
+      <c r="M144" s="32"/>
+      <c r="N144" s="32"/>
       <c r="O144" s="21"/>
       <c r="P144" s="21"/>
       <c r="Q144" s="21"/>
@@ -6131,17 +6689,21 @@
       <c r="B145" s="15"/>
       <c r="C145" s="15"/>
       <c r="D145" s="24"/>
-      <c r="E145" s="38">
+      <c r="E145" s="36">
         <v>5</v>
       </c>
-      <c r="F145" s="56" t="s">
-        <v>137</v>
+      <c r="F145" s="52" t="s">
+        <v>140</v>
       </c>
       <c r="G145" s="19">
         <v>1234568033</v>
       </c>
-      <c r="H145" s="44"/>
-      <c r="I145" s="20"/>
+      <c r="H145" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I145" s="20">
+        <v>10142</v>
+      </c>
       <c r="J145" s="21"/>
       <c r="K145" s="21"/>
       <c r="L145" s="21"/>
@@ -6157,25 +6719,29 @@
       <c r="A146" s="15"/>
       <c r="B146" s="15"/>
       <c r="C146" s="15"/>
-      <c r="D146" s="61"/>
+      <c r="D146" s="57"/>
       <c r="E146" s="27">
         <v>6</v>
       </c>
-      <c r="F146" s="103" t="s">
-        <v>138</v>
+      <c r="F146" s="92" t="s">
+        <v>141</v>
       </c>
       <c r="G146" s="19">
         <v>1234568034</v>
       </c>
-      <c r="H146" s="43"/>
-      <c r="I146" s="36"/>
-      <c r="J146" s="37"/>
-      <c r="K146" s="37"/>
-      <c r="L146" s="37"/>
-      <c r="M146" s="37"/>
-      <c r="N146" s="37"/>
+      <c r="H146" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I146" s="20">
+        <v>10143</v>
+      </c>
+      <c r="J146" s="35"/>
+      <c r="K146" s="35"/>
+      <c r="L146" s="35"/>
+      <c r="M146" s="35"/>
+      <c r="N146" s="35"/>
       <c r="O146" s="21"/>
-      <c r="P146" s="37"/>
+      <c r="P146" s="35"/>
       <c r="Q146" s="21"/>
       <c r="R146" s="23"/>
       <c r="S146" s="21"/>
@@ -6187,24 +6753,28 @@
       <c r="D147" s="16">
         <v>307</v>
       </c>
-      <c r="E147" s="49">
+      <c r="E147" s="45">
         <v>1</v>
       </c>
-      <c r="F147" s="39" t="s">
-        <v>139</v>
+      <c r="F147" s="37" t="s">
+        <v>142</v>
       </c>
       <c r="G147" s="19">
         <v>1234568035</v>
       </c>
-      <c r="H147" s="44"/>
-      <c r="I147" s="32"/>
-      <c r="J147" s="33"/>
-      <c r="K147" s="33"/>
-      <c r="L147" s="33"/>
-      <c r="M147" s="33"/>
-      <c r="N147" s="33"/>
+      <c r="H147" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I147" s="20">
+        <v>10144</v>
+      </c>
+      <c r="J147" s="32"/>
+      <c r="K147" s="32"/>
+      <c r="L147" s="32"/>
+      <c r="M147" s="32"/>
+      <c r="N147" s="32"/>
       <c r="O147" s="21"/>
-      <c r="P147" s="33"/>
+      <c r="P147" s="32"/>
       <c r="Q147" s="21"/>
       <c r="R147" s="23"/>
       <c r="S147" s="21"/>
@@ -6217,26 +6787,30 @@
       <c r="E148" s="17">
         <v>2</v>
       </c>
-      <c r="F148" s="104" t="s">
-        <v>140</v>
+      <c r="F148" s="93" t="s">
+        <v>143</v>
       </c>
       <c r="G148" s="19">
         <v>1234568036</v>
       </c>
-      <c r="H148" s="43"/>
-      <c r="I148" s="20"/>
+      <c r="H148" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I148" s="20">
+        <v>10145</v>
+      </c>
       <c r="J148" s="21"/>
       <c r="K148" s="21"/>
       <c r="L148" s="21"/>
       <c r="M148" s="21"/>
       <c r="N148" s="21"/>
       <c r="O148" s="21"/>
-      <c r="P148" s="101"/>
+      <c r="P148" s="90"/>
       <c r="Q148" s="21"/>
       <c r="R148" s="23"/>
       <c r="S148" s="21"/>
       <c r="U148" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="149" spans="1:21">
@@ -6247,14 +6821,18 @@
       <c r="E149" s="17">
         <v>3</v>
       </c>
-      <c r="F149" s="43" t="s">
-        <v>142</v>
+      <c r="F149" s="40" t="s">
+        <v>145</v>
       </c>
       <c r="G149" s="19">
         <v>1234568037</v>
       </c>
-      <c r="H149" s="44"/>
-      <c r="I149" s="20"/>
+      <c r="H149" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I149" s="20">
+        <v>10146</v>
+      </c>
       <c r="J149" s="21"/>
       <c r="K149" s="21"/>
       <c r="L149" s="21"/>
@@ -6274,19 +6852,23 @@
       <c r="E150" s="17">
         <v>4</v>
       </c>
-      <c r="F150" s="43" t="s">
-        <v>143</v>
+      <c r="F150" s="40" t="s">
+        <v>146</v>
       </c>
       <c r="G150" s="19">
         <v>1234568038</v>
       </c>
-      <c r="H150" s="43"/>
-      <c r="I150" s="32"/>
-      <c r="J150" s="33"/>
-      <c r="K150" s="33"/>
-      <c r="L150" s="33"/>
-      <c r="M150" s="33"/>
-      <c r="N150" s="33"/>
+      <c r="H150" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I150" s="20">
+        <v>10147</v>
+      </c>
+      <c r="J150" s="32"/>
+      <c r="K150" s="32"/>
+      <c r="L150" s="32"/>
+      <c r="M150" s="32"/>
+      <c r="N150" s="32"/>
       <c r="O150" s="21"/>
       <c r="P150" s="21"/>
       <c r="Q150" s="21"/>
@@ -6301,14 +6883,18 @@
       <c r="E151" s="17">
         <v>5</v>
       </c>
-      <c r="F151" s="103" t="s">
-        <v>144</v>
+      <c r="F151" s="92" t="s">
+        <v>147</v>
       </c>
       <c r="G151" s="19">
         <v>1234568039</v>
       </c>
-      <c r="H151" s="44"/>
-      <c r="I151" s="20"/>
+      <c r="H151" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I151" s="20">
+        <v>10148</v>
+      </c>
       <c r="J151" s="21"/>
       <c r="K151" s="21"/>
       <c r="L151" s="21"/>
@@ -6328,14 +6914,18 @@
       <c r="E152" s="17">
         <v>6</v>
       </c>
-      <c r="F152" s="105" t="s">
-        <v>145</v>
+      <c r="F152" s="94" t="s">
+        <v>148</v>
       </c>
       <c r="G152" s="19">
         <v>1234568040</v>
       </c>
-      <c r="H152" s="43"/>
-      <c r="I152" s="20"/>
+      <c r="H152" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I152" s="20">
+        <v>10149</v>
+      </c>
       <c r="J152" s="21"/>
       <c r="K152" s="21"/>
       <c r="L152" s="21"/>
@@ -6354,27 +6944,31 @@
       <c r="D153" s="16">
         <v>308</v>
       </c>
-      <c r="E153" s="49">
+      <c r="E153" s="45">
         <v>1</v>
       </c>
-      <c r="F153" s="39" t="s">
-        <v>146</v>
+      <c r="F153" s="37" t="s">
+        <v>149</v>
       </c>
       <c r="G153" s="19">
         <v>1234568041</v>
       </c>
-      <c r="H153" s="44"/>
-      <c r="I153" s="32"/>
-      <c r="J153" s="33"/>
-      <c r="K153" s="33"/>
-      <c r="L153" s="33"/>
-      <c r="M153" s="33"/>
-      <c r="N153" s="33"/>
-      <c r="O153" s="33"/>
-      <c r="P153" s="33"/>
-      <c r="Q153" s="33"/>
-      <c r="R153" s="34"/>
-      <c r="S153" s="33"/>
+      <c r="H153" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I153" s="20">
+        <v>10150</v>
+      </c>
+      <c r="J153" s="32"/>
+      <c r="K153" s="32"/>
+      <c r="L153" s="32"/>
+      <c r="M153" s="32"/>
+      <c r="N153" s="32"/>
+      <c r="O153" s="32"/>
+      <c r="P153" s="32"/>
+      <c r="Q153" s="32"/>
+      <c r="R153" s="33"/>
+      <c r="S153" s="32"/>
     </row>
     <row r="154" ht="16.35" spans="1:21">
       <c r="A154" s="15"/>
@@ -6384,14 +6978,18 @@
       <c r="E154" s="17">
         <v>2</v>
       </c>
-      <c r="F154" s="35" t="s">
-        <v>147</v>
+      <c r="F154" s="34" t="s">
+        <v>150</v>
       </c>
       <c r="G154" s="19">
         <v>1234568042</v>
       </c>
-      <c r="H154" s="43"/>
-      <c r="I154" s="20"/>
+      <c r="H154" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I154" s="20">
+        <v>10151</v>
+      </c>
       <c r="J154" s="21"/>
       <c r="K154" s="21"/>
       <c r="L154" s="21"/>
@@ -6411,14 +7009,18 @@
       <c r="E155" s="17">
         <v>3</v>
       </c>
-      <c r="F155" s="54" t="s">
-        <v>148</v>
+      <c r="F155" s="50" t="s">
+        <v>151</v>
       </c>
       <c r="G155" s="19">
         <v>1234568043</v>
       </c>
-      <c r="H155" s="44"/>
-      <c r="I155" s="20"/>
+      <c r="H155" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I155" s="20">
+        <v>10152</v>
+      </c>
       <c r="J155" s="21"/>
       <c r="K155" s="21"/>
       <c r="L155" s="21"/>
@@ -6439,13 +7041,17 @@
         <v>4</v>
       </c>
       <c r="F156" s="25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G156" s="19">
         <v>1234568044</v>
       </c>
-      <c r="H156" s="43"/>
-      <c r="I156" s="20"/>
+      <c r="H156" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I156" s="20">
+        <v>10153</v>
+      </c>
       <c r="J156" s="21"/>
       <c r="K156" s="21"/>
       <c r="L156" s="21"/>
@@ -6465,14 +7071,18 @@
       <c r="E157" s="30">
         <v>5</v>
       </c>
-      <c r="F157" s="35" t="s">
-        <v>150</v>
+      <c r="F157" s="34" t="s">
+        <v>153</v>
       </c>
       <c r="G157" s="19">
         <v>1234568045</v>
       </c>
-      <c r="H157" s="44"/>
-      <c r="I157" s="20"/>
+      <c r="H157" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I157" s="20">
+        <v>10154</v>
+      </c>
       <c r="J157" s="21"/>
       <c r="K157" s="21"/>
       <c r="L157" s="21"/>
@@ -6488,28 +7098,32 @@
       <c r="A158" s="15"/>
       <c r="B158" s="15"/>
       <c r="C158" s="15"/>
-      <c r="D158" s="61"/>
+      <c r="D158" s="57"/>
       <c r="E158" s="27">
         <v>6</v>
       </c>
-      <c r="F158" s="40" t="s">
-        <v>151</v>
+      <c r="F158" s="38" t="s">
+        <v>154</v>
       </c>
       <c r="G158" s="19">
         <v>1234568046</v>
       </c>
-      <c r="H158" s="43"/>
-      <c r="I158" s="41"/>
-      <c r="J158" s="42"/>
-      <c r="K158" s="42"/>
-      <c r="L158" s="42"/>
-      <c r="M158" s="42"/>
-      <c r="N158" s="42"/>
-      <c r="O158" s="42"/>
-      <c r="P158" s="42"/>
-      <c r="Q158" s="42"/>
-      <c r="R158" s="97"/>
-      <c r="S158" s="42"/>
+      <c r="H158" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I158" s="20">
+        <v>10155</v>
+      </c>
+      <c r="J158" s="39"/>
+      <c r="K158" s="39"/>
+      <c r="L158" s="39"/>
+      <c r="M158" s="39"/>
+      <c r="N158" s="39"/>
+      <c r="O158" s="39"/>
+      <c r="P158" s="39"/>
+      <c r="Q158" s="39"/>
+      <c r="R158" s="86"/>
+      <c r="S158" s="39"/>
     </row>
     <row r="159" ht="17.1" spans="1:21">
       <c r="A159" s="15"/>
@@ -6518,17 +7132,21 @@
       <c r="D159" s="16">
         <v>309</v>
       </c>
-      <c r="E159" s="49">
+      <c r="E159" s="45">
         <v>1</v>
       </c>
-      <c r="F159" s="69" t="s">
-        <v>152</v>
+      <c r="F159" s="64" t="s">
+        <v>155</v>
       </c>
       <c r="G159" s="19">
         <v>1234568047</v>
       </c>
-      <c r="H159" s="44"/>
-      <c r="I159" s="21"/>
+      <c r="H159" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I159" s="20">
+        <v>10156</v>
+      </c>
       <c r="J159" s="21"/>
       <c r="K159" s="21"/>
       <c r="L159" s="21"/>
@@ -6548,14 +7166,18 @@
       <c r="E160" s="17">
         <v>2</v>
       </c>
-      <c r="F160" s="40" t="s">
-        <v>153</v>
+      <c r="F160" s="38" t="s">
+        <v>156</v>
       </c>
       <c r="G160" s="19">
         <v>1234568048</v>
       </c>
-      <c r="H160" s="40"/>
-      <c r="I160" s="20"/>
+      <c r="H160" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I160" s="20">
+        <v>10157</v>
+      </c>
       <c r="J160" s="21"/>
       <c r="K160" s="21"/>
       <c r="L160" s="21"/>
@@ -6575,14 +7197,18 @@
       <c r="E161" s="17">
         <v>3</v>
       </c>
-      <c r="F161" s="56" t="s">
-        <v>154</v>
+      <c r="F161" s="52" t="s">
+        <v>157</v>
       </c>
       <c r="G161" s="19">
         <v>1234568049</v>
       </c>
-      <c r="H161" s="56"/>
-      <c r="I161" s="20"/>
+      <c r="H161" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I161" s="20">
+        <v>10158</v>
+      </c>
       <c r="J161" s="21"/>
       <c r="K161" s="21"/>
       <c r="L161" s="21"/>
@@ -6602,14 +7228,18 @@
       <c r="E162" s="17">
         <v>4</v>
       </c>
-      <c r="F162" s="56" t="s">
-        <v>155</v>
+      <c r="F162" s="52" t="s">
+        <v>158</v>
       </c>
       <c r="G162" s="19">
         <v>1234568050</v>
       </c>
-      <c r="H162" s="40"/>
-      <c r="I162" s="20"/>
+      <c r="H162" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I162" s="20">
+        <v>10159</v>
+      </c>
       <c r="J162" s="21"/>
       <c r="K162" s="21"/>
       <c r="L162" s="21"/>
@@ -6630,13 +7260,17 @@
         <v>5</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G163" s="19">
         <v>1234568051</v>
       </c>
-      <c r="H163" s="56"/>
-      <c r="I163" s="22"/>
+      <c r="H163" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I163" s="20">
+        <v>10160</v>
+      </c>
       <c r="J163" s="22"/>
       <c r="K163" s="22"/>
       <c r="L163" s="22"/>
@@ -6652,18 +7286,22 @@
       <c r="A164" s="15"/>
       <c r="B164" s="15"/>
       <c r="C164" s="15"/>
-      <c r="D164" s="61"/>
-      <c r="E164" s="95">
-        <v>6</v>
-      </c>
-      <c r="F164" s="35" t="s">
-        <v>157</v>
+      <c r="D164" s="57"/>
+      <c r="E164" s="84">
+        <v>6</v>
+      </c>
+      <c r="F164" s="34" t="s">
+        <v>160</v>
       </c>
       <c r="G164" s="19">
         <v>1234568052</v>
       </c>
-      <c r="H164" s="40"/>
-      <c r="I164" s="20"/>
+      <c r="H164" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I164" s="20">
+        <v>10161</v>
+      </c>
       <c r="J164" s="21"/>
       <c r="K164" s="21"/>
       <c r="L164" s="21"/>
@@ -6682,17 +7320,21 @@
       <c r="D165" s="16">
         <v>310</v>
       </c>
-      <c r="E165" s="68">
+      <c r="E165" s="63">
         <v>1</v>
       </c>
-      <c r="F165" s="43" t="s">
-        <v>158</v>
+      <c r="F165" s="40" t="s">
+        <v>161</v>
       </c>
       <c r="G165" s="19">
         <v>1234568053</v>
       </c>
-      <c r="H165" s="56"/>
-      <c r="I165" s="21"/>
+      <c r="H165" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I165" s="20">
+        <v>10162</v>
+      </c>
       <c r="J165" s="21"/>
       <c r="K165" s="21"/>
       <c r="L165" s="21"/>
@@ -6709,17 +7351,21 @@
       <c r="B166" s="15"/>
       <c r="C166" s="15"/>
       <c r="D166" s="24"/>
-      <c r="E166" s="38">
+      <c r="E166" s="36">
         <v>2</v>
       </c>
-      <c r="F166" s="43" t="s">
-        <v>159</v>
+      <c r="F166" s="40" t="s">
+        <v>162</v>
       </c>
       <c r="G166" s="19">
         <v>1234568054</v>
       </c>
-      <c r="H166" s="40"/>
-      <c r="I166" s="21"/>
+      <c r="H166" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I166" s="20">
+        <v>10163</v>
+      </c>
       <c r="J166" s="21"/>
       <c r="K166" s="21"/>
       <c r="L166" s="21"/>
@@ -6740,13 +7386,17 @@
         <v>3</v>
       </c>
       <c r="F167" s="25" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G167" s="19">
         <v>1234568055</v>
       </c>
-      <c r="H167" s="56"/>
-      <c r="I167" s="20"/>
+      <c r="H167" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I167" s="20">
+        <v>10164</v>
+      </c>
       <c r="J167" s="21"/>
       <c r="K167" s="21"/>
       <c r="L167" s="21"/>
@@ -6763,17 +7413,21 @@
       <c r="B168" s="15"/>
       <c r="C168" s="15"/>
       <c r="D168" s="24"/>
-      <c r="E168" s="38">
+      <c r="E168" s="36">
         <v>4</v>
       </c>
-      <c r="F168" s="65" t="s">
-        <v>161</v>
+      <c r="F168" s="61" t="s">
+        <v>164</v>
       </c>
       <c r="G168" s="19">
         <v>1234568056</v>
       </c>
-      <c r="H168" s="40"/>
-      <c r="I168" s="20"/>
+      <c r="H168" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I168" s="20">
+        <v>10165</v>
+      </c>
       <c r="J168" s="21"/>
       <c r="K168" s="21"/>
       <c r="L168" s="21"/>
@@ -6793,14 +7447,18 @@
       <c r="E169" s="27">
         <v>5</v>
       </c>
-      <c r="F169" s="56" t="s">
-        <v>162</v>
+      <c r="F169" s="52" t="s">
+        <v>165</v>
       </c>
       <c r="G169" s="19">
         <v>1234568057</v>
       </c>
-      <c r="H169" s="56"/>
-      <c r="I169" s="20"/>
+      <c r="H169" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I169" s="20">
+        <v>10166</v>
+      </c>
       <c r="J169" s="21"/>
       <c r="K169" s="21"/>
       <c r="L169" s="21"/>
@@ -6816,23 +7474,27 @@
       <c r="A170" s="15"/>
       <c r="B170" s="15"/>
       <c r="C170" s="15"/>
-      <c r="D170" s="61"/>
-      <c r="E170" s="95">
-        <v>6</v>
-      </c>
-      <c r="F170" s="35" t="s">
-        <v>163</v>
+      <c r="D170" s="57"/>
+      <c r="E170" s="84">
+        <v>6</v>
+      </c>
+      <c r="F170" s="34" t="s">
+        <v>166</v>
       </c>
       <c r="G170" s="19">
         <v>1234568058</v>
       </c>
-      <c r="H170" s="40"/>
-      <c r="I170" s="36"/>
-      <c r="J170" s="37"/>
-      <c r="K170" s="37"/>
-      <c r="L170" s="37"/>
-      <c r="M170" s="37"/>
-      <c r="N170" s="37"/>
+      <c r="H170" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I170" s="20">
+        <v>10167</v>
+      </c>
+      <c r="J170" s="35"/>
+      <c r="K170" s="35"/>
+      <c r="L170" s="35"/>
+      <c r="M170" s="35"/>
+      <c r="N170" s="35"/>
       <c r="O170" s="21"/>
       <c r="P170" s="21"/>
       <c r="Q170" s="21"/>
@@ -6846,22 +7508,26 @@
       <c r="D171" s="16">
         <v>311</v>
       </c>
-      <c r="E171" s="68">
+      <c r="E171" s="63">
         <v>1</v>
       </c>
-      <c r="F171" s="39" t="s">
-        <v>164</v>
+      <c r="F171" s="37" t="s">
+        <v>167</v>
       </c>
       <c r="G171" s="19">
         <v>1234568059</v>
       </c>
-      <c r="H171" s="56"/>
-      <c r="I171" s="32"/>
-      <c r="J171" s="33"/>
-      <c r="K171" s="33"/>
-      <c r="L171" s="33"/>
-      <c r="M171" s="33"/>
-      <c r="N171" s="33"/>
+      <c r="H171" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I171" s="20">
+        <v>10168</v>
+      </c>
+      <c r="J171" s="32"/>
+      <c r="K171" s="32"/>
+      <c r="L171" s="32"/>
+      <c r="M171" s="32"/>
+      <c r="N171" s="32"/>
       <c r="O171" s="21"/>
       <c r="P171" s="21"/>
       <c r="Q171" s="21"/>
@@ -6873,17 +7539,21 @@
       <c r="B172" s="15"/>
       <c r="C172" s="15"/>
       <c r="D172" s="24"/>
-      <c r="E172" s="49">
+      <c r="E172" s="45">
         <v>2</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G172" s="19">
         <v>1234568060</v>
       </c>
-      <c r="H172" s="40"/>
-      <c r="I172" s="32"/>
+      <c r="H172" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I172" s="20">
+        <v>10169</v>
+      </c>
       <c r="J172" s="21"/>
       <c r="K172" s="21"/>
       <c r="L172" s="21"/>
@@ -6903,14 +7573,18 @@
       <c r="E173" s="27">
         <v>3</v>
       </c>
-      <c r="F173" s="106" t="s">
-        <v>165</v>
+      <c r="F173" s="95" t="s">
+        <v>168</v>
       </c>
       <c r="G173" s="19">
         <v>1234568061</v>
       </c>
-      <c r="H173" s="56"/>
-      <c r="I173" s="32"/>
+      <c r="H173" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I173" s="20">
+        <v>10170</v>
+      </c>
       <c r="J173" s="21"/>
       <c r="K173" s="21"/>
       <c r="L173" s="21"/>
@@ -6927,17 +7601,21 @@
       <c r="B174" s="15"/>
       <c r="C174" s="15"/>
       <c r="D174" s="24"/>
-      <c r="E174" s="49">
+      <c r="E174" s="45">
         <v>4</v>
       </c>
-      <c r="F174" s="71" t="s">
-        <v>166</v>
+      <c r="F174" s="65" t="s">
+        <v>169</v>
       </c>
       <c r="G174" s="19">
         <v>1234568062</v>
       </c>
-      <c r="H174" s="40"/>
-      <c r="I174" s="21"/>
+      <c r="H174" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I174" s="20">
+        <v>10171</v>
+      </c>
       <c r="J174" s="21"/>
       <c r="K174" s="21"/>
       <c r="L174" s="21"/>
@@ -6957,14 +7635,18 @@
       <c r="E175" s="27">
         <v>5</v>
       </c>
-      <c r="F175" s="43" t="s">
-        <v>167</v>
+      <c r="F175" s="40" t="s">
+        <v>170</v>
       </c>
       <c r="G175" s="19">
         <v>1234568063</v>
       </c>
-      <c r="H175" s="56"/>
-      <c r="I175" s="21"/>
+      <c r="H175" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I175" s="20">
+        <v>10172</v>
+      </c>
       <c r="J175" s="21"/>
       <c r="K175" s="21"/>
       <c r="L175" s="21"/>
@@ -6980,25 +7662,29 @@
       <c r="A176" s="15"/>
       <c r="B176" s="15"/>
       <c r="C176" s="15"/>
-      <c r="D176" s="61"/>
-      <c r="E176" s="68">
-        <v>6</v>
-      </c>
-      <c r="F176" s="107" t="s">
-        <v>168</v>
+      <c r="D176" s="57"/>
+      <c r="E176" s="63">
+        <v>6</v>
+      </c>
+      <c r="F176" s="96" t="s">
+        <v>171</v>
       </c>
       <c r="G176" s="19">
         <v>1234568064</v>
       </c>
-      <c r="H176" s="40"/>
-      <c r="I176" s="21"/>
-      <c r="J176" s="37"/>
-      <c r="K176" s="37"/>
-      <c r="L176" s="37"/>
-      <c r="M176" s="37"/>
-      <c r="N176" s="37"/>
+      <c r="H176" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I176" s="20">
+        <v>10173</v>
+      </c>
+      <c r="J176" s="35"/>
+      <c r="K176" s="35"/>
+      <c r="L176" s="35"/>
+      <c r="M176" s="35"/>
+      <c r="N176" s="35"/>
       <c r="O176" s="21"/>
-      <c r="P176" s="37"/>
+      <c r="P176" s="35"/>
       <c r="Q176" s="21"/>
       <c r="R176" s="23"/>
       <c r="S176" s="21"/>
@@ -7010,19 +7696,23 @@
       <c r="D177" s="16">
         <v>312</v>
       </c>
-      <c r="E177" s="49">
+      <c r="E177" s="45">
         <v>1</v>
       </c>
-      <c r="F177" s="96" t="s">
-        <v>169</v>
+      <c r="F177" s="85" t="s">
+        <v>172</v>
       </c>
       <c r="G177" s="19">
         <v>1234568065</v>
       </c>
-      <c r="H177" s="56"/>
-      <c r="I177" s="32"/>
-      <c r="J177" s="33"/>
-      <c r="K177" s="33"/>
+      <c r="H177" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I177" s="20">
+        <v>10174</v>
+      </c>
+      <c r="J177" s="32"/>
+      <c r="K177" s="32"/>
       <c r="L177" s="21"/>
       <c r="M177" s="21"/>
       <c r="N177" s="21"/>
@@ -7040,41 +7730,49 @@
       <c r="E178" s="17">
         <v>2</v>
       </c>
-      <c r="F178" s="66" t="s">
-        <v>170</v>
+      <c r="F178" s="62" t="s">
+        <v>173</v>
       </c>
       <c r="G178" s="19">
         <v>1234568066</v>
       </c>
-      <c r="H178" s="40"/>
-      <c r="I178" s="41"/>
-      <c r="J178" s="42"/>
-      <c r="K178" s="42"/>
-      <c r="L178" s="42"/>
-      <c r="M178" s="42"/>
-      <c r="N178" s="42"/>
+      <c r="H178" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I178" s="20">
+        <v>10175</v>
+      </c>
+      <c r="J178" s="39"/>
+      <c r="K178" s="39"/>
+      <c r="L178" s="39"/>
+      <c r="M178" s="39"/>
+      <c r="N178" s="39"/>
       <c r="O178" s="21"/>
-      <c r="P178" s="42"/>
-      <c r="Q178" s="42"/>
+      <c r="P178" s="39"/>
+      <c r="Q178" s="39"/>
       <c r="R178" s="23"/>
       <c r="S178" s="21"/>
     </row>
     <row r="179" s="1" customFormat="1" ht="16.35" spans="1:20">
       <c r="A179" s="15"/>
       <c r="B179" s="15"/>
-      <c r="C179" s="108"/>
+      <c r="C179" s="97"/>
       <c r="D179" s="26"/>
       <c r="E179" s="27">
         <v>3</v>
       </c>
-      <c r="F179" s="39" t="s">
-        <v>171</v>
+      <c r="F179" s="37" t="s">
+        <v>174</v>
       </c>
       <c r="G179" s="19">
         <v>1234568067</v>
       </c>
-      <c r="H179" s="56"/>
-      <c r="I179" s="20"/>
+      <c r="H179" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I179" s="20">
+        <v>10176</v>
+      </c>
       <c r="J179" s="21"/>
       <c r="K179" s="21"/>
       <c r="L179" s="21"/>
@@ -7093,25 +7791,29 @@
       <c r="D180" s="29">
         <v>313</v>
       </c>
-      <c r="E180" s="49">
+      <c r="E180" s="45">
         <v>1</v>
       </c>
-      <c r="F180" s="39" t="s">
-        <v>172</v>
+      <c r="F180" s="37" t="s">
+        <v>175</v>
       </c>
       <c r="G180" s="19">
         <v>1234568068</v>
       </c>
-      <c r="H180" s="40"/>
-      <c r="I180" s="32"/>
-      <c r="J180" s="33"/>
-      <c r="K180" s="33"/>
-      <c r="L180" s="33"/>
-      <c r="M180" s="33"/>
-      <c r="N180" s="33"/>
+      <c r="H180" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I180" s="20">
+        <v>10177</v>
+      </c>
+      <c r="J180" s="32"/>
+      <c r="K180" s="32"/>
+      <c r="L180" s="32"/>
+      <c r="M180" s="32"/>
+      <c r="N180" s="32"/>
       <c r="O180" s="21"/>
-      <c r="P180" s="33"/>
-      <c r="Q180" s="33"/>
+      <c r="P180" s="32"/>
+      <c r="Q180" s="32"/>
       <c r="R180" s="23"/>
       <c r="S180" s="21"/>
     </row>
@@ -7123,15 +7825,20 @@
       <c r="E181" s="17">
         <v>2</v>
       </c>
-      <c r="F181" s="58" t="s">
-        <v>34</v>
+      <c r="F181" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G181" s="19">
         <v>1234568069</v>
       </c>
-      <c r="H181" s="73"/>
-      <c r="O181" s="74"/>
-      <c r="P181" s="33"/>
+      <c r="H181" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I181" s="20">
+        <v>10178</v>
+      </c>
+      <c r="O181" s="67"/>
+      <c r="P181" s="32"/>
     </row>
     <row r="182" ht="17.1" spans="1:20">
       <c r="A182" s="15"/>
@@ -7141,15 +7848,20 @@
       <c r="E182" s="17">
         <v>3</v>
       </c>
-      <c r="F182" s="58" t="s">
-        <v>34</v>
+      <c r="F182" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G182" s="19">
         <v>1234568070</v>
       </c>
-      <c r="H182" s="73"/>
-      <c r="O182" s="74"/>
-      <c r="P182" s="33"/>
+      <c r="H182" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I182" s="20">
+        <v>10179</v>
+      </c>
+      <c r="O182" s="67"/>
+      <c r="P182" s="32"/>
     </row>
     <row r="183" ht="16.35" spans="1:20">
       <c r="A183" s="15"/>
@@ -7159,21 +7871,25 @@
       <c r="E183" s="17">
         <v>4</v>
       </c>
-      <c r="F183" s="109" t="s">
-        <v>173</v>
+      <c r="F183" s="98" t="s">
+        <v>176</v>
       </c>
       <c r="G183" s="19">
         <v>1234568071</v>
       </c>
-      <c r="H183" s="109"/>
-      <c r="I183" s="21"/>
+      <c r="H183" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I183" s="20">
+        <v>10180</v>
+      </c>
       <c r="J183" s="21"/>
       <c r="K183" s="21"/>
       <c r="L183" s="21"/>
       <c r="M183" s="21"/>
       <c r="N183" s="21"/>
       <c r="O183" s="21"/>
-      <c r="P183" s="33"/>
+      <c r="P183" s="32"/>
       <c r="Q183" s="21"/>
       <c r="R183" s="21"/>
       <c r="S183" s="21"/>
@@ -7186,14 +7902,18 @@
       <c r="E184" s="17">
         <v>5</v>
       </c>
-      <c r="F184" s="109" t="s">
-        <v>174</v>
+      <c r="F184" s="98" t="s">
+        <v>177</v>
       </c>
       <c r="G184" s="19">
         <v>1234568072</v>
       </c>
-      <c r="H184" s="109"/>
-      <c r="I184" s="20"/>
+      <c r="H184" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I184" s="20">
+        <v>10181</v>
+      </c>
       <c r="J184" s="21"/>
       <c r="K184" s="21"/>
       <c r="L184" s="21"/>
@@ -7213,14 +7933,18 @@
       <c r="E185" s="27">
         <v>6</v>
       </c>
-      <c r="F185" s="110" t="s">
-        <v>175</v>
+      <c r="F185" s="99" t="s">
+        <v>178</v>
       </c>
       <c r="G185" s="19">
         <v>1234568073</v>
       </c>
-      <c r="H185" s="109"/>
-      <c r="I185" s="20"/>
+      <c r="H185" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I185" s="20">
+        <v>10182</v>
+      </c>
       <c r="J185" s="21"/>
       <c r="K185" s="21"/>
       <c r="L185" s="21"/>
@@ -7239,22 +7963,26 @@
       <c r="D186" s="29">
         <v>314</v>
       </c>
-      <c r="E186" s="49">
+      <c r="E186" s="45">
         <v>1</v>
       </c>
-      <c r="F186" s="96" t="s">
-        <v>176</v>
+      <c r="F186" s="85" t="s">
+        <v>179</v>
       </c>
       <c r="G186" s="19">
         <v>1234568074</v>
       </c>
-      <c r="H186" s="109"/>
-      <c r="I186" s="32"/>
-      <c r="J186" s="33"/>
-      <c r="K186" s="33"/>
-      <c r="L186" s="33"/>
-      <c r="M186" s="33"/>
-      <c r="N186" s="33"/>
+      <c r="H186" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I186" s="20">
+        <v>10183</v>
+      </c>
+      <c r="J186" s="32"/>
+      <c r="K186" s="32"/>
+      <c r="L186" s="32"/>
+      <c r="M186" s="32"/>
+      <c r="N186" s="32"/>
       <c r="O186" s="21"/>
       <c r="P186" s="21"/>
       <c r="Q186" s="21"/>
@@ -7270,13 +7998,17 @@
         <v>2</v>
       </c>
       <c r="F187" s="25" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="G187" s="19">
         <v>1234568075</v>
       </c>
-      <c r="H187" s="109"/>
-      <c r="I187" s="20"/>
+      <c r="H187" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I187" s="20">
+        <v>10184</v>
+      </c>
       <c r="J187" s="21"/>
       <c r="K187" s="21"/>
       <c r="L187" s="21"/>
@@ -7296,14 +8028,18 @@
       <c r="E188" s="17">
         <v>3</v>
       </c>
-      <c r="F188" s="43" t="s">
-        <v>178</v>
+      <c r="F188" s="40" t="s">
+        <v>181</v>
       </c>
       <c r="G188" s="19">
         <v>1234568076</v>
       </c>
-      <c r="H188" s="109"/>
-      <c r="I188" s="20"/>
+      <c r="H188" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I188" s="20">
+        <v>10185</v>
+      </c>
       <c r="J188" s="21"/>
       <c r="K188" s="21"/>
       <c r="L188" s="21"/>
@@ -7323,13 +8059,18 @@
       <c r="E189" s="17">
         <v>4</v>
       </c>
-      <c r="F189" s="58" t="s">
-        <v>34</v>
+      <c r="F189" s="54" t="s">
+        <v>37</v>
       </c>
       <c r="G189" s="19">
         <v>1234568077</v>
       </c>
-      <c r="H189" s="73"/>
+      <c r="H189" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I189" s="20">
+        <v>10186</v>
+      </c>
     </row>
     <row r="190" ht="16.35" spans="1:20">
       <c r="A190" s="15"/>
@@ -7339,19 +8080,23 @@
       <c r="E190" s="17">
         <v>5</v>
       </c>
-      <c r="F190" s="43" t="s">
-        <v>179</v>
+      <c r="F190" s="40" t="s">
+        <v>182</v>
       </c>
       <c r="G190" s="19">
         <v>1234568078</v>
       </c>
-      <c r="H190" s="72"/>
-      <c r="I190" s="32"/>
-      <c r="J190" s="33"/>
-      <c r="K190" s="33"/>
-      <c r="L190" s="33"/>
-      <c r="M190" s="33"/>
-      <c r="N190" s="33"/>
+      <c r="H190" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I190" s="20">
+        <v>10187</v>
+      </c>
+      <c r="J190" s="32"/>
+      <c r="K190" s="32"/>
+      <c r="L190" s="32"/>
+      <c r="M190" s="32"/>
+      <c r="N190" s="32"/>
       <c r="O190" s="21"/>
       <c r="P190" s="21"/>
       <c r="Q190" s="21"/>
@@ -7366,14 +8111,18 @@
       <c r="E191" s="27">
         <v>6</v>
       </c>
-      <c r="F191" s="60" t="s">
-        <v>180</v>
+      <c r="F191" s="56" t="s">
+        <v>183</v>
       </c>
       <c r="G191" s="19">
         <v>1234568079</v>
       </c>
-      <c r="H191" s="111"/>
-      <c r="I191" s="21"/>
+      <c r="H191" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I191" s="20">
+        <v>10188</v>
+      </c>
       <c r="J191" s="21"/>
       <c r="K191" s="21"/>
       <c r="L191" s="21"/>
@@ -7384,7 +8133,7 @@
       <c r="Q191" s="21"/>
       <c r="R191" s="21"/>
       <c r="S191" s="21"/>
-      <c r="T191" s="112"/>
+      <c r="T191" s="100"/>
     </row>
     <row r="192" ht="16.35" spans="1:20">
       <c r="A192" s="15"/>
@@ -7393,17 +8142,21 @@
       <c r="D192" s="29">
         <v>315</v>
       </c>
-      <c r="E192" s="49">
+      <c r="E192" s="45">
         <v>1</v>
       </c>
-      <c r="F192" s="43" t="s">
-        <v>181</v>
+      <c r="F192" s="40" t="s">
+        <v>184</v>
       </c>
       <c r="G192" s="19">
         <v>1234568080</v>
       </c>
-      <c r="H192" s="72"/>
-      <c r="I192" s="20"/>
+      <c r="H192" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I192" s="20">
+        <v>10189</v>
+      </c>
       <c r="J192" s="21"/>
       <c r="K192" s="21"/>
       <c r="L192" s="21"/>
@@ -7423,14 +8176,18 @@
       <c r="E193" s="17">
         <v>2</v>
       </c>
-      <c r="F193" s="113" t="s">
-        <v>182</v>
+      <c r="F193" s="101" t="s">
+        <v>185</v>
       </c>
       <c r="G193" s="19">
         <v>1234568081</v>
       </c>
-      <c r="H193" s="111"/>
-      <c r="I193" s="20"/>
+      <c r="H193" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I193" s="20">
+        <v>10190</v>
+      </c>
       <c r="J193" s="21"/>
       <c r="K193" s="21"/>
       <c r="L193" s="21"/>
@@ -7450,14 +8207,18 @@
       <c r="E194" s="17">
         <v>3</v>
       </c>
-      <c r="F194" s="113" t="s">
-        <v>183</v>
+      <c r="F194" s="101" t="s">
+        <v>186</v>
       </c>
       <c r="G194" s="19">
         <v>1234568082</v>
       </c>
-      <c r="H194" s="72"/>
-      <c r="I194" s="20"/>
+      <c r="H194" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I194" s="20">
+        <v>10191</v>
+      </c>
       <c r="J194" s="21"/>
       <c r="K194" s="21"/>
       <c r="L194" s="21"/>
@@ -7477,14 +8238,18 @@
       <c r="E195" s="17">
         <v>4</v>
       </c>
-      <c r="F195" s="113" t="s">
-        <v>184</v>
+      <c r="F195" s="101" t="s">
+        <v>187</v>
       </c>
       <c r="G195" s="19">
         <v>1234568083</v>
       </c>
-      <c r="H195" s="111"/>
-      <c r="I195" s="20"/>
+      <c r="H195" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I195" s="20">
+        <v>10192</v>
+      </c>
       <c r="J195" s="21"/>
       <c r="K195" s="21"/>
       <c r="L195" s="21"/>
@@ -7504,14 +8269,18 @@
       <c r="E196" s="17">
         <v>5</v>
       </c>
-      <c r="F196" s="113" t="s">
-        <v>185</v>
+      <c r="F196" s="101" t="s">
+        <v>188</v>
       </c>
       <c r="G196" s="19">
         <v>1234568084</v>
       </c>
-      <c r="H196" s="72"/>
-      <c r="I196" s="20"/>
+      <c r="H196" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I196" s="20">
+        <v>10193</v>
+      </c>
       <c r="J196" s="21"/>
       <c r="K196" s="21"/>
       <c r="L196" s="21"/>
@@ -7531,21 +8300,25 @@
       <c r="E197" s="27">
         <v>6</v>
       </c>
-      <c r="F197" s="40" t="s">
-        <v>186</v>
+      <c r="F197" s="38" t="s">
+        <v>189</v>
       </c>
       <c r="G197" s="19">
         <v>1234568085</v>
       </c>
-      <c r="H197" s="111"/>
-      <c r="I197" s="36"/>
-      <c r="J197" s="37"/>
-      <c r="K197" s="37"/>
-      <c r="L197" s="37"/>
-      <c r="M197" s="37"/>
-      <c r="N197" s="37"/>
+      <c r="H197" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I197" s="20">
+        <v>10194</v>
+      </c>
+      <c r="J197" s="35"/>
+      <c r="K197" s="35"/>
+      <c r="L197" s="35"/>
+      <c r="M197" s="35"/>
+      <c r="N197" s="35"/>
       <c r="O197" s="21"/>
-      <c r="P197" s="37"/>
+      <c r="P197" s="35"/>
       <c r="Q197" s="21"/>
       <c r="R197" s="23"/>
       <c r="S197" s="21"/>
@@ -7557,24 +8330,28 @@
       <c r="D198" s="29">
         <v>316</v>
       </c>
-      <c r="E198" s="49">
+      <c r="E198" s="45">
         <v>1</v>
       </c>
-      <c r="F198" s="43" t="s">
-        <v>187</v>
+      <c r="F198" s="40" t="s">
+        <v>190</v>
       </c>
       <c r="G198" s="19">
         <v>1234568086</v>
       </c>
-      <c r="H198" s="72"/>
-      <c r="I198" s="32"/>
-      <c r="J198" s="33"/>
-      <c r="K198" s="33"/>
-      <c r="L198" s="46"/>
-      <c r="M198" s="33"/>
-      <c r="N198" s="33"/>
+      <c r="H198" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I198" s="20">
+        <v>10195</v>
+      </c>
+      <c r="J198" s="32"/>
+      <c r="K198" s="32"/>
+      <c r="L198" s="42"/>
+      <c r="M198" s="32"/>
+      <c r="N198" s="32"/>
       <c r="O198" s="21"/>
-      <c r="P198" s="37"/>
+      <c r="P198" s="35"/>
       <c r="Q198" s="21"/>
       <c r="R198" s="23"/>
       <c r="S198" s="21"/>
@@ -7587,14 +8364,18 @@
       <c r="E199" s="17">
         <v>2</v>
       </c>
-      <c r="F199" s="43" t="s">
-        <v>188</v>
+      <c r="F199" s="40" t="s">
+        <v>191</v>
       </c>
       <c r="G199" s="19">
         <v>1234568087</v>
       </c>
-      <c r="H199" s="111"/>
-      <c r="I199" s="20"/>
+      <c r="H199" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I199" s="20">
+        <v>10196</v>
+      </c>
       <c r="J199" s="21"/>
       <c r="K199" s="21"/>
       <c r="L199" s="21"/>
@@ -7614,14 +8395,18 @@
       <c r="E200" s="17">
         <v>3</v>
       </c>
-      <c r="F200" s="39" t="s">
-        <v>189</v>
+      <c r="F200" s="37" t="s">
+        <v>192</v>
       </c>
       <c r="G200" s="19">
         <v>1234568088</v>
       </c>
-      <c r="H200" s="72"/>
-      <c r="I200" s="20"/>
+      <c r="H200" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I200" s="20">
+        <v>10197</v>
+      </c>
       <c r="J200" s="21"/>
       <c r="K200" s="21"/>
       <c r="L200" s="21"/>
@@ -7642,13 +8427,17 @@
         <v>4</v>
       </c>
       <c r="F201" s="25" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G201" s="19">
         <v>1234568089</v>
       </c>
-      <c r="H201" s="111"/>
-      <c r="I201" s="20"/>
+      <c r="H201" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I201" s="20">
+        <v>10198</v>
+      </c>
       <c r="J201" s="21"/>
       <c r="K201" s="21"/>
       <c r="L201" s="21"/>
@@ -7668,14 +8457,18 @@
       <c r="E202" s="17">
         <v>5</v>
       </c>
-      <c r="F202" s="43" t="s">
-        <v>191</v>
+      <c r="F202" s="40" t="s">
+        <v>194</v>
       </c>
       <c r="G202" s="19">
         <v>1234568090</v>
       </c>
-      <c r="H202" s="72"/>
-      <c r="I202" s="21"/>
+      <c r="H202" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I202" s="20">
+        <v>10199</v>
+      </c>
       <c r="J202" s="21"/>
       <c r="K202" s="21"/>
       <c r="L202" s="21"/>
@@ -7695,610 +8488,614 @@
       <c r="E203" s="27">
         <v>6</v>
       </c>
-      <c r="F203" s="69" t="s">
-        <v>192</v>
+      <c r="F203" s="64" t="s">
+        <v>195</v>
       </c>
       <c r="G203" s="19">
         <v>1234568091</v>
       </c>
-      <c r="H203" s="111"/>
-      <c r="I203" s="114"/>
-      <c r="J203" s="115"/>
-      <c r="K203" s="115"/>
-      <c r="L203" s="115"/>
-      <c r="M203" s="115"/>
-      <c r="N203" s="115"/>
-      <c r="O203" s="33"/>
-      <c r="P203" s="33"/>
-      <c r="Q203" s="33"/>
-      <c r="R203" s="34"/>
-      <c r="S203" s="33"/>
+      <c r="H203" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="I203" s="20">
+        <v>10200</v>
+      </c>
+      <c r="J203" s="102"/>
+      <c r="K203" s="102"/>
+      <c r="L203" s="102"/>
+      <c r="M203" s="102"/>
+      <c r="N203" s="102"/>
+      <c r="O203" s="32"/>
+      <c r="P203" s="32"/>
+      <c r="Q203" s="32"/>
+      <c r="R203" s="33"/>
+      <c r="S203" s="32"/>
     </row>
     <row r="204" ht="16.35" spans="1:19">
-      <c r="D204" s="116"/>
-      <c r="E204" s="66"/>
+      <c r="D204" s="103"/>
+      <c r="E204" s="62"/>
     </row>
     <row r="205" spans="1:19">
-      <c r="D205" s="117"/>
-      <c r="E205" s="118"/>
+      <c r="D205" s="104"/>
+      <c r="E205" s="105"/>
     </row>
     <row r="206" spans="1:19">
-      <c r="D206" s="119"/>
+      <c r="D206" s="106"/>
       <c r="E206" s="23"/>
     </row>
     <row r="207" spans="1:19">
-      <c r="D207" s="120"/>
-      <c r="E207" s="119"/>
+      <c r="D207" s="107"/>
+      <c r="E207" s="106"/>
       <c r="F207" s="23"/>
     </row>
     <row r="208" spans="1:19">
-      <c r="D208" s="121"/>
-      <c r="E208" s="119"/>
+      <c r="D208" s="108"/>
+      <c r="E208" s="106"/>
       <c r="F208" s="23"/>
     </row>
     <row r="209" spans="4:6">
-      <c r="D209" s="121"/>
-      <c r="E209" s="119"/>
+      <c r="D209" s="108"/>
+      <c r="E209" s="106"/>
       <c r="F209" s="23"/>
     </row>
     <row r="210" spans="4:6">
-      <c r="D210" s="122"/>
-      <c r="E210" s="119"/>
+      <c r="D210" s="109"/>
+      <c r="E210" s="106"/>
       <c r="F210" s="23"/>
     </row>
     <row r="211" spans="4:6">
-      <c r="D211" s="120"/>
-      <c r="E211" s="119"/>
+      <c r="D211" s="107"/>
+      <c r="E211" s="106"/>
       <c r="F211" s="23"/>
     </row>
     <row r="212" spans="4:6">
-      <c r="D212" s="121"/>
-      <c r="E212" s="119"/>
+      <c r="D212" s="108"/>
+      <c r="E212" s="106"/>
       <c r="F212" s="23"/>
     </row>
     <row r="213" spans="4:6">
-      <c r="D213" s="121"/>
-      <c r="E213" s="119"/>
+      <c r="D213" s="108"/>
+      <c r="E213" s="106"/>
       <c r="F213" s="23"/>
     </row>
     <row r="214" spans="4:6">
-      <c r="D214" s="122"/>
-      <c r="E214" s="119"/>
+      <c r="D214" s="109"/>
+      <c r="E214" s="106"/>
       <c r="F214" s="23"/>
     </row>
     <row r="215" spans="4:6">
-      <c r="D215" s="120"/>
-      <c r="E215" s="119"/>
+      <c r="D215" s="107"/>
+      <c r="E215" s="106"/>
       <c r="F215" s="23"/>
     </row>
     <row r="216" spans="4:6">
-      <c r="D216" s="121"/>
-      <c r="E216" s="119"/>
+      <c r="D216" s="108"/>
+      <c r="E216" s="106"/>
       <c r="F216" s="23"/>
     </row>
     <row r="217" spans="4:6">
-      <c r="D217" s="121"/>
-      <c r="E217" s="119"/>
+      <c r="D217" s="108"/>
+      <c r="E217" s="106"/>
       <c r="F217" s="23"/>
     </row>
     <row r="218" spans="4:6">
-      <c r="D218" s="122"/>
-      <c r="E218" s="119"/>
+      <c r="D218" s="109"/>
+      <c r="E218" s="106"/>
       <c r="F218" s="23"/>
     </row>
     <row r="219" spans="4:6">
-      <c r="D219" s="120"/>
-      <c r="E219" s="119"/>
+      <c r="D219" s="107"/>
+      <c r="E219" s="106"/>
       <c r="F219" s="23"/>
     </row>
     <row r="220" spans="4:6">
-      <c r="D220" s="121"/>
-      <c r="E220" s="119"/>
+      <c r="D220" s="108"/>
+      <c r="E220" s="106"/>
       <c r="F220" s="23"/>
     </row>
     <row r="221" spans="4:6">
-      <c r="D221" s="121"/>
-      <c r="E221" s="119"/>
+      <c r="D221" s="108"/>
+      <c r="E221" s="106"/>
       <c r="F221" s="23"/>
     </row>
     <row r="222" spans="4:6">
-      <c r="D222" s="122"/>
-      <c r="E222" s="119"/>
+      <c r="D222" s="109"/>
+      <c r="E222" s="106"/>
       <c r="F222" s="23"/>
     </row>
     <row r="223" spans="4:6">
-      <c r="D223" s="120"/>
-      <c r="E223" s="119"/>
+      <c r="D223" s="107"/>
+      <c r="E223" s="106"/>
       <c r="F223" s="23"/>
     </row>
     <row r="224" spans="4:6">
-      <c r="D224" s="121"/>
-      <c r="E224" s="119"/>
+      <c r="D224" s="108"/>
+      <c r="E224" s="106"/>
       <c r="F224" s="23"/>
     </row>
     <row r="225" spans="4:6">
-      <c r="D225" s="121"/>
-      <c r="E225" s="119"/>
+      <c r="D225" s="108"/>
+      <c r="E225" s="106"/>
       <c r="F225" s="23"/>
     </row>
     <row r="226" spans="4:6">
-      <c r="D226" s="122"/>
-      <c r="E226" s="119"/>
+      <c r="D226" s="109"/>
+      <c r="E226" s="106"/>
       <c r="F226" s="23"/>
     </row>
     <row r="227" ht="16.35" spans="4:6">
-      <c r="D227" s="120"/>
-      <c r="E227" s="119"/>
-      <c r="F227" s="35"/>
+      <c r="D227" s="107"/>
+      <c r="E227" s="106"/>
+      <c r="F227" s="34"/>
     </row>
     <row r="228" ht="16.35" spans="4:6">
-      <c r="D228" s="121"/>
-      <c r="E228" s="119"/>
+      <c r="D228" s="108"/>
+      <c r="E228" s="106"/>
       <c r="F228" s="23"/>
     </row>
     <row r="229" spans="4:6">
-      <c r="D229" s="121"/>
-      <c r="E229" s="119"/>
+      <c r="D229" s="108"/>
+      <c r="E229" s="106"/>
       <c r="F229" s="23"/>
     </row>
     <row r="230" spans="4:6">
-      <c r="D230" s="122"/>
-      <c r="E230" s="119"/>
+      <c r="D230" s="109"/>
+      <c r="E230" s="106"/>
       <c r="F230" s="23"/>
     </row>
     <row r="231" spans="4:6">
-      <c r="D231" s="120"/>
-      <c r="E231" s="119"/>
+      <c r="D231" s="107"/>
+      <c r="E231" s="106"/>
       <c r="F231" s="23"/>
     </row>
     <row r="232" spans="4:6">
-      <c r="D232" s="121"/>
-      <c r="E232" s="119"/>
+      <c r="D232" s="108"/>
+      <c r="E232" s="106"/>
       <c r="F232" s="23"/>
     </row>
     <row r="233" spans="4:6">
-      <c r="D233" s="121"/>
-      <c r="E233" s="119"/>
+      <c r="D233" s="108"/>
+      <c r="E233" s="106"/>
       <c r="F233" s="23"/>
     </row>
     <row r="234" spans="4:6">
-      <c r="D234" s="122"/>
-      <c r="E234" s="119"/>
+      <c r="D234" s="109"/>
+      <c r="E234" s="106"/>
       <c r="F234" s="23"/>
     </row>
     <row r="235" spans="4:6">
-      <c r="D235" s="120"/>
-      <c r="E235" s="119"/>
+      <c r="D235" s="107"/>
+      <c r="E235" s="106"/>
       <c r="F235" s="23"/>
     </row>
     <row r="236" spans="4:6">
-      <c r="D236" s="121"/>
-      <c r="E236" s="119"/>
+      <c r="D236" s="108"/>
+      <c r="E236" s="106"/>
       <c r="F236" s="23"/>
     </row>
     <row r="237" spans="4:6">
-      <c r="D237" s="121"/>
-      <c r="E237" s="119"/>
+      <c r="D237" s="108"/>
+      <c r="E237" s="106"/>
       <c r="F237" s="23"/>
     </row>
     <row r="238" spans="4:6">
-      <c r="D238" s="122"/>
-      <c r="E238" s="119"/>
+      <c r="D238" s="109"/>
+      <c r="E238" s="106"/>
       <c r="F238" s="23"/>
     </row>
     <row r="239" spans="4:6">
-      <c r="D239" s="120"/>
-      <c r="E239" s="119"/>
+      <c r="D239" s="107"/>
+      <c r="E239" s="106"/>
       <c r="F239" s="23"/>
     </row>
     <row r="240" spans="4:6">
-      <c r="D240" s="121"/>
-      <c r="E240" s="119"/>
+      <c r="D240" s="108"/>
+      <c r="E240" s="106"/>
       <c r="F240" s="23"/>
     </row>
     <row r="241" spans="4:6">
-      <c r="D241" s="121"/>
-      <c r="E241" s="119"/>
+      <c r="D241" s="108"/>
+      <c r="E241" s="106"/>
       <c r="F241" s="23"/>
     </row>
     <row r="242" spans="4:6">
-      <c r="D242" s="122"/>
-      <c r="E242" s="119"/>
+      <c r="D242" s="109"/>
+      <c r="E242" s="106"/>
       <c r="F242" s="23"/>
     </row>
     <row r="243" spans="4:6">
-      <c r="D243" s="120"/>
-      <c r="E243" s="119"/>
+      <c r="D243" s="107"/>
+      <c r="E243" s="106"/>
       <c r="F243" s="23"/>
     </row>
     <row r="244" spans="4:6">
-      <c r="D244" s="121"/>
-      <c r="E244" s="119"/>
-      <c r="F244" s="123"/>
+      <c r="D244" s="108"/>
+      <c r="E244" s="106"/>
+      <c r="F244" s="110"/>
     </row>
     <row r="245" spans="4:6">
-      <c r="D245" s="122"/>
-      <c r="E245" s="119"/>
+      <c r="D245" s="109"/>
+      <c r="E245" s="106"/>
       <c r="F245" s="23"/>
     </row>
     <row r="246" spans="4:6">
-      <c r="D246" s="120"/>
-      <c r="E246" s="119"/>
+      <c r="D246" s="107"/>
+      <c r="E246" s="106"/>
       <c r="F246" s="18"/>
     </row>
     <row r="247" spans="4:6">
-      <c r="D247" s="121"/>
-      <c r="E247" s="124"/>
+      <c r="D247" s="108"/>
+      <c r="E247" s="111"/>
       <c r="F247" s="18"/>
     </row>
     <row r="248" spans="4:6">
-      <c r="D248" s="121"/>
-      <c r="E248" s="119"/>
+      <c r="D248" s="108"/>
+      <c r="E248" s="106"/>
       <c r="F248" s="18"/>
     </row>
     <row r="249" spans="4:6">
-      <c r="D249" s="122"/>
-      <c r="E249" s="124"/>
-      <c r="F249" s="60"/>
+      <c r="D249" s="109"/>
+      <c r="E249" s="111"/>
+      <c r="F249" s="56"/>
     </row>
     <row r="250" spans="4:6">
-      <c r="D250" s="120"/>
-      <c r="E250" s="119"/>
+      <c r="D250" s="107"/>
+      <c r="E250" s="106"/>
       <c r="F250" s="18"/>
     </row>
     <row r="251" spans="4:6">
-      <c r="D251" s="121"/>
-      <c r="E251" s="119"/>
+      <c r="D251" s="108"/>
+      <c r="E251" s="106"/>
       <c r="F251" s="18"/>
     </row>
     <row r="252" spans="4:6">
-      <c r="D252" s="121"/>
-      <c r="E252" s="119"/>
+      <c r="D252" s="108"/>
+      <c r="E252" s="106"/>
       <c r="F252" s="18"/>
     </row>
     <row r="253" spans="4:6">
-      <c r="D253" s="122"/>
-      <c r="E253" s="119"/>
+      <c r="D253" s="109"/>
+      <c r="E253" s="106"/>
       <c r="F253" s="23"/>
     </row>
     <row r="254" spans="4:6">
-      <c r="D254" s="120"/>
-      <c r="E254" s="119"/>
+      <c r="D254" s="107"/>
+      <c r="E254" s="106"/>
       <c r="F254" s="18"/>
     </row>
     <row r="255" spans="4:6">
-      <c r="D255" s="121"/>
-      <c r="E255" s="119"/>
+      <c r="D255" s="108"/>
+      <c r="E255" s="106"/>
       <c r="F255" s="18"/>
     </row>
     <row r="256" spans="4:6">
-      <c r="D256" s="121"/>
-      <c r="E256" s="119"/>
+      <c r="D256" s="108"/>
+      <c r="E256" s="106"/>
       <c r="F256" s="18"/>
     </row>
     <row r="257" spans="4:6">
-      <c r="D257" s="122"/>
-      <c r="E257" s="119"/>
+      <c r="D257" s="109"/>
+      <c r="E257" s="106"/>
       <c r="F257" s="23"/>
     </row>
     <row r="258" spans="4:6">
-      <c r="D258" s="120"/>
-      <c r="E258" s="119"/>
+      <c r="D258" s="107"/>
+      <c r="E258" s="106"/>
       <c r="F258" s="18"/>
     </row>
     <row r="259" spans="4:6">
-      <c r="D259" s="121"/>
-      <c r="E259" s="119"/>
+      <c r="D259" s="108"/>
+      <c r="E259" s="106"/>
       <c r="F259" s="18"/>
     </row>
     <row r="260" spans="4:6">
-      <c r="D260" s="121"/>
-      <c r="E260" s="119"/>
+      <c r="D260" s="108"/>
+      <c r="E260" s="106"/>
       <c r="F260" s="18"/>
     </row>
     <row r="261" spans="4:6">
-      <c r="D261" s="122"/>
-      <c r="E261" s="119"/>
+      <c r="D261" s="109"/>
+      <c r="E261" s="106"/>
       <c r="F261" s="23"/>
     </row>
     <row r="262" spans="4:6">
-      <c r="D262" s="120"/>
-      <c r="E262" s="119"/>
+      <c r="D262" s="107"/>
+      <c r="E262" s="106"/>
       <c r="F262" s="23"/>
     </row>
     <row r="263" spans="4:6">
-      <c r="D263" s="121"/>
-      <c r="E263" s="119"/>
+      <c r="D263" s="108"/>
+      <c r="E263" s="106"/>
       <c r="F263" s="18"/>
     </row>
     <row r="264" spans="4:6">
-      <c r="D264" s="121"/>
-      <c r="E264" s="119"/>
+      <c r="D264" s="108"/>
+      <c r="E264" s="106"/>
       <c r="F264" s="18"/>
     </row>
     <row r="265" spans="4:6">
-      <c r="D265" s="122"/>
-      <c r="E265" s="119"/>
+      <c r="D265" s="109"/>
+      <c r="E265" s="106"/>
       <c r="F265" s="23"/>
     </row>
     <row r="266" spans="4:6">
-      <c r="D266" s="120"/>
-      <c r="E266" s="119"/>
+      <c r="D266" s="107"/>
+      <c r="E266" s="106"/>
       <c r="F266" s="18"/>
     </row>
     <row r="267" spans="4:6">
-      <c r="D267" s="121"/>
-      <c r="E267" s="119"/>
+      <c r="D267" s="108"/>
+      <c r="E267" s="106"/>
       <c r="F267" s="18"/>
     </row>
     <row r="268" spans="4:6">
-      <c r="D268" s="121"/>
-      <c r="E268" s="119"/>
+      <c r="D268" s="108"/>
+      <c r="E268" s="106"/>
       <c r="F268" s="18"/>
     </row>
     <row r="269" spans="4:6">
-      <c r="D269" s="122"/>
-      <c r="E269" s="119"/>
+      <c r="D269" s="109"/>
+      <c r="E269" s="106"/>
       <c r="F269" s="23"/>
     </row>
     <row r="270" spans="4:6">
-      <c r="D270" s="120"/>
-      <c r="E270" s="119"/>
+      <c r="D270" s="107"/>
+      <c r="E270" s="106"/>
       <c r="F270" s="18"/>
     </row>
     <row r="271" spans="4:6">
-      <c r="D271" s="121"/>
-      <c r="E271" s="119"/>
-      <c r="F271" s="40"/>
+      <c r="D271" s="108"/>
+      <c r="E271" s="106"/>
+      <c r="F271" s="38"/>
     </row>
     <row r="272" spans="4:6">
-      <c r="D272" s="121"/>
-      <c r="E272" s="119"/>
+      <c r="D272" s="108"/>
+      <c r="E272" s="106"/>
       <c r="F272" s="18"/>
     </row>
     <row r="273" spans="4:6">
-      <c r="D273" s="122"/>
-      <c r="E273" s="119"/>
+      <c r="D273" s="109"/>
+      <c r="E273" s="106"/>
       <c r="F273" s="23"/>
     </row>
     <row r="274" ht="16.35" spans="4:6">
-      <c r="D274" s="120"/>
-      <c r="E274" s="119"/>
-      <c r="F274" s="58"/>
+      <c r="D274" s="107"/>
+      <c r="E274" s="106"/>
+      <c r="F274" s="54"/>
     </row>
     <row r="275" ht="16.35" spans="4:6">
-      <c r="D275" s="121"/>
-      <c r="E275" s="119"/>
+      <c r="D275" s="108"/>
+      <c r="E275" s="106"/>
       <c r="F275" s="18"/>
     </row>
     <row r="276" spans="4:6">
-      <c r="D276" s="121"/>
-      <c r="E276" s="119"/>
+      <c r="D276" s="108"/>
+      <c r="E276" s="106"/>
       <c r="F276" s="18"/>
     </row>
     <row r="277" spans="4:6">
-      <c r="D277" s="122"/>
-      <c r="E277" s="119"/>
+      <c r="D277" s="109"/>
+      <c r="E277" s="106"/>
       <c r="F277" s="23"/>
     </row>
     <row r="278" spans="4:6">
-      <c r="D278" s="120"/>
-      <c r="E278" s="119"/>
+      <c r="D278" s="107"/>
+      <c r="E278" s="106"/>
       <c r="F278" s="23"/>
     </row>
     <row r="279" spans="4:6">
-      <c r="D279" s="121"/>
-      <c r="E279" s="119"/>
+      <c r="D279" s="108"/>
+      <c r="E279" s="106"/>
       <c r="F279" s="18"/>
     </row>
     <row r="280" spans="4:6">
-      <c r="D280" s="121"/>
-      <c r="E280" s="119"/>
+      <c r="D280" s="108"/>
+      <c r="E280" s="106"/>
       <c r="F280" s="18"/>
     </row>
     <row r="281" spans="4:6">
-      <c r="D281" s="122"/>
-      <c r="E281" s="119"/>
+      <c r="D281" s="109"/>
+      <c r="E281" s="106"/>
       <c r="F281" s="23"/>
     </row>
     <row r="282" ht="16.35" spans="4:6">
-      <c r="D282" s="120"/>
-      <c r="E282" s="119"/>
-      <c r="F282" s="35"/>
+      <c r="D282" s="107"/>
+      <c r="E282" s="106"/>
+      <c r="F282" s="34"/>
     </row>
     <row r="283" ht="17.1" spans="4:6">
-      <c r="D283" s="121"/>
-      <c r="E283" s="119"/>
-      <c r="F283" s="35"/>
+      <c r="D283" s="108"/>
+      <c r="E283" s="106"/>
+      <c r="F283" s="34"/>
     </row>
     <row r="284" ht="16.35" spans="4:6">
-      <c r="D284" s="122"/>
-      <c r="E284" s="119"/>
-      <c r="F284" s="43"/>
+      <c r="D284" s="109"/>
+      <c r="E284" s="106"/>
+      <c r="F284" s="40"/>
     </row>
     <row r="285" ht="16.35" spans="4:6">
-      <c r="D285" s="120"/>
-      <c r="E285" s="119"/>
-      <c r="F285" s="35"/>
+      <c r="D285" s="107"/>
+      <c r="E285" s="106"/>
+      <c r="F285" s="34"/>
     </row>
     <row r="286" ht="17.1" spans="4:6">
-      <c r="D286" s="121"/>
-      <c r="E286" s="119"/>
-      <c r="F286" s="35"/>
+      <c r="D286" s="108"/>
+      <c r="E286" s="106"/>
+      <c r="F286" s="34"/>
     </row>
     <row r="287" ht="16.35" spans="4:6">
-      <c r="D287" s="121"/>
-      <c r="E287" s="119"/>
-      <c r="F287" s="125"/>
+      <c r="D287" s="108"/>
+      <c r="E287" s="106"/>
+      <c r="F287" s="112"/>
     </row>
     <row r="288" spans="4:6">
-      <c r="D288" s="122"/>
-      <c r="E288" s="119"/>
+      <c r="D288" s="109"/>
+      <c r="E288" s="106"/>
       <c r="F288" s="18"/>
     </row>
     <row r="289" ht="16.35" spans="4:6">
-      <c r="D289" s="120"/>
-      <c r="E289" s="119"/>
-      <c r="F289" s="35"/>
+      <c r="D289" s="107"/>
+      <c r="E289" s="106"/>
+      <c r="F289" s="34"/>
     </row>
     <row r="290" ht="16.35" spans="4:6">
-      <c r="D290" s="121"/>
-      <c r="E290" s="70"/>
-      <c r="F290" s="40"/>
+      <c r="D290" s="108"/>
+      <c r="E290" s="113"/>
+      <c r="F290" s="38"/>
     </row>
     <row r="291" spans="4:6">
-      <c r="D291" s="121"/>
-      <c r="E291" s="119"/>
-      <c r="F291" s="43"/>
+      <c r="D291" s="108"/>
+      <c r="E291" s="106"/>
+      <c r="F291" s="40"/>
     </row>
     <row r="292" spans="4:6">
-      <c r="D292" s="122"/>
-      <c r="E292" s="119"/>
-      <c r="F292" s="60"/>
+      <c r="D292" s="109"/>
+      <c r="E292" s="106"/>
+      <c r="F292" s="56"/>
     </row>
     <row r="293" ht="16.35" spans="4:6">
-      <c r="D293" s="120"/>
-      <c r="E293" s="119"/>
-      <c r="F293" s="58"/>
+      <c r="D293" s="107"/>
+      <c r="E293" s="106"/>
+      <c r="F293" s="54"/>
     </row>
     <row r="294" ht="16.35" spans="4:6">
-      <c r="D294" s="121"/>
-      <c r="E294" s="119"/>
+      <c r="D294" s="108"/>
+      <c r="E294" s="106"/>
       <c r="F294" s="23"/>
     </row>
     <row r="295" spans="4:6">
-      <c r="D295" s="121"/>
-      <c r="E295" s="119"/>
+      <c r="D295" s="108"/>
+      <c r="E295" s="106"/>
       <c r="F295" s="23"/>
     </row>
     <row r="296" spans="4:6">
-      <c r="D296" s="122"/>
-      <c r="E296" s="119"/>
+      <c r="D296" s="109"/>
+      <c r="E296" s="106"/>
       <c r="F296" s="23"/>
     </row>
     <row r="297" spans="4:6">
-      <c r="D297" s="120"/>
-      <c r="E297" s="119"/>
-      <c r="F297" s="70"/>
+      <c r="D297" s="107"/>
+      <c r="E297" s="106"/>
+      <c r="F297" s="113"/>
     </row>
     <row r="298" spans="4:6">
-      <c r="D298" s="121"/>
-      <c r="E298" s="119"/>
+      <c r="D298" s="108"/>
+      <c r="E298" s="106"/>
       <c r="F298" s="23"/>
     </row>
     <row r="299" ht="16.35" spans="4:6">
-      <c r="D299" s="121"/>
-      <c r="E299" s="119"/>
-      <c r="F299" s="35"/>
+      <c r="D299" s="108"/>
+      <c r="E299" s="106"/>
+      <c r="F299" s="34"/>
     </row>
     <row r="300" ht="17.1" spans="4:6">
-      <c r="D300" s="122"/>
-      <c r="E300" s="119"/>
-      <c r="F300" s="35"/>
+      <c r="D300" s="109"/>
+      <c r="E300" s="106"/>
+      <c r="F300" s="34"/>
     </row>
     <row r="301" ht="17.1" spans="4:6">
-      <c r="D301" s="120"/>
-      <c r="E301" s="119"/>
-      <c r="F301" s="58"/>
+      <c r="D301" s="107"/>
+      <c r="E301" s="106"/>
+      <c r="F301" s="54"/>
     </row>
     <row r="302" ht="16.35" spans="4:6">
-      <c r="D302" s="121"/>
-      <c r="E302" s="119"/>
+      <c r="D302" s="108"/>
+      <c r="E302" s="106"/>
       <c r="F302" s="23"/>
     </row>
     <row r="303" spans="4:6">
-      <c r="D303" s="121"/>
-      <c r="E303" s="119"/>
+      <c r="D303" s="108"/>
+      <c r="E303" s="106"/>
       <c r="F303" s="23"/>
     </row>
     <row r="304" spans="4:6">
-      <c r="D304" s="122"/>
-      <c r="E304" s="119"/>
+      <c r="D304" s="109"/>
+      <c r="E304" s="106"/>
       <c r="F304" s="23"/>
     </row>
     <row r="305" spans="4:6">
-      <c r="D305" s="120"/>
-      <c r="E305" s="119"/>
+      <c r="D305" s="107"/>
+      <c r="E305" s="106"/>
       <c r="F305" s="18"/>
     </row>
     <row r="306" ht="16.35" spans="4:6">
-      <c r="D306" s="121"/>
-      <c r="E306" s="119"/>
-      <c r="F306" s="35"/>
+      <c r="D306" s="108"/>
+      <c r="E306" s="106"/>
+      <c r="F306" s="34"/>
     </row>
     <row r="307" ht="16.35" spans="4:6">
-      <c r="D307" s="121"/>
-      <c r="E307" s="119"/>
+      <c r="D307" s="108"/>
+      <c r="E307" s="106"/>
       <c r="F307" s="23"/>
     </row>
     <row r="308" spans="4:6">
-      <c r="D308" s="122"/>
-      <c r="E308" s="119"/>
+      <c r="D308" s="109"/>
+      <c r="E308" s="106"/>
       <c r="F308" s="23"/>
     </row>
     <row r="309" spans="4:6">
-      <c r="D309" s="120"/>
-      <c r="E309" s="119"/>
+      <c r="D309" s="107"/>
+      <c r="E309" s="106"/>
       <c r="F309" s="23"/>
     </row>
     <row r="310" spans="4:6">
-      <c r="D310" s="121"/>
-      <c r="E310" s="119"/>
+      <c r="D310" s="108"/>
+      <c r="E310" s="106"/>
       <c r="F310" s="23"/>
     </row>
     <row r="311" spans="4:6">
-      <c r="D311" s="121"/>
-      <c r="E311" s="119"/>
+      <c r="D311" s="108"/>
+      <c r="E311" s="106"/>
       <c r="F311" s="23"/>
     </row>
     <row r="312" spans="4:6">
-      <c r="D312" s="122"/>
-      <c r="E312" s="119"/>
+      <c r="D312" s="109"/>
+      <c r="E312" s="106"/>
       <c r="F312" s="18"/>
     </row>
     <row r="313" spans="4:6">
-      <c r="D313" s="120"/>
-      <c r="E313" s="119"/>
-      <c r="F313" s="126"/>
+      <c r="D313" s="107"/>
+      <c r="E313" s="106"/>
+      <c r="F313" s="114"/>
     </row>
     <row r="314" spans="4:6">
-      <c r="D314" s="121"/>
-      <c r="E314" s="119"/>
-      <c r="F314" s="43"/>
+      <c r="D314" s="108"/>
+      <c r="E314" s="106"/>
+      <c r="F314" s="40"/>
     </row>
     <row r="315" spans="4:6">
-      <c r="D315" s="121"/>
-      <c r="E315" s="119"/>
+      <c r="D315" s="108"/>
+      <c r="E315" s="106"/>
       <c r="F315" s="18"/>
     </row>
     <row r="316" spans="4:6">
-      <c r="D316" s="122"/>
-      <c r="E316" s="119"/>
+      <c r="D316" s="109"/>
+      <c r="E316" s="106"/>
       <c r="F316" s="23"/>
     </row>
     <row r="317" spans="4:6">
-      <c r="D317" s="120"/>
-      <c r="E317" s="119"/>
+      <c r="D317" s="107"/>
+      <c r="E317" s="106"/>
       <c r="F317" s="23"/>
     </row>
     <row r="318" spans="4:6">
-      <c r="D318" s="121"/>
-      <c r="E318" s="119"/>
+      <c r="D318" s="108"/>
+      <c r="E318" s="106"/>
       <c r="F318" s="23"/>
     </row>
     <row r="319" spans="4:6">
-      <c r="D319" s="121"/>
-      <c r="E319" s="119"/>
+      <c r="D319" s="108"/>
+      <c r="E319" s="106"/>
       <c r="F319" s="23"/>
     </row>
     <row r="320" spans="4:6">
-      <c r="D320" s="122"/>
-      <c r="E320" s="119"/>
-      <c r="F320" s="60"/>
+      <c r="D320" s="109"/>
+      <c r="E320" s="106"/>
+      <c r="F320" s="56"/>
     </row>
     <row r="321" spans="4:6">
-      <c r="D321" s="127"/>
-      <c r="E321" s="119"/>
+      <c r="D321" s="115"/>
+      <c r="E321" s="106"/>
       <c r="F321" s="23"/>
     </row>
   </sheetData>

--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="197">
   <si>
     <t>ROOMS</t>
   </si>
@@ -42,6 +42,9 @@
   </si>
   <si>
     <t>outstanding fees</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Payment Received</t>
   </si>
   <si>
     <t>NAKUL PARAKH</t>
@@ -2256,7 +2259,7 @@
     <col min="7" max="7" width="32.2962962962963" style="3" customWidth="1"/>
     <col min="8" max="8" width="9.68518518518519" style="2" customWidth="1"/>
     <col min="9" max="9" width="22.0833333333333" style="4" customWidth="1"/>
-    <col min="10" max="10" width="11.3333333333333" style="4" customWidth="1"/>
+    <col min="10" max="10" width="19.5" style="4" customWidth="1"/>
     <col min="11" max="11" width="12.3333333333333" style="4" customWidth="1"/>
     <col min="12" max="12" width="16.3333333333333" style="4" customWidth="1"/>
     <col min="13" max="13" width="10.3333333333333" style="4" customWidth="1"/>
@@ -2289,7 +2292,9 @@
       <c r="I2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="10"/>
+      <c r="J2" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
       <c r="M2" s="10"/>
@@ -2311,18 +2316,20 @@
         <v>1</v>
       </c>
       <c r="F3" s="18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3" s="19">
         <v>1234567891</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I3" s="20">
         <v>10000</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="21">
+        <v>85000</v>
+      </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="22"/>
@@ -2342,18 +2349,20 @@
         <v>2</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G4" s="19">
         <v>1234567892</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I4" s="20">
         <v>10001</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21">
+        <v>85001</v>
+      </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
@@ -2373,18 +2382,20 @@
         <v>3</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="19">
         <v>1234567893</v>
       </c>
       <c r="H5" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="20">
         <v>10002</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21">
+        <v>85002</v>
+      </c>
       <c r="K5" s="21"/>
       <c r="L5" s="21"/>
       <c r="M5" s="21"/>
@@ -2404,18 +2415,20 @@
         <v>4</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="19">
         <v>1234567894</v>
       </c>
       <c r="H6" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="20">
         <v>10003</v>
       </c>
-      <c r="J6" s="21"/>
+      <c r="J6" s="21">
+        <v>85003</v>
+      </c>
       <c r="K6" s="21"/>
       <c r="L6" s="21"/>
       <c r="M6" s="21"/>
@@ -2437,18 +2450,20 @@
         <v>1</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="19">
         <v>1234567895</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="20">
         <v>10004</v>
       </c>
-      <c r="J7" s="32"/>
+      <c r="J7" s="21">
+        <v>85004</v>
+      </c>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
@@ -2468,18 +2483,20 @@
         <v>2</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="19">
         <v>1234567896</v>
       </c>
       <c r="H8" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="20">
         <v>10005</v>
       </c>
-      <c r="J8" s="21"/>
+      <c r="J8" s="21">
+        <v>85005</v>
+      </c>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
@@ -2499,18 +2516,20 @@
         <v>3</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="19">
         <v>1234567897</v>
       </c>
       <c r="H9" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="20">
         <v>10006</v>
       </c>
-      <c r="J9" s="21"/>
+      <c r="J9" s="21">
+        <v>85006</v>
+      </c>
       <c r="K9" s="21"/>
       <c r="L9" s="21"/>
       <c r="M9" s="21"/>
@@ -2530,18 +2549,20 @@
         <v>4</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G10" s="19">
         <v>1234567898</v>
       </c>
       <c r="H10" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="20">
         <v>10007</v>
       </c>
-      <c r="J10" s="35"/>
+      <c r="J10" s="21">
+        <v>85007</v>
+      </c>
       <c r="K10" s="35"/>
       <c r="L10" s="35"/>
       <c r="M10" s="35"/>
@@ -2563,18 +2584,20 @@
         <v>1</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G11" s="19">
         <v>1234567899</v>
       </c>
       <c r="H11" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="20">
         <v>10008</v>
       </c>
-      <c r="J11" s="32"/>
+      <c r="J11" s="21">
+        <v>85008</v>
+      </c>
       <c r="K11" s="32"/>
       <c r="L11" s="32"/>
       <c r="M11" s="32"/>
@@ -2594,18 +2617,20 @@
         <v>2</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G12" s="19">
         <v>1234567900</v>
       </c>
       <c r="H12" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" s="20">
         <v>10009</v>
       </c>
-      <c r="J12" s="21"/>
+      <c r="J12" s="21">
+        <v>85009</v>
+      </c>
       <c r="K12" s="21"/>
       <c r="L12" s="21"/>
       <c r="M12" s="21"/>
@@ -2625,18 +2650,20 @@
         <v>3</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G13" s="19">
         <v>1234567901</v>
       </c>
       <c r="H13" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="20">
         <v>10010</v>
       </c>
-      <c r="J13" s="21"/>
+      <c r="J13" s="21">
+        <v>85010</v>
+      </c>
       <c r="K13" s="21"/>
       <c r="L13" s="21"/>
       <c r="M13" s="21"/>
@@ -2656,18 +2683,20 @@
         <v>4</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" s="19">
         <v>1234567902</v>
       </c>
       <c r="H14" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="20">
         <v>10011</v>
       </c>
-      <c r="J14" s="39"/>
+      <c r="J14" s="21">
+        <v>85011</v>
+      </c>
       <c r="K14" s="39"/>
       <c r="L14" s="39"/>
       <c r="M14" s="39"/>
@@ -2685,18 +2714,20 @@
       <c r="D15" s="24"/>
       <c r="E15" s="30"/>
       <c r="F15" s="40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" s="19">
         <v>1234567903</v>
       </c>
       <c r="H15" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="20">
         <v>10012</v>
       </c>
-      <c r="J15" s="21"/>
+      <c r="J15" s="21">
+        <v>85012</v>
+      </c>
       <c r="K15" s="21"/>
       <c r="L15" s="21"/>
       <c r="M15" s="21"/>
@@ -2718,18 +2749,20 @@
         <v>1</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="19">
         <v>1234567904</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="20">
         <v>10013</v>
       </c>
-      <c r="J16" s="32"/>
+      <c r="J16" s="21">
+        <v>85013</v>
+      </c>
       <c r="K16" s="32"/>
       <c r="L16" s="32"/>
       <c r="M16" s="42"/>
@@ -2749,18 +2782,20 @@
         <v>2</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" s="19">
         <v>1234567905</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="20">
         <v>10014</v>
       </c>
-      <c r="J17" s="21"/>
+      <c r="J17" s="21">
+        <v>85014</v>
+      </c>
       <c r="K17" s="21"/>
       <c r="L17" s="21"/>
       <c r="M17" s="21"/>
@@ -2780,18 +2815,20 @@
         <v>3</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="19">
         <v>1234567906</v>
       </c>
       <c r="H18" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="20">
         <v>10015</v>
       </c>
-      <c r="J18" s="21"/>
+      <c r="J18" s="21">
+        <v>85015</v>
+      </c>
       <c r="K18" s="21"/>
       <c r="L18" s="21"/>
       <c r="M18" s="21"/>
@@ -2811,18 +2848,20 @@
         <v>4</v>
       </c>
       <c r="F19" s="43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" s="19">
         <v>1234567907</v>
       </c>
       <c r="H19" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19" s="20">
         <v>10016</v>
       </c>
-      <c r="J19" s="35"/>
+      <c r="J19" s="21">
+        <v>85016</v>
+      </c>
       <c r="K19" s="35"/>
       <c r="L19" s="35"/>
       <c r="M19" s="35"/>
@@ -2844,18 +2883,20 @@
         <v>1</v>
       </c>
       <c r="F20" s="44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" s="19">
         <v>1234567908</v>
       </c>
       <c r="H20" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="20">
         <v>10017</v>
       </c>
-      <c r="J20" s="32"/>
+      <c r="J20" s="21">
+        <v>85017</v>
+      </c>
       <c r="K20" s="32"/>
       <c r="L20" s="32"/>
       <c r="M20" s="32"/>
@@ -2875,18 +2916,20 @@
         <v>2</v>
       </c>
       <c r="F21" s="44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21" s="19">
         <v>1234567909</v>
       </c>
       <c r="H21" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="20">
         <v>10018</v>
       </c>
-      <c r="J21" s="21"/>
+      <c r="J21" s="21">
+        <v>85018</v>
+      </c>
       <c r="K21" s="21"/>
       <c r="L21" s="21"/>
       <c r="M21" s="21"/>
@@ -2906,18 +2949,20 @@
         <v>3</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G22" s="19">
         <v>1234567910</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="20">
         <v>10019</v>
       </c>
-      <c r="J22" s="21"/>
+      <c r="J22" s="21">
+        <v>85019</v>
+      </c>
       <c r="K22" s="21"/>
       <c r="L22" s="21"/>
       <c r="M22" s="21"/>
@@ -2937,18 +2982,20 @@
         <v>4</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G23" s="19">
         <v>1234567911</v>
       </c>
       <c r="H23" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="20">
         <v>10020</v>
       </c>
-      <c r="J23" s="39"/>
+      <c r="J23" s="21">
+        <v>85020</v>
+      </c>
       <c r="K23" s="39"/>
       <c r="L23" s="39"/>
       <c r="M23" s="39"/>
@@ -2966,18 +3013,20 @@
       <c r="D24" s="24"/>
       <c r="E24" s="47"/>
       <c r="F24" s="40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G24" s="19">
         <v>1234567912</v>
       </c>
       <c r="H24" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="20">
         <v>10021</v>
       </c>
-      <c r="J24" s="21"/>
+      <c r="J24" s="21">
+        <v>85021</v>
+      </c>
       <c r="K24" s="21"/>
       <c r="L24" s="21"/>
       <c r="M24" s="21"/>
@@ -2999,18 +3048,20 @@
         <v>1</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G25" s="19">
         <v>1234567913</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="20">
         <v>10022</v>
       </c>
-      <c r="J25" s="32"/>
+      <c r="J25" s="21">
+        <v>85022</v>
+      </c>
       <c r="K25" s="32"/>
       <c r="L25" s="32"/>
       <c r="M25" s="32"/>
@@ -3030,18 +3081,20 @@
         <v>2</v>
       </c>
       <c r="F26" s="49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G26" s="19">
         <v>1234567914</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="20">
         <v>10023</v>
       </c>
-      <c r="J26" s="21"/>
+      <c r="J26" s="21">
+        <v>85023</v>
+      </c>
       <c r="K26" s="21"/>
       <c r="L26" s="21"/>
       <c r="M26" s="21"/>
@@ -3061,18 +3114,20 @@
         <v>3</v>
       </c>
       <c r="F27" s="50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G27" s="19">
         <v>1234567915</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="20">
         <v>10024</v>
       </c>
-      <c r="J27" s="21"/>
+      <c r="J27" s="21">
+        <v>85024</v>
+      </c>
       <c r="K27" s="21"/>
       <c r="L27" s="21"/>
       <c r="M27" s="21"/>
@@ -3092,18 +3147,20 @@
         <v>4</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G28" s="19">
         <v>1234567916</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" s="20">
         <v>10025</v>
       </c>
-      <c r="J28" s="35"/>
+      <c r="J28" s="21">
+        <v>85025</v>
+      </c>
       <c r="K28" s="35"/>
       <c r="L28" s="35"/>
       <c r="M28" s="35"/>
@@ -3125,18 +3182,20 @@
         <v>1</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G29" s="19">
         <v>1234567917</v>
       </c>
       <c r="H29" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="20">
         <v>10026</v>
       </c>
-      <c r="J29" s="32"/>
+      <c r="J29" s="21">
+        <v>85026</v>
+      </c>
       <c r="K29" s="32"/>
       <c r="L29" s="32"/>
       <c r="M29" s="32"/>
@@ -3156,18 +3215,20 @@
         <v>2</v>
       </c>
       <c r="F30" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G30" s="19">
         <v>1234567918</v>
       </c>
       <c r="H30" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="20">
         <v>10027</v>
       </c>
-      <c r="J30" s="21"/>
+      <c r="J30" s="21">
+        <v>85027</v>
+      </c>
       <c r="K30" s="21"/>
       <c r="L30" s="21"/>
       <c r="M30" s="21"/>
@@ -3187,18 +3248,20 @@
         <v>3</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G31" s="19">
         <v>1234567919</v>
       </c>
       <c r="H31" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="20">
         <v>10028</v>
       </c>
-      <c r="J31" s="21"/>
+      <c r="J31" s="21">
+        <v>85028</v>
+      </c>
       <c r="K31" s="21"/>
       <c r="L31" s="21"/>
       <c r="M31" s="21"/>
@@ -3218,18 +3281,20 @@
         <v>4</v>
       </c>
       <c r="F32" s="52" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G32" s="19">
         <v>1234567920</v>
       </c>
       <c r="H32" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="20">
         <v>10029</v>
       </c>
-      <c r="J32" s="21"/>
+      <c r="J32" s="21">
+        <v>85029</v>
+      </c>
       <c r="K32" s="21"/>
       <c r="L32" s="21"/>
       <c r="M32" s="21"/>
@@ -3249,18 +3314,20 @@
         <v>5</v>
       </c>
       <c r="F33" s="53" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G33" s="19">
         <v>1234567921</v>
       </c>
       <c r="H33" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="20">
         <v>10030</v>
       </c>
-      <c r="J33" s="39"/>
+      <c r="J33" s="21">
+        <v>85030</v>
+      </c>
       <c r="K33" s="21"/>
       <c r="L33" s="39"/>
       <c r="M33" s="39"/>
@@ -3278,16 +3345,19 @@
       <c r="D34" s="24"/>
       <c r="E34" s="30"/>
       <c r="F34" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G34" s="19">
         <v>1234567922</v>
       </c>
       <c r="H34" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="20">
         <v>10031</v>
+      </c>
+      <c r="J34" s="21">
+        <v>85031</v>
       </c>
     </row>
     <row r="35" ht="17.1" spans="1:21">
@@ -3299,16 +3369,19 @@
         <v>6</v>
       </c>
       <c r="F35" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G35" s="19">
         <v>1234567923</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35" s="20">
         <v>10032</v>
+      </c>
+      <c r="J35" s="21">
+        <v>85032</v>
       </c>
     </row>
     <row r="36" ht="16.35" spans="1:21">
@@ -3322,18 +3395,20 @@
         <v>1</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G36" s="19">
         <v>1234567924</v>
       </c>
       <c r="H36" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="20">
         <v>10033</v>
       </c>
-      <c r="J36" s="32"/>
+      <c r="J36" s="21">
+        <v>85033</v>
+      </c>
       <c r="K36" s="32"/>
       <c r="L36" s="32"/>
       <c r="M36" s="32"/>
@@ -3353,18 +3428,20 @@
         <v>2</v>
       </c>
       <c r="F37" s="52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G37" s="19">
         <v>1234567925</v>
       </c>
       <c r="H37" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="20">
         <v>10034</v>
       </c>
-      <c r="J37" s="21"/>
+      <c r="J37" s="21">
+        <v>85034</v>
+      </c>
       <c r="K37" s="21"/>
       <c r="L37" s="21"/>
       <c r="M37" s="21"/>
@@ -3384,18 +3461,20 @@
         <v>3</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G38" s="19">
         <v>1234567926</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="20">
         <v>10035</v>
       </c>
-      <c r="J38" s="21"/>
+      <c r="J38" s="21">
+        <v>85035</v>
+      </c>
       <c r="K38" s="21"/>
       <c r="L38" s="21"/>
       <c r="M38" s="21"/>
@@ -3419,18 +3498,20 @@
         <v>4</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G39" s="19">
         <v>1234567927</v>
       </c>
       <c r="H39" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="20">
         <v>10036</v>
       </c>
-      <c r="J39" s="22"/>
+      <c r="J39" s="21">
+        <v>85036</v>
+      </c>
       <c r="K39" s="21"/>
       <c r="L39" s="21"/>
       <c r="M39" s="21"/>
@@ -3450,18 +3531,20 @@
         <v>5</v>
       </c>
       <c r="F40" s="34" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G40" s="19">
         <v>1234567928</v>
       </c>
       <c r="H40" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="20">
         <v>10037</v>
       </c>
-      <c r="J40" s="21"/>
+      <c r="J40" s="21">
+        <v>85037</v>
+      </c>
       <c r="K40" s="21"/>
       <c r="L40" s="21"/>
       <c r="M40" s="21"/>
@@ -3481,18 +3564,20 @@
         <v>6</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G41" s="19">
         <v>1234567929</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="20">
         <v>10038</v>
       </c>
-      <c r="J41" s="35"/>
+      <c r="J41" s="21">
+        <v>85038</v>
+      </c>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
       <c r="M41" s="35"/>
@@ -3514,18 +3599,20 @@
         <v>1</v>
       </c>
       <c r="F42" s="44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G42" s="19">
         <v>1234567930</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I42" s="20">
         <v>10039</v>
       </c>
-      <c r="J42" s="32"/>
+      <c r="J42" s="21">
+        <v>85039</v>
+      </c>
       <c r="K42" s="32"/>
       <c r="L42" s="32"/>
       <c r="M42" s="32"/>
@@ -3545,18 +3632,20 @@
         <v>2</v>
       </c>
       <c r="F43" s="50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G43" s="19">
         <v>1234567931</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="20">
         <v>10040</v>
       </c>
-      <c r="J43" s="21"/>
+      <c r="J43" s="21">
+        <v>85040</v>
+      </c>
       <c r="K43" s="21"/>
       <c r="L43" s="21"/>
       <c r="M43" s="21"/>
@@ -3576,18 +3665,20 @@
         <v>3</v>
       </c>
       <c r="F44" s="58" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G44" s="19">
         <v>1234567932</v>
       </c>
       <c r="H44" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="20">
         <v>10041</v>
       </c>
-      <c r="J44" s="35"/>
+      <c r="J44" s="21">
+        <v>85041</v>
+      </c>
       <c r="K44" s="35"/>
       <c r="L44" s="35"/>
       <c r="M44" s="35"/>
@@ -3609,18 +3700,20 @@
         <v>1</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G45" s="19">
         <v>1234567933</v>
       </c>
       <c r="H45" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="20">
         <v>10042</v>
       </c>
-      <c r="J45" s="32"/>
+      <c r="J45" s="21">
+        <v>85042</v>
+      </c>
       <c r="K45" s="32"/>
       <c r="L45" s="32"/>
       <c r="M45" s="32"/>
@@ -3640,18 +3733,20 @@
         <v>2</v>
       </c>
       <c r="F46" s="59" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G46" s="19">
         <v>1234567934</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="20">
         <v>10043</v>
       </c>
-      <c r="J46" s="21"/>
+      <c r="J46" s="21">
+        <v>85043</v>
+      </c>
       <c r="K46" s="21"/>
       <c r="L46" s="21"/>
       <c r="M46" s="21"/>
@@ -3671,18 +3766,20 @@
         <v>3</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G47" s="19">
         <v>1234567935</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" s="20">
         <v>10044</v>
       </c>
-      <c r="J47" s="32"/>
+      <c r="J47" s="21">
+        <v>85044</v>
+      </c>
       <c r="K47" s="32"/>
       <c r="L47" s="32"/>
       <c r="M47" s="32"/>
@@ -3702,18 +3799,20 @@
         <v>4</v>
       </c>
       <c r="F48" s="60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G48" s="19">
         <v>1234567936</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48" s="20">
         <v>10045</v>
       </c>
-      <c r="J48" s="21"/>
+      <c r="J48" s="21">
+        <v>85045</v>
+      </c>
       <c r="K48" s="21"/>
       <c r="L48" s="21"/>
       <c r="M48" s="21"/>
@@ -3733,18 +3832,20 @@
         <v>5</v>
       </c>
       <c r="F49" s="38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G49" s="19">
         <v>1234567937</v>
       </c>
       <c r="H49" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I49" s="20">
         <v>10046</v>
       </c>
-      <c r="J49" s="21"/>
+      <c r="J49" s="21">
+        <v>85046</v>
+      </c>
       <c r="K49" s="21"/>
       <c r="L49" s="21"/>
       <c r="M49" s="21"/>
@@ -3764,18 +3865,20 @@
         <v>6</v>
       </c>
       <c r="F50" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" s="19">
         <v>1234567938</v>
       </c>
       <c r="H50" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I50" s="20">
         <v>10047</v>
       </c>
-      <c r="J50" s="21"/>
+      <c r="J50" s="21">
+        <v>85047</v>
+      </c>
       <c r="K50" s="21"/>
       <c r="L50" s="21"/>
       <c r="M50" s="21"/>
@@ -3797,18 +3900,20 @@
         <v>1</v>
       </c>
       <c r="F51" s="34" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G51" s="19">
         <v>1234567939</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" s="20">
         <v>10048</v>
       </c>
-      <c r="J51" s="21"/>
+      <c r="J51" s="21">
+        <v>85048</v>
+      </c>
       <c r="K51" s="21"/>
       <c r="L51" s="21"/>
       <c r="M51" s="21"/>
@@ -3828,18 +3933,20 @@
         <v>2</v>
       </c>
       <c r="F52" s="61" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G52" s="19">
         <v>1234567940</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="20">
         <v>10049</v>
       </c>
-      <c r="J52" s="21"/>
+      <c r="J52" s="21">
+        <v>85049</v>
+      </c>
       <c r="K52" s="21"/>
       <c r="L52" s="21"/>
       <c r="M52" s="21"/>
@@ -3859,18 +3966,20 @@
         <v>3</v>
       </c>
       <c r="F53" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G53" s="19">
         <v>1234567941</v>
       </c>
       <c r="H53" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="20">
         <v>10050</v>
       </c>
-      <c r="J53" s="21"/>
+      <c r="J53" s="21">
+        <v>85050</v>
+      </c>
       <c r="K53" s="21"/>
       <c r="L53" s="21"/>
       <c r="M53" s="21"/>
@@ -3890,18 +3999,20 @@
         <v>4</v>
       </c>
       <c r="F54" s="59" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G54" s="19">
         <v>1234567942</v>
       </c>
       <c r="H54" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I54" s="20">
         <v>10051</v>
       </c>
-      <c r="J54" s="21"/>
+      <c r="J54" s="21">
+        <v>85051</v>
+      </c>
       <c r="K54" s="21"/>
       <c r="L54" s="21"/>
       <c r="M54" s="21"/>
@@ -3921,18 +4032,20 @@
         <v>5</v>
       </c>
       <c r="F55" s="40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G55" s="19">
         <v>1234567943</v>
       </c>
       <c r="H55" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I55" s="20">
         <v>10052</v>
       </c>
-      <c r="J55" s="21"/>
+      <c r="J55" s="21">
+        <v>85052</v>
+      </c>
       <c r="K55" s="21"/>
       <c r="L55" s="21"/>
       <c r="M55" s="21"/>
@@ -3952,18 +4065,20 @@
         <v>6</v>
       </c>
       <c r="F56" s="38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G56" s="19">
         <v>1234567944</v>
       </c>
       <c r="H56" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I56" s="20">
         <v>10053</v>
       </c>
-      <c r="J56" s="39"/>
+      <c r="J56" s="21">
+        <v>85053</v>
+      </c>
       <c r="K56" s="39"/>
       <c r="L56" s="39"/>
       <c r="M56" s="39"/>
@@ -3985,18 +4100,20 @@
         <v>1</v>
       </c>
       <c r="F57" s="56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G57" s="19">
         <v>1234567945</v>
       </c>
       <c r="H57" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I57" s="20">
         <v>10054</v>
       </c>
-      <c r="J57" s="21"/>
+      <c r="J57" s="21">
+        <v>85054</v>
+      </c>
       <c r="K57" s="21"/>
       <c r="L57" s="21"/>
       <c r="M57" s="21"/>
@@ -4016,18 +4133,20 @@
         <v>2</v>
       </c>
       <c r="F58" s="62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G58" s="19">
         <v>1234567946</v>
       </c>
       <c r="H58" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I58" s="20">
         <v>10055</v>
       </c>
-      <c r="J58" s="21"/>
+      <c r="J58" s="21">
+        <v>85055</v>
+      </c>
       <c r="K58" s="21"/>
       <c r="L58" s="21"/>
       <c r="M58" s="21"/>
@@ -4047,18 +4166,20 @@
         <v>3</v>
       </c>
       <c r="F59" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G59" s="19">
         <v>1234567947</v>
       </c>
       <c r="H59" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I59" s="20">
         <v>10056</v>
       </c>
-      <c r="J59" s="35"/>
+      <c r="J59" s="21">
+        <v>85056</v>
+      </c>
       <c r="K59" s="35"/>
       <c r="L59" s="35"/>
       <c r="M59" s="35"/>
@@ -4080,18 +4201,20 @@
         <v>1</v>
       </c>
       <c r="F60" s="41" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G60" s="19">
         <v>1234567948</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I60" s="20">
         <v>10057</v>
       </c>
-      <c r="J60" s="42"/>
+      <c r="J60" s="21">
+        <v>85057</v>
+      </c>
       <c r="K60" s="42"/>
       <c r="L60" s="42"/>
       <c r="M60" s="42"/>
@@ -4111,18 +4234,20 @@
         <v>2</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G61" s="19">
         <v>1234567949</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" s="20">
         <v>10058</v>
       </c>
-      <c r="J61" s="21"/>
+      <c r="J61" s="21">
+        <v>85058</v>
+      </c>
       <c r="K61" s="21"/>
       <c r="L61" s="21"/>
       <c r="M61" s="21"/>
@@ -4142,18 +4267,20 @@
         <v>3</v>
       </c>
       <c r="F62" s="34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G62" s="19">
         <v>1234567950</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="20">
         <v>10059</v>
       </c>
-      <c r="J62" s="21"/>
+      <c r="J62" s="21">
+        <v>85059</v>
+      </c>
       <c r="K62" s="21"/>
       <c r="L62" s="21"/>
       <c r="M62" s="21"/>
@@ -4175,18 +4302,20 @@
         <v>1</v>
       </c>
       <c r="F63" s="37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G63" s="19">
         <v>1234567951</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="20">
         <v>10060</v>
       </c>
-      <c r="J63" s="32"/>
+      <c r="J63" s="21">
+        <v>85060</v>
+      </c>
       <c r="K63" s="32"/>
       <c r="L63" s="32"/>
       <c r="M63" s="32"/>
@@ -4206,18 +4335,20 @@
         <v>2</v>
       </c>
       <c r="F64" s="52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G64" s="19">
         <v>1234567952</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I64" s="20">
         <v>10061</v>
       </c>
-      <c r="J64" s="21"/>
+      <c r="J64" s="21">
+        <v>85061</v>
+      </c>
       <c r="K64" s="21"/>
       <c r="L64" s="21"/>
       <c r="M64" s="21"/>
@@ -4237,18 +4368,20 @@
         <v>3</v>
       </c>
       <c r="F65" s="52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G65" s="19">
         <v>1234567953</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I65" s="20">
         <v>10062</v>
       </c>
-      <c r="J65" s="21"/>
+      <c r="J65" s="21">
+        <v>85062</v>
+      </c>
       <c r="K65" s="21"/>
       <c r="L65" s="21"/>
       <c r="M65" s="21"/>
@@ -4268,18 +4401,20 @@
         <v>4</v>
       </c>
       <c r="F66" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G66" s="19">
         <v>1234567954</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I66" s="20">
         <v>10063</v>
       </c>
-      <c r="J66" s="21"/>
+      <c r="J66" s="21">
+        <v>85063</v>
+      </c>
       <c r="K66" s="21"/>
       <c r="L66" s="21"/>
       <c r="M66" s="21"/>
@@ -4299,18 +4434,20 @@
         <v>5</v>
       </c>
       <c r="F67" s="64" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G67" s="19">
         <v>1234567955</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I67" s="20">
         <v>10064</v>
       </c>
-      <c r="J67" s="22"/>
+      <c r="J67" s="21">
+        <v>85064</v>
+      </c>
       <c r="K67" s="22"/>
       <c r="L67" s="22"/>
       <c r="M67" s="22"/>
@@ -4329,18 +4466,20 @@
         <v>6</v>
       </c>
       <c r="F68" s="65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G68" s="19">
         <v>1234567956</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I68" s="20">
         <v>10065</v>
       </c>
-      <c r="J68" s="35"/>
+      <c r="J68" s="21">
+        <v>85065</v>
+      </c>
       <c r="K68" s="35"/>
       <c r="L68" s="35"/>
       <c r="M68" s="35"/>
@@ -4358,18 +4497,20 @@
       <c r="D69" s="24"/>
       <c r="E69" s="47"/>
       <c r="F69" s="37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G69" s="19">
         <v>1234567957</v>
       </c>
       <c r="H69" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I69" s="20">
         <v>10066</v>
       </c>
-      <c r="J69" s="32"/>
+      <c r="J69" s="21">
+        <v>85066</v>
+      </c>
       <c r="K69" s="32"/>
       <c r="L69" s="32"/>
       <c r="M69" s="32"/>
@@ -4391,18 +4532,20 @@
         <v>1</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G70" s="19">
         <v>1234567958</v>
       </c>
       <c r="H70" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I70" s="20">
         <v>10067</v>
       </c>
-      <c r="J70" s="32"/>
+      <c r="J70" s="21">
+        <v>85067</v>
+      </c>
       <c r="K70" s="32"/>
       <c r="L70" s="32"/>
       <c r="M70" s="32"/>
@@ -4422,18 +4565,20 @@
         <v>2</v>
       </c>
       <c r="F71" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G71" s="19">
         <v>1234567959</v>
       </c>
       <c r="H71" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I71" s="20">
         <v>10068</v>
       </c>
-      <c r="J71" s="21"/>
+      <c r="J71" s="21">
+        <v>85068</v>
+      </c>
       <c r="K71" s="21"/>
       <c r="L71" s="21"/>
       <c r="M71" s="21"/>
@@ -4453,18 +4598,20 @@
         <v>3</v>
       </c>
       <c r="F72" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G72" s="19">
         <v>1234567960</v>
       </c>
       <c r="H72" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I72" s="20">
         <v>10069</v>
       </c>
-      <c r="J72" s="21"/>
+      <c r="J72" s="21">
+        <v>85069</v>
+      </c>
       <c r="K72" s="21"/>
       <c r="L72" s="21"/>
       <c r="M72" s="21"/>
@@ -4484,18 +4631,20 @@
         <v>4</v>
       </c>
       <c r="F73" s="37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G73" s="19">
         <v>1234567961</v>
       </c>
       <c r="H73" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I73" s="20">
         <v>10070</v>
       </c>
-      <c r="J73" s="21"/>
+      <c r="J73" s="21">
+        <v>85070</v>
+      </c>
       <c r="K73" s="21"/>
       <c r="L73" s="21"/>
       <c r="M73" s="21"/>
@@ -4515,18 +4664,20 @@
         <v>5</v>
       </c>
       <c r="F74" s="37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G74" s="19">
         <v>1234567962</v>
       </c>
       <c r="H74" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I74" s="20">
         <v>10071</v>
       </c>
-      <c r="J74" s="32"/>
+      <c r="J74" s="21">
+        <v>85071</v>
+      </c>
       <c r="K74" s="32"/>
       <c r="L74" s="32"/>
       <c r="M74" s="32"/>
@@ -4546,16 +4697,19 @@
         <v>6</v>
       </c>
       <c r="F75" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G75" s="19">
         <v>1234567963</v>
       </c>
       <c r="H75" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I75" s="20">
         <v>10072</v>
+      </c>
+      <c r="J75" s="21">
+        <v>85072</v>
       </c>
     </row>
     <row r="76" ht="16.35" spans="1:19">
@@ -4569,18 +4723,20 @@
         <v>1</v>
       </c>
       <c r="F76" s="37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G76" s="19">
         <v>1234567964</v>
       </c>
       <c r="H76" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I76" s="20">
         <v>10073</v>
       </c>
-      <c r="J76" s="32"/>
+      <c r="J76" s="21">
+        <v>85073</v>
+      </c>
       <c r="K76" s="32"/>
       <c r="L76" s="32"/>
       <c r="M76" s="32"/>
@@ -4600,18 +4756,20 @@
         <v>2</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G77" s="19">
         <v>1234567965</v>
       </c>
       <c r="H77" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I77" s="20">
         <v>10074</v>
       </c>
-      <c r="J77" s="21"/>
+      <c r="J77" s="21">
+        <v>85074</v>
+      </c>
       <c r="K77" s="21"/>
       <c r="L77" s="21"/>
       <c r="M77" s="21"/>
@@ -4631,18 +4789,20 @@
         <v>3</v>
       </c>
       <c r="F78" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G78" s="19">
         <v>1234567966</v>
       </c>
       <c r="H78" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I78" s="20">
         <v>10075</v>
       </c>
-      <c r="J78" s="21"/>
+      <c r="J78" s="21">
+        <v>85075</v>
+      </c>
       <c r="K78" s="21"/>
       <c r="L78" s="21"/>
       <c r="M78" s="21"/>
@@ -4664,18 +4824,20 @@
         <v>1</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G79" s="19">
         <v>1234567967</v>
       </c>
       <c r="H79" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I79" s="20">
         <v>10076</v>
       </c>
-      <c r="J79" s="32"/>
+      <c r="J79" s="21">
+        <v>85076</v>
+      </c>
       <c r="K79" s="32"/>
       <c r="L79" s="32"/>
       <c r="M79" s="32"/>
@@ -4695,16 +4857,19 @@
         <v>2</v>
       </c>
       <c r="F80" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G80" s="19">
         <v>1234567968</v>
       </c>
       <c r="H80" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I80" s="20">
         <v>10077</v>
+      </c>
+      <c r="J80" s="21">
+        <v>85077</v>
       </c>
       <c r="O80" s="67"/>
       <c r="P80" s="32"/>
@@ -4718,18 +4883,20 @@
         <v>3</v>
       </c>
       <c r="F81" s="64" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G81" s="19">
         <v>1234567969</v>
       </c>
       <c r="H81" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I81" s="20">
         <v>10078</v>
       </c>
-      <c r="J81" s="21"/>
+      <c r="J81" s="21">
+        <v>85078</v>
+      </c>
       <c r="K81" s="21"/>
       <c r="L81" s="21"/>
       <c r="M81" s="21"/>
@@ -4749,18 +4916,20 @@
         <v>4</v>
       </c>
       <c r="F82" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G82" s="19">
         <v>1234567970</v>
       </c>
       <c r="H82" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I82" s="20">
         <v>10079</v>
       </c>
-      <c r="J82" s="21"/>
+      <c r="J82" s="21">
+        <v>85079</v>
+      </c>
       <c r="K82" s="21"/>
       <c r="L82" s="21"/>
       <c r="M82" s="21"/>
@@ -4780,18 +4949,20 @@
         <v>5</v>
       </c>
       <c r="F83" s="40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G83" s="19">
         <v>1234567971</v>
       </c>
       <c r="H83" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I83" s="20">
         <v>10080</v>
       </c>
-      <c r="J83" s="21"/>
+      <c r="J83" s="21">
+        <v>85080</v>
+      </c>
       <c r="K83" s="21"/>
       <c r="L83" s="21"/>
       <c r="M83" s="21"/>
@@ -4811,18 +4982,20 @@
         <v>6</v>
       </c>
       <c r="F84" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G84" s="19">
         <v>1234567972</v>
       </c>
       <c r="H84" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I84" s="20">
         <v>10081</v>
       </c>
-      <c r="J84" s="69"/>
+      <c r="J84" s="21">
+        <v>85081</v>
+      </c>
       <c r="K84" s="69"/>
       <c r="L84" s="69"/>
       <c r="M84" s="69"/>
@@ -4844,18 +5017,20 @@
         <v>1</v>
       </c>
       <c r="F85" s="25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G85" s="19">
         <v>1234567973</v>
       </c>
       <c r="H85" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I85" s="20">
         <v>10082</v>
       </c>
-      <c r="J85" s="21"/>
+      <c r="J85" s="21">
+        <v>85082</v>
+      </c>
       <c r="K85" s="21"/>
       <c r="L85" s="21"/>
       <c r="M85" s="21"/>
@@ -4873,18 +5048,20 @@
       <c r="D86" s="24"/>
       <c r="E86" s="45"/>
       <c r="F86" s="40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G86" s="19">
         <v>1234567974</v>
       </c>
       <c r="H86" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I86" s="20">
         <v>10083</v>
       </c>
-      <c r="J86" s="21"/>
+      <c r="J86" s="21">
+        <v>85083</v>
+      </c>
       <c r="K86" s="21"/>
       <c r="L86" s="21"/>
       <c r="M86" s="21"/>
@@ -4904,16 +5081,19 @@
         <v>2</v>
       </c>
       <c r="F87" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G87" s="19">
         <v>1234567975</v>
       </c>
       <c r="H87" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I87" s="20">
         <v>10084</v>
+      </c>
+      <c r="J87" s="21">
+        <v>85084</v>
       </c>
     </row>
     <row r="88" ht="17.1" spans="1:19">
@@ -4923,18 +5103,20 @@
       <c r="D88" s="24"/>
       <c r="E88" s="45"/>
       <c r="F88" s="25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G88" s="19">
         <v>1234567976</v>
       </c>
       <c r="H88" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I88" s="20">
         <v>10085</v>
       </c>
-      <c r="J88" s="21"/>
+      <c r="J88" s="21">
+        <v>85085</v>
+      </c>
       <c r="K88" s="21"/>
       <c r="L88" s="21"/>
       <c r="M88" s="21"/>
@@ -4954,16 +5136,19 @@
         <v>3</v>
       </c>
       <c r="F89" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G89" s="19">
         <v>1234567977</v>
       </c>
       <c r="H89" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I89" s="20">
         <v>10086</v>
+      </c>
+      <c r="J89" s="21">
+        <v>85086</v>
       </c>
     </row>
     <row r="90" ht="17.1" spans="1:19">
@@ -4975,18 +5160,20 @@
         <v>4</v>
       </c>
       <c r="F90" s="56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G90" s="19">
         <v>1234567978</v>
       </c>
       <c r="H90" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I90" s="20">
         <v>10087</v>
       </c>
-      <c r="J90" s="21"/>
+      <c r="J90" s="21">
+        <v>85087</v>
+      </c>
       <c r="K90" s="21"/>
       <c r="L90" s="21"/>
       <c r="M90" s="21"/>
@@ -5006,18 +5193,20 @@
         <v>5</v>
       </c>
       <c r="F91" s="59" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G91" s="19">
         <v>1234567979</v>
       </c>
       <c r="H91" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I91" s="20">
         <v>10088</v>
       </c>
-      <c r="J91" s="21"/>
+      <c r="J91" s="21">
+        <v>85088</v>
+      </c>
       <c r="K91" s="21"/>
       <c r="L91" s="21"/>
       <c r="M91" s="21"/>
@@ -5037,18 +5226,20 @@
         <v>6</v>
       </c>
       <c r="F92" s="43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G92" s="19">
         <v>1234567980</v>
       </c>
       <c r="H92" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I92" s="20">
         <v>10089</v>
       </c>
-      <c r="J92" s="71"/>
+      <c r="J92" s="21">
+        <v>85089</v>
+      </c>
       <c r="K92" s="71"/>
       <c r="L92" s="71"/>
       <c r="M92" s="71"/>
@@ -5070,18 +5261,20 @@
         <v>1</v>
       </c>
       <c r="F93" s="73" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G93" s="19">
         <v>1234567981</v>
       </c>
       <c r="H93" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I93" s="20">
         <v>10090</v>
       </c>
-      <c r="J93" s="32"/>
+      <c r="J93" s="21">
+        <v>85090</v>
+      </c>
       <c r="K93" s="32"/>
       <c r="L93" s="32"/>
       <c r="M93" s="32"/>
@@ -5101,18 +5294,20 @@
         <v>2</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G94" s="19">
         <v>1234567982</v>
       </c>
       <c r="H94" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I94" s="20">
         <v>10091</v>
       </c>
-      <c r="J94" s="21"/>
+      <c r="J94" s="21">
+        <v>85091</v>
+      </c>
       <c r="K94" s="21"/>
       <c r="L94" s="21"/>
       <c r="M94" s="21"/>
@@ -5132,18 +5327,20 @@
         <v>3</v>
       </c>
       <c r="F95" s="43" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G95" s="19">
         <v>1234567983</v>
       </c>
       <c r="H95" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I95" s="20">
         <v>10092</v>
       </c>
-      <c r="J95" s="35"/>
+      <c r="J95" s="21">
+        <v>85092</v>
+      </c>
       <c r="K95" s="35"/>
       <c r="L95" s="35"/>
       <c r="M95" s="35"/>
@@ -5165,18 +5362,20 @@
         <v>1</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G96" s="19">
         <v>1234567984</v>
       </c>
       <c r="H96" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I96" s="20">
         <v>10093</v>
       </c>
-      <c r="J96" s="32"/>
+      <c r="J96" s="21">
+        <v>85093</v>
+      </c>
       <c r="K96" s="32"/>
       <c r="L96" s="32"/>
       <c r="M96" s="32"/>
@@ -5196,18 +5395,20 @@
         <v>2</v>
       </c>
       <c r="F97" s="40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G97" s="19">
         <v>1234567985</v>
       </c>
       <c r="H97" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I97" s="20">
         <v>10094</v>
       </c>
-      <c r="J97" s="21"/>
+      <c r="J97" s="21">
+        <v>85094</v>
+      </c>
       <c r="K97" s="21"/>
       <c r="L97" s="21"/>
       <c r="M97" s="21"/>
@@ -5227,18 +5428,20 @@
         <v>3</v>
       </c>
       <c r="F98" s="40" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G98" s="19">
         <v>1234567986</v>
       </c>
       <c r="H98" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I98" s="20">
         <v>10095</v>
       </c>
-      <c r="J98" s="21"/>
+      <c r="J98" s="21">
+        <v>85095</v>
+      </c>
       <c r="K98" s="21"/>
       <c r="L98" s="21"/>
       <c r="M98" s="21"/>
@@ -5258,18 +5461,20 @@
         <v>4</v>
       </c>
       <c r="F99" s="40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G99" s="19">
         <v>1234567987</v>
       </c>
       <c r="H99" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I99" s="20">
         <v>10096</v>
       </c>
-      <c r="J99" s="21"/>
+      <c r="J99" s="21">
+        <v>85096</v>
+      </c>
       <c r="K99" s="21"/>
       <c r="L99" s="21"/>
       <c r="M99" s="21"/>
@@ -5292,18 +5497,20 @@
         <v>5</v>
       </c>
       <c r="F100" s="75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G100" s="19">
         <v>1234567988</v>
       </c>
       <c r="H100" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I100" s="20">
         <v>10097</v>
       </c>
-      <c r="J100" s="32"/>
+      <c r="J100" s="21">
+        <v>85097</v>
+      </c>
       <c r="K100" s="32"/>
       <c r="L100" s="32"/>
       <c r="M100" s="32"/>
@@ -5323,18 +5530,20 @@
         <v>6</v>
       </c>
       <c r="F101" s="64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G101" s="19">
         <v>1234567989</v>
       </c>
       <c r="H101" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I101" s="20">
         <v>10098</v>
       </c>
-      <c r="J101" s="77"/>
+      <c r="J101" s="21">
+        <v>85098</v>
+      </c>
       <c r="K101" s="77"/>
       <c r="L101" s="77"/>
       <c r="M101" s="77"/>
@@ -5356,18 +5565,20 @@
         <v>1</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G102" s="19">
         <v>1234567990</v>
       </c>
       <c r="H102" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I102" s="20">
         <v>10099</v>
       </c>
-      <c r="J102" s="32"/>
+      <c r="J102" s="21">
+        <v>85099</v>
+      </c>
       <c r="K102" s="32"/>
       <c r="L102" s="32"/>
       <c r="M102" s="32"/>
@@ -5387,18 +5598,20 @@
         <v>2</v>
       </c>
       <c r="F103" s="25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G103" s="19">
         <v>1234567991</v>
       </c>
       <c r="H103" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I103" s="20">
         <v>10100</v>
       </c>
-      <c r="J103" s="21"/>
+      <c r="J103" s="21">
+        <v>85100</v>
+      </c>
       <c r="K103" s="21"/>
       <c r="L103" s="21"/>
       <c r="M103" s="21"/>
@@ -5418,18 +5631,20 @@
         <v>3</v>
       </c>
       <c r="F104" s="40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G104" s="19">
         <v>1234567992</v>
       </c>
       <c r="H104" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I104" s="20">
         <v>10101</v>
       </c>
-      <c r="J104" s="21"/>
+      <c r="J104" s="21">
+        <v>85101</v>
+      </c>
       <c r="K104" s="21"/>
       <c r="L104" s="21"/>
       <c r="M104" s="21"/>
@@ -5449,18 +5664,20 @@
         <v>4</v>
       </c>
       <c r="F105" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G105" s="19">
         <v>1234567993</v>
       </c>
       <c r="H105" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I105" s="20">
         <v>10102</v>
       </c>
-      <c r="J105" s="78"/>
+      <c r="J105" s="21">
+        <v>85102</v>
+      </c>
       <c r="K105" s="78"/>
       <c r="L105" s="78"/>
       <c r="M105" s="78"/>
@@ -5480,18 +5697,20 @@
         <v>5</v>
       </c>
       <c r="F106" s="40" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G106" s="19">
         <v>1234567994</v>
       </c>
       <c r="H106" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I106" s="20">
         <v>10103</v>
       </c>
-      <c r="J106" s="21"/>
+      <c r="J106" s="21">
+        <v>85103</v>
+      </c>
       <c r="K106" s="21"/>
       <c r="L106" s="21"/>
       <c r="M106" s="21"/>
@@ -5511,18 +5730,20 @@
         <v>6</v>
       </c>
       <c r="F107" s="64" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G107" s="19">
         <v>1234567995</v>
       </c>
       <c r="H107" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I107" s="20">
         <v>10104</v>
       </c>
-      <c r="J107" s="35"/>
+      <c r="J107" s="21">
+        <v>85104</v>
+      </c>
       <c r="K107" s="35"/>
       <c r="L107" s="35"/>
       <c r="M107" s="35"/>
@@ -5544,18 +5765,20 @@
         <v>1</v>
       </c>
       <c r="F108" s="37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G108" s="19">
         <v>1234567996</v>
       </c>
       <c r="H108" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I108" s="20">
         <v>10105</v>
       </c>
-      <c r="J108" s="32"/>
+      <c r="J108" s="21">
+        <v>85105</v>
+      </c>
       <c r="K108" s="32"/>
       <c r="L108" s="32"/>
       <c r="M108" s="32"/>
@@ -5575,18 +5798,20 @@
         <v>2</v>
       </c>
       <c r="F109" s="38" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G109" s="19">
         <v>1234567997</v>
       </c>
       <c r="H109" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I109" s="20">
         <v>10106</v>
       </c>
-      <c r="J109" s="21"/>
+      <c r="J109" s="21">
+        <v>85106</v>
+      </c>
       <c r="K109" s="21"/>
       <c r="L109" s="21"/>
       <c r="M109" s="21"/>
@@ -5606,18 +5831,20 @@
         <v>3</v>
       </c>
       <c r="F110" s="62" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G110" s="19">
         <v>1234567998</v>
       </c>
       <c r="H110" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I110" s="20">
         <v>10107</v>
       </c>
-      <c r="J110" s="21"/>
+      <c r="J110" s="21">
+        <v>85107</v>
+      </c>
       <c r="K110" s="21"/>
       <c r="L110" s="21"/>
       <c r="M110" s="21"/>
@@ -5637,18 +5864,20 @@
         <v>4</v>
       </c>
       <c r="F111" s="49" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G111" s="19">
         <v>1234567999</v>
       </c>
       <c r="H111" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I111" s="20">
         <v>10108</v>
       </c>
-      <c r="J111" s="21"/>
+      <c r="J111" s="21">
+        <v>85108</v>
+      </c>
       <c r="K111" s="21"/>
       <c r="L111" s="21"/>
       <c r="M111" s="21"/>
@@ -5668,18 +5897,20 @@
         <v>5</v>
       </c>
       <c r="F112" s="64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G112" s="19">
         <v>1234568000</v>
       </c>
       <c r="H112" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I112" s="20">
         <v>10109</v>
       </c>
-      <c r="J112" s="21"/>
+      <c r="J112" s="21">
+        <v>85109</v>
+      </c>
       <c r="K112" s="21"/>
       <c r="L112" s="21"/>
       <c r="M112" s="21"/>
@@ -5699,18 +5930,20 @@
         <v>6</v>
       </c>
       <c r="F113" s="52" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G113" s="19">
         <v>1234568001</v>
       </c>
       <c r="H113" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I113" s="20">
         <v>10110</v>
       </c>
-      <c r="J113" s="21"/>
+      <c r="J113" s="21">
+        <v>85110</v>
+      </c>
       <c r="K113" s="21"/>
       <c r="L113" s="21"/>
       <c r="M113" s="21"/>
@@ -5732,18 +5965,20 @@
         <v>1</v>
       </c>
       <c r="F114" s="48" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G114" s="19">
         <v>1234568002</v>
       </c>
       <c r="H114" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I114" s="20">
         <v>10111</v>
       </c>
-      <c r="J114" s="32"/>
+      <c r="J114" s="21">
+        <v>85111</v>
+      </c>
       <c r="K114" s="32"/>
       <c r="L114" s="32"/>
       <c r="M114" s="32"/>
@@ -5763,18 +5998,20 @@
         <v>2</v>
       </c>
       <c r="F115" s="82" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G115" s="19">
         <v>1234568003</v>
       </c>
       <c r="H115" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I115" s="20">
         <v>10112</v>
       </c>
-      <c r="J115" s="21"/>
+      <c r="J115" s="21">
+        <v>85112</v>
+      </c>
       <c r="K115" s="21"/>
       <c r="L115" s="21"/>
       <c r="M115" s="21"/>
@@ -5794,18 +6031,20 @@
         <v>3</v>
       </c>
       <c r="F116" s="40" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G116" s="19">
         <v>1234568004</v>
       </c>
       <c r="H116" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I116" s="20">
         <v>10113</v>
       </c>
-      <c r="J116" s="21"/>
+      <c r="J116" s="21">
+        <v>85113</v>
+      </c>
       <c r="K116" s="21"/>
       <c r="L116" s="21"/>
       <c r="M116" s="21"/>
@@ -5827,18 +6066,20 @@
         <v>1</v>
       </c>
       <c r="F117" s="37" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G117" s="19">
         <v>1234568005</v>
       </c>
       <c r="H117" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I117" s="20">
         <v>10114</v>
       </c>
-      <c r="J117" s="32"/>
+      <c r="J117" s="21">
+        <v>85114</v>
+      </c>
       <c r="K117" s="32"/>
       <c r="L117" s="32"/>
       <c r="M117" s="32"/>
@@ -5858,18 +6099,20 @@
         <v>2</v>
       </c>
       <c r="F118" s="59" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G118" s="19">
         <v>1234568006</v>
       </c>
       <c r="H118" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I118" s="20">
         <v>10115</v>
       </c>
-      <c r="J118" s="21"/>
+      <c r="J118" s="21">
+        <v>85115</v>
+      </c>
       <c r="K118" s="21"/>
       <c r="L118" s="21"/>
       <c r="M118" s="21"/>
@@ -5889,18 +6132,20 @@
         <v>3</v>
       </c>
       <c r="F119" s="53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G119" s="19">
         <v>1234568007</v>
       </c>
       <c r="H119" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I119" s="20">
         <v>10116</v>
       </c>
-      <c r="J119" s="21"/>
+      <c r="J119" s="21">
+        <v>85116</v>
+      </c>
       <c r="K119" s="21"/>
       <c r="L119" s="21"/>
       <c r="M119" s="21"/>
@@ -5920,18 +6165,20 @@
         <v>4</v>
       </c>
       <c r="F120" s="83" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G120" s="19">
         <v>1234568008</v>
       </c>
       <c r="H120" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I120" s="20">
         <v>10117</v>
       </c>
-      <c r="J120" s="21"/>
+      <c r="J120" s="21">
+        <v>85117</v>
+      </c>
       <c r="K120" s="21"/>
       <c r="L120" s="21"/>
       <c r="M120" s="21"/>
@@ -5951,18 +6198,20 @@
         <v>5</v>
       </c>
       <c r="F121" s="38" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G121" s="19">
         <v>1234568009</v>
       </c>
       <c r="H121" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I121" s="20">
         <v>10118</v>
       </c>
-      <c r="J121" s="39"/>
+      <c r="J121" s="21">
+        <v>85118</v>
+      </c>
       <c r="K121" s="39"/>
       <c r="L121" s="39"/>
       <c r="M121" s="39"/>
@@ -5982,18 +6231,20 @@
         <v>6</v>
       </c>
       <c r="F122" s="34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G122" s="19">
         <v>1234568010</v>
       </c>
       <c r="H122" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I122" s="20">
         <v>10119</v>
       </c>
-      <c r="J122" s="35"/>
+      <c r="J122" s="21">
+        <v>85119</v>
+      </c>
       <c r="K122" s="35"/>
       <c r="L122" s="35"/>
       <c r="M122" s="35"/>
@@ -6015,18 +6266,20 @@
         <v>1</v>
       </c>
       <c r="F123" s="85" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G123" s="19">
         <v>1234568011</v>
       </c>
       <c r="H123" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I123" s="20">
         <v>10120</v>
       </c>
-      <c r="J123" s="32"/>
+      <c r="J123" s="21">
+        <v>85120</v>
+      </c>
       <c r="K123" s="32"/>
       <c r="L123" s="32"/>
       <c r="M123" s="32"/>
@@ -6046,18 +6299,20 @@
         <v>2</v>
       </c>
       <c r="F124" s="25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G124" s="19">
         <v>1234568012</v>
       </c>
       <c r="H124" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I124" s="20">
         <v>10121</v>
       </c>
-      <c r="J124" s="21"/>
+      <c r="J124" s="21">
+        <v>85121</v>
+      </c>
       <c r="K124" s="21"/>
       <c r="L124" s="21"/>
       <c r="M124" s="21"/>
@@ -6077,18 +6332,20 @@
         <v>3</v>
       </c>
       <c r="F125" s="25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G125" s="19">
         <v>1234568013</v>
       </c>
       <c r="H125" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I125" s="20">
         <v>10122</v>
       </c>
-      <c r="J125" s="21"/>
+      <c r="J125" s="21">
+        <v>85122</v>
+      </c>
       <c r="K125" s="21"/>
       <c r="L125" s="21"/>
       <c r="M125" s="21"/>
@@ -6108,18 +6365,20 @@
         <v>4</v>
       </c>
       <c r="F126" s="38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G126" s="19">
         <v>1234568014</v>
       </c>
       <c r="H126" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I126" s="20">
         <v>10123</v>
       </c>
-      <c r="J126" s="21"/>
+      <c r="J126" s="21">
+        <v>85123</v>
+      </c>
       <c r="K126" s="21"/>
       <c r="L126" s="21"/>
       <c r="M126" s="21"/>
@@ -6139,18 +6398,20 @@
         <v>5</v>
       </c>
       <c r="F127" s="52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G127" s="19">
         <v>1234568015</v>
       </c>
       <c r="H127" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I127" s="20">
         <v>10124</v>
       </c>
-      <c r="J127" s="21"/>
+      <c r="J127" s="21">
+        <v>85124</v>
+      </c>
       <c r="K127" s="21"/>
       <c r="L127" s="21"/>
       <c r="M127" s="21"/>
@@ -6170,18 +6431,20 @@
         <v>6</v>
       </c>
       <c r="F128" s="65" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G128" s="19">
         <v>1234568016</v>
       </c>
       <c r="H128" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I128" s="20">
         <v>10125</v>
       </c>
-      <c r="J128" s="35"/>
+      <c r="J128" s="21">
+        <v>85125</v>
+      </c>
       <c r="K128" s="35"/>
       <c r="L128" s="35"/>
       <c r="M128" s="35"/>
@@ -6203,18 +6466,20 @@
         <v>1</v>
       </c>
       <c r="F129" s="66" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G129" s="19">
         <v>1234568017</v>
       </c>
       <c r="H129" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I129" s="20">
         <v>10126</v>
       </c>
-      <c r="J129" s="42"/>
+      <c r="J129" s="21">
+        <v>85126</v>
+      </c>
       <c r="K129" s="22"/>
       <c r="L129" s="42"/>
       <c r="M129" s="22"/>
@@ -6234,18 +6499,20 @@
         <v>2</v>
       </c>
       <c r="F130" s="37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G130" s="19">
         <v>1234568018</v>
       </c>
       <c r="H130" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I130" s="20">
         <v>10127</v>
       </c>
-      <c r="J130" s="21"/>
+      <c r="J130" s="21">
+        <v>85127</v>
+      </c>
       <c r="K130" s="21"/>
       <c r="L130" s="21"/>
       <c r="M130" s="21"/>
@@ -6265,18 +6532,20 @@
         <v>3</v>
       </c>
       <c r="F131" s="75" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G131" s="19">
         <v>1234568019</v>
       </c>
       <c r="H131" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I131" s="20">
         <v>10128</v>
       </c>
-      <c r="J131" s="39"/>
+      <c r="J131" s="21">
+        <v>85128</v>
+      </c>
       <c r="K131" s="39"/>
       <c r="L131" s="39"/>
       <c r="M131" s="39"/>
@@ -6296,16 +6565,19 @@
         <v>4</v>
       </c>
       <c r="F132" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G132" s="19">
         <v>1234568020</v>
       </c>
       <c r="H132" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I132" s="20">
         <v>10129</v>
+      </c>
+      <c r="J132" s="21">
+        <v>85129</v>
       </c>
     </row>
     <row r="133" ht="17.1" spans="1:19">
@@ -6317,18 +6589,20 @@
         <v>5</v>
       </c>
       <c r="F133" s="41" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G133" s="19">
         <v>1234568021</v>
       </c>
       <c r="H133" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I133" s="20">
         <v>10130</v>
       </c>
-      <c r="J133" s="21"/>
+      <c r="J133" s="21">
+        <v>85130</v>
+      </c>
       <c r="K133" s="21"/>
       <c r="L133" s="21"/>
       <c r="M133" s="21"/>
@@ -6348,18 +6622,20 @@
         <v>6</v>
       </c>
       <c r="F134" s="88" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G134" s="19">
         <v>1234568022</v>
       </c>
       <c r="H134" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I134" s="20">
         <v>10131</v>
       </c>
-      <c r="J134" s="39"/>
+      <c r="J134" s="21">
+        <v>85131</v>
+      </c>
       <c r="K134" s="39"/>
       <c r="L134" s="39"/>
       <c r="M134" s="39"/>
@@ -6381,18 +6657,20 @@
         <v>1</v>
       </c>
       <c r="F135" s="40" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G135" s="19">
         <v>1234568023</v>
       </c>
       <c r="H135" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I135" s="20">
         <v>10132</v>
       </c>
-      <c r="J135" s="21"/>
+      <c r="J135" s="21">
+        <v>85132</v>
+      </c>
       <c r="K135" s="21"/>
       <c r="L135" s="21"/>
       <c r="M135" s="21"/>
@@ -6412,18 +6690,20 @@
         <v>2</v>
       </c>
       <c r="F136" s="89" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G136" s="19">
         <v>1234568024</v>
       </c>
       <c r="H136" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I136" s="20">
         <v>10133</v>
       </c>
-      <c r="J136" s="32"/>
+      <c r="J136" s="21">
+        <v>85133</v>
+      </c>
       <c r="K136" s="32"/>
       <c r="L136" s="32"/>
       <c r="M136" s="32"/>
@@ -6443,18 +6723,20 @@
         <v>3</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G137" s="19">
         <v>1234568025</v>
       </c>
       <c r="H137" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I137" s="20">
         <v>10134</v>
       </c>
-      <c r="J137" s="21"/>
+      <c r="J137" s="21">
+        <v>85134</v>
+      </c>
       <c r="K137" s="21"/>
       <c r="L137" s="21"/>
       <c r="M137" s="21"/>
@@ -6474,18 +6756,20 @@
         <v>4</v>
       </c>
       <c r="F138" s="75" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G138" s="19">
         <v>1234568026</v>
       </c>
       <c r="H138" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I138" s="20">
         <v>10135</v>
       </c>
-      <c r="J138" s="21"/>
+      <c r="J138" s="21">
+        <v>85135</v>
+      </c>
       <c r="K138" s="21"/>
       <c r="L138" s="21"/>
       <c r="M138" s="21"/>
@@ -6505,18 +6789,20 @@
         <v>5</v>
       </c>
       <c r="F139" s="40" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G139" s="19">
         <v>1234568027</v>
       </c>
       <c r="H139" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I139" s="20">
         <v>10136</v>
       </c>
-      <c r="J139" s="21"/>
+      <c r="J139" s="21">
+        <v>85136</v>
+      </c>
       <c r="K139" s="21"/>
       <c r="L139" s="21"/>
       <c r="M139" s="21"/>
@@ -6536,18 +6822,20 @@
         <v>6</v>
       </c>
       <c r="F140" s="62" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G140" s="19">
         <v>1234568028</v>
       </c>
       <c r="H140" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I140" s="20">
         <v>10137</v>
       </c>
-      <c r="J140" s="21"/>
+      <c r="J140" s="21">
+        <v>85137</v>
+      </c>
       <c r="K140" s="21"/>
       <c r="L140" s="21"/>
       <c r="M140" s="21"/>
@@ -6569,18 +6857,20 @@
         <v>1</v>
       </c>
       <c r="F141" s="90" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G141" s="19">
         <v>1234568029</v>
       </c>
       <c r="H141" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I141" s="20">
         <v>10138</v>
       </c>
-      <c r="J141" s="21"/>
+      <c r="J141" s="21">
+        <v>85138</v>
+      </c>
       <c r="K141" s="21"/>
       <c r="L141" s="21"/>
       <c r="M141" s="21"/>
@@ -6600,18 +6890,20 @@
         <v>2</v>
       </c>
       <c r="F142" s="91" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G142" s="19">
         <v>1234568030</v>
       </c>
       <c r="H142" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I142" s="20">
         <v>10139</v>
       </c>
-      <c r="J142" s="21"/>
+      <c r="J142" s="21">
+        <v>85139</v>
+      </c>
       <c r="K142" s="21"/>
       <c r="L142" s="21"/>
       <c r="M142" s="21"/>
@@ -6631,18 +6923,20 @@
         <v>3</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G143" s="19">
         <v>1234568031</v>
       </c>
       <c r="H143" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I143" s="20">
         <v>10140</v>
       </c>
-      <c r="J143" s="21"/>
+      <c r="J143" s="21">
+        <v>85140</v>
+      </c>
       <c r="K143" s="21"/>
       <c r="L143" s="21"/>
       <c r="M143" s="21"/>
@@ -6662,18 +6956,20 @@
         <v>4</v>
       </c>
       <c r="F144" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G144" s="19">
         <v>1234568032</v>
       </c>
       <c r="H144" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I144" s="20">
         <v>10141</v>
       </c>
-      <c r="J144" s="32"/>
+      <c r="J144" s="21">
+        <v>85141</v>
+      </c>
       <c r="K144" s="32"/>
       <c r="L144" s="32"/>
       <c r="M144" s="32"/>
@@ -6693,18 +6989,20 @@
         <v>5</v>
       </c>
       <c r="F145" s="52" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G145" s="19">
         <v>1234568033</v>
       </c>
       <c r="H145" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I145" s="20">
         <v>10142</v>
       </c>
-      <c r="J145" s="21"/>
+      <c r="J145" s="21">
+        <v>85142</v>
+      </c>
       <c r="K145" s="21"/>
       <c r="L145" s="21"/>
       <c r="M145" s="21"/>
@@ -6724,18 +7022,20 @@
         <v>6</v>
       </c>
       <c r="F146" s="92" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G146" s="19">
         <v>1234568034</v>
       </c>
       <c r="H146" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I146" s="20">
         <v>10143</v>
       </c>
-      <c r="J146" s="35"/>
+      <c r="J146" s="21">
+        <v>85143</v>
+      </c>
       <c r="K146" s="35"/>
       <c r="L146" s="35"/>
       <c r="M146" s="35"/>
@@ -6757,18 +7057,20 @@
         <v>1</v>
       </c>
       <c r="F147" s="37" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G147" s="19">
         <v>1234568035</v>
       </c>
       <c r="H147" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I147" s="20">
         <v>10144</v>
       </c>
-      <c r="J147" s="32"/>
+      <c r="J147" s="21">
+        <v>85144</v>
+      </c>
       <c r="K147" s="32"/>
       <c r="L147" s="32"/>
       <c r="M147" s="32"/>
@@ -6788,18 +7090,20 @@
         <v>2</v>
       </c>
       <c r="F148" s="93" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G148" s="19">
         <v>1234568036</v>
       </c>
       <c r="H148" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I148" s="20">
         <v>10145</v>
       </c>
-      <c r="J148" s="21"/>
+      <c r="J148" s="21">
+        <v>85145</v>
+      </c>
       <c r="K148" s="21"/>
       <c r="L148" s="21"/>
       <c r="M148" s="21"/>
@@ -6810,7 +7114,7 @@
       <c r="R148" s="23"/>
       <c r="S148" s="21"/>
       <c r="U148" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="149" spans="1:21">
@@ -6822,18 +7126,20 @@
         <v>3</v>
       </c>
       <c r="F149" s="40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G149" s="19">
         <v>1234568037</v>
       </c>
       <c r="H149" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I149" s="20">
         <v>10146</v>
       </c>
-      <c r="J149" s="21"/>
+      <c r="J149" s="21">
+        <v>85146</v>
+      </c>
       <c r="K149" s="21"/>
       <c r="L149" s="21"/>
       <c r="M149" s="21"/>
@@ -6853,18 +7159,20 @@
         <v>4</v>
       </c>
       <c r="F150" s="40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G150" s="19">
         <v>1234568038</v>
       </c>
       <c r="H150" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I150" s="20">
         <v>10147</v>
       </c>
-      <c r="J150" s="32"/>
+      <c r="J150" s="21">
+        <v>85147</v>
+      </c>
       <c r="K150" s="32"/>
       <c r="L150" s="32"/>
       <c r="M150" s="32"/>
@@ -6884,18 +7192,20 @@
         <v>5</v>
       </c>
       <c r="F151" s="92" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G151" s="19">
         <v>1234568039</v>
       </c>
       <c r="H151" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I151" s="20">
         <v>10148</v>
       </c>
-      <c r="J151" s="21"/>
+      <c r="J151" s="21">
+        <v>85148</v>
+      </c>
       <c r="K151" s="21"/>
       <c r="L151" s="21"/>
       <c r="M151" s="21"/>
@@ -6915,18 +7225,20 @@
         <v>6</v>
       </c>
       <c r="F152" s="94" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G152" s="19">
         <v>1234568040</v>
       </c>
       <c r="H152" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I152" s="20">
         <v>10149</v>
       </c>
-      <c r="J152" s="21"/>
+      <c r="J152" s="21">
+        <v>85149</v>
+      </c>
       <c r="K152" s="21"/>
       <c r="L152" s="21"/>
       <c r="M152" s="21"/>
@@ -6948,18 +7260,20 @@
         <v>1</v>
       </c>
       <c r="F153" s="37" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G153" s="19">
         <v>1234568041</v>
       </c>
       <c r="H153" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I153" s="20">
         <v>10150</v>
       </c>
-      <c r="J153" s="32"/>
+      <c r="J153" s="21">
+        <v>85150</v>
+      </c>
       <c r="K153" s="32"/>
       <c r="L153" s="32"/>
       <c r="M153" s="32"/>
@@ -6979,18 +7293,20 @@
         <v>2</v>
       </c>
       <c r="F154" s="34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G154" s="19">
         <v>1234568042</v>
       </c>
       <c r="H154" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I154" s="20">
         <v>10151</v>
       </c>
-      <c r="J154" s="21"/>
+      <c r="J154" s="21">
+        <v>85151</v>
+      </c>
       <c r="K154" s="21"/>
       <c r="L154" s="21"/>
       <c r="M154" s="21"/>
@@ -7010,18 +7326,20 @@
         <v>3</v>
       </c>
       <c r="F155" s="50" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G155" s="19">
         <v>1234568043</v>
       </c>
       <c r="H155" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I155" s="20">
         <v>10152</v>
       </c>
-      <c r="J155" s="21"/>
+      <c r="J155" s="21">
+        <v>85152</v>
+      </c>
       <c r="K155" s="21"/>
       <c r="L155" s="21"/>
       <c r="M155" s="21"/>
@@ -7041,18 +7359,20 @@
         <v>4</v>
       </c>
       <c r="F156" s="25" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G156" s="19">
         <v>1234568044</v>
       </c>
       <c r="H156" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I156" s="20">
         <v>10153</v>
       </c>
-      <c r="J156" s="21"/>
+      <c r="J156" s="21">
+        <v>85153</v>
+      </c>
       <c r="K156" s="21"/>
       <c r="L156" s="21"/>
       <c r="M156" s="21"/>
@@ -7072,18 +7392,20 @@
         <v>5</v>
       </c>
       <c r="F157" s="34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G157" s="19">
         <v>1234568045</v>
       </c>
       <c r="H157" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I157" s="20">
         <v>10154</v>
       </c>
-      <c r="J157" s="21"/>
+      <c r="J157" s="21">
+        <v>85154</v>
+      </c>
       <c r="K157" s="21"/>
       <c r="L157" s="21"/>
       <c r="M157" s="21"/>
@@ -7103,18 +7425,20 @@
         <v>6</v>
       </c>
       <c r="F158" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G158" s="19">
         <v>1234568046</v>
       </c>
       <c r="H158" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I158" s="20">
         <v>10155</v>
       </c>
-      <c r="J158" s="39"/>
+      <c r="J158" s="21">
+        <v>85155</v>
+      </c>
       <c r="K158" s="39"/>
       <c r="L158" s="39"/>
       <c r="M158" s="39"/>
@@ -7136,18 +7460,20 @@
         <v>1</v>
       </c>
       <c r="F159" s="64" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G159" s="19">
         <v>1234568047</v>
       </c>
       <c r="H159" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I159" s="20">
         <v>10156</v>
       </c>
-      <c r="J159" s="21"/>
+      <c r="J159" s="21">
+        <v>85156</v>
+      </c>
       <c r="K159" s="21"/>
       <c r="L159" s="21"/>
       <c r="M159" s="21"/>
@@ -7167,18 +7493,20 @@
         <v>2</v>
       </c>
       <c r="F160" s="38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G160" s="19">
         <v>1234568048</v>
       </c>
       <c r="H160" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I160" s="20">
         <v>10157</v>
       </c>
-      <c r="J160" s="21"/>
+      <c r="J160" s="21">
+        <v>85157</v>
+      </c>
       <c r="K160" s="21"/>
       <c r="L160" s="21"/>
       <c r="M160" s="21"/>
@@ -7198,18 +7526,20 @@
         <v>3</v>
       </c>
       <c r="F161" s="52" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G161" s="19">
         <v>1234568049</v>
       </c>
       <c r="H161" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I161" s="20">
         <v>10158</v>
       </c>
-      <c r="J161" s="21"/>
+      <c r="J161" s="21">
+        <v>85158</v>
+      </c>
       <c r="K161" s="21"/>
       <c r="L161" s="21"/>
       <c r="M161" s="21"/>
@@ -7229,18 +7559,20 @@
         <v>4</v>
       </c>
       <c r="F162" s="52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G162" s="19">
         <v>1234568050</v>
       </c>
       <c r="H162" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I162" s="20">
         <v>10159</v>
       </c>
-      <c r="J162" s="21"/>
+      <c r="J162" s="21">
+        <v>85159</v>
+      </c>
       <c r="K162" s="21"/>
       <c r="L162" s="21"/>
       <c r="M162" s="21"/>
@@ -7260,18 +7592,20 @@
         <v>5</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G163" s="19">
         <v>1234568051</v>
       </c>
       <c r="H163" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I163" s="20">
         <v>10160</v>
       </c>
-      <c r="J163" s="22"/>
+      <c r="J163" s="21">
+        <v>85160</v>
+      </c>
       <c r="K163" s="22"/>
       <c r="L163" s="22"/>
       <c r="M163" s="22"/>
@@ -7291,18 +7625,20 @@
         <v>6</v>
       </c>
       <c r="F164" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G164" s="19">
         <v>1234568052</v>
       </c>
       <c r="H164" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I164" s="20">
         <v>10161</v>
       </c>
-      <c r="J164" s="21"/>
+      <c r="J164" s="21">
+        <v>85161</v>
+      </c>
       <c r="K164" s="21"/>
       <c r="L164" s="21"/>
       <c r="M164" s="21"/>
@@ -7324,18 +7660,20 @@
         <v>1</v>
       </c>
       <c r="F165" s="40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G165" s="19">
         <v>1234568053</v>
       </c>
       <c r="H165" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I165" s="20">
         <v>10162</v>
       </c>
-      <c r="J165" s="21"/>
+      <c r="J165" s="21">
+        <v>85162</v>
+      </c>
       <c r="K165" s="21"/>
       <c r="L165" s="21"/>
       <c r="M165" s="21"/>
@@ -7355,18 +7693,20 @@
         <v>2</v>
       </c>
       <c r="F166" s="40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G166" s="19">
         <v>1234568054</v>
       </c>
       <c r="H166" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I166" s="20">
         <v>10163</v>
       </c>
-      <c r="J166" s="21"/>
+      <c r="J166" s="21">
+        <v>85163</v>
+      </c>
       <c r="K166" s="21"/>
       <c r="L166" s="21"/>
       <c r="M166" s="21"/>
@@ -7386,18 +7726,20 @@
         <v>3</v>
       </c>
       <c r="F167" s="25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G167" s="19">
         <v>1234568055</v>
       </c>
       <c r="H167" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I167" s="20">
         <v>10164</v>
       </c>
-      <c r="J167" s="21"/>
+      <c r="J167" s="21">
+        <v>85164</v>
+      </c>
       <c r="K167" s="21"/>
       <c r="L167" s="21"/>
       <c r="M167" s="21"/>
@@ -7417,18 +7759,20 @@
         <v>4</v>
       </c>
       <c r="F168" s="61" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G168" s="19">
         <v>1234568056</v>
       </c>
       <c r="H168" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I168" s="20">
         <v>10165</v>
       </c>
-      <c r="J168" s="21"/>
+      <c r="J168" s="21">
+        <v>85165</v>
+      </c>
       <c r="K168" s="21"/>
       <c r="L168" s="21"/>
       <c r="M168" s="21"/>
@@ -7448,18 +7792,20 @@
         <v>5</v>
       </c>
       <c r="F169" s="52" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G169" s="19">
         <v>1234568057</v>
       </c>
       <c r="H169" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I169" s="20">
         <v>10166</v>
       </c>
-      <c r="J169" s="21"/>
+      <c r="J169" s="21">
+        <v>85166</v>
+      </c>
       <c r="K169" s="21"/>
       <c r="L169" s="21"/>
       <c r="M169" s="21"/>
@@ -7479,18 +7825,20 @@
         <v>6</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G170" s="19">
         <v>1234568058</v>
       </c>
       <c r="H170" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I170" s="20">
         <v>10167</v>
       </c>
-      <c r="J170" s="35"/>
+      <c r="J170" s="21">
+        <v>85167</v>
+      </c>
       <c r="K170" s="35"/>
       <c r="L170" s="35"/>
       <c r="M170" s="35"/>
@@ -7512,18 +7860,20 @@
         <v>1</v>
       </c>
       <c r="F171" s="37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G171" s="19">
         <v>1234568059</v>
       </c>
       <c r="H171" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I171" s="20">
         <v>10168</v>
       </c>
-      <c r="J171" s="32"/>
+      <c r="J171" s="21">
+        <v>85168</v>
+      </c>
       <c r="K171" s="32"/>
       <c r="L171" s="32"/>
       <c r="M171" s="32"/>
@@ -7543,18 +7893,20 @@
         <v>2</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G172" s="19">
         <v>1234568060</v>
       </c>
       <c r="H172" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I172" s="20">
         <v>10169</v>
       </c>
-      <c r="J172" s="21"/>
+      <c r="J172" s="21">
+        <v>85169</v>
+      </c>
       <c r="K172" s="21"/>
       <c r="L172" s="21"/>
       <c r="M172" s="21"/>
@@ -7574,18 +7926,20 @@
         <v>3</v>
       </c>
       <c r="F173" s="95" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G173" s="19">
         <v>1234568061</v>
       </c>
       <c r="H173" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I173" s="20">
         <v>10170</v>
       </c>
-      <c r="J173" s="21"/>
+      <c r="J173" s="21">
+        <v>85170</v>
+      </c>
       <c r="K173" s="21"/>
       <c r="L173" s="21"/>
       <c r="M173" s="21"/>
@@ -7605,18 +7959,20 @@
         <v>4</v>
       </c>
       <c r="F174" s="65" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G174" s="19">
         <v>1234568062</v>
       </c>
       <c r="H174" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I174" s="20">
         <v>10171</v>
       </c>
-      <c r="J174" s="21"/>
+      <c r="J174" s="21">
+        <v>85171</v>
+      </c>
       <c r="K174" s="21"/>
       <c r="L174" s="21"/>
       <c r="M174" s="21"/>
@@ -7636,18 +7992,20 @@
         <v>5</v>
       </c>
       <c r="F175" s="40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G175" s="19">
         <v>1234568063</v>
       </c>
       <c r="H175" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I175" s="20">
         <v>10172</v>
       </c>
-      <c r="J175" s="21"/>
+      <c r="J175" s="21">
+        <v>85172</v>
+      </c>
       <c r="K175" s="21"/>
       <c r="L175" s="21"/>
       <c r="M175" s="21"/>
@@ -7667,18 +8025,20 @@
         <v>6</v>
       </c>
       <c r="F176" s="96" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G176" s="19">
         <v>1234568064</v>
       </c>
       <c r="H176" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I176" s="20">
         <v>10173</v>
       </c>
-      <c r="J176" s="35"/>
+      <c r="J176" s="21">
+        <v>85173</v>
+      </c>
       <c r="K176" s="35"/>
       <c r="L176" s="35"/>
       <c r="M176" s="35"/>
@@ -7700,18 +8060,20 @@
         <v>1</v>
       </c>
       <c r="F177" s="85" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G177" s="19">
         <v>1234568065</v>
       </c>
       <c r="H177" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I177" s="20">
         <v>10174</v>
       </c>
-      <c r="J177" s="32"/>
+      <c r="J177" s="21">
+        <v>85174</v>
+      </c>
       <c r="K177" s="32"/>
       <c r="L177" s="21"/>
       <c r="M177" s="21"/>
@@ -7731,18 +8093,20 @@
         <v>2</v>
       </c>
       <c r="F178" s="62" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G178" s="19">
         <v>1234568066</v>
       </c>
       <c r="H178" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I178" s="20">
         <v>10175</v>
       </c>
-      <c r="J178" s="39"/>
+      <c r="J178" s="21">
+        <v>85175</v>
+      </c>
       <c r="K178" s="39"/>
       <c r="L178" s="39"/>
       <c r="M178" s="39"/>
@@ -7762,18 +8126,20 @@
         <v>3</v>
       </c>
       <c r="F179" s="37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G179" s="19">
         <v>1234568067</v>
       </c>
       <c r="H179" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I179" s="20">
         <v>10176</v>
       </c>
-      <c r="J179" s="21"/>
+      <c r="J179" s="21">
+        <v>85176</v>
+      </c>
       <c r="K179" s="21"/>
       <c r="L179" s="21"/>
       <c r="M179" s="21"/>
@@ -7795,18 +8161,20 @@
         <v>1</v>
       </c>
       <c r="F180" s="37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G180" s="19">
         <v>1234568068</v>
       </c>
       <c r="H180" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I180" s="20">
         <v>10177</v>
       </c>
-      <c r="J180" s="32"/>
+      <c r="J180" s="21">
+        <v>85177</v>
+      </c>
       <c r="K180" s="32"/>
       <c r="L180" s="32"/>
       <c r="M180" s="32"/>
@@ -7826,16 +8194,19 @@
         <v>2</v>
       </c>
       <c r="F181" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G181" s="19">
         <v>1234568069</v>
       </c>
       <c r="H181" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I181" s="20">
         <v>10178</v>
+      </c>
+      <c r="J181" s="21">
+        <v>85178</v>
       </c>
       <c r="O181" s="67"/>
       <c r="P181" s="32"/>
@@ -7849,16 +8220,19 @@
         <v>3</v>
       </c>
       <c r="F182" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G182" s="19">
         <v>1234568070</v>
       </c>
       <c r="H182" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I182" s="20">
         <v>10179</v>
+      </c>
+      <c r="J182" s="21">
+        <v>85179</v>
       </c>
       <c r="O182" s="67"/>
       <c r="P182" s="32"/>
@@ -7872,18 +8246,20 @@
         <v>4</v>
       </c>
       <c r="F183" s="98" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G183" s="19">
         <v>1234568071</v>
       </c>
       <c r="H183" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I183" s="20">
         <v>10180</v>
       </c>
-      <c r="J183" s="21"/>
+      <c r="J183" s="21">
+        <v>85180</v>
+      </c>
       <c r="K183" s="21"/>
       <c r="L183" s="21"/>
       <c r="M183" s="21"/>
@@ -7903,18 +8279,20 @@
         <v>5</v>
       </c>
       <c r="F184" s="98" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G184" s="19">
         <v>1234568072</v>
       </c>
       <c r="H184" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I184" s="20">
         <v>10181</v>
       </c>
-      <c r="J184" s="21"/>
+      <c r="J184" s="21">
+        <v>85181</v>
+      </c>
       <c r="K184" s="21"/>
       <c r="L184" s="21"/>
       <c r="M184" s="21"/>
@@ -7934,18 +8312,20 @@
         <v>6</v>
       </c>
       <c r="F185" s="99" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G185" s="19">
         <v>1234568073</v>
       </c>
       <c r="H185" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I185" s="20">
         <v>10182</v>
       </c>
-      <c r="J185" s="21"/>
+      <c r="J185" s="21">
+        <v>85182</v>
+      </c>
       <c r="K185" s="21"/>
       <c r="L185" s="21"/>
       <c r="M185" s="21"/>
@@ -7967,18 +8347,20 @@
         <v>1</v>
       </c>
       <c r="F186" s="85" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G186" s="19">
         <v>1234568074</v>
       </c>
       <c r="H186" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I186" s="20">
         <v>10183</v>
       </c>
-      <c r="J186" s="32"/>
+      <c r="J186" s="21">
+        <v>85183</v>
+      </c>
       <c r="K186" s="32"/>
       <c r="L186" s="32"/>
       <c r="M186" s="32"/>
@@ -7998,18 +8380,20 @@
         <v>2</v>
       </c>
       <c r="F187" s="25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G187" s="19">
         <v>1234568075</v>
       </c>
       <c r="H187" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I187" s="20">
         <v>10184</v>
       </c>
-      <c r="J187" s="21"/>
+      <c r="J187" s="21">
+        <v>85184</v>
+      </c>
       <c r="K187" s="21"/>
       <c r="L187" s="21"/>
       <c r="M187" s="21"/>
@@ -8029,18 +8413,20 @@
         <v>3</v>
       </c>
       <c r="F188" s="40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G188" s="19">
         <v>1234568076</v>
       </c>
       <c r="H188" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I188" s="20">
         <v>10185</v>
       </c>
-      <c r="J188" s="21"/>
+      <c r="J188" s="21">
+        <v>85185</v>
+      </c>
       <c r="K188" s="21"/>
       <c r="L188" s="21"/>
       <c r="M188" s="21"/>
@@ -8060,16 +8446,19 @@
         <v>4</v>
       </c>
       <c r="F189" s="54" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G189" s="19">
         <v>1234568077</v>
       </c>
       <c r="H189" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I189" s="20">
         <v>10186</v>
+      </c>
+      <c r="J189" s="21">
+        <v>85186</v>
       </c>
     </row>
     <row r="190" ht="16.35" spans="1:20">
@@ -8081,18 +8470,20 @@
         <v>5</v>
       </c>
       <c r="F190" s="40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G190" s="19">
         <v>1234568078</v>
       </c>
       <c r="H190" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I190" s="20">
         <v>10187</v>
       </c>
-      <c r="J190" s="32"/>
+      <c r="J190" s="21">
+        <v>85187</v>
+      </c>
       <c r="K190" s="32"/>
       <c r="L190" s="32"/>
       <c r="M190" s="32"/>
@@ -8112,18 +8503,20 @@
         <v>6</v>
       </c>
       <c r="F191" s="56" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G191" s="19">
         <v>1234568079</v>
       </c>
       <c r="H191" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I191" s="20">
         <v>10188</v>
       </c>
-      <c r="J191" s="21"/>
+      <c r="J191" s="21">
+        <v>85188</v>
+      </c>
       <c r="K191" s="21"/>
       <c r="L191" s="21"/>
       <c r="M191" s="21"/>
@@ -8146,18 +8539,20 @@
         <v>1</v>
       </c>
       <c r="F192" s="40" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G192" s="19">
         <v>1234568080</v>
       </c>
       <c r="H192" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I192" s="20">
         <v>10189</v>
       </c>
-      <c r="J192" s="21"/>
+      <c r="J192" s="21">
+        <v>85189</v>
+      </c>
       <c r="K192" s="21"/>
       <c r="L192" s="21"/>
       <c r="M192" s="21"/>
@@ -8177,18 +8572,20 @@
         <v>2</v>
       </c>
       <c r="F193" s="101" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G193" s="19">
         <v>1234568081</v>
       </c>
       <c r="H193" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I193" s="20">
         <v>10190</v>
       </c>
-      <c r="J193" s="21"/>
+      <c r="J193" s="21">
+        <v>85190</v>
+      </c>
       <c r="K193" s="21"/>
       <c r="L193" s="21"/>
       <c r="M193" s="21"/>
@@ -8208,18 +8605,20 @@
         <v>3</v>
       </c>
       <c r="F194" s="101" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G194" s="19">
         <v>1234568082</v>
       </c>
       <c r="H194" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I194" s="20">
         <v>10191</v>
       </c>
-      <c r="J194" s="21"/>
+      <c r="J194" s="21">
+        <v>85191</v>
+      </c>
       <c r="K194" s="21"/>
       <c r="L194" s="21"/>
       <c r="M194" s="21"/>
@@ -8239,18 +8638,20 @@
         <v>4</v>
       </c>
       <c r="F195" s="101" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G195" s="19">
         <v>1234568083</v>
       </c>
       <c r="H195" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I195" s="20">
         <v>10192</v>
       </c>
-      <c r="J195" s="21"/>
+      <c r="J195" s="21">
+        <v>85192</v>
+      </c>
       <c r="K195" s="21"/>
       <c r="L195" s="21"/>
       <c r="M195" s="21"/>
@@ -8270,18 +8671,20 @@
         <v>5</v>
       </c>
       <c r="F196" s="101" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G196" s="19">
         <v>1234568084</v>
       </c>
       <c r="H196" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I196" s="20">
         <v>10193</v>
       </c>
-      <c r="J196" s="21"/>
+      <c r="J196" s="21">
+        <v>85193</v>
+      </c>
       <c r="K196" s="21"/>
       <c r="L196" s="21"/>
       <c r="M196" s="21"/>
@@ -8301,18 +8704,20 @@
         <v>6</v>
       </c>
       <c r="F197" s="38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G197" s="19">
         <v>1234568085</v>
       </c>
       <c r="H197" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I197" s="20">
         <v>10194</v>
       </c>
-      <c r="J197" s="35"/>
+      <c r="J197" s="21">
+        <v>85194</v>
+      </c>
       <c r="K197" s="35"/>
       <c r="L197" s="35"/>
       <c r="M197" s="35"/>
@@ -8334,18 +8739,20 @@
         <v>1</v>
       </c>
       <c r="F198" s="40" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G198" s="19">
         <v>1234568086</v>
       </c>
       <c r="H198" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I198" s="20">
         <v>10195</v>
       </c>
-      <c r="J198" s="32"/>
+      <c r="J198" s="21">
+        <v>85195</v>
+      </c>
       <c r="K198" s="32"/>
       <c r="L198" s="42"/>
       <c r="M198" s="32"/>
@@ -8365,18 +8772,20 @@
         <v>2</v>
       </c>
       <c r="F199" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G199" s="19">
         <v>1234568087</v>
       </c>
       <c r="H199" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I199" s="20">
         <v>10196</v>
       </c>
-      <c r="J199" s="21"/>
+      <c r="J199" s="21">
+        <v>85196</v>
+      </c>
       <c r="K199" s="21"/>
       <c r="L199" s="21"/>
       <c r="M199" s="21"/>
@@ -8396,18 +8805,20 @@
         <v>3</v>
       </c>
       <c r="F200" s="37" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G200" s="19">
         <v>1234568088</v>
       </c>
       <c r="H200" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I200" s="20">
         <v>10197</v>
       </c>
-      <c r="J200" s="21"/>
+      <c r="J200" s="21">
+        <v>85197</v>
+      </c>
       <c r="K200" s="21"/>
       <c r="L200" s="21"/>
       <c r="M200" s="21"/>
@@ -8427,18 +8838,20 @@
         <v>4</v>
       </c>
       <c r="F201" s="25" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G201" s="19">
         <v>1234568089</v>
       </c>
       <c r="H201" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I201" s="20">
         <v>10198</v>
       </c>
-      <c r="J201" s="21"/>
+      <c r="J201" s="21">
+        <v>85198</v>
+      </c>
       <c r="K201" s="21"/>
       <c r="L201" s="21"/>
       <c r="M201" s="21"/>
@@ -8458,18 +8871,20 @@
         <v>5</v>
       </c>
       <c r="F202" s="40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G202" s="19">
         <v>1234568090</v>
       </c>
       <c r="H202" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I202" s="20">
         <v>10199</v>
       </c>
-      <c r="J202" s="21"/>
+      <c r="J202" s="21">
+        <v>85199</v>
+      </c>
       <c r="K202" s="21"/>
       <c r="L202" s="21"/>
       <c r="M202" s="21"/>
@@ -8489,18 +8904,20 @@
         <v>6</v>
       </c>
       <c r="F203" s="64" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G203" s="19">
         <v>1234568091</v>
       </c>
       <c r="H203" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I203" s="20">
         <v>10200</v>
       </c>
-      <c r="J203" s="102"/>
+      <c r="J203" s="21">
+        <v>85200</v>
+      </c>
       <c r="K203" s="102"/>
       <c r="L203" s="102"/>
       <c r="M203" s="102"/>

--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HIMANSHU\hostel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D310BA04-7035-4375-BCFD-FDD1BB90F950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13120FF-75D8-4FDE-87F3-6E4C905812C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="298">
   <si>
     <t>ROOMS</t>
   </si>
@@ -1110,12 +1110,63 @@
   <si>
     <t>vacate</t>
   </si>
+  <si>
+    <t>DORM</t>
+  </si>
+  <si>
+    <t>Kavish Navin Joshi</t>
+  </si>
+  <si>
+    <t>Vansh Kishor Jain</t>
+  </si>
+  <si>
+    <t>Laksh Tejraj Gogad</t>
+  </si>
+  <si>
+    <t>Akshay Anil Jain</t>
+  </si>
+  <si>
+    <t>Ayush Nitin Sharma</t>
+  </si>
+  <si>
+    <t>Pratham Santoshkumar Nahata</t>
+  </si>
+  <si>
+    <t>Sankalp Sheetalkumar Jain</t>
+  </si>
+  <si>
+    <t>Gaurang Milind Sharma</t>
+  </si>
+  <si>
+    <t>Veer Anand Sethi</t>
+  </si>
+  <si>
+    <t>Tanish Vikas Kochar</t>
+  </si>
+  <si>
+    <t>Param Shailesh Jain</t>
+  </si>
+  <si>
+    <t>Vatsal Rahul Achaliya</t>
+  </si>
+  <si>
+    <t>Bhavesh Ratimohan Modi</t>
+  </si>
+  <si>
+    <t>Yug Tushar Jain</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1166,6 +1217,18 @@
       <name val="Kokila"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Kokila"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1175,7 +1238,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1253,11 +1316,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1304,8 +1391,29 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1581,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D1:J208"/>
+  <dimension ref="D1:J268"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="6" max="6" width="20.21875" customWidth="1"/>
@@ -6189,21 +6297,1034 @@
       <c r="J207" s="19"/>
     </row>
     <row r="208" spans="4:10" ht="19.2">
-      <c r="D208" s="7">
+      <c r="D208" s="23">
         <v>317</v>
       </c>
-      <c r="E208" s="14">
+      <c r="E208" s="24">
         <v>6</v>
       </c>
-      <c r="F208" s="18" t="s">
+      <c r="F208" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="G208" s="19"/>
-      <c r="H208" s="19"/>
-      <c r="I208" s="19"/>
-      <c r="J208" s="19"/>
+      <c r="G208" s="26"/>
+      <c r="H208" s="26"/>
+      <c r="I208" s="26"/>
+      <c r="J208" s="26"/>
+    </row>
+    <row r="209" spans="4:10" ht="19.2">
+      <c r="D209" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E209" s="27">
+        <v>1</v>
+      </c>
+      <c r="F209" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G209" s="20">
+        <v>8889310551</v>
+      </c>
+      <c r="H209" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="I209" s="22">
+        <v>0</v>
+      </c>
+      <c r="J209" s="22">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="210" spans="4:10" ht="19.2">
+      <c r="D210" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E210" s="27">
+        <v>2</v>
+      </c>
+      <c r="F210" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G210" s="21">
+        <v>9421614398</v>
+      </c>
+      <c r="H210" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="I210" s="22">
+        <v>3500</v>
+      </c>
+      <c r="J210" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="4:10" ht="19.2">
+      <c r="D211" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E211" s="27">
+        <v>3</v>
+      </c>
+      <c r="F211" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G211" s="21">
+        <v>9423193271</v>
+      </c>
+      <c r="H211" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="I211" s="22">
+        <v>7000</v>
+      </c>
+      <c r="J211" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="4:10" ht="19.2">
+      <c r="D212" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E212" s="27">
+        <v>4</v>
+      </c>
+      <c r="F212" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G212" s="21">
+        <v>9423918667</v>
+      </c>
+      <c r="H212" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="I212" s="22">
+        <v>7000</v>
+      </c>
+      <c r="J212" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="4:10" ht="19.2">
+      <c r="D213" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E213" s="27">
+        <v>5</v>
+      </c>
+      <c r="F213" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G213" s="21">
+        <v>9545516001</v>
+      </c>
+      <c r="H213" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="I213" s="22">
+        <v>9000</v>
+      </c>
+      <c r="J213" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="4:10" ht="19.2">
+      <c r="D214" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E214" s="27">
+        <v>6</v>
+      </c>
+      <c r="F214" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="G214" s="20">
+        <v>9689839096</v>
+      </c>
+      <c r="H214" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I214" s="22">
+        <v>7000</v>
+      </c>
+      <c r="J214" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="4:10" ht="19.2">
+      <c r="D215" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E215" s="27">
+        <v>7</v>
+      </c>
+      <c r="F215" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="G215" s="20">
+        <v>9424070113</v>
+      </c>
+      <c r="H215" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="I215" s="22">
+        <v>27000</v>
+      </c>
+      <c r="J215" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="4:10" ht="19.2">
+      <c r="D216" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E216" s="27">
+        <v>8</v>
+      </c>
+      <c r="F216" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="G216" s="20">
+        <v>8208718482</v>
+      </c>
+      <c r="H216" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I216" s="22">
+        <v>28000</v>
+      </c>
+      <c r="J216" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="4:10" ht="19.2">
+      <c r="D217" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E217" s="27">
+        <v>9</v>
+      </c>
+      <c r="F217" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="G217" s="20">
+        <v>9322434650</v>
+      </c>
+      <c r="H217" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I217" s="22">
+        <v>20000</v>
+      </c>
+      <c r="J217" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="4:10" ht="19.2">
+      <c r="D218" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E218" s="27">
+        <v>10</v>
+      </c>
+      <c r="F218" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="G218" s="20">
+        <v>9604379567</v>
+      </c>
+      <c r="H218" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I218" s="22">
+        <v>15000</v>
+      </c>
+      <c r="J218" s="22">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="219" spans="4:10" ht="19.2">
+      <c r="D219" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E219" s="27">
+        <v>11</v>
+      </c>
+      <c r="F219" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="G219" s="20">
+        <v>9421443513</v>
+      </c>
+      <c r="H219" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I219" s="22">
+        <v>12000</v>
+      </c>
+      <c r="J219" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="4:10" ht="19.2">
+      <c r="D220" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E220" s="27">
+        <v>12</v>
+      </c>
+      <c r="F220" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="G220" s="20">
+        <v>9850984144</v>
+      </c>
+      <c r="H220" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I220" s="22">
+        <v>0</v>
+      </c>
+      <c r="J220" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="4:10" ht="19.2">
+      <c r="D221" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E221" s="27">
+        <v>13</v>
+      </c>
+      <c r="F221" s="19" t="s">
+        <v>294</v>
+      </c>
+      <c r="G221" s="20">
+        <v>7387938800</v>
+      </c>
+      <c r="H221" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I221" s="22">
+        <v>12000</v>
+      </c>
+      <c r="J221" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="4:10" ht="19.2">
+      <c r="D222" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E222" s="27">
+        <v>14</v>
+      </c>
+      <c r="F222" s="19" t="s">
+        <v>295</v>
+      </c>
+      <c r="G222" s="20">
+        <v>7773902888</v>
+      </c>
+      <c r="H222" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="I222" s="22">
+        <v>10000</v>
+      </c>
+      <c r="J222" s="22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="4:10" ht="19.2">
+      <c r="D223" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E223" s="27">
+        <v>15</v>
+      </c>
+      <c r="F223" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G223" s="19"/>
+      <c r="H223" s="19"/>
+      <c r="I223" s="19"/>
+      <c r="J223" s="19"/>
+    </row>
+    <row r="224" spans="4:10" ht="19.2">
+      <c r="D224" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E224" s="27">
+        <v>16</v>
+      </c>
+      <c r="F224" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G224" s="19"/>
+      <c r="H224" s="19"/>
+      <c r="I224" s="19"/>
+      <c r="J224" s="19"/>
+    </row>
+    <row r="225" spans="4:10" ht="19.2">
+      <c r="D225" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E225" s="27">
+        <v>17</v>
+      </c>
+      <c r="F225" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G225" s="19"/>
+      <c r="H225" s="19"/>
+      <c r="I225" s="19"/>
+      <c r="J225" s="19"/>
+    </row>
+    <row r="226" spans="4:10" ht="19.2">
+      <c r="D226" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E226" s="27">
+        <v>18</v>
+      </c>
+      <c r="F226" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G226" s="19"/>
+      <c r="H226" s="19"/>
+      <c r="I226" s="19"/>
+      <c r="J226" s="19"/>
+    </row>
+    <row r="227" spans="4:10" ht="19.2">
+      <c r="D227" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E227" s="27">
+        <v>19</v>
+      </c>
+      <c r="F227" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G227" s="19"/>
+      <c r="H227" s="19"/>
+      <c r="I227" s="19"/>
+      <c r="J227" s="19"/>
+    </row>
+    <row r="228" spans="4:10" ht="19.2">
+      <c r="D228" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E228" s="27">
+        <v>20</v>
+      </c>
+      <c r="F228" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G228" s="19"/>
+      <c r="H228" s="19"/>
+      <c r="I228" s="19"/>
+      <c r="J228" s="19"/>
+    </row>
+    <row r="229" spans="4:10" ht="19.2">
+      <c r="D229" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E229" s="27">
+        <v>21</v>
+      </c>
+      <c r="F229" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G229" s="19"/>
+      <c r="H229" s="19"/>
+      <c r="I229" s="19"/>
+      <c r="J229" s="19"/>
+    </row>
+    <row r="230" spans="4:10" ht="19.2">
+      <c r="D230" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E230" s="27">
+        <v>22</v>
+      </c>
+      <c r="F230" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G230" s="19"/>
+      <c r="H230" s="19"/>
+      <c r="I230" s="19"/>
+      <c r="J230" s="19"/>
+    </row>
+    <row r="231" spans="4:10" ht="19.2">
+      <c r="D231" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E231" s="27">
+        <v>23</v>
+      </c>
+      <c r="F231" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G231" s="19"/>
+      <c r="H231" s="19"/>
+      <c r="I231" s="19"/>
+      <c r="J231" s="19"/>
+    </row>
+    <row r="232" spans="4:10" ht="19.2">
+      <c r="D232" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E232" s="27">
+        <v>24</v>
+      </c>
+      <c r="F232" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G232" s="19"/>
+      <c r="H232" s="19"/>
+      <c r="I232" s="19"/>
+      <c r="J232" s="19"/>
+    </row>
+    <row r="233" spans="4:10" ht="19.2">
+      <c r="D233" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E233" s="27">
+        <v>25</v>
+      </c>
+      <c r="F233" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G233" s="19"/>
+      <c r="H233" s="19"/>
+      <c r="I233" s="19"/>
+      <c r="J233" s="19"/>
+    </row>
+    <row r="234" spans="4:10" ht="19.2">
+      <c r="D234" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E234" s="27">
+        <v>26</v>
+      </c>
+      <c r="F234" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G234" s="19"/>
+      <c r="H234" s="19"/>
+      <c r="I234" s="19"/>
+      <c r="J234" s="19"/>
+    </row>
+    <row r="235" spans="4:10" ht="19.2">
+      <c r="D235" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E235" s="27">
+        <v>27</v>
+      </c>
+      <c r="F235" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G235" s="19"/>
+      <c r="H235" s="19"/>
+      <c r="I235" s="19"/>
+      <c r="J235" s="19"/>
+    </row>
+    <row r="236" spans="4:10" ht="19.2">
+      <c r="D236" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E236" s="27">
+        <v>28</v>
+      </c>
+      <c r="F236" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G236" s="19"/>
+      <c r="H236" s="19"/>
+      <c r="I236" s="19"/>
+      <c r="J236" s="19"/>
+    </row>
+    <row r="237" spans="4:10" ht="19.2">
+      <c r="D237" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E237" s="27">
+        <v>29</v>
+      </c>
+      <c r="F237" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G237" s="19"/>
+      <c r="H237" s="19"/>
+      <c r="I237" s="19"/>
+      <c r="J237" s="19"/>
+    </row>
+    <row r="238" spans="4:10" ht="19.2">
+      <c r="D238" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E238" s="27">
+        <v>30</v>
+      </c>
+      <c r="F238" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G238" s="19"/>
+      <c r="H238" s="19"/>
+      <c r="I238" s="19"/>
+      <c r="J238" s="19"/>
+    </row>
+    <row r="239" spans="4:10" ht="19.2">
+      <c r="D239" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E239" s="27">
+        <v>31</v>
+      </c>
+      <c r="F239" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G239" s="19"/>
+      <c r="H239" s="19"/>
+      <c r="I239" s="19"/>
+      <c r="J239" s="19"/>
+    </row>
+    <row r="240" spans="4:10" ht="19.2">
+      <c r="D240" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E240" s="27">
+        <v>32</v>
+      </c>
+      <c r="F240" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G240" s="19"/>
+      <c r="H240" s="19"/>
+      <c r="I240" s="19"/>
+      <c r="J240" s="19"/>
+    </row>
+    <row r="241" spans="4:10" ht="19.2">
+      <c r="D241" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E241" s="27">
+        <v>33</v>
+      </c>
+      <c r="F241" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G241" s="19"/>
+      <c r="H241" s="19"/>
+      <c r="I241" s="19"/>
+      <c r="J241" s="19"/>
+    </row>
+    <row r="242" spans="4:10" ht="19.2">
+      <c r="D242" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E242" s="27">
+        <v>34</v>
+      </c>
+      <c r="F242" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G242" s="19"/>
+      <c r="H242" s="19"/>
+      <c r="I242" s="19"/>
+      <c r="J242" s="19"/>
+    </row>
+    <row r="243" spans="4:10" ht="19.2">
+      <c r="D243" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E243" s="27">
+        <v>35</v>
+      </c>
+      <c r="F243" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G243" s="19"/>
+      <c r="H243" s="19"/>
+      <c r="I243" s="19"/>
+      <c r="J243" s="19"/>
+    </row>
+    <row r="244" spans="4:10" ht="19.2">
+      <c r="D244" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E244" s="27">
+        <v>36</v>
+      </c>
+      <c r="F244" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G244" s="19"/>
+      <c r="H244" s="19"/>
+      <c r="I244" s="19"/>
+      <c r="J244" s="19"/>
+    </row>
+    <row r="245" spans="4:10" ht="19.2">
+      <c r="D245" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E245" s="27">
+        <v>37</v>
+      </c>
+      <c r="F245" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G245" s="19"/>
+      <c r="H245" s="19"/>
+      <c r="I245" s="19"/>
+      <c r="J245" s="19"/>
+    </row>
+    <row r="246" spans="4:10" ht="19.2">
+      <c r="D246" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E246" s="27">
+        <v>38</v>
+      </c>
+      <c r="F246" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G246" s="19"/>
+      <c r="H246" s="19"/>
+      <c r="I246" s="19"/>
+      <c r="J246" s="19"/>
+    </row>
+    <row r="247" spans="4:10" ht="19.2">
+      <c r="D247" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E247" s="27">
+        <v>39</v>
+      </c>
+      <c r="F247" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G247" s="19"/>
+      <c r="H247" s="19"/>
+      <c r="I247" s="19"/>
+      <c r="J247" s="19"/>
+    </row>
+    <row r="248" spans="4:10" ht="19.2">
+      <c r="D248" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E248" s="27">
+        <v>40</v>
+      </c>
+      <c r="F248" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G248" s="19"/>
+      <c r="H248" s="19"/>
+      <c r="I248" s="19"/>
+      <c r="J248" s="19"/>
+    </row>
+    <row r="249" spans="4:10" ht="19.2">
+      <c r="D249" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E249" s="27">
+        <v>41</v>
+      </c>
+      <c r="F249" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G249" s="19"/>
+      <c r="H249" s="19"/>
+      <c r="I249" s="19"/>
+      <c r="J249" s="19"/>
+    </row>
+    <row r="250" spans="4:10" ht="19.2">
+      <c r="D250" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E250" s="27">
+        <v>42</v>
+      </c>
+      <c r="F250" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G250" s="19"/>
+      <c r="H250" s="19"/>
+      <c r="I250" s="19"/>
+      <c r="J250" s="19"/>
+    </row>
+    <row r="251" spans="4:10" ht="19.2">
+      <c r="D251" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E251" s="27">
+        <v>43</v>
+      </c>
+      <c r="F251" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G251" s="19"/>
+      <c r="H251" s="19"/>
+      <c r="I251" s="19"/>
+      <c r="J251" s="19"/>
+    </row>
+    <row r="252" spans="4:10" ht="19.2">
+      <c r="D252" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E252" s="27">
+        <v>44</v>
+      </c>
+      <c r="F252" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G252" s="19"/>
+      <c r="H252" s="19"/>
+      <c r="I252" s="19"/>
+      <c r="J252" s="19"/>
+    </row>
+    <row r="253" spans="4:10" ht="19.2">
+      <c r="D253" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E253" s="27">
+        <v>45</v>
+      </c>
+      <c r="F253" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G253" s="19"/>
+      <c r="H253" s="19"/>
+      <c r="I253" s="19"/>
+      <c r="J253" s="19"/>
+    </row>
+    <row r="254" spans="4:10" ht="19.2">
+      <c r="D254" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E254" s="27">
+        <v>46</v>
+      </c>
+      <c r="F254" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G254" s="19"/>
+      <c r="H254" s="19"/>
+      <c r="I254" s="19"/>
+      <c r="J254" s="19"/>
+    </row>
+    <row r="255" spans="4:10" ht="19.2">
+      <c r="D255" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E255" s="27">
+        <v>47</v>
+      </c>
+      <c r="F255" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G255" s="19"/>
+      <c r="H255" s="19"/>
+      <c r="I255" s="19"/>
+      <c r="J255" s="19"/>
+    </row>
+    <row r="256" spans="4:10" ht="19.2">
+      <c r="D256" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E256" s="27">
+        <v>48</v>
+      </c>
+      <c r="F256" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G256" s="19"/>
+      <c r="H256" s="19"/>
+      <c r="I256" s="19"/>
+      <c r="J256" s="19"/>
+    </row>
+    <row r="257" spans="4:10" ht="19.2">
+      <c r="D257" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E257" s="27">
+        <v>49</v>
+      </c>
+      <c r="F257" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G257" s="19"/>
+      <c r="H257" s="19"/>
+      <c r="I257" s="19"/>
+      <c r="J257" s="19"/>
+    </row>
+    <row r="258" spans="4:10" ht="19.2">
+      <c r="D258" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E258" s="27">
+        <v>50</v>
+      </c>
+      <c r="F258" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G258" s="19"/>
+      <c r="H258" s="19"/>
+      <c r="I258" s="19"/>
+      <c r="J258" s="19"/>
+    </row>
+    <row r="259" spans="4:10" ht="19.2">
+      <c r="D259" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E259" s="27">
+        <v>51</v>
+      </c>
+      <c r="F259" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G259" s="19"/>
+      <c r="H259" s="19"/>
+      <c r="I259" s="19"/>
+      <c r="J259" s="19"/>
+    </row>
+    <row r="260" spans="4:10" ht="19.2">
+      <c r="D260" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E260" s="27">
+        <v>52</v>
+      </c>
+      <c r="F260" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G260" s="19"/>
+      <c r="H260" s="19"/>
+      <c r="I260" s="19"/>
+      <c r="J260" s="19"/>
+    </row>
+    <row r="261" spans="4:10" ht="19.2">
+      <c r="D261" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E261" s="27">
+        <v>53</v>
+      </c>
+      <c r="F261" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G261" s="19"/>
+      <c r="H261" s="19"/>
+      <c r="I261" s="19"/>
+      <c r="J261" s="19"/>
+    </row>
+    <row r="262" spans="4:10" ht="19.2">
+      <c r="D262" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E262" s="27">
+        <v>54</v>
+      </c>
+      <c r="F262" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G262" s="19"/>
+      <c r="H262" s="19"/>
+      <c r="I262" s="19"/>
+      <c r="J262" s="19"/>
+    </row>
+    <row r="263" spans="4:10" ht="19.2">
+      <c r="D263" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E263" s="27">
+        <v>55</v>
+      </c>
+      <c r="F263" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G263" s="19"/>
+      <c r="H263" s="19"/>
+      <c r="I263" s="19"/>
+      <c r="J263" s="19"/>
+    </row>
+    <row r="264" spans="4:10" ht="19.2">
+      <c r="D264" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E264" s="27">
+        <v>56</v>
+      </c>
+      <c r="F264" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G264" s="19"/>
+      <c r="H264" s="19"/>
+      <c r="I264" s="19"/>
+      <c r="J264" s="19"/>
+    </row>
+    <row r="265" spans="4:10" ht="19.2">
+      <c r="D265" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E265" s="27">
+        <v>57</v>
+      </c>
+      <c r="F265" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G265" s="19"/>
+      <c r="H265" s="19"/>
+      <c r="I265" s="19"/>
+      <c r="J265" s="19"/>
+    </row>
+    <row r="266" spans="4:10" ht="19.2">
+      <c r="D266" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E266" s="27">
+        <v>58</v>
+      </c>
+      <c r="F266" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G266" s="19"/>
+      <c r="H266" s="19"/>
+      <c r="I266" s="19"/>
+      <c r="J266" s="19"/>
+    </row>
+    <row r="267" spans="4:10" ht="19.2">
+      <c r="D267" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E267" s="27">
+        <v>59</v>
+      </c>
+      <c r="F267" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G267" s="19"/>
+      <c r="H267" s="19"/>
+      <c r="I267" s="19"/>
+      <c r="J267" s="19"/>
+    </row>
+    <row r="268" spans="4:10" ht="19.2">
+      <c r="D268" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="E268" s="27">
+        <v>60</v>
+      </c>
+      <c r="F268" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="G268" s="19"/>
+      <c r="H268" s="19"/>
+      <c r="I268" s="19"/>
+      <c r="J268" s="19"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HIMANSHU\hostel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39993BB1-E113-4C4C-B445-579F0B4F2045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2C3F09-2845-4288-954F-E69EC021E993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="429">
   <si>
     <t>ROOMS</t>
   </si>
@@ -1460,6 +1460,99 @@
   </si>
   <si>
     <t>Kaushal Umesh Shah</t>
+  </si>
+  <si>
+    <t>NB 201</t>
+  </si>
+  <si>
+    <t>NB202</t>
+  </si>
+  <si>
+    <t>NB 202</t>
+  </si>
+  <si>
+    <t>NB203</t>
+  </si>
+  <si>
+    <t>NB204</t>
+  </si>
+  <si>
+    <t>NB205</t>
+  </si>
+  <si>
+    <t>NB206</t>
+  </si>
+  <si>
+    <t>NB207</t>
+  </si>
+  <si>
+    <t>NB208</t>
+  </si>
+  <si>
+    <t>NB209</t>
+  </si>
+  <si>
+    <t>NB210</t>
+  </si>
+  <si>
+    <t>NB301</t>
+  </si>
+  <si>
+    <t>NB302</t>
+  </si>
+  <si>
+    <t>NB303</t>
+  </si>
+  <si>
+    <t>NB304</t>
+  </si>
+  <si>
+    <t>NB305</t>
+  </si>
+  <si>
+    <t>NB306</t>
+  </si>
+  <si>
+    <t>NB307</t>
+  </si>
+  <si>
+    <t>NB308</t>
+  </si>
+  <si>
+    <t>NB309</t>
+  </si>
+  <si>
+    <t>NB310</t>
+  </si>
+  <si>
+    <t>NB401</t>
+  </si>
+  <si>
+    <t>NB402</t>
+  </si>
+  <si>
+    <t>NB403</t>
+  </si>
+  <si>
+    <t>NB404</t>
+  </si>
+  <si>
+    <t>NB405</t>
+  </si>
+  <si>
+    <t>NB406</t>
+  </si>
+  <si>
+    <t>NB407</t>
+  </si>
+  <si>
+    <t>NB408</t>
+  </si>
+  <si>
+    <t>NB409</t>
+  </si>
+  <si>
+    <t>NB410</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1618,14 +1711,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6537,10 +6626,10 @@
       <c r="I209" s="6">
         <v>9000</v>
       </c>
-      <c r="J209" s="17">
-        <v>0</v>
-      </c>
-      <c r="K209" s="18"/>
+      <c r="J209" s="15">
+        <v>0</v>
+      </c>
+      <c r="K209" s="16"/>
     </row>
     <row r="210" spans="4:11" ht="19.2">
       <c r="D210" s="3" t="s">
@@ -6561,10 +6650,10 @@
       <c r="I210" s="6">
         <v>0</v>
       </c>
-      <c r="J210" s="17">
+      <c r="J210" s="15">
         <v>3500</v>
       </c>
-      <c r="K210" s="18"/>
+      <c r="K210" s="16"/>
     </row>
     <row r="211" spans="4:11" ht="19.2">
       <c r="D211" s="3" t="s">
@@ -6585,10 +6674,10 @@
       <c r="I211" s="6">
         <v>0</v>
       </c>
-      <c r="J211" s="17">
+      <c r="J211" s="15">
         <v>7000</v>
       </c>
-      <c r="K211" s="18"/>
+      <c r="K211" s="16"/>
     </row>
     <row r="212" spans="4:11" ht="19.2">
       <c r="D212" s="3" t="s">
@@ -6609,10 +6698,10 @@
       <c r="I212" s="6">
         <v>0</v>
       </c>
-      <c r="J212" s="17">
+      <c r="J212" s="15">
         <v>7000</v>
       </c>
-      <c r="K212" s="18"/>
+      <c r="K212" s="16"/>
     </row>
     <row r="213" spans="4:11" ht="19.2">
       <c r="D213" s="3" t="s">
@@ -6633,10 +6722,10 @@
       <c r="I213" s="6">
         <v>0</v>
       </c>
-      <c r="J213" s="17">
+      <c r="J213" s="15">
         <v>9000</v>
       </c>
-      <c r="K213" s="18"/>
+      <c r="K213" s="16"/>
     </row>
     <row r="214" spans="4:11" ht="19.2">
       <c r="D214" s="3" t="s">
@@ -6657,10 +6746,10 @@
       <c r="I214" s="6">
         <v>0</v>
       </c>
-      <c r="J214" s="17">
+      <c r="J214" s="15">
         <v>7000</v>
       </c>
-      <c r="K214" s="18"/>
+      <c r="K214" s="16"/>
     </row>
     <row r="215" spans="4:11" ht="19.2">
       <c r="D215" s="3" t="s">
@@ -6681,10 +6770,10 @@
       <c r="I215" s="6">
         <v>0</v>
       </c>
-      <c r="J215" s="17">
+      <c r="J215" s="15">
         <v>27000</v>
       </c>
-      <c r="K215" s="18"/>
+      <c r="K215" s="16"/>
     </row>
     <row r="216" spans="4:11" ht="19.2">
       <c r="D216" s="3" t="s">
@@ -6705,10 +6794,10 @@
       <c r="I216" s="6">
         <v>0</v>
       </c>
-      <c r="J216" s="17">
+      <c r="J216" s="15">
         <v>28000</v>
       </c>
-      <c r="K216" s="18"/>
+      <c r="K216" s="16"/>
     </row>
     <row r="217" spans="4:11" ht="19.2">
       <c r="D217" s="3" t="s">
@@ -6729,10 +6818,10 @@
       <c r="I217" s="6">
         <v>0</v>
       </c>
-      <c r="J217" s="17">
+      <c r="J217" s="15">
         <v>20000</v>
       </c>
-      <c r="K217" s="18"/>
+      <c r="K217" s="16"/>
     </row>
     <row r="218" spans="4:11" ht="19.2">
       <c r="D218" s="3" t="s">
@@ -6753,10 +6842,10 @@
       <c r="I218" s="6">
         <v>2000</v>
       </c>
-      <c r="J218" s="17">
+      <c r="J218" s="15">
         <v>15000</v>
       </c>
-      <c r="K218" s="18"/>
+      <c r="K218" s="16"/>
     </row>
     <row r="219" spans="4:11" ht="19.2">
       <c r="D219" s="3" t="s">
@@ -6777,10 +6866,10 @@
       <c r="I219" s="6">
         <v>0</v>
       </c>
-      <c r="J219" s="17">
+      <c r="J219" s="15">
         <v>12000</v>
       </c>
-      <c r="K219" s="18"/>
+      <c r="K219" s="16"/>
     </row>
     <row r="220" spans="4:11" ht="19.2">
       <c r="D220" s="3" t="s">
@@ -6801,10 +6890,10 @@
       <c r="I220" s="6">
         <v>0</v>
       </c>
-      <c r="J220" s="17">
-        <v>0</v>
-      </c>
-      <c r="K220" s="18"/>
+      <c r="J220" s="15">
+        <v>0</v>
+      </c>
+      <c r="K220" s="16"/>
     </row>
     <row r="221" spans="4:11" ht="19.2">
       <c r="D221" s="3" t="s">
@@ -6825,10 +6914,10 @@
       <c r="I221" s="6">
         <v>0</v>
       </c>
-      <c r="J221" s="17">
+      <c r="J221" s="15">
         <v>12000</v>
       </c>
-      <c r="K221" s="18"/>
+      <c r="K221" s="16"/>
     </row>
     <row r="222" spans="4:11" ht="19.2">
       <c r="D222" s="3" t="s">
@@ -6849,10 +6938,10 @@
       <c r="I222" s="6">
         <v>0</v>
       </c>
-      <c r="J222" s="17">
+      <c r="J222" s="15">
         <v>10000</v>
       </c>
-      <c r="K222" s="18"/>
+      <c r="K222" s="16"/>
     </row>
     <row r="223" spans="4:11" ht="19.2">
       <c r="D223" s="3" t="s">
@@ -7361,10 +7450,10 @@
       </c>
     </row>
     <row r="269" spans="4:10" ht="19.2">
-      <c r="D269" s="3">
-        <v>201</v>
-      </c>
-      <c r="E269" s="15">
+      <c r="D269" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E269" s="7">
         <v>1</v>
       </c>
       <c r="F269" s="3" t="s">
@@ -7384,10 +7473,10 @@
       </c>
     </row>
     <row r="270" spans="4:10" ht="19.2">
-      <c r="D270" s="3">
-        <v>201</v>
-      </c>
-      <c r="E270" s="15">
+      <c r="D270" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E270" s="7">
         <v>2</v>
       </c>
       <c r="F270" s="3" t="s">
@@ -7407,10 +7496,10 @@
       </c>
     </row>
     <row r="271" spans="4:10" ht="19.2">
-      <c r="D271" s="3">
-        <v>201</v>
-      </c>
-      <c r="E271" s="15">
+      <c r="D271" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E271" s="7">
         <v>3</v>
       </c>
       <c r="F271" s="3" t="s">
@@ -7430,10 +7519,10 @@
       </c>
     </row>
     <row r="272" spans="4:10" ht="19.2">
-      <c r="D272" s="3">
-        <v>201</v>
-      </c>
-      <c r="E272" s="15">
+      <c r="D272" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E272" s="7">
         <v>4</v>
       </c>
       <c r="F272" s="3" t="s">
@@ -7453,10 +7542,10 @@
       </c>
     </row>
     <row r="273" spans="4:10" ht="19.2">
-      <c r="D273" s="3">
-        <v>202</v>
-      </c>
-      <c r="E273" s="15">
+      <c r="D273" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E273" s="7">
         <v>1</v>
       </c>
       <c r="F273" s="3" t="s">
@@ -7476,10 +7565,10 @@
       </c>
     </row>
     <row r="274" spans="4:10" ht="19.2">
-      <c r="D274" s="3">
-        <v>202</v>
-      </c>
-      <c r="E274" s="15">
+      <c r="D274" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E274" s="7">
         <v>2</v>
       </c>
       <c r="F274" s="3" t="s">
@@ -7499,21 +7588,21 @@
       </c>
     </row>
     <row r="275" spans="4:10" ht="19.2">
-      <c r="D275" s="3">
-        <v>202</v>
-      </c>
-      <c r="E275" s="15">
+      <c r="D275" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E275" s="7">
         <v>3</v>
       </c>
-      <c r="F275" s="16" t="s">
+      <c r="F275" s="3" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="276" spans="4:10" ht="19.2">
-      <c r="D276" s="3">
-        <v>202</v>
-      </c>
-      <c r="E276" s="15">
+      <c r="D276" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="E276" s="7">
         <v>4</v>
       </c>
       <c r="F276" s="3" t="s">
@@ -7521,10 +7610,10 @@
       </c>
     </row>
     <row r="277" spans="4:10" ht="19.2">
-      <c r="D277" s="3">
-        <v>203</v>
-      </c>
-      <c r="E277" s="15">
+      <c r="D277" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E277" s="7">
         <v>1</v>
       </c>
       <c r="F277" s="3" t="s">
@@ -7544,10 +7633,10 @@
       </c>
     </row>
     <row r="278" spans="4:10" ht="19.2">
-      <c r="D278" s="3">
-        <v>203</v>
-      </c>
-      <c r="E278" s="15">
+      <c r="D278" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E278" s="7">
         <v>2</v>
       </c>
       <c r="F278" s="3" t="s">
@@ -7567,10 +7656,10 @@
       </c>
     </row>
     <row r="279" spans="4:10" ht="19.2">
-      <c r="D279" s="3">
-        <v>203</v>
-      </c>
-      <c r="E279" s="15">
+      <c r="D279" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E279" s="7">
         <v>3</v>
       </c>
       <c r="F279" s="3" t="s">
@@ -7590,10 +7679,10 @@
       </c>
     </row>
     <row r="280" spans="4:10" ht="19.2">
-      <c r="D280" s="3">
-        <v>203</v>
-      </c>
-      <c r="E280" s="15">
+      <c r="D280" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="E280" s="7">
         <v>4</v>
       </c>
       <c r="F280" s="3" t="s">
@@ -7613,10 +7702,10 @@
       </c>
     </row>
     <row r="281" spans="4:10" ht="19.2">
-      <c r="D281" s="3">
-        <v>204</v>
-      </c>
-      <c r="E281" s="15">
+      <c r="D281" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E281" s="7">
         <v>1</v>
       </c>
       <c r="F281" s="3" t="s">
@@ -7636,10 +7725,10 @@
       </c>
     </row>
     <row r="282" spans="4:10" ht="19.2">
-      <c r="D282" s="3">
-        <v>204</v>
-      </c>
-      <c r="E282" s="15">
+      <c r="D282" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E282" s="7">
         <v>2</v>
       </c>
       <c r="F282" s="3" t="s">
@@ -7659,10 +7748,10 @@
       </c>
     </row>
     <row r="283" spans="4:10" ht="19.2">
-      <c r="D283" s="3">
-        <v>204</v>
-      </c>
-      <c r="E283" s="15">
+      <c r="D283" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E283" s="7">
         <v>3</v>
       </c>
       <c r="F283" s="3" t="s">
@@ -7682,10 +7771,10 @@
       </c>
     </row>
     <row r="284" spans="4:10" ht="19.2">
-      <c r="D284" s="3">
-        <v>204</v>
-      </c>
-      <c r="E284" s="15">
+      <c r="D284" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="E284" s="7">
         <v>4</v>
       </c>
       <c r="F284" s="3" t="s">
@@ -7705,10 +7794,10 @@
       </c>
     </row>
     <row r="285" spans="4:10" ht="19.2">
-      <c r="D285" s="3">
-        <v>205</v>
-      </c>
-      <c r="E285" s="15">
+      <c r="D285" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E285" s="7">
         <v>1</v>
       </c>
       <c r="F285" s="3" t="s">
@@ -7728,10 +7817,10 @@
       </c>
     </row>
     <row r="286" spans="4:10" ht="19.2">
-      <c r="D286" s="3">
-        <v>205</v>
-      </c>
-      <c r="E286" s="15">
+      <c r="D286" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E286" s="7">
         <v>2</v>
       </c>
       <c r="F286" s="3" t="s">
@@ -7751,10 +7840,10 @@
       </c>
     </row>
     <row r="287" spans="4:10" ht="19.2">
-      <c r="D287" s="3">
-        <v>205</v>
-      </c>
-      <c r="E287" s="15">
+      <c r="D287" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E287" s="7">
         <v>3</v>
       </c>
       <c r="F287" s="3" t="s">
@@ -7774,10 +7863,10 @@
       </c>
     </row>
     <row r="288" spans="4:10" ht="19.2">
-      <c r="D288" s="3">
-        <v>205</v>
-      </c>
-      <c r="E288" s="15">
+      <c r="D288" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="E288" s="7">
         <v>4</v>
       </c>
       <c r="F288" s="3" t="s">
@@ -7797,10 +7886,10 @@
       </c>
     </row>
     <row r="289" spans="4:10" ht="19.2">
-      <c r="D289" s="3">
-        <v>206</v>
-      </c>
-      <c r="E289" s="15">
+      <c r="D289" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E289" s="7">
         <v>1</v>
       </c>
       <c r="F289" s="3" t="s">
@@ -7820,10 +7909,10 @@
       </c>
     </row>
     <row r="290" spans="4:10" ht="19.2">
-      <c r="D290" s="3">
-        <v>206</v>
-      </c>
-      <c r="E290" s="15">
+      <c r="D290" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E290" s="7">
         <v>2</v>
       </c>
       <c r="F290" s="3" t="s">
@@ -7843,10 +7932,10 @@
       </c>
     </row>
     <row r="291" spans="4:10" ht="19.2">
-      <c r="D291" s="3">
-        <v>206</v>
-      </c>
-      <c r="E291" s="15">
+      <c r="D291" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E291" s="7">
         <v>3</v>
       </c>
       <c r="F291" s="3" t="s">
@@ -7854,10 +7943,10 @@
       </c>
     </row>
     <row r="292" spans="4:10" ht="19.2">
-      <c r="D292" s="3">
-        <v>206</v>
-      </c>
-      <c r="E292" s="15">
+      <c r="D292" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E292" s="7">
         <v>4</v>
       </c>
       <c r="F292" s="3" t="s">
@@ -7865,10 +7954,10 @@
       </c>
     </row>
     <row r="293" spans="4:10" ht="19.2">
-      <c r="D293" s="3">
-        <v>207</v>
-      </c>
-      <c r="E293" s="15">
+      <c r="D293" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E293" s="7">
         <v>1</v>
       </c>
       <c r="F293" s="3" t="s">
@@ -7888,10 +7977,10 @@
       </c>
     </row>
     <row r="294" spans="4:10" ht="19.2">
-      <c r="D294" s="3">
-        <v>207</v>
-      </c>
-      <c r="E294" s="15">
+      <c r="D294" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E294" s="7">
         <v>2</v>
       </c>
       <c r="F294" s="3" t="s">
@@ -7911,10 +8000,10 @@
       </c>
     </row>
     <row r="295" spans="4:10" ht="19.2">
-      <c r="D295" s="3">
-        <v>207</v>
-      </c>
-      <c r="E295" s="15">
+      <c r="D295" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E295" s="7">
         <v>3</v>
       </c>
       <c r="F295" s="3" t="s">
@@ -7934,10 +8023,10 @@
       </c>
     </row>
     <row r="296" spans="4:10" ht="19.2">
-      <c r="D296" s="3">
-        <v>207</v>
-      </c>
-      <c r="E296" s="15">
+      <c r="D296" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="E296" s="7">
         <v>4</v>
       </c>
       <c r="F296" s="3" t="s">
@@ -7957,10 +8046,10 @@
       </c>
     </row>
     <row r="297" spans="4:10" ht="19.2">
-      <c r="D297" s="3">
-        <v>208</v>
-      </c>
-      <c r="E297" s="15">
+      <c r="D297" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E297" s="7">
         <v>1</v>
       </c>
       <c r="F297" s="3" t="s">
@@ -7980,10 +8069,10 @@
       </c>
     </row>
     <row r="298" spans="4:10" ht="19.2">
-      <c r="D298" s="3">
-        <v>208</v>
-      </c>
-      <c r="E298" s="15">
+      <c r="D298" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E298" s="7">
         <v>2</v>
       </c>
       <c r="F298" s="3" t="s">
@@ -8003,10 +8092,10 @@
       </c>
     </row>
     <row r="299" spans="4:10" ht="19.2">
-      <c r="D299" s="3">
-        <v>208</v>
-      </c>
-      <c r="E299" s="15">
+      <c r="D299" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E299" s="7">
         <v>3</v>
       </c>
       <c r="F299" s="3" t="s">
@@ -8026,10 +8115,10 @@
       </c>
     </row>
     <row r="300" spans="4:10" ht="19.2">
-      <c r="D300" s="3">
-        <v>208</v>
-      </c>
-      <c r="E300" s="15">
+      <c r="D300" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E300" s="7">
         <v>4</v>
       </c>
       <c r="F300" s="3" t="s">
@@ -8037,10 +8126,10 @@
       </c>
     </row>
     <row r="301" spans="4:10" ht="19.2">
-      <c r="D301" s="3">
-        <v>209</v>
-      </c>
-      <c r="E301" s="15">
+      <c r="D301" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E301" s="7">
         <v>1</v>
       </c>
       <c r="F301" s="3" t="s">
@@ -8060,10 +8149,10 @@
       </c>
     </row>
     <row r="302" spans="4:10" ht="19.2">
-      <c r="D302" s="3">
-        <v>209</v>
-      </c>
-      <c r="E302" s="15">
+      <c r="D302" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E302" s="7">
         <v>2</v>
       </c>
       <c r="F302" s="3" t="s">
@@ -8083,10 +8172,10 @@
       </c>
     </row>
     <row r="303" spans="4:10" ht="19.2">
-      <c r="D303" s="3">
-        <v>209</v>
-      </c>
-      <c r="E303" s="15">
+      <c r="D303" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E303" s="7">
         <v>3</v>
       </c>
       <c r="F303" s="3" t="s">
@@ -8106,10 +8195,10 @@
       </c>
     </row>
     <row r="304" spans="4:10" ht="19.2">
-      <c r="D304" s="3">
-        <v>209</v>
-      </c>
-      <c r="E304" s="15">
+      <c r="D304" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="E304" s="7">
         <v>4</v>
       </c>
       <c r="F304" s="3" t="s">
@@ -8129,10 +8218,10 @@
       </c>
     </row>
     <row r="305" spans="4:10" ht="19.2">
-      <c r="D305" s="3">
-        <v>210</v>
-      </c>
-      <c r="E305" s="15">
+      <c r="D305" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E305" s="7">
         <v>1</v>
       </c>
       <c r="F305" s="3" t="s">
@@ -8152,10 +8241,10 @@
       </c>
     </row>
     <row r="306" spans="4:10" ht="19.2">
-      <c r="D306" s="3">
-        <v>210</v>
-      </c>
-      <c r="E306" s="15">
+      <c r="D306" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E306" s="7">
         <v>2</v>
       </c>
       <c r="F306" s="3" t="s">
@@ -8175,10 +8264,10 @@
       </c>
     </row>
     <row r="307" spans="4:10" ht="19.2">
-      <c r="D307" s="3">
-        <v>210</v>
-      </c>
-      <c r="E307" s="15">
+      <c r="D307" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E307" s="7">
         <v>3</v>
       </c>
       <c r="F307" s="3" t="s">
@@ -8198,10 +8287,10 @@
       </c>
     </row>
     <row r="308" spans="4:10" ht="19.2">
-      <c r="D308" s="3">
-        <v>210</v>
-      </c>
-      <c r="E308" s="15">
+      <c r="D308" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E308" s="7">
         <v>4</v>
       </c>
       <c r="F308" s="3" t="s">
@@ -8221,10 +8310,10 @@
       </c>
     </row>
     <row r="309" spans="4:10" ht="19.2">
-      <c r="D309" s="3">
-        <v>301</v>
-      </c>
-      <c r="E309" s="15">
+      <c r="D309" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E309" s="7">
         <v>1</v>
       </c>
       <c r="F309" s="3" t="s">
@@ -8244,10 +8333,10 @@
       </c>
     </row>
     <row r="310" spans="4:10" ht="19.2">
-      <c r="D310" s="3">
-        <v>301</v>
-      </c>
-      <c r="E310" s="15">
+      <c r="D310" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E310" s="7">
         <v>2</v>
       </c>
       <c r="F310" s="3" t="s">
@@ -8267,10 +8356,10 @@
       </c>
     </row>
     <row r="311" spans="4:10" ht="19.2">
-      <c r="D311" s="3">
-        <v>301</v>
-      </c>
-      <c r="E311" s="15">
+      <c r="D311" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E311" s="7">
         <v>3</v>
       </c>
       <c r="F311" s="3" t="s">
@@ -8290,10 +8379,10 @@
       </c>
     </row>
     <row r="312" spans="4:10" ht="19.2">
-      <c r="D312" s="3">
-        <v>301</v>
-      </c>
-      <c r="E312" s="15">
+      <c r="D312" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E312" s="7">
         <v>4</v>
       </c>
       <c r="F312" s="3" t="s">
@@ -8301,10 +8390,10 @@
       </c>
     </row>
     <row r="313" spans="4:10" ht="19.2">
-      <c r="D313" s="3">
-        <v>302</v>
-      </c>
-      <c r="E313" s="15">
+      <c r="D313" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E313" s="7">
         <v>1</v>
       </c>
       <c r="F313" s="3" t="s">
@@ -8324,10 +8413,10 @@
       </c>
     </row>
     <row r="314" spans="4:10" ht="19.2">
-      <c r="D314" s="3">
-        <v>302</v>
-      </c>
-      <c r="E314" s="15">
+      <c r="D314" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E314" s="7">
         <v>2</v>
       </c>
       <c r="F314" s="3" t="s">
@@ -8347,10 +8436,10 @@
       </c>
     </row>
     <row r="315" spans="4:10" ht="19.2">
-      <c r="D315" s="3">
-        <v>302</v>
-      </c>
-      <c r="E315" s="15">
+      <c r="D315" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E315" s="7">
         <v>3</v>
       </c>
       <c r="F315" s="3" t="s">
@@ -8370,10 +8459,10 @@
       </c>
     </row>
     <row r="316" spans="4:10" ht="19.2">
-      <c r="D316" s="3">
-        <v>302</v>
-      </c>
-      <c r="E316" s="15">
+      <c r="D316" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E316" s="7">
         <v>4</v>
       </c>
       <c r="F316" s="3" t="s">
@@ -8393,10 +8482,10 @@
       </c>
     </row>
     <row r="317" spans="4:10" ht="19.2">
-      <c r="D317" s="3">
-        <v>303</v>
-      </c>
-      <c r="E317" s="15">
+      <c r="D317" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E317" s="7">
         <v>1</v>
       </c>
       <c r="F317" s="3" t="s">
@@ -8416,10 +8505,10 @@
       </c>
     </row>
     <row r="318" spans="4:10" ht="19.2">
-      <c r="D318" s="3">
-        <v>303</v>
-      </c>
-      <c r="E318" s="15">
+      <c r="D318" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E318" s="7">
         <v>2</v>
       </c>
       <c r="F318" s="3" t="s">
@@ -8439,10 +8528,10 @@
       </c>
     </row>
     <row r="319" spans="4:10" ht="19.2">
-      <c r="D319" s="3">
-        <v>303</v>
-      </c>
-      <c r="E319" s="15">
+      <c r="D319" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E319" s="7">
         <v>3</v>
       </c>
       <c r="F319" s="3" t="s">
@@ -8462,10 +8551,10 @@
       </c>
     </row>
     <row r="320" spans="4:10" ht="19.2">
-      <c r="D320" s="3">
-        <v>303</v>
-      </c>
-      <c r="E320" s="15">
+      <c r="D320" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="E320" s="7">
         <v>4</v>
       </c>
       <c r="F320" s="3" t="s">
@@ -8485,10 +8574,10 @@
       </c>
     </row>
     <row r="321" spans="4:10" ht="19.2">
-      <c r="D321" s="3">
-        <v>304</v>
-      </c>
-      <c r="E321" s="15">
+      <c r="D321" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E321" s="7">
         <v>1</v>
       </c>
       <c r="F321" s="3" t="s">
@@ -8508,10 +8597,10 @@
       </c>
     </row>
     <row r="322" spans="4:10" ht="19.2">
-      <c r="D322" s="3">
-        <v>304</v>
-      </c>
-      <c r="E322" s="15">
+      <c r="D322" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E322" s="7">
         <v>2</v>
       </c>
       <c r="F322" s="3" t="s">
@@ -8531,10 +8620,10 @@
       </c>
     </row>
     <row r="323" spans="4:10" ht="19.2">
-      <c r="D323" s="3">
-        <v>304</v>
-      </c>
-      <c r="E323" s="15">
+      <c r="D323" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E323" s="7">
         <v>3</v>
       </c>
       <c r="F323" s="3" t="s">
@@ -8554,10 +8643,10 @@
       </c>
     </row>
     <row r="324" spans="4:10" ht="19.2">
-      <c r="D324" s="3">
-        <v>304</v>
-      </c>
-      <c r="E324" s="15">
+      <c r="D324" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E324" s="7">
         <v>4</v>
       </c>
       <c r="F324" s="3" t="s">
@@ -8577,10 +8666,10 @@
       </c>
     </row>
     <row r="325" spans="4:10" ht="19.2">
-      <c r="D325" s="3">
-        <v>305</v>
-      </c>
-      <c r="E325" s="15">
+      <c r="D325" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E325" s="7">
         <v>1</v>
       </c>
       <c r="F325" s="3" t="s">
@@ -8600,10 +8689,10 @@
       </c>
     </row>
     <row r="326" spans="4:10" ht="19.2">
-      <c r="D326" s="3">
-        <v>305</v>
-      </c>
-      <c r="E326" s="15">
+      <c r="D326" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E326" s="7">
         <v>2</v>
       </c>
       <c r="F326" s="3" t="s">
@@ -8623,10 +8712,10 @@
       </c>
     </row>
     <row r="327" spans="4:10" ht="19.2">
-      <c r="D327" s="3">
-        <v>305</v>
-      </c>
-      <c r="E327" s="15">
+      <c r="D327" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E327" s="7">
         <v>3</v>
       </c>
       <c r="F327" s="3" t="s">
@@ -8646,10 +8735,10 @@
       </c>
     </row>
     <row r="328" spans="4:10" ht="19.2">
-      <c r="D328" s="3">
-        <v>305</v>
-      </c>
-      <c r="E328" s="15">
+      <c r="D328" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E328" s="7">
         <v>4</v>
       </c>
       <c r="F328" s="3" t="s">
@@ -8669,10 +8758,10 @@
       </c>
     </row>
     <row r="329" spans="4:10" ht="19.2">
-      <c r="D329" s="3">
-        <v>306</v>
-      </c>
-      <c r="E329" s="15">
+      <c r="D329" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E329" s="7">
         <v>1</v>
       </c>
       <c r="F329" s="3" t="s">
@@ -8692,10 +8781,10 @@
       </c>
     </row>
     <row r="330" spans="4:10" ht="19.2">
-      <c r="D330" s="3">
-        <v>306</v>
-      </c>
-      <c r="E330" s="15">
+      <c r="D330" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E330" s="7">
         <v>2</v>
       </c>
       <c r="F330" s="3" t="s">
@@ -8715,10 +8804,10 @@
       </c>
     </row>
     <row r="331" spans="4:10" ht="19.2">
-      <c r="D331" s="3">
-        <v>306</v>
-      </c>
-      <c r="E331" s="15">
+      <c r="D331" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E331" s="7">
         <v>3</v>
       </c>
       <c r="F331" s="3" t="s">
@@ -8726,10 +8815,10 @@
       </c>
     </row>
     <row r="332" spans="4:10" ht="19.2">
-      <c r="D332" s="3">
-        <v>306</v>
-      </c>
-      <c r="E332" s="15">
+      <c r="D332" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E332" s="7">
         <v>4</v>
       </c>
       <c r="F332" s="3" t="s">
@@ -8737,10 +8826,10 @@
       </c>
     </row>
     <row r="333" spans="4:10" ht="19.2">
-      <c r="D333" s="3">
-        <v>307</v>
-      </c>
-      <c r="E333" s="15">
+      <c r="D333" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E333" s="7">
         <v>1</v>
       </c>
       <c r="F333" s="3" t="s">
@@ -8760,10 +8849,10 @@
       </c>
     </row>
     <row r="334" spans="4:10" ht="19.2">
-      <c r="D334" s="3">
-        <v>307</v>
-      </c>
-      <c r="E334" s="15">
+      <c r="D334" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E334" s="7">
         <v>2</v>
       </c>
       <c r="F334" s="3" t="s">
@@ -8781,10 +8870,10 @@
       </c>
     </row>
     <row r="335" spans="4:10" ht="19.2">
-      <c r="D335" s="3">
-        <v>307</v>
-      </c>
-      <c r="E335" s="15">
+      <c r="D335" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E335" s="7">
         <v>3</v>
       </c>
       <c r="F335" s="3" t="s">
@@ -8804,10 +8893,10 @@
       </c>
     </row>
     <row r="336" spans="4:10" ht="19.2">
-      <c r="D336" s="3">
-        <v>307</v>
-      </c>
-      <c r="E336" s="15">
+      <c r="D336" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="E336" s="7">
         <v>4</v>
       </c>
       <c r="F336" s="3" t="s">
@@ -8815,10 +8904,10 @@
       </c>
     </row>
     <row r="337" spans="4:10" ht="19.2">
-      <c r="D337" s="3">
-        <v>308</v>
-      </c>
-      <c r="E337" s="15">
+      <c r="D337" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E337" s="7">
         <v>1</v>
       </c>
       <c r="F337" s="3" t="s">
@@ -8838,10 +8927,10 @@
       </c>
     </row>
     <row r="338" spans="4:10" ht="19.2">
-      <c r="D338" s="3">
-        <v>308</v>
-      </c>
-      <c r="E338" s="15">
+      <c r="D338" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E338" s="7">
         <v>2</v>
       </c>
       <c r="F338" s="3" t="s">
@@ -8861,10 +8950,10 @@
       </c>
     </row>
     <row r="339" spans="4:10" ht="19.2">
-      <c r="D339" s="3">
-        <v>308</v>
-      </c>
-      <c r="E339" s="15">
+      <c r="D339" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E339" s="7">
         <v>3</v>
       </c>
       <c r="F339" s="3" t="s">
@@ -8872,10 +8961,10 @@
       </c>
     </row>
     <row r="340" spans="4:10" ht="19.2">
-      <c r="D340" s="3">
-        <v>308</v>
-      </c>
-      <c r="E340" s="15">
+      <c r="D340" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E340" s="7">
         <v>4</v>
       </c>
       <c r="F340" s="3" t="s">
@@ -8883,10 +8972,10 @@
       </c>
     </row>
     <row r="341" spans="4:10" ht="19.2">
-      <c r="D341" s="3">
-        <v>309</v>
-      </c>
-      <c r="E341" s="15">
+      <c r="D341" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E341" s="7">
         <v>1</v>
       </c>
       <c r="F341" s="3" t="s">
@@ -8906,10 +8995,10 @@
       </c>
     </row>
     <row r="342" spans="4:10" ht="19.2">
-      <c r="D342" s="3">
-        <v>309</v>
-      </c>
-      <c r="E342" s="15">
+      <c r="D342" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E342" s="7">
         <v>2</v>
       </c>
       <c r="F342" s="3" t="s">
@@ -8929,10 +9018,10 @@
       </c>
     </row>
     <row r="343" spans="4:10" ht="19.2">
-      <c r="D343" s="3">
-        <v>309</v>
-      </c>
-      <c r="E343" s="15">
+      <c r="D343" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E343" s="7">
         <v>3</v>
       </c>
       <c r="F343" s="3" t="s">
@@ -8952,10 +9041,10 @@
       </c>
     </row>
     <row r="344" spans="4:10" ht="19.2">
-      <c r="D344" s="3">
-        <v>309</v>
-      </c>
-      <c r="E344" s="15">
+      <c r="D344" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E344" s="7">
         <v>4</v>
       </c>
       <c r="F344" s="3" t="s">
@@ -8975,10 +9064,10 @@
       </c>
     </row>
     <row r="345" spans="4:10" ht="19.2">
-      <c r="D345" s="3">
-        <v>310</v>
-      </c>
-      <c r="E345" s="15">
+      <c r="D345" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E345" s="7">
         <v>1</v>
       </c>
       <c r="F345" s="3" t="s">
@@ -8998,10 +9087,10 @@
       </c>
     </row>
     <row r="346" spans="4:10" ht="19.2">
-      <c r="D346" s="3">
-        <v>310</v>
-      </c>
-      <c r="E346" s="15">
+      <c r="D346" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E346" s="7">
         <v>2</v>
       </c>
       <c r="F346" s="3" t="s">
@@ -9021,10 +9110,10 @@
       </c>
     </row>
     <row r="347" spans="4:10" ht="19.2">
-      <c r="D347" s="3">
-        <v>310</v>
-      </c>
-      <c r="E347" s="15">
+      <c r="D347" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E347" s="7">
         <v>3</v>
       </c>
       <c r="F347" s="3" t="s">
@@ -9044,10 +9133,10 @@
       </c>
     </row>
     <row r="348" spans="4:10" ht="19.2">
-      <c r="D348" s="3">
-        <v>310</v>
-      </c>
-      <c r="E348" s="15">
+      <c r="D348" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E348" s="7">
         <v>4</v>
       </c>
       <c r="F348" s="3" t="s">
@@ -9055,10 +9144,10 @@
       </c>
     </row>
     <row r="349" spans="4:10" ht="19.2">
-      <c r="D349" s="3">
-        <v>401</v>
-      </c>
-      <c r="E349" s="15">
+      <c r="D349" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E349" s="7">
         <v>1</v>
       </c>
       <c r="F349" s="3" t="s">
@@ -9066,10 +9155,10 @@
       </c>
     </row>
     <row r="350" spans="4:10" ht="19.2">
-      <c r="D350" s="3">
-        <v>401</v>
-      </c>
-      <c r="E350" s="15">
+      <c r="D350" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E350" s="7">
         <v>2</v>
       </c>
       <c r="F350" s="3" t="s">
@@ -9077,10 +9166,10 @@
       </c>
     </row>
     <row r="351" spans="4:10" ht="19.2">
-      <c r="D351" s="3">
-        <v>401</v>
-      </c>
-      <c r="E351" s="15">
+      <c r="D351" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E351" s="7">
         <v>3</v>
       </c>
       <c r="F351" s="3" t="s">
@@ -9088,10 +9177,10 @@
       </c>
     </row>
     <row r="352" spans="4:10" ht="19.2">
-      <c r="D352" s="3">
-        <v>401</v>
-      </c>
-      <c r="E352" s="15">
+      <c r="D352" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E352" s="7">
         <v>4</v>
       </c>
       <c r="F352" s="3" t="s">
@@ -9099,10 +9188,10 @@
       </c>
     </row>
     <row r="353" spans="4:10" ht="19.2">
-      <c r="D353" s="3">
-        <v>402</v>
-      </c>
-      <c r="E353" s="15">
+      <c r="D353" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E353" s="7">
         <v>1</v>
       </c>
       <c r="F353" s="3" t="s">
@@ -9122,10 +9211,10 @@
       </c>
     </row>
     <row r="354" spans="4:10" ht="19.2">
-      <c r="D354" s="3">
-        <v>402</v>
-      </c>
-      <c r="E354" s="15">
+      <c r="D354" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E354" s="7">
         <v>2</v>
       </c>
       <c r="F354" s="3" t="s">
@@ -9145,10 +9234,10 @@
       </c>
     </row>
     <row r="355" spans="4:10" ht="19.2">
-      <c r="D355" s="3">
-        <v>402</v>
-      </c>
-      <c r="E355" s="15">
+      <c r="D355" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E355" s="7">
         <v>3</v>
       </c>
       <c r="F355" s="3" t="s">
@@ -9168,10 +9257,10 @@
       </c>
     </row>
     <row r="356" spans="4:10" ht="19.2">
-      <c r="D356" s="3">
-        <v>402</v>
-      </c>
-      <c r="E356" s="15">
+      <c r="D356" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E356" s="7">
         <v>4</v>
       </c>
       <c r="F356" s="3" t="s">
@@ -9191,10 +9280,10 @@
       </c>
     </row>
     <row r="357" spans="4:10" ht="19.2">
-      <c r="D357" s="3">
-        <v>403</v>
-      </c>
-      <c r="E357" s="15">
+      <c r="D357" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E357" s="7">
         <v>1</v>
       </c>
       <c r="F357" s="3" t="s">
@@ -9214,10 +9303,10 @@
       </c>
     </row>
     <row r="358" spans="4:10" ht="19.2">
-      <c r="D358" s="3">
-        <v>403</v>
-      </c>
-      <c r="E358" s="15">
+      <c r="D358" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E358" s="7">
         <v>2</v>
       </c>
       <c r="F358" s="3" t="s">
@@ -9237,10 +9326,10 @@
       </c>
     </row>
     <row r="359" spans="4:10" ht="19.2">
-      <c r="D359" s="3">
-        <v>403</v>
-      </c>
-      <c r="E359" s="15">
+      <c r="D359" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E359" s="7">
         <v>3</v>
       </c>
       <c r="F359" s="3" t="s">
@@ -9260,10 +9349,10 @@
       </c>
     </row>
     <row r="360" spans="4:10" ht="19.2">
-      <c r="D360" s="3">
-        <v>403</v>
-      </c>
-      <c r="E360" s="15">
+      <c r="D360" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="E360" s="7">
         <v>4</v>
       </c>
       <c r="F360" s="3" t="s">
@@ -9271,10 +9360,10 @@
       </c>
     </row>
     <row r="361" spans="4:10" ht="19.2">
-      <c r="D361" s="3">
-        <v>404</v>
-      </c>
-      <c r="E361" s="15">
+      <c r="D361" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E361" s="7">
         <v>1</v>
       </c>
       <c r="F361" s="3" t="s">
@@ -9294,10 +9383,10 @@
       </c>
     </row>
     <row r="362" spans="4:10" ht="19.2">
-      <c r="D362" s="3">
-        <v>404</v>
-      </c>
-      <c r="E362" s="15">
+      <c r="D362" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E362" s="7">
         <v>2</v>
       </c>
       <c r="F362" s="3" t="s">
@@ -9317,10 +9406,10 @@
       </c>
     </row>
     <row r="363" spans="4:10" ht="19.2">
-      <c r="D363" s="3">
-        <v>404</v>
-      </c>
-      <c r="E363" s="15">
+      <c r="D363" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E363" s="7">
         <v>3</v>
       </c>
       <c r="F363" s="3" t="s">
@@ -9340,10 +9429,10 @@
       </c>
     </row>
     <row r="364" spans="4:10" ht="19.2">
-      <c r="D364" s="3">
-        <v>404</v>
-      </c>
-      <c r="E364" s="15">
+      <c r="D364" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E364" s="7">
         <v>4</v>
       </c>
       <c r="F364" s="3" t="s">
@@ -9361,10 +9450,10 @@
       </c>
     </row>
     <row r="365" spans="4:10" ht="19.2">
-      <c r="D365" s="3">
-        <v>405</v>
-      </c>
-      <c r="E365" s="15">
+      <c r="D365" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E365" s="7">
         <v>1</v>
       </c>
       <c r="F365" s="3" t="s">
@@ -9384,10 +9473,10 @@
       </c>
     </row>
     <row r="366" spans="4:10" ht="19.2">
-      <c r="D366" s="3">
-        <v>405</v>
-      </c>
-      <c r="E366" s="15">
+      <c r="D366" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E366" s="7">
         <v>2</v>
       </c>
       <c r="F366" s="3" t="s">
@@ -9407,10 +9496,10 @@
       </c>
     </row>
     <row r="367" spans="4:10" ht="19.2">
-      <c r="D367" s="3">
-        <v>405</v>
-      </c>
-      <c r="E367" s="15">
+      <c r="D367" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E367" s="7">
         <v>3</v>
       </c>
       <c r="F367" s="3" t="s">
@@ -9430,10 +9519,10 @@
       </c>
     </row>
     <row r="368" spans="4:10" ht="19.2">
-      <c r="D368" s="3">
-        <v>405</v>
-      </c>
-      <c r="E368" s="15">
+      <c r="D368" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="E368" s="7">
         <v>4</v>
       </c>
       <c r="F368" s="3" t="s">
@@ -9453,10 +9542,10 @@
       </c>
     </row>
     <row r="369" spans="4:10" ht="19.2">
-      <c r="D369" s="3">
-        <v>406</v>
-      </c>
-      <c r="E369" s="15">
+      <c r="D369" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E369" s="7">
         <v>1</v>
       </c>
       <c r="F369" s="3" t="s">
@@ -9476,10 +9565,10 @@
       </c>
     </row>
     <row r="370" spans="4:10" ht="19.2">
-      <c r="D370" s="3">
-        <v>406</v>
-      </c>
-      <c r="E370" s="15">
+      <c r="D370" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E370" s="7">
         <v>2</v>
       </c>
       <c r="F370" s="3" t="s">
@@ -9499,10 +9588,10 @@
       </c>
     </row>
     <row r="371" spans="4:10" ht="19.2">
-      <c r="D371" s="3">
-        <v>406</v>
-      </c>
-      <c r="E371" s="15">
+      <c r="D371" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E371" s="7">
         <v>3</v>
       </c>
       <c r="F371" s="3" t="s">
@@ -9522,10 +9611,10 @@
       </c>
     </row>
     <row r="372" spans="4:10" ht="19.2">
-      <c r="D372" s="3">
-        <v>406</v>
-      </c>
-      <c r="E372" s="15">
+      <c r="D372" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="E372" s="7">
         <v>4</v>
       </c>
       <c r="F372" s="3" t="s">
@@ -9543,10 +9632,10 @@
       </c>
     </row>
     <row r="373" spans="4:10" ht="19.2">
-      <c r="D373" s="3">
-        <v>407</v>
-      </c>
-      <c r="E373" s="15">
+      <c r="D373" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E373" s="7">
         <v>1</v>
       </c>
       <c r="F373" s="3" t="s">
@@ -9566,10 +9655,10 @@
       </c>
     </row>
     <row r="374" spans="4:10" ht="19.2">
-      <c r="D374" s="3">
-        <v>407</v>
-      </c>
-      <c r="E374" s="15">
+      <c r="D374" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E374" s="7">
         <v>2</v>
       </c>
       <c r="F374" s="3" t="s">
@@ -9589,10 +9678,10 @@
       </c>
     </row>
     <row r="375" spans="4:10" ht="19.2">
-      <c r="D375" s="3">
-        <v>407</v>
-      </c>
-      <c r="E375" s="15">
+      <c r="D375" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E375" s="7">
         <v>3</v>
       </c>
       <c r="F375" s="3" t="s">
@@ -9612,10 +9701,10 @@
       </c>
     </row>
     <row r="376" spans="4:10" ht="19.2">
-      <c r="D376" s="3">
-        <v>407</v>
-      </c>
-      <c r="E376" s="15">
+      <c r="D376" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E376" s="7">
         <v>4</v>
       </c>
       <c r="F376" s="3" t="s">
@@ -9635,10 +9724,10 @@
       </c>
     </row>
     <row r="377" spans="4:10" ht="19.2">
-      <c r="D377" s="3">
-        <v>408</v>
-      </c>
-      <c r="E377" s="15">
+      <c r="D377" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E377" s="7">
         <v>1</v>
       </c>
       <c r="F377" s="3" t="s">
@@ -9658,10 +9747,10 @@
       </c>
     </row>
     <row r="378" spans="4:10" ht="19.2">
-      <c r="D378" s="3">
-        <v>408</v>
-      </c>
-      <c r="E378" s="15">
+      <c r="D378" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E378" s="7">
         <v>2</v>
       </c>
       <c r="F378" s="3" t="s">
@@ -9681,10 +9770,10 @@
       </c>
     </row>
     <row r="379" spans="4:10" ht="19.2">
-      <c r="D379" s="3">
-        <v>408</v>
-      </c>
-      <c r="E379" s="15">
+      <c r="D379" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E379" s="7">
         <v>3</v>
       </c>
       <c r="F379" s="3" t="s">
@@ -9704,10 +9793,10 @@
       </c>
     </row>
     <row r="380" spans="4:10" ht="19.2">
-      <c r="D380" s="3">
-        <v>408</v>
-      </c>
-      <c r="E380" s="15">
+      <c r="D380" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E380" s="7">
         <v>4</v>
       </c>
       <c r="F380" s="3" t="s">
@@ -9727,10 +9816,10 @@
       </c>
     </row>
     <row r="381" spans="4:10" ht="19.2">
-      <c r="D381" s="3">
-        <v>409</v>
-      </c>
-      <c r="E381" s="15">
+      <c r="D381" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E381" s="7">
         <v>1</v>
       </c>
       <c r="F381" s="3" t="s">
@@ -9750,10 +9839,10 @@
       </c>
     </row>
     <row r="382" spans="4:10" ht="19.2">
-      <c r="D382" s="3">
-        <v>409</v>
-      </c>
-      <c r="E382" s="15">
+      <c r="D382" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E382" s="7">
         <v>2</v>
       </c>
       <c r="F382" s="3" t="s">
@@ -9761,10 +9850,10 @@
       </c>
     </row>
     <row r="383" spans="4:10" ht="19.2">
-      <c r="D383" s="3">
-        <v>409</v>
-      </c>
-      <c r="E383" s="15">
+      <c r="D383" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E383" s="7">
         <v>3</v>
       </c>
       <c r="F383" s="3" t="s">
@@ -9772,10 +9861,10 @@
       </c>
     </row>
     <row r="384" spans="4:10" ht="19.2">
-      <c r="D384" s="3">
-        <v>409</v>
-      </c>
-      <c r="E384" s="15">
+      <c r="D384" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E384" s="7">
         <v>4</v>
       </c>
       <c r="F384" s="3" t="s">
@@ -9783,10 +9872,10 @@
       </c>
     </row>
     <row r="385" spans="4:10" ht="19.2">
-      <c r="D385" s="3">
-        <v>410</v>
-      </c>
-      <c r="E385" s="15">
+      <c r="D385" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E385" s="7">
         <v>1</v>
       </c>
       <c r="F385" s="3" t="s">
@@ -9803,10 +9892,10 @@
       </c>
     </row>
     <row r="386" spans="4:10" ht="19.2">
-      <c r="D386" s="3">
-        <v>410</v>
-      </c>
-      <c r="E386" s="15">
+      <c r="D386" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E386" s="7">
         <v>2</v>
       </c>
       <c r="F386" s="3" t="s">
@@ -9823,10 +9912,10 @@
       </c>
     </row>
     <row r="387" spans="4:10" ht="19.2">
-      <c r="D387" s="3">
-        <v>410</v>
-      </c>
-      <c r="E387" s="15">
+      <c r="D387" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E387" s="7">
         <v>3</v>
       </c>
       <c r="F387" s="3" t="s">
@@ -9843,10 +9932,10 @@
       </c>
     </row>
     <row r="388" spans="4:10" ht="19.2">
-      <c r="D388" s="3">
-        <v>410</v>
-      </c>
-      <c r="E388" s="15">
+      <c r="D388" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E388" s="7">
         <v>4</v>
       </c>
       <c r="F388" s="3" t="s">

--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HIMANSHU\hostel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2C3F09-2845-4288-954F-E69EC021E993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3B4773-EDF5-4158-8FAC-E83F1829AE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="428">
   <si>
     <t>ROOMS</t>
   </si>
@@ -1466,9 +1466,6 @@
   </si>
   <si>
     <t>NB202</t>
-  </si>
-  <si>
-    <t>NB 202</t>
   </si>
   <si>
     <t>NB203</t>
@@ -7589,7 +7586,7 @@
     </row>
     <row r="275" spans="4:10" ht="19.2">
       <c r="D275" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E275" s="7">
         <v>3</v>
@@ -7611,7 +7608,7 @@
     </row>
     <row r="277" spans="4:10" ht="19.2">
       <c r="D277" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E277" s="7">
         <v>1</v>
@@ -7634,7 +7631,7 @@
     </row>
     <row r="278" spans="4:10" ht="19.2">
       <c r="D278" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E278" s="7">
         <v>2</v>
@@ -7657,7 +7654,7 @@
     </row>
     <row r="279" spans="4:10" ht="19.2">
       <c r="D279" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E279" s="7">
         <v>3</v>
@@ -7680,7 +7677,7 @@
     </row>
     <row r="280" spans="4:10" ht="19.2">
       <c r="D280" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E280" s="7">
         <v>4</v>
@@ -7703,7 +7700,7 @@
     </row>
     <row r="281" spans="4:10" ht="19.2">
       <c r="D281" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E281" s="7">
         <v>1</v>
@@ -7726,7 +7723,7 @@
     </row>
     <row r="282" spans="4:10" ht="19.2">
       <c r="D282" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E282" s="7">
         <v>2</v>
@@ -7749,7 +7746,7 @@
     </row>
     <row r="283" spans="4:10" ht="19.2">
       <c r="D283" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E283" s="7">
         <v>3</v>
@@ -7772,7 +7769,7 @@
     </row>
     <row r="284" spans="4:10" ht="19.2">
       <c r="D284" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E284" s="7">
         <v>4</v>
@@ -7795,7 +7792,7 @@
     </row>
     <row r="285" spans="4:10" ht="19.2">
       <c r="D285" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E285" s="7">
         <v>1</v>
@@ -7818,7 +7815,7 @@
     </row>
     <row r="286" spans="4:10" ht="19.2">
       <c r="D286" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E286" s="7">
         <v>2</v>
@@ -7841,7 +7838,7 @@
     </row>
     <row r="287" spans="4:10" ht="19.2">
       <c r="D287" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E287" s="7">
         <v>3</v>
@@ -7864,7 +7861,7 @@
     </row>
     <row r="288" spans="4:10" ht="19.2">
       <c r="D288" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E288" s="7">
         <v>4</v>
@@ -7887,7 +7884,7 @@
     </row>
     <row r="289" spans="4:10" ht="19.2">
       <c r="D289" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E289" s="7">
         <v>1</v>
@@ -7910,7 +7907,7 @@
     </row>
     <row r="290" spans="4:10" ht="19.2">
       <c r="D290" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E290" s="7">
         <v>2</v>
@@ -7933,7 +7930,7 @@
     </row>
     <row r="291" spans="4:10" ht="19.2">
       <c r="D291" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E291" s="7">
         <v>3</v>
@@ -7944,7 +7941,7 @@
     </row>
     <row r="292" spans="4:10" ht="19.2">
       <c r="D292" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E292" s="7">
         <v>4</v>
@@ -7955,7 +7952,7 @@
     </row>
     <row r="293" spans="4:10" ht="19.2">
       <c r="D293" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E293" s="7">
         <v>1</v>
@@ -7978,7 +7975,7 @@
     </row>
     <row r="294" spans="4:10" ht="19.2">
       <c r="D294" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E294" s="7">
         <v>2</v>
@@ -8001,7 +7998,7 @@
     </row>
     <row r="295" spans="4:10" ht="19.2">
       <c r="D295" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E295" s="7">
         <v>3</v>
@@ -8024,7 +8021,7 @@
     </row>
     <row r="296" spans="4:10" ht="19.2">
       <c r="D296" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E296" s="7">
         <v>4</v>
@@ -8047,7 +8044,7 @@
     </row>
     <row r="297" spans="4:10" ht="19.2">
       <c r="D297" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E297" s="7">
         <v>1</v>
@@ -8070,7 +8067,7 @@
     </row>
     <row r="298" spans="4:10" ht="19.2">
       <c r="D298" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E298" s="7">
         <v>2</v>
@@ -8093,7 +8090,7 @@
     </row>
     <row r="299" spans="4:10" ht="19.2">
       <c r="D299" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E299" s="7">
         <v>3</v>
@@ -8116,7 +8113,7 @@
     </row>
     <row r="300" spans="4:10" ht="19.2">
       <c r="D300" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E300" s="7">
         <v>4</v>
@@ -8127,7 +8124,7 @@
     </row>
     <row r="301" spans="4:10" ht="19.2">
       <c r="D301" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E301" s="7">
         <v>1</v>
@@ -8150,7 +8147,7 @@
     </row>
     <row r="302" spans="4:10" ht="19.2">
       <c r="D302" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E302" s="7">
         <v>2</v>
@@ -8173,7 +8170,7 @@
     </row>
     <row r="303" spans="4:10" ht="19.2">
       <c r="D303" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E303" s="7">
         <v>3</v>
@@ -8196,7 +8193,7 @@
     </row>
     <row r="304" spans="4:10" ht="19.2">
       <c r="D304" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E304" s="7">
         <v>4</v>
@@ -8219,7 +8216,7 @@
     </row>
     <row r="305" spans="4:10" ht="19.2">
       <c r="D305" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E305" s="7">
         <v>1</v>
@@ -8242,7 +8239,7 @@
     </row>
     <row r="306" spans="4:10" ht="19.2">
       <c r="D306" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E306" s="7">
         <v>2</v>
@@ -8265,7 +8262,7 @@
     </row>
     <row r="307" spans="4:10" ht="19.2">
       <c r="D307" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E307" s="7">
         <v>3</v>
@@ -8288,7 +8285,7 @@
     </row>
     <row r="308" spans="4:10" ht="19.2">
       <c r="D308" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E308" s="7">
         <v>4</v>
@@ -8311,7 +8308,7 @@
     </row>
     <row r="309" spans="4:10" ht="19.2">
       <c r="D309" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E309" s="7">
         <v>1</v>
@@ -8334,7 +8331,7 @@
     </row>
     <row r="310" spans="4:10" ht="19.2">
       <c r="D310" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E310" s="7">
         <v>2</v>
@@ -8357,7 +8354,7 @@
     </row>
     <row r="311" spans="4:10" ht="19.2">
       <c r="D311" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E311" s="7">
         <v>3</v>
@@ -8380,7 +8377,7 @@
     </row>
     <row r="312" spans="4:10" ht="19.2">
       <c r="D312" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E312" s="7">
         <v>4</v>
@@ -8391,7 +8388,7 @@
     </row>
     <row r="313" spans="4:10" ht="19.2">
       <c r="D313" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E313" s="7">
         <v>1</v>
@@ -8414,7 +8411,7 @@
     </row>
     <row r="314" spans="4:10" ht="19.2">
       <c r="D314" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E314" s="7">
         <v>2</v>
@@ -8437,7 +8434,7 @@
     </row>
     <row r="315" spans="4:10" ht="19.2">
       <c r="D315" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E315" s="7">
         <v>3</v>
@@ -8460,7 +8457,7 @@
     </row>
     <row r="316" spans="4:10" ht="19.2">
       <c r="D316" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E316" s="7">
         <v>4</v>
@@ -8483,7 +8480,7 @@
     </row>
     <row r="317" spans="4:10" ht="19.2">
       <c r="D317" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E317" s="7">
         <v>1</v>
@@ -8506,7 +8503,7 @@
     </row>
     <row r="318" spans="4:10" ht="19.2">
       <c r="D318" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E318" s="7">
         <v>2</v>
@@ -8529,7 +8526,7 @@
     </row>
     <row r="319" spans="4:10" ht="19.2">
       <c r="D319" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E319" s="7">
         <v>3</v>
@@ -8552,7 +8549,7 @@
     </row>
     <row r="320" spans="4:10" ht="19.2">
       <c r="D320" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E320" s="7">
         <v>4</v>
@@ -8575,7 +8572,7 @@
     </row>
     <row r="321" spans="4:10" ht="19.2">
       <c r="D321" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E321" s="7">
         <v>1</v>
@@ -8598,7 +8595,7 @@
     </row>
     <row r="322" spans="4:10" ht="19.2">
       <c r="D322" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E322" s="7">
         <v>2</v>
@@ -8621,7 +8618,7 @@
     </row>
     <row r="323" spans="4:10" ht="19.2">
       <c r="D323" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E323" s="7">
         <v>3</v>
@@ -8644,7 +8641,7 @@
     </row>
     <row r="324" spans="4:10" ht="19.2">
       <c r="D324" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E324" s="7">
         <v>4</v>
@@ -8667,7 +8664,7 @@
     </row>
     <row r="325" spans="4:10" ht="19.2">
       <c r="D325" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E325" s="7">
         <v>1</v>
@@ -8690,7 +8687,7 @@
     </row>
     <row r="326" spans="4:10" ht="19.2">
       <c r="D326" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E326" s="7">
         <v>2</v>
@@ -8713,7 +8710,7 @@
     </row>
     <row r="327" spans="4:10" ht="19.2">
       <c r="D327" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E327" s="7">
         <v>3</v>
@@ -8736,7 +8733,7 @@
     </row>
     <row r="328" spans="4:10" ht="19.2">
       <c r="D328" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E328" s="7">
         <v>4</v>
@@ -8759,7 +8756,7 @@
     </row>
     <row r="329" spans="4:10" ht="19.2">
       <c r="D329" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E329" s="7">
         <v>1</v>
@@ -8782,7 +8779,7 @@
     </row>
     <row r="330" spans="4:10" ht="19.2">
       <c r="D330" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E330" s="7">
         <v>2</v>
@@ -8805,7 +8802,7 @@
     </row>
     <row r="331" spans="4:10" ht="19.2">
       <c r="D331" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E331" s="7">
         <v>3</v>
@@ -8816,7 +8813,7 @@
     </row>
     <row r="332" spans="4:10" ht="19.2">
       <c r="D332" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E332" s="7">
         <v>4</v>
@@ -8827,7 +8824,7 @@
     </row>
     <row r="333" spans="4:10" ht="19.2">
       <c r="D333" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E333" s="7">
         <v>1</v>
@@ -8850,7 +8847,7 @@
     </row>
     <row r="334" spans="4:10" ht="19.2">
       <c r="D334" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E334" s="7">
         <v>2</v>
@@ -8871,7 +8868,7 @@
     </row>
     <row r="335" spans="4:10" ht="19.2">
       <c r="D335" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E335" s="7">
         <v>3</v>
@@ -8894,7 +8891,7 @@
     </row>
     <row r="336" spans="4:10" ht="19.2">
       <c r="D336" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E336" s="7">
         <v>4</v>
@@ -8905,7 +8902,7 @@
     </row>
     <row r="337" spans="4:10" ht="19.2">
       <c r="D337" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E337" s="7">
         <v>1</v>
@@ -8928,7 +8925,7 @@
     </row>
     <row r="338" spans="4:10" ht="19.2">
       <c r="D338" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E338" s="7">
         <v>2</v>
@@ -8951,7 +8948,7 @@
     </row>
     <row r="339" spans="4:10" ht="19.2">
       <c r="D339" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E339" s="7">
         <v>3</v>
@@ -8962,7 +8959,7 @@
     </row>
     <row r="340" spans="4:10" ht="19.2">
       <c r="D340" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E340" s="7">
         <v>4</v>
@@ -8973,7 +8970,7 @@
     </row>
     <row r="341" spans="4:10" ht="19.2">
       <c r="D341" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E341" s="7">
         <v>1</v>
@@ -8996,7 +8993,7 @@
     </row>
     <row r="342" spans="4:10" ht="19.2">
       <c r="D342" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E342" s="7">
         <v>2</v>
@@ -9019,7 +9016,7 @@
     </row>
     <row r="343" spans="4:10" ht="19.2">
       <c r="D343" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E343" s="7">
         <v>3</v>
@@ -9042,7 +9039,7 @@
     </row>
     <row r="344" spans="4:10" ht="19.2">
       <c r="D344" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E344" s="7">
         <v>4</v>
@@ -9065,7 +9062,7 @@
     </row>
     <row r="345" spans="4:10" ht="19.2">
       <c r="D345" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E345" s="7">
         <v>1</v>
@@ -9088,7 +9085,7 @@
     </row>
     <row r="346" spans="4:10" ht="19.2">
       <c r="D346" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E346" s="7">
         <v>2</v>
@@ -9111,7 +9108,7 @@
     </row>
     <row r="347" spans="4:10" ht="19.2">
       <c r="D347" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E347" s="7">
         <v>3</v>
@@ -9134,7 +9131,7 @@
     </row>
     <row r="348" spans="4:10" ht="19.2">
       <c r="D348" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E348" s="7">
         <v>4</v>
@@ -9145,7 +9142,7 @@
     </row>
     <row r="349" spans="4:10" ht="19.2">
       <c r="D349" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E349" s="7">
         <v>1</v>
@@ -9156,7 +9153,7 @@
     </row>
     <row r="350" spans="4:10" ht="19.2">
       <c r="D350" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E350" s="7">
         <v>2</v>
@@ -9167,7 +9164,7 @@
     </row>
     <row r="351" spans="4:10" ht="19.2">
       <c r="D351" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E351" s="7">
         <v>3</v>
@@ -9178,7 +9175,7 @@
     </row>
     <row r="352" spans="4:10" ht="19.2">
       <c r="D352" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E352" s="7">
         <v>4</v>
@@ -9189,7 +9186,7 @@
     </row>
     <row r="353" spans="4:10" ht="19.2">
       <c r="D353" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E353" s="7">
         <v>1</v>
@@ -9212,7 +9209,7 @@
     </row>
     <row r="354" spans="4:10" ht="19.2">
       <c r="D354" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E354" s="7">
         <v>2</v>
@@ -9235,7 +9232,7 @@
     </row>
     <row r="355" spans="4:10" ht="19.2">
       <c r="D355" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E355" s="7">
         <v>3</v>
@@ -9258,7 +9255,7 @@
     </row>
     <row r="356" spans="4:10" ht="19.2">
       <c r="D356" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E356" s="7">
         <v>4</v>
@@ -9281,7 +9278,7 @@
     </row>
     <row r="357" spans="4:10" ht="19.2">
       <c r="D357" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E357" s="7">
         <v>1</v>
@@ -9304,7 +9301,7 @@
     </row>
     <row r="358" spans="4:10" ht="19.2">
       <c r="D358" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E358" s="7">
         <v>2</v>
@@ -9327,7 +9324,7 @@
     </row>
     <row r="359" spans="4:10" ht="19.2">
       <c r="D359" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E359" s="7">
         <v>3</v>
@@ -9350,7 +9347,7 @@
     </row>
     <row r="360" spans="4:10" ht="19.2">
       <c r="D360" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E360" s="7">
         <v>4</v>
@@ -9361,7 +9358,7 @@
     </row>
     <row r="361" spans="4:10" ht="19.2">
       <c r="D361" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E361" s="7">
         <v>1</v>
@@ -9384,7 +9381,7 @@
     </row>
     <row r="362" spans="4:10" ht="19.2">
       <c r="D362" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E362" s="7">
         <v>2</v>
@@ -9407,7 +9404,7 @@
     </row>
     <row r="363" spans="4:10" ht="19.2">
       <c r="D363" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E363" s="7">
         <v>3</v>
@@ -9430,7 +9427,7 @@
     </row>
     <row r="364" spans="4:10" ht="19.2">
       <c r="D364" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E364" s="7">
         <v>4</v>
@@ -9451,7 +9448,7 @@
     </row>
     <row r="365" spans="4:10" ht="19.2">
       <c r="D365" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E365" s="7">
         <v>1</v>
@@ -9474,7 +9471,7 @@
     </row>
     <row r="366" spans="4:10" ht="19.2">
       <c r="D366" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E366" s="7">
         <v>2</v>
@@ -9497,7 +9494,7 @@
     </row>
     <row r="367" spans="4:10" ht="19.2">
       <c r="D367" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E367" s="7">
         <v>3</v>
@@ -9520,7 +9517,7 @@
     </row>
     <row r="368" spans="4:10" ht="19.2">
       <c r="D368" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E368" s="7">
         <v>4</v>
@@ -9543,7 +9540,7 @@
     </row>
     <row r="369" spans="4:10" ht="19.2">
       <c r="D369" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E369" s="7">
         <v>1</v>
@@ -9566,7 +9563,7 @@
     </row>
     <row r="370" spans="4:10" ht="19.2">
       <c r="D370" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E370" s="7">
         <v>2</v>
@@ -9589,7 +9586,7 @@
     </row>
     <row r="371" spans="4:10" ht="19.2">
       <c r="D371" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E371" s="7">
         <v>3</v>
@@ -9612,7 +9609,7 @@
     </row>
     <row r="372" spans="4:10" ht="19.2">
       <c r="D372" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E372" s="7">
         <v>4</v>
@@ -9633,7 +9630,7 @@
     </row>
     <row r="373" spans="4:10" ht="19.2">
       <c r="D373" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E373" s="7">
         <v>1</v>
@@ -9656,7 +9653,7 @@
     </row>
     <row r="374" spans="4:10" ht="19.2">
       <c r="D374" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E374" s="7">
         <v>2</v>
@@ -9679,7 +9676,7 @@
     </row>
     <row r="375" spans="4:10" ht="19.2">
       <c r="D375" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E375" s="7">
         <v>3</v>
@@ -9702,7 +9699,7 @@
     </row>
     <row r="376" spans="4:10" ht="19.2">
       <c r="D376" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E376" s="7">
         <v>4</v>
@@ -9725,7 +9722,7 @@
     </row>
     <row r="377" spans="4:10" ht="19.2">
       <c r="D377" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E377" s="7">
         <v>1</v>
@@ -9748,7 +9745,7 @@
     </row>
     <row r="378" spans="4:10" ht="19.2">
       <c r="D378" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E378" s="7">
         <v>2</v>
@@ -9771,7 +9768,7 @@
     </row>
     <row r="379" spans="4:10" ht="19.2">
       <c r="D379" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E379" s="7">
         <v>3</v>
@@ -9794,7 +9791,7 @@
     </row>
     <row r="380" spans="4:10" ht="19.2">
       <c r="D380" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E380" s="7">
         <v>4</v>
@@ -9817,7 +9814,7 @@
     </row>
     <row r="381" spans="4:10" ht="19.2">
       <c r="D381" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E381" s="7">
         <v>1</v>
@@ -9840,7 +9837,7 @@
     </row>
     <row r="382" spans="4:10" ht="19.2">
       <c r="D382" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E382" s="7">
         <v>2</v>
@@ -9851,7 +9848,7 @@
     </row>
     <row r="383" spans="4:10" ht="19.2">
       <c r="D383" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E383" s="7">
         <v>3</v>
@@ -9862,7 +9859,7 @@
     </row>
     <row r="384" spans="4:10" ht="19.2">
       <c r="D384" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E384" s="7">
         <v>4</v>
@@ -9873,7 +9870,7 @@
     </row>
     <row r="385" spans="4:10" ht="19.2">
       <c r="D385" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E385" s="7">
         <v>1</v>
@@ -9893,7 +9890,7 @@
     </row>
     <row r="386" spans="4:10" ht="19.2">
       <c r="D386" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E386" s="7">
         <v>2</v>
@@ -9913,7 +9910,7 @@
     </row>
     <row r="387" spans="4:10" ht="19.2">
       <c r="D387" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E387" s="7">
         <v>3</v>
@@ -9933,7 +9930,7 @@
     </row>
     <row r="388" spans="4:10" ht="19.2">
       <c r="D388" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E388" s="7">
         <v>4</v>

--- a/Fees Details 2024-25.xlsx
+++ b/Fees Details 2024-25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HIMANSHU\hostel-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3B4773-EDF5-4158-8FAC-E83F1829AE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC46FF93-8943-4864-8029-A219040B7B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="429">
   <si>
     <t>ROOMS</t>
   </si>
@@ -1550,6 +1550,9 @@
   </si>
   <si>
     <t>NB410</t>
+  </si>
+  <si>
+    <t>BH.NB410</t>
   </si>
 </sst>
 </file>
@@ -1992,7 +1995,9 @@
   <dimension ref="D1:K388"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="5" width="8.88671875" style="3"/>
+    <col min="3" max="3" width="8.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="3"/>
     <col min="6" max="6" width="28.5546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="22.77734375" style="3" customWidth="1"/>
     <col min="8" max="8" width="22.44140625" style="3" customWidth="1"/>
@@ -9910,7 +9915,7 @@
     </row>
     <row r="387" spans="4:10" ht="19.2">
       <c r="D387" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E387" s="7">
         <v>3</v>
@@ -9930,7 +9935,7 @@
     </row>
     <row r="388" spans="4:10" ht="19.2">
       <c r="D388" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E388" s="7">
         <v>4</v>
